--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77FBE084-1235-4309-AB67-3DAF25CE95E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16184ED5-92D1-4DAE-ACB3-A45D1ED55254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="6" activeTab="17" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -19444,10 +19444,10 @@
         <v>11</v>
       </c>
       <c r="G42">
-        <v>95</v>
+        <v>105</v>
       </c>
       <c r="H42">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -21204,10 +21204,10 @@
         <v>14</v>
       </c>
       <c r="G38">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H38">
-        <v>268</v>
+        <v>294</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -21230,10 +21230,10 @@
         <v>11</v>
       </c>
       <c r="G39">
-        <v>45.5</v>
+        <v>48.5</v>
       </c>
       <c r="H39">
-        <v>47</v>
+        <v>50</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -21906,10 +21906,10 @@
         <v>14</v>
       </c>
       <c r="G65">
-        <v>255</v>
+        <v>285</v>
       </c>
       <c r="H65">
-        <v>262.5</v>
+        <v>293.5</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -21932,10 +21932,10 @@
         <v>14</v>
       </c>
       <c r="G66">
-        <v>212.5</v>
+        <v>237.5</v>
       </c>
       <c r="H66">
-        <v>219</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -21958,10 +21958,10 @@
         <v>11</v>
       </c>
       <c r="G67">
-        <v>44.5</v>
+        <v>49.5</v>
       </c>
       <c r="H67">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1553C9AD-56D4-4725-9AF5-E1D1115ECBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B98AA6-0CE7-41DD-B0B0-16EE5264316F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3540" uniqueCount="1084">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3568" uniqueCount="1102">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2775,18 +2775,6 @@
     <t>BALA GELATINA BEIJO</t>
   </si>
   <si>
-    <t>bala-geatina-cobrinha-citrica</t>
-  </si>
-  <si>
-    <t>BALA GEATINA COBRINHA CITRICA</t>
-  </si>
-  <si>
-    <t>bala-geatina-diversas</t>
-  </si>
-  <si>
-    <t>BALA GEATINA DIVERSAS</t>
-  </si>
-  <si>
     <t>bala-gelatina-mix-formatos</t>
   </si>
   <si>
@@ -3289,6 +3277,72 @@
   </si>
   <si>
     <t>POTE RETANGULAR 13,8L</t>
+  </si>
+  <si>
+    <t>doce-brigadeiro</t>
+  </si>
+  <si>
+    <t>DOCE DE BRIGADEIRO</t>
+  </si>
+  <si>
+    <t>X50G</t>
+  </si>
+  <si>
+    <t>doce-de-leite-docura-fazenda</t>
+  </si>
+  <si>
+    <t>DOCE DE LEITE DOÇURA FAZENDA</t>
+  </si>
+  <si>
+    <t>X55G</t>
+  </si>
+  <si>
+    <t>doce-geleia-de-mocoto</t>
+  </si>
+  <si>
+    <t>DOCE GELEIA DE MOCOTO</t>
+  </si>
+  <si>
+    <t>X37,5G</t>
+  </si>
+  <si>
+    <t>doce-palha-italiana</t>
+  </si>
+  <si>
+    <t>DOCE PALHA ITALIANA</t>
+  </si>
+  <si>
+    <t>doce-pingo-bel</t>
+  </si>
+  <si>
+    <t>DOCE PINGO BEL</t>
+  </si>
+  <si>
+    <t>doce-de-leite-souvenir</t>
+  </si>
+  <si>
+    <t>DOCE DE LEITE SOUVENIR</t>
+  </si>
+  <si>
+    <t>doce-de-leite-c-cocosouvenir</t>
+  </si>
+  <si>
+    <t>DOCE DE LEITE C/COCOSUVENIR</t>
+  </si>
+  <si>
+    <t>X400g</t>
+  </si>
+  <si>
+    <t>bala-gelatina-cobrinha-citrica</t>
+  </si>
+  <si>
+    <t>bala-gelatina-diversas</t>
+  </si>
+  <si>
+    <t>BALA GELATINA DIVERSAS</t>
+  </si>
+  <si>
+    <t>BALA GELATINA COBRINHA CITRICA</t>
   </si>
 </sst>
 </file>
@@ -9844,7 +9898,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:H114"/>
+  <dimension ref="A1:H121"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10715,10 +10769,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>912</v>
+        <v>1098</v>
       </c>
       <c r="B34" t="s">
-        <v>913</v>
+        <v>1101</v>
       </c>
       <c r="C34">
         <v>4446</v>
@@ -10741,10 +10795,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>914</v>
+        <v>1099</v>
       </c>
       <c r="B35" t="s">
-        <v>915</v>
+        <v>1100</v>
       </c>
       <c r="C35">
         <v>4476</v>
@@ -10767,10 +10821,10 @@
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
       <c r="B36" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="C36">
         <v>4348</v>
@@ -10793,10 +10847,10 @@
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
       <c r="B37" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="C37">
         <v>4456</v>
@@ -10819,10 +10873,10 @@
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="B38" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="C38">
         <v>4051</v>
@@ -10845,10 +10899,10 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="B39" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
       <c r="C39">
         <v>4408</v>
@@ -10871,10 +10925,10 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="B40" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
       <c r="C40">
         <v>4341</v>
@@ -10897,10 +10951,10 @@
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="B41" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
       <c r="C41">
         <v>4265</v>
@@ -10923,10 +10977,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="B42" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
       <c r="C42">
         <v>4266</v>
@@ -10949,10 +11003,10 @@
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="B43" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
       <c r="C43">
         <v>4269</v>
@@ -10975,10 +11029,10 @@
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>932</v>
+        <v>928</v>
       </c>
       <c r="B44" t="s">
-        <v>933</v>
+        <v>929</v>
       </c>
       <c r="C44">
         <v>4273</v>
@@ -11001,10 +11055,10 @@
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>934</v>
+        <v>930</v>
       </c>
       <c r="B45" t="s">
-        <v>935</v>
+        <v>931</v>
       </c>
       <c r="C45">
         <v>4405</v>
@@ -11027,10 +11081,10 @@
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="B46" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="C46">
         <v>4406</v>
@@ -11053,10 +11107,10 @@
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>938</v>
+        <v>934</v>
       </c>
       <c r="B47" t="s">
-        <v>939</v>
+        <v>935</v>
       </c>
       <c r="C47">
         <v>4267</v>
@@ -11079,10 +11133,10 @@
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>940</v>
+        <v>936</v>
       </c>
       <c r="B48" t="s">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="C48">
         <v>4271</v>
@@ -11105,10 +11159,10 @@
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="B49" t="s">
-        <v>943</v>
+        <v>939</v>
       </c>
       <c r="C49">
         <v>4276</v>
@@ -11131,10 +11185,10 @@
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="B50" t="s">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="C50">
         <v>4342</v>
@@ -11157,10 +11211,10 @@
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="B51" t="s">
-        <v>947</v>
+        <v>943</v>
       </c>
       <c r="C51">
         <v>4398</v>
@@ -11183,10 +11237,10 @@
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="B52" t="s">
-        <v>949</v>
+        <v>945</v>
       </c>
       <c r="C52">
         <v>4270</v>
@@ -11209,10 +11263,10 @@
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="B53" t="s">
-        <v>951</v>
+        <v>947</v>
       </c>
       <c r="C53">
         <v>4275</v>
@@ -11235,10 +11289,10 @@
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="B54" t="s">
-        <v>953</v>
+        <v>949</v>
       </c>
       <c r="C54">
         <v>4274</v>
@@ -11261,10 +11315,10 @@
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="B55" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
       <c r="C55">
         <v>4399</v>
@@ -11287,10 +11341,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="B56" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
       <c r="C56">
         <v>4404</v>
@@ -11313,10 +11367,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>958</v>
+        <v>954</v>
       </c>
       <c r="B57" t="s">
-        <v>959</v>
+        <v>955</v>
       </c>
       <c r="C57">
         <v>4262</v>
@@ -11339,10 +11393,10 @@
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>960</v>
+        <v>956</v>
       </c>
       <c r="B58" t="s">
-        <v>961</v>
+        <v>957</v>
       </c>
       <c r="C58">
         <v>4263</v>
@@ -11365,10 +11419,10 @@
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>962</v>
+        <v>958</v>
       </c>
       <c r="B59" t="s">
-        <v>963</v>
+        <v>959</v>
       </c>
       <c r="C59">
         <v>4264</v>
@@ -11391,10 +11445,10 @@
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>964</v>
+        <v>960</v>
       </c>
       <c r="B60" t="s">
-        <v>965</v>
+        <v>961</v>
       </c>
       <c r="C60">
         <v>4407</v>
@@ -11417,10 +11471,10 @@
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>966</v>
+        <v>962</v>
       </c>
       <c r="B61" t="s">
-        <v>967</v>
+        <v>963</v>
       </c>
       <c r="C61">
         <v>4397</v>
@@ -11443,10 +11497,10 @@
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>968</v>
+        <v>964</v>
       </c>
       <c r="B62" t="s">
-        <v>969</v>
+        <v>965</v>
       </c>
       <c r="C62">
         <v>4343</v>
@@ -11469,10 +11523,10 @@
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>970</v>
+        <v>966</v>
       </c>
       <c r="B63" t="s">
-        <v>971</v>
+        <v>967</v>
       </c>
       <c r="C63">
         <v>4268</v>
@@ -11495,10 +11549,10 @@
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B64" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C64">
         <v>2833</v>
@@ -11521,10 +11575,10 @@
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>972</v>
+        <v>968</v>
       </c>
       <c r="B65" t="s">
-        <v>973</v>
+        <v>969</v>
       </c>
       <c r="C65">
         <v>3125</v>
@@ -11547,10 +11601,10 @@
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B66" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="C66">
         <v>3752</v>
@@ -11573,10 +11627,10 @@
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>974</v>
+        <v>970</v>
       </c>
       <c r="B67" t="s">
-        <v>975</v>
+        <v>971</v>
       </c>
       <c r="C67">
         <v>3753</v>
@@ -11599,10 +11653,10 @@
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>976</v>
+        <v>972</v>
       </c>
       <c r="B68" t="s">
-        <v>977</v>
+        <v>973</v>
       </c>
       <c r="C68">
         <v>2511</v>
@@ -11625,10 +11679,10 @@
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>978</v>
+        <v>974</v>
       </c>
       <c r="B69" t="s">
-        <v>979</v>
+        <v>975</v>
       </c>
       <c r="C69">
         <v>4311</v>
@@ -11651,10 +11705,10 @@
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B70" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C70">
         <v>4046</v>
@@ -11677,10 +11731,10 @@
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>980</v>
+        <v>976</v>
       </c>
       <c r="B71" t="s">
-        <v>981</v>
+        <v>977</v>
       </c>
       <c r="C71">
         <v>4047</v>
@@ -11703,10 +11757,10 @@
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>982</v>
+        <v>978</v>
       </c>
       <c r="B72" t="s">
-        <v>983</v>
+        <v>979</v>
       </c>
       <c r="C72">
         <v>4312</v>
@@ -11729,10 +11783,10 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>984</v>
+        <v>980</v>
       </c>
       <c r="B73" t="s">
-        <v>985</v>
+        <v>981</v>
       </c>
       <c r="C73">
         <v>4310</v>
@@ -11755,10 +11809,10 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>986</v>
+        <v>982</v>
       </c>
       <c r="B74" t="s">
-        <v>987</v>
+        <v>983</v>
       </c>
       <c r="C74">
         <v>4074</v>
@@ -11767,7 +11821,7 @@
         <v>1</v>
       </c>
       <c r="E74" t="s">
-        <v>988</v>
+        <v>984</v>
       </c>
       <c r="F74" t="s">
         <v>11</v>
@@ -11781,10 +11835,10 @@
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>989</v>
+        <v>985</v>
       </c>
       <c r="B75" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C75">
         <v>4076</v>
@@ -11793,10 +11847,10 @@
         <v>1</v>
       </c>
       <c r="E75" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="F75" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G75">
         <v>32.5</v>
@@ -11807,10 +11861,10 @@
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="B76" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="C76">
         <v>4133</v>
@@ -11822,7 +11876,7 @@
         <v>408</v>
       </c>
       <c r="F76" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="G76">
         <v>72</v>
@@ -11833,10 +11887,10 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B77" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C77">
         <v>3068</v>
@@ -11859,10 +11913,10 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="B78" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="C78">
         <v>3087</v>
@@ -11885,10 +11939,10 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="B79" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="C79">
         <v>4560</v>
@@ -11911,10 +11965,10 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B80" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C80">
         <v>4531</v>
@@ -11937,10 +11991,10 @@
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="B81" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="C81">
         <v>4532</v>
@@ -11963,10 +12017,10 @@
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="B82" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="C82">
         <v>4559</v>
@@ -11989,10 +12043,10 @@
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="B83" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="C83">
         <v>4493</v>
@@ -12015,10 +12069,10 @@
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="B84" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="C84">
         <v>4102</v>
@@ -12027,7 +12081,7 @@
         <v>10</v>
       </c>
       <c r="E84" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F84" t="s">
         <v>11</v>
@@ -12041,10 +12095,10 @@
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="B85" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C85">
         <v>4103</v>
@@ -12053,7 +12107,7 @@
         <v>10</v>
       </c>
       <c r="E85" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F85" t="s">
         <v>33</v>
@@ -12067,568 +12121,568 @@
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1010</v>
+        <v>1080</v>
       </c>
       <c r="B86" t="s">
-        <v>1011</v>
+        <v>1081</v>
       </c>
       <c r="C86">
-        <v>4547</v>
+        <v>4624</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E86" t="s">
-        <v>1007</v>
+        <v>1082</v>
       </c>
       <c r="F86" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G86">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="H86">
-        <v>79.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>1012</v>
+        <v>1083</v>
       </c>
       <c r="B87" t="s">
-        <v>1013</v>
+        <v>1084</v>
       </c>
       <c r="C87">
-        <v>4104</v>
+        <v>4627</v>
       </c>
       <c r="D87">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
-        <v>1007</v>
+        <v>1085</v>
       </c>
       <c r="F87" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G87">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="H87">
-        <v>79.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>1014</v>
+        <v>1086</v>
       </c>
       <c r="B88" t="s">
-        <v>1015</v>
+        <v>1087</v>
       </c>
       <c r="C88">
-        <v>4101</v>
+        <v>4628</v>
       </c>
       <c r="D88">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E88" t="s">
-        <v>1007</v>
+        <v>1088</v>
       </c>
       <c r="F88" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G88">
-        <v>77</v>
+        <v>28</v>
       </c>
       <c r="H88">
-        <v>79.5</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1016</v>
+        <v>1089</v>
       </c>
       <c r="B89" t="s">
-        <v>1017</v>
+        <v>1090</v>
       </c>
       <c r="C89">
-        <v>4105</v>
+        <v>4625</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E89" t="s">
-        <v>1007</v>
+        <v>1082</v>
       </c>
       <c r="F89" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G89">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="H89">
-        <v>79.5</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>1018</v>
+        <v>1091</v>
       </c>
       <c r="B90" t="s">
-        <v>1019</v>
+        <v>1092</v>
       </c>
       <c r="C90">
-        <v>3705</v>
+        <v>4626</v>
       </c>
       <c r="D90">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="E90" t="s">
-        <v>1020</v>
+        <v>1082</v>
       </c>
       <c r="F90" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G90">
-        <v>123.5</v>
+        <v>48</v>
       </c>
       <c r="H90">
-        <v>127</v>
+        <v>49.5</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1021</v>
+        <v>1093</v>
       </c>
       <c r="B91" t="s">
-        <v>1022</v>
+        <v>1094</v>
       </c>
       <c r="C91">
-        <v>3823</v>
+        <v>4629</v>
       </c>
       <c r="D91">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
       </c>
       <c r="G91">
-        <v>77</v>
+        <v>195</v>
       </c>
       <c r="H91">
-        <v>79.5</v>
+        <v>201</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1023</v>
+        <v>1095</v>
       </c>
       <c r="B92" t="s">
-        <v>1024</v>
+        <v>1096</v>
       </c>
       <c r="C92">
-        <v>4308</v>
+        <v>4630</v>
       </c>
       <c r="D92">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>1025</v>
+        <v>1097</v>
       </c>
       <c r="F92" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G92">
-        <v>68.5</v>
+        <v>127.5</v>
       </c>
       <c r="H92">
-        <v>70.5</v>
+        <v>131</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1026</v>
+        <v>1006</v>
       </c>
       <c r="B93" t="s">
-        <v>1027</v>
+        <v>1007</v>
       </c>
       <c r="C93">
-        <v>4309</v>
+        <v>4547</v>
       </c>
       <c r="D93">
         <v>10</v>
       </c>
       <c r="E93" t="s">
-        <v>1025</v>
+        <v>1003</v>
       </c>
       <c r="F93" t="s">
-        <v>992</v>
+        <v>33</v>
       </c>
       <c r="G93">
-        <v>68.5</v>
+        <v>77</v>
       </c>
       <c r="H93">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1028</v>
+        <v>1008</v>
       </c>
       <c r="B94" t="s">
-        <v>1029</v>
+        <v>1009</v>
       </c>
       <c r="C94">
-        <v>4412</v>
+        <v>4104</v>
       </c>
       <c r="D94">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>1003</v>
       </c>
       <c r="F94" t="s">
-        <v>992</v>
+        <v>33</v>
       </c>
       <c r="G94">
-        <v>71.5</v>
+        <v>77</v>
       </c>
       <c r="H94">
-        <v>73.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1030</v>
+        <v>1010</v>
       </c>
       <c r="B95" t="s">
-        <v>1031</v>
+        <v>1011</v>
       </c>
       <c r="C95">
-        <v>4413</v>
+        <v>4101</v>
       </c>
       <c r="D95">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E95" t="s">
-        <v>10</v>
+        <v>1003</v>
       </c>
       <c r="F95" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G95">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="H95">
-        <v>511</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1030</v>
+        <v>1012</v>
       </c>
       <c r="B96" t="s">
-        <v>1031</v>
+        <v>1013</v>
       </c>
       <c r="C96">
-        <v>4414</v>
+        <v>4105</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
-        <v>10</v>
+        <v>1003</v>
       </c>
       <c r="F96" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G96">
-        <v>101</v>
+        <v>77</v>
       </c>
       <c r="H96">
-        <v>104</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1032</v>
+        <v>1014</v>
       </c>
       <c r="B97" t="s">
-        <v>1033</v>
+        <v>1015</v>
       </c>
       <c r="C97">
-        <v>4415</v>
+        <v>3705</v>
       </c>
       <c r="D97">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>10</v>
+        <v>1016</v>
       </c>
       <c r="F97" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G97">
-        <v>414</v>
+        <v>123.5</v>
       </c>
       <c r="H97">
-        <v>426.5</v>
+        <v>127</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1032</v>
+        <v>1017</v>
       </c>
       <c r="B98" t="s">
-        <v>1033</v>
+        <v>1018</v>
       </c>
       <c r="C98">
-        <v>4416</v>
+        <v>3823</v>
       </c>
       <c r="D98">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
-        <v>10</v>
+        <v>1003</v>
       </c>
       <c r="F98" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G98">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="H98">
-        <v>87</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1034</v>
+        <v>1019</v>
       </c>
       <c r="B99" t="s">
-        <v>1035</v>
+        <v>1020</v>
       </c>
       <c r="C99">
-        <v>4475</v>
+        <v>4308</v>
       </c>
       <c r="D99">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E99" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="F99" t="s">
         <v>11</v>
       </c>
       <c r="G99">
-        <v>9</v>
+        <v>68.5</v>
       </c>
       <c r="H99">
-        <v>9.5</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1037</v>
+        <v>1022</v>
       </c>
       <c r="B100" t="s">
-        <v>1038</v>
+        <v>1023</v>
       </c>
       <c r="C100">
-        <v>4354</v>
+        <v>4309</v>
       </c>
       <c r="D100">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>1036</v>
+        <v>1021</v>
       </c>
       <c r="F100" t="s">
-        <v>750</v>
+        <v>988</v>
       </c>
       <c r="G100">
-        <v>79.5</v>
+        <v>68.5</v>
       </c>
       <c r="H100">
-        <v>82</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1039</v>
+        <v>1024</v>
       </c>
       <c r="B101" t="s">
-        <v>1040</v>
+        <v>1025</v>
       </c>
       <c r="C101">
-        <v>4445</v>
+        <v>4412</v>
       </c>
       <c r="D101">
-        <v>12</v>
+        <v>2.5</v>
       </c>
       <c r="E101" t="s">
-        <v>1036</v>
+        <v>10</v>
       </c>
       <c r="F101" t="s">
-        <v>25</v>
+        <v>988</v>
       </c>
       <c r="G101">
-        <v>79.5</v>
+        <v>71.5</v>
       </c>
       <c r="H101">
-        <v>82</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1041</v>
+        <v>1026</v>
       </c>
       <c r="B102" t="s">
-        <v>1042</v>
+        <v>1027</v>
       </c>
       <c r="C102">
-        <v>4353</v>
+        <v>4413</v>
       </c>
       <c r="D102">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E102" t="s">
-        <v>1036</v>
+        <v>10</v>
       </c>
       <c r="F102" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G102">
-        <v>79.5</v>
+        <v>496</v>
       </c>
       <c r="H102">
-        <v>82</v>
+        <v>511</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1043</v>
+        <v>1026</v>
       </c>
       <c r="B103" t="s">
-        <v>1044</v>
+        <v>1027</v>
       </c>
       <c r="C103">
-        <v>4350</v>
+        <v>4414</v>
       </c>
       <c r="D103">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E103" t="s">
-        <v>1036</v>
+        <v>10</v>
       </c>
       <c r="F103" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G103">
-        <v>79.5</v>
+        <v>101</v>
       </c>
       <c r="H103">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1045</v>
+        <v>1028</v>
       </c>
       <c r="B104" t="s">
-        <v>1046</v>
+        <v>1029</v>
       </c>
       <c r="C104">
-        <v>4352</v>
+        <v>4415</v>
       </c>
       <c r="D104">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E104" t="s">
-        <v>1036</v>
+        <v>10</v>
       </c>
       <c r="F104" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G104">
-        <v>79.5</v>
+        <v>414</v>
       </c>
       <c r="H104">
-        <v>82</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1047</v>
+        <v>1028</v>
       </c>
       <c r="B105" t="s">
-        <v>1048</v>
+        <v>1029</v>
       </c>
       <c r="C105">
-        <v>4349</v>
+        <v>4416</v>
       </c>
       <c r="D105">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E105" t="s">
-        <v>1036</v>
+        <v>10</v>
       </c>
       <c r="F105" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G105">
-        <v>79.5</v>
+        <v>85</v>
       </c>
       <c r="H105">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1049</v>
+        <v>1030</v>
       </c>
       <c r="B106" t="s">
-        <v>1050</v>
+        <v>1031</v>
       </c>
       <c r="C106">
-        <v>4351</v>
+        <v>4475</v>
       </c>
       <c r="D106">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E106" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="F106" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G106">
-        <v>79.5</v>
+        <v>9</v>
       </c>
       <c r="H106">
-        <v>82</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1051</v>
+        <v>1033</v>
       </c>
       <c r="B107" t="s">
-        <v>1052</v>
+        <v>1034</v>
       </c>
       <c r="C107">
-        <v>4581</v>
+        <v>4354</v>
       </c>
       <c r="D107">
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="F107" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="G107">
         <v>79.5</v>
@@ -12639,183 +12693,365 @@
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1053</v>
+        <v>1035</v>
       </c>
       <c r="B108" t="s">
-        <v>1054</v>
+        <v>1036</v>
       </c>
       <c r="C108">
-        <v>4096</v>
+        <v>4445</v>
       </c>
       <c r="D108">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>10</v>
+        <v>1032</v>
       </c>
       <c r="F108" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G108">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="H108">
-        <v>81.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1055</v>
+        <v>1037</v>
       </c>
       <c r="B109" t="s">
-        <v>1056</v>
+        <v>1038</v>
       </c>
       <c r="C109">
-        <v>4123</v>
+        <v>4353</v>
       </c>
       <c r="D109">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>1020</v>
+        <v>1032</v>
       </c>
       <c r="F109" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G109">
-        <v>60</v>
+        <v>79.5</v>
       </c>
       <c r="H109">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1057</v>
+        <v>1039</v>
       </c>
       <c r="B110" t="s">
-        <v>1058</v>
+        <v>1040</v>
       </c>
       <c r="C110">
-        <v>4306</v>
+        <v>4350</v>
       </c>
       <c r="D110">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E110" t="s">
-        <v>1007</v>
+        <v>1032</v>
       </c>
       <c r="F110" t="s">
-        <v>992</v>
+        <v>25</v>
       </c>
       <c r="G110">
-        <v>81</v>
+        <v>79.5</v>
       </c>
       <c r="H110">
-        <v>83.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1059</v>
+        <v>1041</v>
       </c>
       <c r="B111" t="s">
-        <v>1060</v>
+        <v>1042</v>
       </c>
       <c r="C111">
-        <v>4307</v>
+        <v>4352</v>
       </c>
       <c r="D111">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>1007</v>
+        <v>1032</v>
       </c>
       <c r="F111" t="s">
-        <v>992</v>
+        <v>25</v>
       </c>
       <c r="G111">
-        <v>81</v>
+        <v>79.5</v>
       </c>
       <c r="H111">
-        <v>83.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1061</v>
+        <v>1043</v>
       </c>
       <c r="B112" t="s">
-        <v>1062</v>
+        <v>1044</v>
       </c>
       <c r="C112">
-        <v>2659</v>
+        <v>4349</v>
       </c>
       <c r="D112">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>1063</v>
+        <v>1032</v>
       </c>
       <c r="F112" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G112">
-        <v>27.5</v>
+        <v>79.5</v>
       </c>
       <c r="H112">
-        <v>28.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1061</v>
+        <v>1045</v>
       </c>
       <c r="B113" t="s">
-        <v>1062</v>
+        <v>1046</v>
       </c>
       <c r="C113">
-        <v>2621</v>
+        <v>4351</v>
       </c>
       <c r="D113">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>1064</v>
+        <v>1032</v>
       </c>
       <c r="F113" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G113">
-        <v>24.5</v>
+        <v>79.5</v>
       </c>
       <c r="H113">
-        <v>25</v>
+        <v>82</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1065</v>
+        <v>1047</v>
       </c>
       <c r="B114" t="s">
-        <v>1066</v>
+        <v>1048</v>
       </c>
       <c r="C114">
+        <v>4581</v>
+      </c>
+      <c r="D114">
+        <v>12</v>
+      </c>
+      <c r="E114" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F114" t="s">
+        <v>25</v>
+      </c>
+      <c r="G114">
+        <v>79.5</v>
+      </c>
+      <c r="H114">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B115" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C115">
+        <v>4096</v>
+      </c>
+      <c r="D115">
+        <v>5</v>
+      </c>
+      <c r="E115" t="s">
+        <v>10</v>
+      </c>
+      <c r="F115" t="s">
+        <v>11</v>
+      </c>
+      <c r="G115">
+        <v>79</v>
+      </c>
+      <c r="H115">
+        <v>81.5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B116" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C116">
+        <v>4123</v>
+      </c>
+      <c r="D116">
+        <v>10</v>
+      </c>
+      <c r="E116" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F116" t="s">
+        <v>11</v>
+      </c>
+      <c r="G116">
+        <v>60</v>
+      </c>
+      <c r="H116">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B117" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C117">
+        <v>4306</v>
+      </c>
+      <c r="D117">
+        <v>10</v>
+      </c>
+      <c r="E117" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F117" t="s">
+        <v>988</v>
+      </c>
+      <c r="G117">
+        <v>81</v>
+      </c>
+      <c r="H117">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B118" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C118">
+        <v>4307</v>
+      </c>
+      <c r="D118">
+        <v>10</v>
+      </c>
+      <c r="E118" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F118" t="s">
+        <v>988</v>
+      </c>
+      <c r="G118">
+        <v>81</v>
+      </c>
+      <c r="H118">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B119" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C119">
+        <v>2659</v>
+      </c>
+      <c r="D119">
+        <v>20</v>
+      </c>
+      <c r="E119" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F119" t="s">
+        <v>33</v>
+      </c>
+      <c r="G119">
+        <v>27.5</v>
+      </c>
+      <c r="H119">
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B120" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C120">
+        <v>2621</v>
+      </c>
+      <c r="D120">
+        <v>5</v>
+      </c>
+      <c r="E120" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F120" t="s">
+        <v>33</v>
+      </c>
+      <c r="G120">
+        <v>24.5</v>
+      </c>
+      <c r="H120">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B121" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C121">
         <v>3656</v>
       </c>
-      <c r="D114">
-        <v>5</v>
-      </c>
-      <c r="E114" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F114" t="s">
+      <c r="D121">
+        <v>5</v>
+      </c>
+      <c r="E121" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F121" t="s">
         <v>33</v>
       </c>
-      <c r="G114">
+      <c r="G121">
         <v>27</v>
       </c>
-      <c r="H114">
+      <c r="H121">
         <v>28</v>
       </c>
     </row>
@@ -12865,10 +13101,10 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1067</v>
+        <v>1063</v>
       </c>
       <c r="B2" t="s">
-        <v>1068</v>
+        <v>1064</v>
       </c>
       <c r="C2">
         <v>3459</v>
@@ -12891,10 +13127,10 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>1069</v>
+        <v>1065</v>
       </c>
       <c r="B3" t="s">
-        <v>1070</v>
+        <v>1066</v>
       </c>
       <c r="C3">
         <v>3803</v>
@@ -12917,10 +13153,10 @@
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B4" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="C4">
         <v>3425</v>
@@ -12943,10 +13179,10 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>1071</v>
+        <v>1067</v>
       </c>
       <c r="B5" t="s">
-        <v>1072</v>
+        <v>1068</v>
       </c>
       <c r="C5">
         <v>3426</v>
@@ -12969,10 +13205,10 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B6" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C6">
         <v>3427</v>
@@ -12995,10 +13231,10 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>1073</v>
+        <v>1069</v>
       </c>
       <c r="B7" t="s">
-        <v>1074</v>
+        <v>1070</v>
       </c>
       <c r="C7">
         <v>3428</v>
@@ -13021,10 +13257,10 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B8" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="C8">
         <v>3429</v>
@@ -13047,10 +13283,10 @@
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>1075</v>
+        <v>1071</v>
       </c>
       <c r="B9" t="s">
-        <v>1076</v>
+        <v>1072</v>
       </c>
       <c r="C9">
         <v>3430</v>
@@ -13073,10 +13309,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B10" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C10">
         <v>3913</v>
@@ -13099,10 +13335,10 @@
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="B11" t="s">
-        <v>1078</v>
+        <v>1074</v>
       </c>
       <c r="C11">
         <v>3872</v>
@@ -13125,10 +13361,10 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="B12" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C12">
         <v>3422</v>
@@ -13151,10 +13387,10 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1079</v>
+        <v>1075</v>
       </c>
       <c r="B13" t="s">
-        <v>1080</v>
+        <v>1076</v>
       </c>
       <c r="C13">
         <v>3423</v>
@@ -13163,7 +13399,7 @@
         <v>12</v>
       </c>
       <c r="E13" t="s">
-        <v>1081</v>
+        <v>1077</v>
       </c>
       <c r="F13" t="s">
         <v>25</v>
@@ -13177,10 +13413,10 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B14" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C14">
         <v>3431</v>
@@ -13203,10 +13439,10 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>1082</v>
+        <v>1078</v>
       </c>
       <c r="B15" t="s">
-        <v>1083</v>
+        <v>1079</v>
       </c>
       <c r="C15">
         <v>3432</v>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B98AA6-0CE7-41DD-B0B0-16EE5264316F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F08226-FF50-41F9-B2FF-B1536D04EF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="12" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -24703,10 +24703,10 @@
         <v>14</v>
       </c>
       <c r="G36">
-        <v>28.5</v>
+        <v>31.5</v>
       </c>
       <c r="H36">
-        <v>29.5</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -24729,10 +24729,10 @@
         <v>33</v>
       </c>
       <c r="G37">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H37">
-        <v>41</v>
+        <v>45</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -24755,10 +24755,10 @@
         <v>14</v>
       </c>
       <c r="G38">
-        <v>30.5</v>
+        <v>33</v>
       </c>
       <c r="H38">
-        <v>31.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -24781,10 +24781,10 @@
         <v>33</v>
       </c>
       <c r="G39">
-        <v>42.5</v>
+        <v>46</v>
       </c>
       <c r="H39">
-        <v>44</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34F08226-FF50-41F9-B2FF-B1536D04EF87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3414BB-1C1A-498C-9C7E-4FB6B7E96079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3568" uniqueCount="1102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3572" uniqueCount="1105">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3343,6 +3343,15 @@
   </si>
   <si>
     <t>BALA GELATINA COBRINHA CITRICA</t>
+  </si>
+  <si>
+    <t>gota-chocolate-branco</t>
+  </si>
+  <si>
+    <t>GOTA CHOCOLATE BRANCO</t>
+  </si>
+  <si>
+    <t>500G</t>
   </si>
 </sst>
 </file>
@@ -9898,7 +9907,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:H121"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -12511,54 +12520,54 @@
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1024</v>
+        <v>1102</v>
       </c>
       <c r="B101" t="s">
-        <v>1025</v>
+        <v>1103</v>
       </c>
       <c r="C101">
-        <v>4412</v>
+        <v>4635</v>
       </c>
       <c r="D101">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="E101" t="s">
-        <v>10</v>
+        <v>1104</v>
       </c>
       <c r="F101" t="s">
         <v>988</v>
       </c>
       <c r="G101">
-        <v>71.5</v>
+        <v>167</v>
       </c>
       <c r="H101">
-        <v>73.5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="B102" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="C102">
-        <v>4413</v>
+        <v>4412</v>
       </c>
       <c r="D102">
-        <v>25</v>
+        <v>2.5</v>
       </c>
       <c r="E102" t="s">
         <v>10</v>
       </c>
       <c r="F102" t="s">
-        <v>11</v>
+        <v>988</v>
       </c>
       <c r="G102">
-        <v>496</v>
+        <v>71.5</v>
       </c>
       <c r="H102">
-        <v>511</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -12569,10 +12578,10 @@
         <v>1027</v>
       </c>
       <c r="C103">
-        <v>4414</v>
+        <v>4413</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E103" t="s">
         <v>10</v>
@@ -12581,24 +12590,24 @@
         <v>11</v>
       </c>
       <c r="G103">
-        <v>101</v>
+        <v>496</v>
       </c>
       <c r="H103">
-        <v>104</v>
+        <v>511</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="B104" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="C104">
-        <v>4415</v>
+        <v>4414</v>
       </c>
       <c r="D104">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E104" t="s">
         <v>10</v>
@@ -12607,10 +12616,10 @@
         <v>11</v>
       </c>
       <c r="G104">
-        <v>414</v>
+        <v>101</v>
       </c>
       <c r="H104">
-        <v>426.5</v>
+        <v>104</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -12621,10 +12630,10 @@
         <v>1029</v>
       </c>
       <c r="C105">
-        <v>4416</v>
+        <v>4415</v>
       </c>
       <c r="D105">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
@@ -12633,73 +12642,73 @@
         <v>11</v>
       </c>
       <c r="G105">
-        <v>85</v>
+        <v>414</v>
       </c>
       <c r="H105">
-        <v>87</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="B106" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
       <c r="C106">
-        <v>4475</v>
+        <v>4416</v>
       </c>
       <c r="D106">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
-        <v>1032</v>
+        <v>10</v>
       </c>
       <c r="F106" t="s">
         <v>11</v>
       </c>
       <c r="G106">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="H106">
-        <v>9.5</v>
+        <v>87</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="B107" t="s">
-        <v>1034</v>
+        <v>1031</v>
       </c>
       <c r="C107">
-        <v>4354</v>
+        <v>4475</v>
       </c>
       <c r="D107">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E107" t="s">
         <v>1032</v>
       </c>
       <c r="F107" t="s">
-        <v>750</v>
+        <v>11</v>
       </c>
       <c r="G107">
-        <v>79.5</v>
+        <v>9</v>
       </c>
       <c r="H107">
-        <v>82</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="B108" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
       <c r="C108">
-        <v>4445</v>
+        <v>4354</v>
       </c>
       <c r="D108">
         <v>12</v>
@@ -12708,7 +12717,7 @@
         <v>1032</v>
       </c>
       <c r="F108" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="G108">
         <v>79.5</v>
@@ -12719,13 +12728,13 @@
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="B109" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="C109">
-        <v>4353</v>
+        <v>4445</v>
       </c>
       <c r="D109">
         <v>12</v>
@@ -12745,13 +12754,13 @@
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="B110" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="C110">
-        <v>4350</v>
+        <v>4353</v>
       </c>
       <c r="D110">
         <v>12</v>
@@ -12771,13 +12780,13 @@
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="B111" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="C111">
-        <v>4352</v>
+        <v>4350</v>
       </c>
       <c r="D111">
         <v>12</v>
@@ -12797,13 +12806,13 @@
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
       <c r="B112" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
       <c r="C112">
-        <v>4349</v>
+        <v>4352</v>
       </c>
       <c r="D112">
         <v>12</v>
@@ -12823,13 +12832,13 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
       <c r="B113" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="C113">
-        <v>4351</v>
+        <v>4349</v>
       </c>
       <c r="D113">
         <v>12</v>
@@ -12849,13 +12858,13 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B114" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="C114">
-        <v>4581</v>
+        <v>4351</v>
       </c>
       <c r="D114">
         <v>12</v>
@@ -12875,91 +12884,91 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
       <c r="B115" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
       <c r="C115">
-        <v>4096</v>
+        <v>4581</v>
       </c>
       <c r="D115">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>10</v>
+        <v>1032</v>
       </c>
       <c r="F115" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G115">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="H115">
-        <v>81.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="B116" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="C116">
-        <v>4123</v>
+        <v>4096</v>
       </c>
       <c r="D116">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E116" t="s">
-        <v>1016</v>
+        <v>10</v>
       </c>
       <c r="F116" t="s">
         <v>11</v>
       </c>
       <c r="G116">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="H116">
-        <v>62</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B117" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C117">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D117">
         <v>10</v>
       </c>
       <c r="E117" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="F117" t="s">
-        <v>988</v>
+        <v>11</v>
       </c>
       <c r="G117">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="H117">
-        <v>83.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B118" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C118">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D118">
         <v>10</v>
@@ -12979,28 +12988,28 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B119" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C119">
-        <v>2659</v>
+        <v>4307</v>
       </c>
       <c r="D119">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E119" t="s">
-        <v>1059</v>
+        <v>1003</v>
       </c>
       <c r="F119" t="s">
-        <v>33</v>
+        <v>988</v>
       </c>
       <c r="G119">
-        <v>27.5</v>
+        <v>81</v>
       </c>
       <c r="H119">
-        <v>28.5</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
@@ -13011,47 +13020,73 @@
         <v>1058</v>
       </c>
       <c r="C120">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D120">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E120" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F120" t="s">
         <v>33</v>
       </c>
       <c r="G120">
-        <v>24.5</v>
+        <v>27.5</v>
       </c>
       <c r="H120">
-        <v>25</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B121" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C121">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D121">
         <v>5</v>
       </c>
       <c r="E121" t="s">
-        <v>1003</v>
+        <v>1060</v>
       </c>
       <c r="F121" t="s">
         <v>33</v>
       </c>
       <c r="G121">
+        <v>24.5</v>
+      </c>
+      <c r="H121">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B122" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C122">
+        <v>3656</v>
+      </c>
+      <c r="D122">
+        <v>5</v>
+      </c>
+      <c r="E122" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F122" t="s">
+        <v>33</v>
+      </c>
+      <c r="G122">
         <v>27</v>
       </c>
-      <c r="H121">
+      <c r="H122">
         <v>28</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3414BB-1C1A-498C-9C7E-4FB6B7E96079}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987A25CA-6D33-4EEF-A56A-179A7C0ABE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="570" yWindow="780" windowWidth="27300" windowHeight="13920" firstSheet="8" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3572" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3580" uniqueCount="1107">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3352,6 +3352,12 @@
   </si>
   <si>
     <t>500G</t>
+  </si>
+  <si>
+    <t>castanha-do-para-large-paratini</t>
+  </si>
+  <si>
+    <t>CASTANHA DO PARA LARGE PARATINI</t>
   </si>
 </sst>
 </file>
@@ -13505,7 +13511,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H90"/>
+  <dimension ref="A1:H92"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -14948,13 +14954,13 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>161</v>
+        <v>1105</v>
       </c>
       <c r="B56" t="s">
-        <v>162</v>
+        <v>1106</v>
       </c>
       <c r="C56">
-        <v>3534</v>
+        <v>2291</v>
       </c>
       <c r="D56">
         <v>20</v>
@@ -14966,21 +14972,21 @@
         <v>25</v>
       </c>
       <c r="G56">
-        <v>1700</v>
+        <v>1820</v>
       </c>
       <c r="H56">
-        <v>1751</v>
+        <v>1874.5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>161</v>
+        <v>1105</v>
       </c>
       <c r="B57" t="s">
-        <v>162</v>
+        <v>1106</v>
       </c>
       <c r="C57">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D57">
         <v>5</v>
@@ -14992,151 +14998,151 @@
         <v>11</v>
       </c>
       <c r="G57">
-        <v>427</v>
+        <v>457</v>
       </c>
       <c r="H57">
-        <v>440</v>
+        <v>470.5</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B58" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C58">
-        <v>2340</v>
+        <v>3534</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G58">
-        <v>417</v>
+        <v>1560</v>
       </c>
       <c r="H58">
-        <v>429.5</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B59" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C59">
-        <v>3533</v>
+        <v>2250</v>
       </c>
       <c r="D59">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G59">
-        <v>1660</v>
+        <v>392</v>
       </c>
       <c r="H59">
-        <v>1710</v>
+        <v>404</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B60" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C60">
-        <v>3532</v>
+        <v>2340</v>
       </c>
       <c r="D60">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G60">
-        <v>1440</v>
+        <v>372</v>
       </c>
       <c r="H60">
-        <v>1483</v>
+        <v>383</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B61" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C61">
-        <v>2251</v>
+        <v>3533</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G61">
-        <v>362</v>
+        <v>1480</v>
       </c>
       <c r="H61">
-        <v>373</v>
+        <v>1524.5</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B62" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C62">
-        <v>3081</v>
+        <v>3532</v>
       </c>
       <c r="D62">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G62">
-        <v>135</v>
+        <v>1040</v>
       </c>
       <c r="H62">
-        <v>139</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="B63" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C63">
-        <v>3818</v>
+        <v>2251</v>
       </c>
       <c r="D63">
         <v>5</v>
@@ -15148,24 +15154,24 @@
         <v>11</v>
       </c>
       <c r="G63">
-        <v>69.5</v>
+        <v>262</v>
       </c>
       <c r="H63">
-        <v>71.5</v>
+        <v>270</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B64" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C64">
-        <v>2534</v>
+        <v>3081</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
@@ -15174,24 +15180,24 @@
         <v>11</v>
       </c>
       <c r="G64">
-        <v>69.5</v>
+        <v>135</v>
       </c>
       <c r="H64">
-        <v>71.5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B65" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C65">
-        <v>2234</v>
+        <v>3818</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
@@ -15200,24 +15206,24 @@
         <v>11</v>
       </c>
       <c r="G65">
-        <v>135</v>
+        <v>69.5</v>
       </c>
       <c r="H65">
-        <v>139</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B66" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C66">
-        <v>2238</v>
+        <v>2534</v>
       </c>
       <c r="D66">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -15226,24 +15232,24 @@
         <v>11</v>
       </c>
       <c r="G66">
-        <v>135</v>
+        <v>69.5</v>
       </c>
       <c r="H66">
-        <v>139</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="B67" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C67">
-        <v>2535</v>
+        <v>2234</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -15252,21 +15258,21 @@
         <v>11</v>
       </c>
       <c r="G67">
-        <v>69.5</v>
+        <v>135</v>
       </c>
       <c r="H67">
-        <v>71.5</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B68" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C68">
-        <v>2512</v>
+        <v>2238</v>
       </c>
       <c r="D68">
         <v>10</v>
@@ -15278,21 +15284,21 @@
         <v>11</v>
       </c>
       <c r="G68">
-        <v>166</v>
+        <v>135</v>
       </c>
       <c r="H68">
-        <v>171</v>
+        <v>139</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B69" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C69">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="D69">
         <v>5</v>
@@ -15304,21 +15310,21 @@
         <v>11</v>
       </c>
       <c r="G69">
-        <v>83</v>
+        <v>69.5</v>
       </c>
       <c r="H69">
-        <v>85</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B70" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C70">
-        <v>2236</v>
+        <v>2512</v>
       </c>
       <c r="D70">
         <v>10</v>
@@ -15330,21 +15336,21 @@
         <v>11</v>
       </c>
       <c r="G70">
-        <v>135</v>
+        <v>166</v>
       </c>
       <c r="H70">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B71" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C71">
-        <v>2546</v>
+        <v>2537</v>
       </c>
       <c r="D71">
         <v>5</v>
@@ -15356,21 +15362,21 @@
         <v>11</v>
       </c>
       <c r="G71">
-        <v>69.5</v>
+        <v>83</v>
       </c>
       <c r="H71">
-        <v>71.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B72" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C72">
-        <v>2232</v>
+        <v>2236</v>
       </c>
       <c r="D72">
         <v>10</v>
@@ -15390,13 +15396,13 @@
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B73" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C73">
-        <v>2536</v>
+        <v>2546</v>
       </c>
       <c r="D73">
         <v>5</v>
@@ -15416,13 +15422,13 @@
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B74" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C74">
-        <v>3815</v>
+        <v>2232</v>
       </c>
       <c r="D74">
         <v>10</v>
@@ -15431,27 +15437,27 @@
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G74">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="H74">
-        <v>129</v>
+        <v>139</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B75" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C75">
-        <v>3713</v>
+        <v>2536</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -15460,21 +15466,21 @@
         <v>11</v>
       </c>
       <c r="G75">
-        <v>125</v>
+        <v>69.5</v>
       </c>
       <c r="H75">
-        <v>129</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="B76" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="C76">
-        <v>3712</v>
+        <v>3815</v>
       </c>
       <c r="D76">
         <v>10</v>
@@ -15494,13 +15500,13 @@
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B77" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="C77">
-        <v>3714</v>
+        <v>3713</v>
       </c>
       <c r="D77">
         <v>10</v>
@@ -15520,13 +15526,13 @@
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B78" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="C78">
-        <v>3715</v>
+        <v>3712</v>
       </c>
       <c r="D78">
         <v>10</v>
@@ -15546,16 +15552,16 @@
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="B79" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C79">
-        <v>4021</v>
+        <v>3714</v>
       </c>
       <c r="D79">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -15572,13 +15578,13 @@
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B80" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C80">
-        <v>4135</v>
+        <v>3715</v>
       </c>
       <c r="D80">
         <v>10</v>
@@ -15587,27 +15593,27 @@
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G80">
-        <v>1250</v>
+        <v>125</v>
       </c>
       <c r="H80">
-        <v>1287.5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B81" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C81">
-        <v>2852</v>
+        <v>4021</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -15616,21 +15622,21 @@
         <v>11</v>
       </c>
       <c r="G81">
-        <v>325</v>
+        <v>125</v>
       </c>
       <c r="H81">
-        <v>335</v>
+        <v>129</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B82" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C82">
-        <v>3601</v>
+        <v>4135</v>
       </c>
       <c r="D82">
         <v>10</v>
@@ -15639,53 +15645,53 @@
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G82">
-        <v>650</v>
+        <v>1250</v>
       </c>
       <c r="H82">
-        <v>669.5</v>
+        <v>1287.5</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B83" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C83">
-        <v>3093</v>
+        <v>2852</v>
       </c>
       <c r="D83">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G83">
-        <v>693</v>
+        <v>325</v>
       </c>
       <c r="H83">
-        <v>713</v>
+        <v>335</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B84" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C84">
-        <v>2632</v>
+        <v>3601</v>
       </c>
       <c r="D84">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -15694,21 +15700,21 @@
         <v>11</v>
       </c>
       <c r="G84">
-        <v>317</v>
+        <v>650</v>
       </c>
       <c r="H84">
-        <v>326.5</v>
+        <v>669.5</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B85" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C85">
-        <v>4179</v>
+        <v>3093</v>
       </c>
       <c r="D85">
         <v>11</v>
@@ -15720,36 +15726,36 @@
         <v>25</v>
       </c>
       <c r="G85">
-        <v>572</v>
+        <v>693</v>
       </c>
       <c r="H85">
-        <v>589</v>
+        <v>713</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B86" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C86">
-        <v>2330</v>
+        <v>2632</v>
       </c>
       <c r="D86">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G86">
-        <v>520</v>
+        <v>317</v>
       </c>
       <c r="H86">
-        <v>589</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -15760,36 +15766,36 @@
         <v>197</v>
       </c>
       <c r="C87">
-        <v>2385</v>
+        <v>4179</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G87">
-        <v>262</v>
+        <v>572</v>
       </c>
       <c r="H87">
-        <v>270</v>
+        <v>589</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B88" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C88">
-        <v>2384</v>
+        <v>2330</v>
       </c>
       <c r="D88">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -15798,36 +15804,36 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>187.5</v>
+        <v>520</v>
       </c>
       <c r="H88">
-        <v>193</v>
+        <v>589</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B89" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C89">
-        <v>3851</v>
+        <v>2385</v>
       </c>
       <c r="D89">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G89">
-        <v>75</v>
+        <v>262</v>
       </c>
       <c r="H89">
-        <v>77</v>
+        <v>270</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -15838,21 +15844,73 @@
         <v>199</v>
       </c>
       <c r="C90">
+        <v>2384</v>
+      </c>
+      <c r="D90">
+        <v>25</v>
+      </c>
+      <c r="E90" t="s">
+        <v>10</v>
+      </c>
+      <c r="F90" t="s">
+        <v>25</v>
+      </c>
+      <c r="G90">
+        <v>187.5</v>
+      </c>
+      <c r="H90">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>198</v>
+      </c>
+      <c r="B91" t="s">
+        <v>199</v>
+      </c>
+      <c r="C91">
+        <v>3851</v>
+      </c>
+      <c r="D91">
+        <v>10</v>
+      </c>
+      <c r="E91" t="s">
+        <v>10</v>
+      </c>
+      <c r="F91" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91">
+        <v>75</v>
+      </c>
+      <c r="H91">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>198</v>
+      </c>
+      <c r="B92" t="s">
+        <v>199</v>
+      </c>
+      <c r="C92">
         <v>2424</v>
       </c>
-      <c r="D90">
-        <v>5</v>
-      </c>
-      <c r="E90" t="s">
-        <v>10</v>
-      </c>
-      <c r="F90" t="s">
-        <v>11</v>
-      </c>
-      <c r="G90">
+      <c r="D92">
+        <v>5</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" t="s">
+        <v>11</v>
+      </c>
+      <c r="G92">
         <v>39.5</v>
       </c>
-      <c r="H90">
+      <c r="H92">
         <v>40.5</v>
       </c>
     </row>
@@ -16632,10 +16690,10 @@
         <v>25</v>
       </c>
       <c r="G2">
-        <v>420</v>
+        <v>448</v>
       </c>
       <c r="H2">
-        <v>432.5</v>
+        <v>461.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -16658,10 +16716,10 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="H3">
-        <v>109</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -21816,10 +21874,10 @@
         <v>14</v>
       </c>
       <c r="G54">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="H54">
-        <v>278</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -21842,10 +21900,10 @@
         <v>14</v>
       </c>
       <c r="G55">
-        <v>135</v>
+        <v>157.5</v>
       </c>
       <c r="H55">
-        <v>139</v>
+        <v>162</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -21868,10 +21926,10 @@
         <v>11</v>
       </c>
       <c r="G56">
-        <v>24.5</v>
+        <v>28.5</v>
       </c>
       <c r="H56">
-        <v>25.5</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{987A25CA-6D33-4EEF-A56A-179A7C0ABE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEAA872-EFFF-4855-BE43-4F5AA6E21133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -4488,10 +4488,10 @@
         <v>25</v>
       </c>
       <c r="G19">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="H19">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AEAA872-EFFF-4855-BE43-4F5AA6E21133}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA5D795-263B-421C-8C22-3DE2DDAB0DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="11" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3580" uniqueCount="1107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="1111">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3358,6 +3358,18 @@
   </si>
   <si>
     <t>CASTANHA DO PARA LARGE PARATINI</t>
+  </si>
+  <si>
+    <t>ameixa-em-po</t>
+  </si>
+  <si>
+    <t>AMEIXA EM PÓ</t>
+  </si>
+  <si>
+    <t>flocos-de-arroz</t>
+  </si>
+  <si>
+    <t>FLOCOS DE ARROZ</t>
   </si>
 </sst>
 </file>
@@ -5559,7 +5571,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H116"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -5772,10 +5784,10 @@
         <v>33</v>
       </c>
       <c r="G8">
-        <v>57.5</v>
+        <v>62</v>
       </c>
       <c r="H8">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -5798,10 +5810,10 @@
         <v>33</v>
       </c>
       <c r="G9">
-        <v>65</v>
+        <v>69.5</v>
       </c>
       <c r="H9">
-        <v>67</v>
+        <v>71.5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -5824,10 +5836,10 @@
         <v>33</v>
       </c>
       <c r="G10">
-        <v>141.5</v>
+        <v>153.5</v>
       </c>
       <c r="H10">
-        <v>146</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -6014,28 +6026,28 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>666</v>
+        <v>1107</v>
       </c>
       <c r="B18" t="s">
-        <v>667</v>
+        <v>1108</v>
       </c>
       <c r="C18">
-        <v>2336</v>
+        <v>4639</v>
       </c>
       <c r="D18">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
       </c>
       <c r="F18" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>750</v>
+        <v>295</v>
       </c>
       <c r="H18">
-        <v>772.5</v>
+        <v>304</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -6046,48 +6058,48 @@
         <v>667</v>
       </c>
       <c r="C19">
-        <v>2421</v>
+        <v>2336</v>
       </c>
       <c r="D19">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G19">
-        <v>91</v>
+        <v>750</v>
       </c>
       <c r="H19">
-        <v>94</v>
+        <v>772.5</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B20" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C20">
-        <v>2568</v>
+        <v>2421</v>
       </c>
       <c r="D20">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20">
-        <v>260</v>
+        <v>91</v>
       </c>
       <c r="H20">
-        <v>268</v>
+        <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -6098,59 +6110,59 @@
         <v>669</v>
       </c>
       <c r="C21">
-        <v>3009</v>
+        <v>2568</v>
       </c>
       <c r="D21">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G21">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="H21">
-        <v>80.5</v>
+        <v>268</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B22" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C22">
-        <v>2778</v>
+        <v>3009</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G22">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="H22">
-        <v>185.5</v>
+        <v>80.5</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B23" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C23">
-        <v>3106</v>
+        <v>2778</v>
       </c>
       <c r="D23">
         <v>5</v>
@@ -6159,39 +6171,39 @@
         <v>10</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G23">
-        <v>260</v>
+        <v>180</v>
       </c>
       <c r="H23">
-        <v>268</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B24" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C24">
-        <v>3489</v>
+        <v>3106</v>
       </c>
       <c r="D24">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>700</v>
+        <v>260</v>
       </c>
       <c r="H24">
-        <v>721</v>
+        <v>268</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -6202,22 +6214,22 @@
         <v>675</v>
       </c>
       <c r="C25">
-        <v>2783</v>
+        <v>3489</v>
       </c>
       <c r="D25">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G25">
-        <v>142</v>
+        <v>700</v>
       </c>
       <c r="H25">
-        <v>159.5</v>
+        <v>721</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -6228,10 +6240,10 @@
         <v>675</v>
       </c>
       <c r="C26">
-        <v>3755</v>
+        <v>2783</v>
       </c>
       <c r="D26">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
@@ -6240,36 +6252,36 @@
         <v>11</v>
       </c>
       <c r="G26">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="H26">
-        <v>88</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B27" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C27">
-        <v>3486</v>
+        <v>3755</v>
       </c>
       <c r="D27">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G27">
-        <v>595</v>
+        <v>85</v>
       </c>
       <c r="H27">
-        <v>613</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -6280,10 +6292,10 @@
         <v>677</v>
       </c>
       <c r="C28">
-        <v>4488</v>
+        <v>3487</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
@@ -6292,47 +6304,47 @@
         <v>11</v>
       </c>
       <c r="G28">
-        <v>299.5</v>
+        <v>180</v>
       </c>
       <c r="H28">
-        <v>308.5</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B29" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C29">
-        <v>4333</v>
+        <v>3486</v>
       </c>
       <c r="D29">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G29">
-        <v>259.5</v>
+        <v>595</v>
       </c>
       <c r="H29">
-        <v>267</v>
+        <v>613</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="B30" t="s">
-        <v>681</v>
+        <v>677</v>
       </c>
       <c r="C30">
-        <v>4388</v>
+        <v>4488</v>
       </c>
       <c r="D30">
         <v>5</v>
@@ -6344,21 +6356,21 @@
         <v>11</v>
       </c>
       <c r="G30">
-        <v>145</v>
+        <v>299.5</v>
       </c>
       <c r="H30">
-        <v>149.5</v>
+        <v>308.5</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>682</v>
+        <v>678</v>
       </c>
       <c r="B31" t="s">
-        <v>683</v>
+        <v>679</v>
       </c>
       <c r="C31">
-        <v>4389</v>
+        <v>4333</v>
       </c>
       <c r="D31">
         <v>5</v>
@@ -6370,47 +6382,47 @@
         <v>11</v>
       </c>
       <c r="G31">
-        <v>102</v>
+        <v>259.5</v>
       </c>
       <c r="H31">
-        <v>105</v>
+        <v>267</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>684</v>
+        <v>680</v>
       </c>
       <c r="B32" t="s">
-        <v>685</v>
+        <v>681</v>
       </c>
       <c r="C32">
-        <v>3488</v>
+        <v>4388</v>
       </c>
       <c r="D32">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G32">
-        <v>220</v>
+        <v>145</v>
       </c>
       <c r="H32">
-        <v>226.5</v>
+        <v>149.5</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B33" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C33">
-        <v>3400</v>
+        <v>4389</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -6422,73 +6434,73 @@
         <v>11</v>
       </c>
       <c r="G33">
-        <v>57</v>
+        <v>102</v>
       </c>
       <c r="H33">
-        <v>59</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>95</v>
+        <v>684</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>685</v>
       </c>
       <c r="C34">
-        <v>2257</v>
+        <v>3488</v>
       </c>
       <c r="D34">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G34">
-        <v>16</v>
+        <v>220</v>
       </c>
       <c r="H34">
-        <v>16.5</v>
+        <v>226.5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>95</v>
+        <v>684</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>685</v>
       </c>
       <c r="C35">
-        <v>565</v>
+        <v>3400</v>
       </c>
       <c r="D35">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G35">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="H35">
-        <v>129</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>686</v>
+        <v>95</v>
       </c>
       <c r="B36" t="s">
-        <v>687</v>
+        <v>96</v>
       </c>
       <c r="C36">
-        <v>4474</v>
+        <v>2257</v>
       </c>
       <c r="D36">
         <v>3</v>
@@ -6500,47 +6512,47 @@
         <v>11</v>
       </c>
       <c r="G36">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="H36">
-        <v>40</v>
+        <v>16.5</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>688</v>
+        <v>95</v>
       </c>
       <c r="B37" t="s">
-        <v>689</v>
+        <v>96</v>
       </c>
       <c r="C37">
-        <v>4473</v>
+        <v>565</v>
       </c>
       <c r="D37">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G37">
-        <v>39</v>
+        <v>123</v>
       </c>
       <c r="H37">
-        <v>40</v>
+        <v>129</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>690</v>
+        <v>686</v>
       </c>
       <c r="B38" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C38">
-        <v>2658</v>
+        <v>4474</v>
       </c>
       <c r="D38">
         <v>3</v>
@@ -6560,13 +6572,13 @@
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>692</v>
+        <v>688</v>
       </c>
       <c r="B39" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C39">
-        <v>2657</v>
+        <v>4473</v>
       </c>
       <c r="D39">
         <v>3</v>
@@ -6586,276 +6598,276 @@
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="B40" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C40">
-        <v>3537</v>
+        <v>2658</v>
       </c>
       <c r="D40">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E40" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F40" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G40">
-        <v>162</v>
+        <v>39</v>
       </c>
       <c r="H40">
-        <v>166.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>696</v>
+        <v>692</v>
       </c>
       <c r="B41" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="C41">
-        <v>2732</v>
+        <v>2657</v>
       </c>
       <c r="D41">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G41">
-        <v>189</v>
+        <v>39</v>
       </c>
       <c r="H41">
-        <v>194.5</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>696</v>
+        <v>1109</v>
       </c>
       <c r="B42" t="s">
-        <v>697</v>
+        <v>1110</v>
       </c>
       <c r="C42">
-        <v>2733</v>
+        <v>4640</v>
       </c>
       <c r="D42">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F42" t="s">
         <v>11</v>
       </c>
       <c r="G42">
-        <v>96.5</v>
+        <v>82.5</v>
       </c>
       <c r="H42">
-        <v>99.5</v>
+        <v>85</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="B43" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="C43">
-        <v>2584</v>
+        <v>3537</v>
       </c>
       <c r="D43">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F43" t="s">
         <v>25</v>
       </c>
       <c r="G43">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="H43">
-        <v>130</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B44" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C44">
-        <v>2677</v>
+        <v>2732</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
       </c>
       <c r="F44" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G44">
-        <v>113.5</v>
+        <v>189</v>
       </c>
       <c r="H44">
-        <v>117</v>
+        <v>194.5</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>700</v>
+        <v>696</v>
       </c>
       <c r="B45" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="C45">
-        <v>2495</v>
+        <v>2733</v>
       </c>
       <c r="D45">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
       </c>
       <c r="F45" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G45">
-        <v>220</v>
+        <v>96.5</v>
       </c>
       <c r="H45">
-        <v>226.5</v>
+        <v>99.5</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B46" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C46">
-        <v>2678</v>
+        <v>2584</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G46">
-        <v>112</v>
+        <v>223</v>
       </c>
       <c r="H46">
-        <v>115.5</v>
+        <v>130</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="B47" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="C47">
-        <v>4498</v>
+        <v>2677</v>
       </c>
       <c r="D47">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>240</v>
+        <v>113.5</v>
       </c>
       <c r="H47">
-        <v>247</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B48" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C48">
-        <v>4253</v>
+        <v>2495</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G48">
-        <v>112</v>
+        <v>220</v>
       </c>
       <c r="H48">
-        <v>115.5</v>
+        <v>226.5</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>704</v>
+        <v>700</v>
       </c>
       <c r="B49" t="s">
-        <v>705</v>
+        <v>701</v>
       </c>
       <c r="C49">
-        <v>4500</v>
+        <v>2678</v>
       </c>
       <c r="D49">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
       </c>
       <c r="F49" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G49">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="H49">
-        <v>230</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B50" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C50">
-        <v>4249</v>
+        <v>4498</v>
       </c>
       <c r="D50">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E50" t="s">
         <v>30</v>
@@ -6864,10 +6876,10 @@
         <v>33</v>
       </c>
       <c r="G50">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="H50">
-        <v>237</v>
+        <v>247</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -6878,62 +6890,62 @@
         <v>705</v>
       </c>
       <c r="C51">
-        <v>3724</v>
+        <v>4253</v>
       </c>
       <c r="D51">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
         <v>33</v>
       </c>
       <c r="G51">
-        <v>224</v>
+        <v>112</v>
       </c>
       <c r="H51">
-        <v>230</v>
+        <v>115.5</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="B52" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C52">
-        <v>3736</v>
+        <v>4500</v>
       </c>
       <c r="D52">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E52" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G52">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="H52">
-        <v>166.5</v>
+        <v>230</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B53" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C53">
-        <v>4499</v>
+        <v>4249</v>
       </c>
       <c r="D53">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E53" t="s">
         <v>30</v>
@@ -6942,125 +6954,125 @@
         <v>33</v>
       </c>
       <c r="G53">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H53">
-        <v>247</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="B54" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C54">
-        <v>3536</v>
+        <v>3724</v>
       </c>
       <c r="D54">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E54" t="s">
         <v>30</v>
       </c>
       <c r="F54" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G54">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="H54">
-        <v>166.5</v>
+        <v>230</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
       <c r="B55" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="C55">
-        <v>2494</v>
+        <v>3736</v>
       </c>
       <c r="D55">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F55" t="s">
         <v>25</v>
       </c>
       <c r="G55">
-        <v>188.5</v>
+        <v>162</v>
       </c>
       <c r="H55">
-        <v>194</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B56" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C56">
-        <v>2679</v>
+        <v>4499</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G56">
-        <v>96</v>
+        <v>240</v>
       </c>
       <c r="H56">
-        <v>99</v>
+        <v>247</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B57" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C57">
-        <v>4497</v>
+        <v>3536</v>
       </c>
       <c r="D57">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E57" t="s">
         <v>30</v>
       </c>
       <c r="F57" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G57">
-        <v>240</v>
+        <v>162</v>
       </c>
       <c r="H57">
-        <v>247</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B58" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C58">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D58">
         <v>10</v>
@@ -7072,232 +7084,232 @@
         <v>25</v>
       </c>
       <c r="G58">
-        <v>180</v>
+        <v>188.5</v>
       </c>
       <c r="H58">
-        <v>185.5</v>
+        <v>194</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="B59" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="C59">
-        <v>3535</v>
+        <v>2679</v>
       </c>
       <c r="D59">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G59">
-        <v>162</v>
+        <v>96</v>
       </c>
       <c r="H59">
-        <v>166.5</v>
+        <v>99</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="B60" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C60">
-        <v>2498</v>
+        <v>4497</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F60" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G60">
-        <v>92</v>
+        <v>240</v>
       </c>
       <c r="H60">
-        <v>94</v>
+        <v>247</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B61" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C61">
-        <v>2806</v>
+        <v>2493</v>
       </c>
       <c r="D61">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
       </c>
       <c r="F61" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G61">
-        <v>472.5</v>
+        <v>180</v>
       </c>
       <c r="H61">
-        <v>487</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="B62" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C62">
-        <v>2807</v>
+        <v>3535</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F62" t="s">
         <v>25</v>
       </c>
       <c r="G62">
-        <v>159.5</v>
+        <v>162</v>
       </c>
       <c r="H62">
-        <v>164.5</v>
+        <v>166.5</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="B63" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="C63">
-        <v>4556</v>
+        <v>2498</v>
       </c>
       <c r="D63">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G63">
-        <v>900</v>
+        <v>92</v>
       </c>
       <c r="H63">
-        <v>927</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="B64" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C64">
-        <v>4557</v>
+        <v>2806</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="G64">
-        <v>182</v>
+        <v>472.5</v>
       </c>
       <c r="H64">
-        <v>187.5</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B65" t="s">
-        <v>725</v>
+        <v>721</v>
       </c>
       <c r="C65">
-        <v>4018</v>
+        <v>2807</v>
       </c>
       <c r="D65">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G65">
-        <v>230</v>
+        <v>159.5</v>
       </c>
       <c r="H65">
-        <v>240</v>
+        <v>164.5</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="B66" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C66">
-        <v>2652</v>
+        <v>4556</v>
       </c>
       <c r="D66">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G66">
-        <v>117</v>
+        <v>900</v>
       </c>
       <c r="H66">
-        <v>120.5</v>
+        <v>927</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>726</v>
+        <v>722</v>
       </c>
       <c r="B67" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="C67">
-        <v>4049</v>
+        <v>4557</v>
       </c>
       <c r="D67">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -7306,24 +7318,24 @@
         <v>11</v>
       </c>
       <c r="G67">
-        <v>210</v>
+        <v>182</v>
       </c>
       <c r="H67">
-        <v>213.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="B68" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C68">
-        <v>3737</v>
+        <v>4018</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
@@ -7332,24 +7344,24 @@
         <v>11</v>
       </c>
       <c r="G68">
-        <v>107</v>
+        <v>230</v>
       </c>
       <c r="H68">
-        <v>110</v>
+        <v>240</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>728</v>
+        <v>724</v>
       </c>
       <c r="B69" t="s">
-        <v>729</v>
+        <v>725</v>
       </c>
       <c r="C69">
-        <v>4301</v>
+        <v>2652</v>
       </c>
       <c r="D69">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
@@ -7358,24 +7370,24 @@
         <v>11</v>
       </c>
       <c r="G69">
-        <v>235</v>
+        <v>117</v>
       </c>
       <c r="H69">
-        <v>242</v>
+        <v>120.5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>730</v>
+        <v>726</v>
       </c>
       <c r="B70" t="s">
-        <v>731</v>
+        <v>727</v>
       </c>
       <c r="C70">
-        <v>4334</v>
+        <v>4049</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
@@ -7384,50 +7396,50 @@
         <v>11</v>
       </c>
       <c r="G70">
-        <v>376.5</v>
+        <v>210</v>
       </c>
       <c r="H70">
-        <v>388</v>
+        <v>213.5</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>89</v>
+        <v>726</v>
       </c>
       <c r="B71" t="s">
-        <v>90</v>
+        <v>727</v>
       </c>
       <c r="C71">
-        <v>195</v>
+        <v>3737</v>
       </c>
       <c r="D71">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G71">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="H71">
-        <v>262.5</v>
+        <v>110</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>89</v>
+        <v>728</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>729</v>
       </c>
       <c r="C72">
-        <v>54</v>
+        <v>4301</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
@@ -7436,128 +7448,128 @@
         <v>11</v>
       </c>
       <c r="G72">
-        <v>53</v>
+        <v>235</v>
       </c>
       <c r="H72">
-        <v>54.5</v>
+        <v>242</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="B73" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C73">
-        <v>63</v>
+        <v>4334</v>
       </c>
       <c r="D73">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G73">
-        <v>255</v>
+        <v>376.5</v>
       </c>
       <c r="H73">
-        <v>244.5</v>
+        <v>388</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>732</v>
+        <v>89</v>
       </c>
       <c r="B74" t="s">
-        <v>733</v>
+        <v>90</v>
       </c>
       <c r="C74">
-        <v>2483</v>
+        <v>195</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G74">
-        <v>53</v>
+        <v>255</v>
       </c>
       <c r="H74">
-        <v>51</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>734</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>735</v>
+        <v>90</v>
       </c>
       <c r="C75">
-        <v>2974</v>
+        <v>54</v>
       </c>
       <c r="D75">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G75">
-        <v>250</v>
+        <v>53</v>
       </c>
       <c r="H75">
-        <v>257.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="B76" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C76">
-        <v>2831</v>
+        <v>63</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G76">
-        <v>127</v>
+        <v>255</v>
       </c>
       <c r="H76">
-        <v>131</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B77" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="C77">
-        <v>4137</v>
+        <v>2483</v>
       </c>
       <c r="D77">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
@@ -7566,47 +7578,47 @@
         <v>11</v>
       </c>
       <c r="G77">
-        <v>270</v>
+        <v>53</v>
       </c>
       <c r="H77">
-        <v>278</v>
+        <v>51</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>738</v>
+        <v>734</v>
       </c>
       <c r="B78" t="s">
-        <v>739</v>
+        <v>735</v>
       </c>
       <c r="C78">
-        <v>4380</v>
+        <v>2974</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G78">
-        <v>270</v>
+        <v>250</v>
       </c>
       <c r="H78">
-        <v>278</v>
+        <v>257.5</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
       <c r="B79" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="C79">
-        <v>4566</v>
+        <v>2831</v>
       </c>
       <c r="D79">
         <v>5</v>
@@ -7618,24 +7630,24 @@
         <v>11</v>
       </c>
       <c r="G79">
-        <v>240</v>
+        <v>127</v>
       </c>
       <c r="H79">
-        <v>247</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="B80" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="C80">
-        <v>4567</v>
+        <v>4137</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
@@ -7644,24 +7656,24 @@
         <v>11</v>
       </c>
       <c r="G80">
-        <v>240</v>
+        <v>270</v>
       </c>
       <c r="H80">
-        <v>247</v>
+        <v>278</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
       <c r="B81" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="C81">
-        <v>4204</v>
+        <v>4380</v>
       </c>
       <c r="D81">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
@@ -7670,50 +7682,50 @@
         <v>11</v>
       </c>
       <c r="G81">
-        <v>145.5</v>
+        <v>270</v>
       </c>
       <c r="H81">
-        <v>150</v>
+        <v>278</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>744</v>
+        <v>740</v>
       </c>
       <c r="B82" t="s">
-        <v>745</v>
+        <v>741</v>
       </c>
       <c r="C82">
-        <v>4205</v>
+        <v>4566</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G82">
-        <v>360</v>
+        <v>240</v>
       </c>
       <c r="H82">
-        <v>371</v>
+        <v>247</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="B83" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C83">
-        <v>4225</v>
+        <v>4567</v>
       </c>
       <c r="D83">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -7722,50 +7734,50 @@
         <v>11</v>
       </c>
       <c r="G83">
-        <v>900</v>
+        <v>240</v>
       </c>
       <c r="H83">
-        <v>927</v>
+        <v>247</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B84" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C84">
-        <v>4378</v>
+        <v>4204</v>
       </c>
       <c r="D84">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
       </c>
       <c r="F84" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G84">
-        <v>430</v>
+        <v>145.5</v>
       </c>
       <c r="H84">
-        <v>443</v>
+        <v>150</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="B85" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C85">
-        <v>4379</v>
+        <v>4205</v>
       </c>
       <c r="D85">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
@@ -7774,258 +7786,258 @@
         <v>14</v>
       </c>
       <c r="G85">
-        <v>43</v>
+        <v>360</v>
       </c>
       <c r="H85">
-        <v>44.5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="B86" t="s">
-        <v>749</v>
+        <v>745</v>
       </c>
       <c r="C86">
-        <v>3524</v>
+        <v>4225</v>
       </c>
       <c r="D86">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>750</v>
+        <v>11</v>
       </c>
       <c r="G86">
-        <v>350</v>
+        <v>900</v>
       </c>
       <c r="H86">
-        <v>360.5</v>
+        <v>927</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="B87" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C87">
-        <v>3523</v>
+        <v>4378</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>750</v>
+        <v>14</v>
       </c>
       <c r="G87">
-        <v>72</v>
+        <v>430</v>
       </c>
       <c r="H87">
-        <v>74</v>
+        <v>443</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>751</v>
+        <v>746</v>
       </c>
       <c r="B88" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="C88">
-        <v>3521</v>
+        <v>4379</v>
       </c>
       <c r="D88">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>753</v>
+        <v>10</v>
       </c>
       <c r="F88" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G88">
-        <v>158</v>
+        <v>43</v>
       </c>
       <c r="H88">
-        <v>163</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="B89" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="C89">
-        <v>3522</v>
+        <v>3524</v>
       </c>
       <c r="D89">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="E89" t="s">
-        <v>408</v>
+        <v>10</v>
       </c>
       <c r="F89" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="G89">
-        <v>216.5</v>
+        <v>350</v>
       </c>
       <c r="H89">
-        <v>223</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="B90" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="C90">
-        <v>64</v>
+        <v>3523</v>
       </c>
       <c r="D90">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="E90" t="s">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="F90" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="G90">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="H90">
-        <v>136</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>756</v>
+        <v>751</v>
       </c>
       <c r="B91" t="s">
-        <v>757</v>
+        <v>752</v>
       </c>
       <c r="C91">
-        <v>90</v>
+        <v>3521</v>
       </c>
       <c r="D91">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E91" t="s">
-        <v>30</v>
+        <v>753</v>
       </c>
       <c r="F91" t="s">
         <v>25</v>
       </c>
       <c r="G91">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="H91">
-        <v>136</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="B92" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="C92">
-        <v>3637</v>
+        <v>3522</v>
       </c>
       <c r="D92">
+        <v>12</v>
+      </c>
+      <c r="E92" t="s">
+        <v>408</v>
+      </c>
+      <c r="F92" t="s">
         <v>25</v>
       </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>14</v>
-      </c>
       <c r="G92">
-        <v>375</v>
+        <v>216.5</v>
       </c>
       <c r="H92">
-        <v>386</v>
+        <v>223</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>758</v>
+        <v>754</v>
       </c>
       <c r="B93" t="s">
-        <v>759</v>
+        <v>755</v>
       </c>
       <c r="C93">
-        <v>2805</v>
+        <v>64</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E93" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F93" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="G93">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="H93">
-        <v>154.5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B94" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C94">
-        <v>2427</v>
+        <v>90</v>
       </c>
       <c r="D94">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E94" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="F94" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G94">
-        <v>46</v>
+        <v>132</v>
       </c>
       <c r="H94">
-        <v>47.5</v>
+        <v>136</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B95" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C95">
-        <v>3437</v>
+        <v>3637</v>
       </c>
       <c r="D95">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E95" t="s">
         <v>10</v>
@@ -8034,284 +8046,284 @@
         <v>14</v>
       </c>
       <c r="G95">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="H95">
-        <v>402</v>
+        <v>386</v>
       </c>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="B96" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C96">
-        <v>3396</v>
+        <v>2805</v>
       </c>
       <c r="D96">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E96" t="s">
         <v>10</v>
       </c>
       <c r="F96" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G96">
-        <v>197</v>
+        <v>150</v>
       </c>
       <c r="H96">
-        <v>203</v>
+        <v>154.5</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B97" t="s">
-        <v>763</v>
+        <v>759</v>
       </c>
       <c r="C97">
-        <v>3395</v>
+        <v>2427</v>
       </c>
       <c r="D97">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>764</v>
+        <v>10</v>
       </c>
       <c r="F97" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G97">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="H97">
-        <v>55.5</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="B98" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="C98">
-        <v>3490</v>
+        <v>3437</v>
       </c>
       <c r="D98">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E98" t="s">
-        <v>764</v>
+        <v>10</v>
       </c>
       <c r="F98" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G98">
-        <v>169</v>
+        <v>390</v>
       </c>
       <c r="H98">
-        <v>174</v>
+        <v>402</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>767</v>
+        <v>760</v>
       </c>
       <c r="B99" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="C99">
-        <v>458</v>
+        <v>3396</v>
       </c>
       <c r="D99">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E99" t="s">
-        <v>769</v>
+        <v>10</v>
       </c>
       <c r="F99" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G99">
-        <v>269.5</v>
+        <v>197</v>
       </c>
       <c r="H99">
-        <v>278</v>
+        <v>203</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="B100" t="s">
-        <v>771</v>
+        <v>763</v>
       </c>
       <c r="C100">
-        <v>2641</v>
+        <v>3395</v>
       </c>
       <c r="D100">
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="F100" t="s">
         <v>25</v>
       </c>
       <c r="G100">
-        <v>222</v>
+        <v>54</v>
       </c>
       <c r="H100">
-        <v>229</v>
+        <v>55.5</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="B101" t="s">
-        <v>773</v>
+        <v>766</v>
       </c>
       <c r="C101">
-        <v>4293</v>
+        <v>3490</v>
       </c>
       <c r="D101">
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="F101" t="s">
         <v>25</v>
       </c>
       <c r="G101">
-        <v>210</v>
+        <v>169</v>
       </c>
       <c r="H101">
-        <v>216.5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="B102" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="C102">
-        <v>2396</v>
+        <v>458</v>
       </c>
       <c r="D102">
+        <v>12</v>
+      </c>
+      <c r="E102" t="s">
+        <v>769</v>
+      </c>
+      <c r="F102" t="s">
         <v>25</v>
       </c>
-      <c r="E102" t="s">
-        <v>10</v>
-      </c>
-      <c r="F102" t="s">
-        <v>14</v>
-      </c>
       <c r="G102">
-        <v>675</v>
+        <v>269.5</v>
       </c>
       <c r="H102">
-        <v>695.5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="B103" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="C103">
-        <v>2426</v>
+        <v>2641</v>
       </c>
       <c r="D103">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>10</v>
+        <v>769</v>
       </c>
       <c r="F103" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G103">
-        <v>137</v>
+        <v>222</v>
       </c>
       <c r="H103">
-        <v>141</v>
+        <v>229</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="B104" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="C104">
-        <v>4335</v>
+        <v>4293</v>
       </c>
       <c r="D104">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>769</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G104">
-        <v>440</v>
+        <v>210</v>
       </c>
       <c r="H104">
-        <v>440</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="B105" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="C105">
-        <v>4477</v>
+        <v>2396</v>
       </c>
       <c r="D105">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E105" t="s">
         <v>10</v>
       </c>
       <c r="F105" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G105">
-        <v>252</v>
+        <v>675</v>
       </c>
       <c r="H105">
-        <v>259.5</v>
+        <v>695.5</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="B106" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C106">
-        <v>4479</v>
+        <v>2426</v>
       </c>
       <c r="D106">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
@@ -8320,21 +8332,21 @@
         <v>11</v>
       </c>
       <c r="G106">
-        <v>252</v>
+        <v>137</v>
       </c>
       <c r="H106">
-        <v>259.5</v>
+        <v>141</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="B107" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C107">
-        <v>4478</v>
+        <v>4335</v>
       </c>
       <c r="D107">
         <v>3</v>
@@ -8346,165 +8358,243 @@
         <v>11</v>
       </c>
       <c r="G107">
-        <v>252</v>
+        <v>440</v>
       </c>
       <c r="H107">
-        <v>259.5</v>
+        <v>440</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="B108" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
       <c r="C108">
-        <v>2646</v>
+        <v>4477</v>
       </c>
       <c r="D108">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E108" t="s">
-        <v>786</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G108">
-        <v>50.5</v>
+        <v>252</v>
       </c>
       <c r="H108">
-        <v>52</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="B109" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C109">
-        <v>2645</v>
+        <v>4479</v>
       </c>
       <c r="D109">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E109" t="s">
-        <v>787</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G109">
-        <v>78</v>
+        <v>252</v>
       </c>
       <c r="H109">
-        <v>80</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B110" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C110">
-        <v>2638</v>
+        <v>4478</v>
       </c>
       <c r="D110">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E110" t="s">
-        <v>788</v>
+        <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G110">
-        <v>65</v>
+        <v>252</v>
       </c>
       <c r="H110">
-        <v>67</v>
+        <v>259.5</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B111" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="C111">
-        <v>4294</v>
+        <v>2646</v>
       </c>
       <c r="D111">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>791</v>
+        <v>786</v>
       </c>
       <c r="F111" t="s">
         <v>33</v>
       </c>
       <c r="G111">
-        <v>150</v>
+        <v>53</v>
       </c>
       <c r="H111">
-        <v>154.5</v>
+        <v>54.5</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>792</v>
+        <v>784</v>
       </c>
       <c r="B112" t="s">
-        <v>793</v>
+        <v>785</v>
       </c>
       <c r="C112">
-        <v>4314</v>
+        <v>2645</v>
       </c>
       <c r="D112">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E112" t="s">
-        <v>408</v>
+        <v>787</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="G112">
-        <v>252</v>
+        <v>81.5</v>
       </c>
       <c r="H112">
-        <v>260</v>
+        <v>84</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
+        <v>784</v>
+      </c>
+      <c r="B113" t="s">
+        <v>785</v>
+      </c>
+      <c r="C113">
+        <v>2638</v>
+      </c>
+      <c r="D113">
+        <v>9</v>
+      </c>
+      <c r="E113" t="s">
+        <v>788</v>
+      </c>
+      <c r="F113" t="s">
+        <v>33</v>
+      </c>
+      <c r="G113">
+        <v>70</v>
+      </c>
+      <c r="H113">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>789</v>
+      </c>
+      <c r="B114" t="s">
+        <v>790</v>
+      </c>
+      <c r="C114">
+        <v>4294</v>
+      </c>
+      <c r="D114">
+        <v>18</v>
+      </c>
+      <c r="E114" t="s">
+        <v>791</v>
+      </c>
+      <c r="F114" t="s">
+        <v>33</v>
+      </c>
+      <c r="G114">
+        <v>150</v>
+      </c>
+      <c r="H114">
+        <v>154.5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>792</v>
+      </c>
+      <c r="B115" t="s">
+        <v>793</v>
+      </c>
+      <c r="C115">
+        <v>4314</v>
+      </c>
+      <c r="D115">
+        <v>15</v>
+      </c>
+      <c r="E115" t="s">
+        <v>408</v>
+      </c>
+      <c r="F115" t="s">
+        <v>25</v>
+      </c>
+      <c r="G115">
+        <v>252</v>
+      </c>
+      <c r="H115">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
         <v>794</v>
       </c>
-      <c r="B113" t="s">
+      <c r="B116" t="s">
         <v>795</v>
       </c>
-      <c r="C113">
+      <c r="C116">
         <v>4315</v>
       </c>
-      <c r="D113">
+      <c r="D116">
         <v>15</v>
       </c>
-      <c r="E113" t="s">
+      <c r="E116" t="s">
         <v>796</v>
       </c>
-      <c r="F113" t="s">
+      <c r="F116" t="s">
         <v>25</v>
       </c>
-      <c r="G113">
+      <c r="G116">
         <v>450</v>
       </c>
-      <c r="H113">
+      <c r="H116">
         <v>463.5</v>
       </c>
     </row>
@@ -13038,10 +13128,10 @@
         <v>33</v>
       </c>
       <c r="G120">
-        <v>27.5</v>
+        <v>30</v>
       </c>
       <c r="H120">
-        <v>28.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -13064,10 +13154,10 @@
         <v>33</v>
       </c>
       <c r="G121">
-        <v>24.5</v>
+        <v>25.5</v>
       </c>
       <c r="H121">
-        <v>25</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDA5D795-263B-421C-8C22-3DE2DDAB0DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C155E12B-6BF2-41A5-ACE3-5C29FA7E6C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="11" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3592" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3596" uniqueCount="1114">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3370,6 +3370,15 @@
   </si>
   <si>
     <t>FLOCOS DE ARROZ</t>
+  </si>
+  <si>
+    <t>pacoca-de-amendoim-espeto</t>
+  </si>
+  <si>
+    <t>PAÇOCA DE AMENDOIM ESPETO</t>
+  </si>
+  <si>
+    <t>X90G</t>
   </si>
 </sst>
 </file>
@@ -10003,7 +10012,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -12660,10 +12669,10 @@
         <v>988</v>
       </c>
       <c r="G102">
-        <v>71.5</v>
+        <v>75.5</v>
       </c>
       <c r="H102">
-        <v>73.5</v>
+        <v>78</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -13032,65 +13041,65 @@
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1051</v>
+        <v>1111</v>
       </c>
       <c r="B117" t="s">
-        <v>1052</v>
+        <v>1112</v>
       </c>
       <c r="C117">
-        <v>4123</v>
+        <v>4582</v>
       </c>
       <c r="D117">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="E117" t="s">
-        <v>1016</v>
+        <v>1113</v>
       </c>
       <c r="F117" t="s">
         <v>11</v>
       </c>
       <c r="G117">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="H117">
-        <v>62</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="B118" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="C118">
-        <v>4306</v>
+        <v>4123</v>
       </c>
       <c r="D118">
         <v>10</v>
       </c>
       <c r="E118" t="s">
-        <v>1003</v>
+        <v>1016</v>
       </c>
       <c r="F118" t="s">
-        <v>988</v>
+        <v>11</v>
       </c>
       <c r="G118">
-        <v>81</v>
+        <v>60</v>
       </c>
       <c r="H118">
-        <v>83.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="B119" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="C119">
-        <v>4307</v>
+        <v>4306</v>
       </c>
       <c r="D119">
         <v>10</v>
@@ -13110,28 +13119,28 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="B120" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
       <c r="C120">
-        <v>2659</v>
+        <v>4307</v>
       </c>
       <c r="D120">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E120" t="s">
-        <v>1059</v>
+        <v>1003</v>
       </c>
       <c r="F120" t="s">
-        <v>33</v>
+        <v>988</v>
       </c>
       <c r="G120">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="H120">
-        <v>31</v>
+        <v>83.5</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
@@ -13142,47 +13151,73 @@
         <v>1058</v>
       </c>
       <c r="C121">
-        <v>2621</v>
+        <v>2659</v>
       </c>
       <c r="D121">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="E121" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="F121" t="s">
         <v>33</v>
       </c>
       <c r="G121">
-        <v>25.5</v>
+        <v>30</v>
       </c>
       <c r="H121">
-        <v>26.5</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="B122" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C122">
-        <v>3656</v>
+        <v>2621</v>
       </c>
       <c r="D122">
         <v>5</v>
       </c>
       <c r="E122" t="s">
-        <v>1003</v>
+        <v>1060</v>
       </c>
       <c r="F122" t="s">
         <v>33</v>
       </c>
       <c r="G122">
+        <v>25.5</v>
+      </c>
+      <c r="H122">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B123" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C123">
+        <v>3656</v>
+      </c>
+      <c r="D123">
+        <v>5</v>
+      </c>
+      <c r="E123" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F123" t="s">
+        <v>33</v>
+      </c>
+      <c r="G123">
         <v>27</v>
       </c>
-      <c r="H122">
+      <c r="H123">
         <v>28</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C155E12B-6BF2-41A5-ACE3-5C29FA7E6C8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61851D42-DD5D-450F-BC7A-C1FB74E96172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="11" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3596" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3612" uniqueCount="1117">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3330,9 +3330,6 @@
     <t>DOCE DE LEITE C/COCOSUVENIR</t>
   </si>
   <si>
-    <t>X400g</t>
-  </si>
-  <si>
     <t>bala-gelatina-cobrinha-citrica</t>
   </si>
   <si>
@@ -3379,6 +3376,18 @@
   </si>
   <si>
     <t>X90G</t>
+  </si>
+  <si>
+    <t>doce-de-leite-c-cacausouvenir</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DOCE DE LEITE C/CACAUSOUVENIR </t>
+  </si>
+  <si>
+    <t>doce-abobora-c-coco</t>
+  </si>
+  <si>
+    <t>DOCE ABÓBORA C/ COCO</t>
   </si>
 </sst>
 </file>
@@ -6035,10 +6044,10 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B18" t="s">
         <v>1107</v>
-      </c>
-      <c r="B18" t="s">
-        <v>1108</v>
       </c>
       <c r="C18">
         <v>4639</v>
@@ -6659,10 +6668,10 @@
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B42" t="s">
         <v>1109</v>
-      </c>
-      <c r="B42" t="s">
-        <v>1110</v>
       </c>
       <c r="C42">
         <v>4640</v>
@@ -10012,7 +10021,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -10883,10 +10892,10 @@
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="B34" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C34">
         <v>4446</v>
@@ -10909,10 +10918,10 @@
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B35" t="s">
         <v>1099</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1100</v>
       </c>
       <c r="C35">
         <v>4476</v>
@@ -12391,91 +12400,91 @@
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="B92" t="s">
-        <v>1096</v>
+        <v>1094</v>
       </c>
       <c r="C92">
-        <v>4630</v>
+        <v>4643</v>
       </c>
       <c r="D92">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="E92" t="s">
-        <v>1097</v>
+        <v>1003</v>
       </c>
       <c r="F92" t="s">
         <v>25</v>
       </c>
       <c r="G92">
-        <v>127.5</v>
+        <v>97.5</v>
       </c>
       <c r="H92">
-        <v>131</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>1006</v>
+        <v>1095</v>
       </c>
       <c r="B93" t="s">
-        <v>1007</v>
+        <v>1096</v>
       </c>
       <c r="C93">
-        <v>4547</v>
+        <v>4630</v>
       </c>
       <c r="D93">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E93" t="s">
         <v>1003</v>
       </c>
       <c r="F93" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G93">
-        <v>77</v>
+        <v>127.5</v>
       </c>
       <c r="H93">
-        <v>79.5</v>
+        <v>131</v>
       </c>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>1008</v>
+        <v>1113</v>
       </c>
       <c r="B94" t="s">
-        <v>1009</v>
+        <v>1114</v>
       </c>
       <c r="C94">
-        <v>4104</v>
+        <v>4644</v>
       </c>
       <c r="D94">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E94" t="s">
         <v>1003</v>
       </c>
       <c r="F94" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="G94">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="H94">
-        <v>79.5</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="B95" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="C95">
-        <v>4101</v>
+        <v>4547</v>
       </c>
       <c r="D95">
         <v>10</v>
@@ -12495,13 +12504,13 @@
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="B96" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C96">
-        <v>4105</v>
+        <v>4104</v>
       </c>
       <c r="D96">
         <v>10</v>
@@ -12521,403 +12530,403 @@
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="B97" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="C97">
-        <v>3705</v>
+        <v>4101</v>
       </c>
       <c r="D97">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E97" t="s">
-        <v>1016</v>
+        <v>1003</v>
       </c>
       <c r="F97" t="s">
         <v>33</v>
       </c>
       <c r="G97">
-        <v>123.5</v>
+        <v>77</v>
       </c>
       <c r="H97">
-        <v>127</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>1017</v>
+        <v>1115</v>
       </c>
       <c r="B98" t="s">
-        <v>1018</v>
+        <v>1116</v>
       </c>
       <c r="C98">
-        <v>3823</v>
+        <v>4641</v>
       </c>
       <c r="D98">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="E98" t="s">
         <v>1003</v>
       </c>
       <c r="F98" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G98">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="H98">
-        <v>79.5</v>
+        <v>74</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>1019</v>
+        <v>1115</v>
       </c>
       <c r="B99" t="s">
-        <v>1020</v>
+        <v>1116</v>
       </c>
       <c r="C99">
-        <v>4308</v>
+        <v>4583</v>
       </c>
       <c r="D99">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="F99" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G99">
-        <v>68.5</v>
+        <v>144</v>
       </c>
       <c r="H99">
-        <v>70.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1022</v>
+        <v>1012</v>
       </c>
       <c r="B100" t="s">
-        <v>1023</v>
+        <v>1013</v>
       </c>
       <c r="C100">
-        <v>4309</v>
+        <v>4105</v>
       </c>
       <c r="D100">
         <v>10</v>
       </c>
       <c r="E100" t="s">
-        <v>1021</v>
+        <v>1003</v>
       </c>
       <c r="F100" t="s">
-        <v>988</v>
+        <v>33</v>
       </c>
       <c r="G100">
-        <v>68.5</v>
+        <v>77</v>
       </c>
       <c r="H100">
-        <v>70.5</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>1102</v>
+        <v>1014</v>
       </c>
       <c r="B101" t="s">
-        <v>1103</v>
+        <v>1015</v>
       </c>
       <c r="C101">
-        <v>4635</v>
+        <v>3705</v>
       </c>
       <c r="D101">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>1104</v>
+        <v>1016</v>
       </c>
       <c r="F101" t="s">
-        <v>988</v>
+        <v>33</v>
       </c>
       <c r="G101">
-        <v>167</v>
+        <v>123.5</v>
       </c>
       <c r="H101">
-        <v>172</v>
+        <v>127</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1024</v>
+        <v>1017</v>
       </c>
       <c r="B102" t="s">
-        <v>1025</v>
+        <v>1018</v>
       </c>
       <c r="C102">
-        <v>4412</v>
+        <v>3823</v>
       </c>
       <c r="D102">
-        <v>2.5</v>
+        <v>10</v>
       </c>
       <c r="E102" t="s">
-        <v>10</v>
+        <v>1003</v>
       </c>
       <c r="F102" t="s">
-        <v>988</v>
+        <v>25</v>
       </c>
       <c r="G102">
-        <v>75.5</v>
+        <v>77</v>
       </c>
       <c r="H102">
-        <v>78</v>
+        <v>79.5</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>1026</v>
+        <v>1019</v>
       </c>
       <c r="B103" t="s">
-        <v>1027</v>
+        <v>1020</v>
       </c>
       <c r="C103">
-        <v>4413</v>
+        <v>4308</v>
       </c>
       <c r="D103">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E103" t="s">
-        <v>10</v>
+        <v>1021</v>
       </c>
       <c r="F103" t="s">
         <v>11</v>
       </c>
       <c r="G103">
-        <v>496</v>
+        <v>68.5</v>
       </c>
       <c r="H103">
-        <v>511</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="B104" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="C104">
-        <v>4414</v>
+        <v>4309</v>
       </c>
       <c r="D104">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E104" t="s">
-        <v>10</v>
+        <v>1021</v>
       </c>
       <c r="F104" t="s">
-        <v>11</v>
+        <v>988</v>
       </c>
       <c r="G104">
-        <v>101</v>
+        <v>68.5</v>
       </c>
       <c r="H104">
-        <v>104</v>
+        <v>70.5</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>1028</v>
+        <v>1101</v>
       </c>
       <c r="B105" t="s">
-        <v>1029</v>
+        <v>1102</v>
       </c>
       <c r="C105">
-        <v>4415</v>
+        <v>4635</v>
       </c>
       <c r="D105">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E105" t="s">
-        <v>10</v>
+        <v>1103</v>
       </c>
       <c r="F105" t="s">
-        <v>11</v>
+        <v>988</v>
       </c>
       <c r="G105">
-        <v>414</v>
+        <v>167</v>
       </c>
       <c r="H105">
-        <v>426.5</v>
+        <v>172</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="B106" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C106">
-        <v>4416</v>
+        <v>4412</v>
       </c>
       <c r="D106">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="E106" t="s">
         <v>10</v>
       </c>
       <c r="F106" t="s">
-        <v>11</v>
+        <v>988</v>
       </c>
       <c r="G106">
-        <v>85</v>
+        <v>75.5</v>
       </c>
       <c r="H106">
-        <v>87</v>
+        <v>78</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="B107" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="C107">
-        <v>4475</v>
+        <v>4413</v>
       </c>
       <c r="D107">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="E107" t="s">
-        <v>1032</v>
+        <v>10</v>
       </c>
       <c r="F107" t="s">
         <v>11</v>
       </c>
       <c r="G107">
-        <v>9</v>
+        <v>496</v>
       </c>
       <c r="H107">
-        <v>9.5</v>
+        <v>511</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>1033</v>
+        <v>1026</v>
       </c>
       <c r="B108" t="s">
-        <v>1034</v>
+        <v>1027</v>
       </c>
       <c r="C108">
-        <v>4354</v>
+        <v>4414</v>
       </c>
       <c r="D108">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E108" t="s">
-        <v>1032</v>
+        <v>10</v>
       </c>
       <c r="F108" t="s">
-        <v>750</v>
+        <v>11</v>
       </c>
       <c r="G108">
-        <v>79.5</v>
+        <v>101</v>
       </c>
       <c r="H108">
-        <v>82</v>
+        <v>104</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>1035</v>
+        <v>1028</v>
       </c>
       <c r="B109" t="s">
-        <v>1036</v>
+        <v>1029</v>
       </c>
       <c r="C109">
-        <v>4445</v>
+        <v>4415</v>
       </c>
       <c r="D109">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="E109" t="s">
-        <v>1032</v>
+        <v>10</v>
       </c>
       <c r="F109" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G109">
-        <v>79.5</v>
+        <v>414</v>
       </c>
       <c r="H109">
-        <v>82</v>
+        <v>426.5</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
       <c r="B110" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
       <c r="C110">
-        <v>4353</v>
+        <v>4416</v>
       </c>
       <c r="D110">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E110" t="s">
-        <v>1032</v>
+        <v>10</v>
       </c>
       <c r="F110" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G110">
-        <v>79.5</v>
+        <v>85</v>
       </c>
       <c r="H110">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
       <c r="B111" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
       <c r="C111">
-        <v>4350</v>
+        <v>4475</v>
       </c>
       <c r="D111">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="E111" t="s">
         <v>1032</v>
       </c>
       <c r="F111" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G111">
-        <v>79.5</v>
+        <v>9</v>
       </c>
       <c r="H111">
-        <v>82</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1041</v>
+        <v>1033</v>
       </c>
       <c r="B112" t="s">
-        <v>1042</v>
+        <v>1034</v>
       </c>
       <c r="C112">
-        <v>4352</v>
+        <v>4354</v>
       </c>
       <c r="D112">
         <v>12</v>
@@ -12926,7 +12935,7 @@
         <v>1032</v>
       </c>
       <c r="F112" t="s">
-        <v>25</v>
+        <v>750</v>
       </c>
       <c r="G112">
         <v>79.5</v>
@@ -12937,13 +12946,13 @@
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>1043</v>
+        <v>1035</v>
       </c>
       <c r="B113" t="s">
-        <v>1044</v>
+        <v>1036</v>
       </c>
       <c r="C113">
-        <v>4349</v>
+        <v>4445</v>
       </c>
       <c r="D113">
         <v>12</v>
@@ -12963,13 +12972,13 @@
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1045</v>
+        <v>1037</v>
       </c>
       <c r="B114" t="s">
-        <v>1046</v>
+        <v>1038</v>
       </c>
       <c r="C114">
-        <v>4351</v>
+        <v>4353</v>
       </c>
       <c r="D114">
         <v>12</v>
@@ -12989,13 +12998,13 @@
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1047</v>
+        <v>1039</v>
       </c>
       <c r="B115" t="s">
-        <v>1048</v>
+        <v>1040</v>
       </c>
       <c r="C115">
-        <v>4581</v>
+        <v>4350</v>
       </c>
       <c r="D115">
         <v>12</v>
@@ -13015,209 +13024,313 @@
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>1049</v>
+        <v>1041</v>
       </c>
       <c r="B116" t="s">
-        <v>1050</v>
+        <v>1042</v>
       </c>
       <c r="C116">
-        <v>4096</v>
+        <v>4352</v>
       </c>
       <c r="D116">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>10</v>
+        <v>1032</v>
       </c>
       <c r="F116" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G116">
-        <v>79</v>
+        <v>79.5</v>
       </c>
       <c r="H116">
-        <v>81.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1111</v>
+        <v>1043</v>
       </c>
       <c r="B117" t="s">
-        <v>1112</v>
+        <v>1044</v>
       </c>
       <c r="C117">
-        <v>4582</v>
+        <v>4349</v>
       </c>
       <c r="D117">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="E117" t="s">
-        <v>1113</v>
+        <v>1032</v>
       </c>
       <c r="F117" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G117">
-        <v>45</v>
+        <v>79.5</v>
       </c>
       <c r="H117">
-        <v>46.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1051</v>
+        <v>1045</v>
       </c>
       <c r="B118" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
       <c r="C118">
-        <v>4123</v>
+        <v>4351</v>
       </c>
       <c r="D118">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E118" t="s">
-        <v>1016</v>
+        <v>1032</v>
       </c>
       <c r="F118" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G118">
-        <v>60</v>
+        <v>79.5</v>
       </c>
       <c r="H118">
-        <v>62</v>
+        <v>82</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
       <c r="B119" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
       <c r="C119">
-        <v>4306</v>
+        <v>4581</v>
       </c>
       <c r="D119">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E119" t="s">
-        <v>1003</v>
+        <v>1032</v>
       </c>
       <c r="F119" t="s">
-        <v>988</v>
+        <v>25</v>
       </c>
       <c r="G119">
-        <v>81</v>
+        <v>79.5</v>
       </c>
       <c r="H119">
-        <v>83.5</v>
+        <v>82</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
       <c r="B120" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C120">
-        <v>4307</v>
+        <v>4096</v>
       </c>
       <c r="D120">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E120" t="s">
-        <v>1003</v>
+        <v>10</v>
       </c>
       <c r="F120" t="s">
-        <v>988</v>
+        <v>11</v>
       </c>
       <c r="G120">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="H120">
-        <v>83.5</v>
+        <v>81.5</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>1057</v>
+        <v>1110</v>
       </c>
       <c r="B121" t="s">
-        <v>1058</v>
+        <v>1111</v>
       </c>
       <c r="C121">
-        <v>2659</v>
+        <v>4582</v>
       </c>
       <c r="D121">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="E121" t="s">
-        <v>1059</v>
+        <v>1112</v>
       </c>
       <c r="F121" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G121">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="H121">
-        <v>31</v>
+        <v>46.5</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B122" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="C122">
-        <v>2621</v>
+        <v>4123</v>
       </c>
       <c r="D122">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E122" t="s">
-        <v>1060</v>
+        <v>1016</v>
       </c>
       <c r="F122" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="G122">
-        <v>25.5</v>
+        <v>60</v>
       </c>
       <c r="H122">
-        <v>26.5</v>
+        <v>62</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>1061</v>
+        <v>1053</v>
       </c>
       <c r="B123" t="s">
-        <v>1062</v>
+        <v>1054</v>
       </c>
       <c r="C123">
-        <v>3656</v>
+        <v>4306</v>
       </c>
       <c r="D123">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E123" t="s">
         <v>1003</v>
       </c>
       <c r="F123" t="s">
+        <v>988</v>
+      </c>
+      <c r="G123">
+        <v>81</v>
+      </c>
+      <c r="H123">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B124" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C124">
+        <v>4307</v>
+      </c>
+      <c r="D124">
+        <v>10</v>
+      </c>
+      <c r="E124" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F124" t="s">
+        <v>988</v>
+      </c>
+      <c r="G124">
+        <v>81</v>
+      </c>
+      <c r="H124">
+        <v>83.5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B125" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C125">
+        <v>2659</v>
+      </c>
+      <c r="D125">
+        <v>20</v>
+      </c>
+      <c r="E125" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F125" t="s">
         <v>33</v>
       </c>
-      <c r="G123">
+      <c r="G125">
+        <v>30</v>
+      </c>
+      <c r="H125">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B126" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C126">
+        <v>2621</v>
+      </c>
+      <c r="D126">
+        <v>5</v>
+      </c>
+      <c r="E126" t="s">
+        <v>1060</v>
+      </c>
+      <c r="F126" t="s">
+        <v>33</v>
+      </c>
+      <c r="G126">
+        <v>25.5</v>
+      </c>
+      <c r="H126">
+        <v>26.5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>1061</v>
+      </c>
+      <c r="B127" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C127">
+        <v>3656</v>
+      </c>
+      <c r="D127">
+        <v>5</v>
+      </c>
+      <c r="E127" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F127" t="s">
+        <v>33</v>
+      </c>
+      <c r="G127">
         <v>27</v>
       </c>
-      <c r="H123">
+      <c r="H127">
         <v>28</v>
       </c>
     </row>
@@ -15079,10 +15192,10 @@
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B56" t="s">
         <v>1105</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1106</v>
       </c>
       <c r="C56">
         <v>2291</v>
@@ -15105,10 +15218,10 @@
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B57" t="s">
         <v>1105</v>
-      </c>
-      <c r="B57" t="s">
-        <v>1106</v>
       </c>
       <c r="C57">
         <v>2252</v>
@@ -21583,10 +21696,10 @@
         <v>14</v>
       </c>
       <c r="G38">
-        <v>280</v>
+        <v>360</v>
       </c>
       <c r="H38">
-        <v>294</v>
+        <v>372</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -21609,10 +21722,10 @@
         <v>11</v>
       </c>
       <c r="G39">
-        <v>48.5</v>
+        <v>62</v>
       </c>
       <c r="H39">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -21999,10 +22112,10 @@
         <v>14</v>
       </c>
       <c r="G54">
-        <v>315</v>
+        <v>375</v>
       </c>
       <c r="H54">
-        <v>324.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -22025,10 +22138,10 @@
         <v>14</v>
       </c>
       <c r="G55">
-        <v>157.5</v>
+        <v>187.5</v>
       </c>
       <c r="H55">
-        <v>162</v>
+        <v>193</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -22051,10 +22164,10 @@
         <v>11</v>
       </c>
       <c r="G56">
-        <v>28.5</v>
+        <v>33.5</v>
       </c>
       <c r="H56">
-        <v>29.5</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61851D42-DD5D-450F-BC7A-C1FB74E96172}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1A7A38-A70D-46CF-B802-B0501E06D81D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3612" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="1117">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3740,7 +3740,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.28515625" bestFit="1" customWidth="1"/>
@@ -3780,39 +3780,39 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C2">
-        <v>2229</v>
+        <v>195</v>
       </c>
       <c r="D2">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E2" t="s">
         <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G2">
-        <v>145</v>
+        <v>245</v>
       </c>
       <c r="H2">
-        <v>180</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C3">
-        <v>195</v>
+        <v>569</v>
       </c>
       <c r="D3">
         <v>25</v>
@@ -3824,21 +3824,21 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>245</v>
+        <v>117</v>
       </c>
       <c r="H3">
-        <v>262.5</v>
+        <v>121.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C4">
-        <v>569</v>
+        <v>282</v>
       </c>
       <c r="D4">
         <v>25</v>
@@ -3858,13 +3858,13 @@
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>93</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>94</v>
+        <v>35</v>
       </c>
       <c r="C5">
-        <v>282</v>
+        <v>564</v>
       </c>
       <c r="D5">
         <v>25</v>
@@ -3884,13 +3884,13 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="B6" t="s">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="C6">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D6">
         <v>25</v>
@@ -3902,21 +3902,21 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="H6">
-        <v>121.5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="B7" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7">
-        <v>565</v>
+        <v>109</v>
       </c>
       <c r="D7">
         <v>25</v>
@@ -3928,21 +3928,21 @@
         <v>14</v>
       </c>
       <c r="G7">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="H7">
-        <v>129</v>
+        <v>162</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C8">
-        <v>109</v>
+        <v>3110</v>
       </c>
       <c r="D8">
         <v>25</v>
@@ -3954,21 +3954,21 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>155</v>
+        <v>81</v>
       </c>
       <c r="H8">
-        <v>162</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C9">
-        <v>3110</v>
+        <v>8</v>
       </c>
       <c r="D9">
         <v>25</v>
@@ -3980,35 +3980,9 @@
         <v>14</v>
       </c>
       <c r="G9">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="H9">
-        <v>91.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>101</v>
-      </c>
-      <c r="B10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10">
-        <v>8</v>
-      </c>
-      <c r="D10">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>14</v>
-      </c>
-      <c r="G10">
-        <v>88</v>
-      </c>
-      <c r="H10">
         <v>94</v>
       </c>
     </row>
@@ -4622,7 +4596,7 @@
         <v>25</v>
       </c>
       <c r="G23">
-        <v>140</v>
+        <v>175</v>
       </c>
       <c r="H23">
         <v>180</v>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBDEE78-EDF0-45D3-8026-CBE547FC4FFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA0ABE3-A653-4F2A-B405-C09A91BB4539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -18877,48 +18877,48 @@
         <v>195</v>
       </c>
       <c r="C86">
-        <v>2632</v>
+        <v>263</v>
       </c>
       <c r="D86">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="G86">
-        <v>317</v>
+        <v>630</v>
       </c>
       <c r="H86">
-        <v>326.5</v>
+        <v>649</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B87" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C87">
-        <v>4179</v>
+        <v>2632</v>
       </c>
       <c r="D87">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
       </c>
       <c r="F87" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="G87">
-        <v>572</v>
+        <v>317</v>
       </c>
       <c r="H87">
-        <v>589</v>
+        <v>326.5</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CA0ABE3-A653-4F2A-B405-C09A91BB4539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E692ECA0-D9E2-43EC-9A20-57D91FD454ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -20763,10 +20763,10 @@
         <v>14</v>
       </c>
       <c r="G38">
-        <v>600</v>
+        <v>660</v>
       </c>
       <c r="H38">
-        <v>618</v>
+        <v>680</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -20789,10 +20789,10 @@
         <v>11</v>
       </c>
       <c r="G39">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H39">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E692ECA0-D9E2-43EC-9A20-57D91FD454ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7683B9F5-3EF5-4F36-AC8C-EC5FC8656B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -5316,10 +5316,10 @@
         <v>11</v>
       </c>
       <c r="G49">
-        <v>115</v>
+        <v>125</v>
       </c>
       <c r="H49">
-        <v>118.5</v>
+        <v>129</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -11958,10 +11958,10 @@
         <v>33</v>
       </c>
       <c r="G2">
-        <v>162</v>
+        <v>171.5</v>
       </c>
       <c r="H2">
-        <v>167</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -11984,10 +11984,10 @@
         <v>33</v>
       </c>
       <c r="G3">
-        <v>84</v>
+        <v>86.5</v>
       </c>
       <c r="H3">
-        <v>86.5</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -12010,10 +12010,10 @@
         <v>33</v>
       </c>
       <c r="G4">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H4">
-        <v>86.5</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -12036,10 +12036,10 @@
         <v>33</v>
       </c>
       <c r="G5">
-        <v>162</v>
+        <v>171.5</v>
       </c>
       <c r="H5">
-        <v>167</v>
+        <v>176.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -12062,10 +12062,10 @@
         <v>11</v>
       </c>
       <c r="G6">
-        <v>26</v>
+        <v>33.5</v>
       </c>
       <c r="H6">
-        <v>27</v>
+        <v>34.5</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -12088,10 +12088,10 @@
         <v>33</v>
       </c>
       <c r="G7">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H7">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -12114,10 +12114,10 @@
         <v>33</v>
       </c>
       <c r="G8">
-        <v>33</v>
+        <v>35.5</v>
       </c>
       <c r="H8">
-        <v>34</v>
+        <v>36.5</v>
       </c>
     </row>
   </sheetData>
@@ -12340,10 +12340,10 @@
         <v>25</v>
       </c>
       <c r="G8">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="H8">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -12366,10 +12366,10 @@
         <v>25</v>
       </c>
       <c r="G9">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="H9">
-        <v>98</v>
+        <v>105</v>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7683B9F5-3EF5-4F36-AC8C-EC5FC8656B61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D51440-EC86-4394-A221-0F40A3558554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="345" yWindow="945" windowWidth="27300" windowHeight="13920" firstSheet="5" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4005" yWindow="420" windowWidth="13710" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3604" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="1105">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3764,7 +3764,7 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H2">
         <v>162</v>
@@ -3790,10 +3790,10 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="H3">
-        <v>91.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -3816,10 +3816,10 @@
         <v>14</v>
       </c>
       <c r="G4">
-        <v>78.5</v>
+        <v>80</v>
       </c>
       <c r="H4">
-        <v>81</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -3842,10 +3842,10 @@
         <v>14</v>
       </c>
       <c r="G5">
-        <v>112.5</v>
+        <v>113</v>
       </c>
       <c r="H5">
-        <v>116</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -4024,10 +4024,10 @@
         <v>11</v>
       </c>
       <c r="G12">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="H12">
-        <v>299</v>
+        <v>386.5</v>
       </c>
     </row>
   </sheetData>
@@ -4510,10 +4510,10 @@
         <v>14</v>
       </c>
       <c r="G18">
-        <v>1450</v>
+        <v>1875</v>
       </c>
       <c r="H18">
-        <v>1493.5</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
@@ -4536,10 +4536,10 @@
         <v>11</v>
       </c>
       <c r="G19">
-        <v>290</v>
+        <v>375</v>
       </c>
       <c r="H19">
-        <v>299</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -7770,10 +7770,10 @@
         <v>11</v>
       </c>
       <c r="G5">
-        <v>72</v>
+        <v>64.5</v>
       </c>
       <c r="H5">
-        <v>74</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -7796,10 +7796,10 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>350</v>
+        <v>312.5</v>
       </c>
       <c r="H6">
-        <v>360.5</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -7978,10 +7978,10 @@
         <v>11</v>
       </c>
       <c r="G13">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="H13">
-        <v>162</v>
+        <v>159.5</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -8186,10 +8186,10 @@
         <v>14</v>
       </c>
       <c r="G21">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="H21">
-        <v>87.5</v>
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -8524,10 +8524,10 @@
         <v>11</v>
       </c>
       <c r="G34">
-        <v>525</v>
+        <v>475</v>
       </c>
       <c r="H34">
-        <v>541</v>
+        <v>489.5</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -8550,10 +8550,10 @@
         <v>14</v>
       </c>
       <c r="G35">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="H35">
-        <v>110</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -18863,10 +18863,10 @@
         <v>25</v>
       </c>
       <c r="G85">
-        <v>693</v>
+        <v>583</v>
       </c>
       <c r="H85">
-        <v>713</v>
+        <v>600.5</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -18889,10 +18889,10 @@
         <v>25</v>
       </c>
       <c r="G86">
-        <v>630</v>
+        <v>530</v>
       </c>
       <c r="H86">
-        <v>649</v>
+        <v>546</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
@@ -18915,10 +18915,10 @@
         <v>11</v>
       </c>
       <c r="G87">
-        <v>317</v>
+        <v>267</v>
       </c>
       <c r="H87">
-        <v>326.5</v>
+        <v>275</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
@@ -18941,10 +18941,10 @@
         <v>25</v>
       </c>
       <c r="G88">
-        <v>520</v>
+        <v>480</v>
       </c>
       <c r="H88">
-        <v>589</v>
+        <v>494.5</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -18967,10 +18967,10 @@
         <v>11</v>
       </c>
       <c r="G89">
-        <v>262</v>
+        <v>242</v>
       </c>
       <c r="H89">
-        <v>270</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -22887,10 +22887,10 @@
         <v>14</v>
       </c>
       <c r="G44">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="H44">
-        <v>82.5</v>
+        <v>85.5</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -22913,10 +22913,10 @@
         <v>11</v>
       </c>
       <c r="G45">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="H45">
-        <v>18.5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -22939,10 +22939,10 @@
         <v>14</v>
       </c>
       <c r="G46">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H46">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -22965,10 +22965,10 @@
         <v>11</v>
       </c>
       <c r="G47">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="H47">
-        <v>11.5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -23277,10 +23277,10 @@
         <v>14</v>
       </c>
       <c r="G59">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="H59">
-        <v>129</v>
+        <v>125.5</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -23602,7 +23602,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H92"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -23659,10 +23659,10 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>78.5</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>81</v>
+        <v>82.5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -23685,10 +23685,10 @@
         <v>11</v>
       </c>
       <c r="G3">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="H3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -23711,10 +23711,10 @@
         <v>14</v>
       </c>
       <c r="G4">
-        <v>112.5</v>
+        <v>113</v>
       </c>
       <c r="H4">
-        <v>116</v>
+        <v>116.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -23763,10 +23763,10 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H6">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -23815,10 +23815,10 @@
         <v>14</v>
       </c>
       <c r="G8">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H8">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -23867,10 +23867,10 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H10">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -24101,10 +24101,10 @@
         <v>14</v>
       </c>
       <c r="G19">
-        <v>660</v>
+        <v>590</v>
       </c>
       <c r="H19">
-        <v>680</v>
+        <v>608</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -24127,10 +24127,10 @@
         <v>11</v>
       </c>
       <c r="G20">
-        <v>112</v>
+        <v>100.5</v>
       </c>
       <c r="H20">
-        <v>115.5</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -24153,10 +24153,10 @@
         <v>14</v>
       </c>
       <c r="G21">
-        <v>660</v>
+        <v>540</v>
       </c>
       <c r="H21">
-        <v>680</v>
+        <v>556</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -24179,10 +24179,10 @@
         <v>11</v>
       </c>
       <c r="G22">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H22">
-        <v>115.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -24205,10 +24205,10 @@
         <v>11</v>
       </c>
       <c r="G23">
-        <v>660</v>
+        <v>540</v>
       </c>
       <c r="H23">
-        <v>680</v>
+        <v>556</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -24231,10 +24231,10 @@
         <v>14</v>
       </c>
       <c r="G24">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H24">
-        <v>115.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -24257,10 +24257,10 @@
         <v>14</v>
       </c>
       <c r="G25">
-        <v>660</v>
+        <v>540</v>
       </c>
       <c r="H25">
-        <v>680</v>
+        <v>556</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -24283,10 +24283,10 @@
         <v>11</v>
       </c>
       <c r="G26">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H26">
-        <v>115.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -24309,10 +24309,10 @@
         <v>14</v>
       </c>
       <c r="G27">
-        <v>660</v>
+        <v>540</v>
       </c>
       <c r="H27">
-        <v>680</v>
+        <v>556</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -24335,10 +24335,10 @@
         <v>11</v>
       </c>
       <c r="G28">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="H28">
-        <v>115.5</v>
+        <v>95</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -24647,10 +24647,10 @@
         <v>11</v>
       </c>
       <c r="G40">
-        <v>26</v>
+        <v>24.5</v>
       </c>
       <c r="H40">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -24673,10 +24673,10 @@
         <v>14</v>
       </c>
       <c r="G41">
-        <v>142.5</v>
+        <v>135</v>
       </c>
       <c r="H41">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -24699,10 +24699,10 @@
         <v>14</v>
       </c>
       <c r="G42">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="H42">
-        <v>293.5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -24713,10 +24713,10 @@
         <v>345</v>
       </c>
       <c r="C43">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D43">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -24725,10 +24725,10 @@
         <v>14</v>
       </c>
       <c r="G43">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="H43">
-        <v>103</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -24739,10 +24739,10 @@
         <v>345</v>
       </c>
       <c r="C44">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D44">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -24751,24 +24751,24 @@
         <v>14</v>
       </c>
       <c r="G44">
-        <v>22</v>
+        <v>102.5</v>
       </c>
       <c r="H44">
-        <v>23</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B45" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C45">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D45">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -24777,10 +24777,10 @@
         <v>14</v>
       </c>
       <c r="G45">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="H45">
-        <v>206</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -24791,48 +24791,48 @@
         <v>347</v>
       </c>
       <c r="C46">
-        <v>2543</v>
+        <v>3025</v>
       </c>
       <c r="D46">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G46">
-        <v>35.5</v>
+        <v>200</v>
       </c>
       <c r="H46">
-        <v>36.5</v>
+        <v>206</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B47" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C47">
-        <v>98</v>
+        <v>2543</v>
       </c>
       <c r="D47">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G47">
-        <v>338</v>
+        <v>35.5</v>
       </c>
       <c r="H47">
-        <v>348</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -24843,10 +24843,10 @@
         <v>349</v>
       </c>
       <c r="C48">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D48">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
@@ -24855,24 +24855,24 @@
         <v>14</v>
       </c>
       <c r="G48">
-        <v>58.5</v>
+        <v>320</v>
       </c>
       <c r="H48">
-        <v>60</v>
+        <v>329.5</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B49" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C49">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D49">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -24881,10 +24881,10 @@
         <v>14</v>
       </c>
       <c r="G49">
-        <v>362.5</v>
+        <v>55.5</v>
       </c>
       <c r="H49">
-        <v>373.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -24895,48 +24895,48 @@
         <v>351</v>
       </c>
       <c r="C50">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D50">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G50">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
       <c r="H50">
-        <v>77</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B51" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C51">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D51">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G51">
-        <v>255</v>
+        <v>74.5</v>
       </c>
       <c r="H51">
-        <v>262.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -24947,10 +24947,10 @@
         <v>353</v>
       </c>
       <c r="C52">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D52">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
@@ -24959,10 +24959,10 @@
         <v>14</v>
       </c>
       <c r="G52">
-        <v>212.5</v>
+        <v>255</v>
       </c>
       <c r="H52">
-        <v>219</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -24973,48 +24973,48 @@
         <v>353</v>
       </c>
       <c r="C53">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D53">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G53">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
       <c r="H53">
-        <v>46</v>
+        <v>219</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B54" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C54">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D54">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G54">
-        <v>375</v>
+        <v>44.5</v>
       </c>
       <c r="H54">
-        <v>386.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -25025,10 +25025,10 @@
         <v>355</v>
       </c>
       <c r="C55">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D55">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
@@ -25037,10 +25037,10 @@
         <v>14</v>
       </c>
       <c r="G55">
-        <v>187.5</v>
+        <v>350</v>
       </c>
       <c r="H55">
-        <v>193</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -25051,48 +25051,48 @@
         <v>355</v>
       </c>
       <c r="C56">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D56">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G56">
-        <v>33.5</v>
+        <v>175</v>
       </c>
       <c r="H56">
-        <v>34.5</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B57" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C57">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D57">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G57">
-        <v>275</v>
+        <v>31</v>
       </c>
       <c r="H57">
-        <v>283.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -25103,48 +25103,48 @@
         <v>357</v>
       </c>
       <c r="C58">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D58">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G58">
-        <v>57</v>
+        <v>275</v>
       </c>
       <c r="H58">
-        <v>59</v>
+        <v>283.5</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B59" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C59">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D59">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G59">
-        <v>240</v>
+        <v>57</v>
       </c>
       <c r="H59">
-        <v>247</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -25155,10 +25155,10 @@
         <v>359</v>
       </c>
       <c r="C60">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D60">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
@@ -25167,24 +25167,24 @@
         <v>14</v>
       </c>
       <c r="G60">
-        <v>42</v>
+        <v>280</v>
       </c>
       <c r="H60">
-        <v>43</v>
+        <v>288.5</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B61" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C61">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D61">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -25193,10 +25193,10 @@
         <v>14</v>
       </c>
       <c r="G61">
-        <v>375</v>
+        <v>48.5</v>
       </c>
       <c r="H61">
-        <v>386.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -25207,48 +25207,48 @@
         <v>361</v>
       </c>
       <c r="C62">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D62">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G62">
-        <v>64.5</v>
+        <v>375</v>
       </c>
       <c r="H62">
-        <v>66.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B63" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C63">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D63">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G63">
-        <v>330</v>
+        <v>64.5</v>
       </c>
       <c r="H63">
-        <v>340</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -25259,48 +25259,48 @@
         <v>363</v>
       </c>
       <c r="C64">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D64">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G64">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="H64">
-        <v>59</v>
+        <v>340</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B65" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C65">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D65">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G65">
-        <v>285</v>
+        <v>57</v>
       </c>
       <c r="H65">
-        <v>293.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -25311,10 +25311,10 @@
         <v>365</v>
       </c>
       <c r="C66">
-        <v>3740</v>
+        <v>3670</v>
       </c>
       <c r="D66">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
@@ -25323,10 +25323,10 @@
         <v>14</v>
       </c>
       <c r="G66">
-        <v>237.5</v>
+        <v>285</v>
       </c>
       <c r="H66">
-        <v>244.5</v>
+        <v>293.5</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -25337,48 +25337,48 @@
         <v>365</v>
       </c>
       <c r="C67">
-        <v>2469</v>
+        <v>3740</v>
       </c>
       <c r="D67">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
       </c>
       <c r="F67" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G67">
-        <v>49.5</v>
+        <v>237.5</v>
       </c>
       <c r="H67">
-        <v>51</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B68" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C68">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D68">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G68">
-        <v>312.5</v>
+        <v>49.5</v>
       </c>
       <c r="H68">
-        <v>322</v>
+        <v>51</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -25389,48 +25389,48 @@
         <v>367</v>
       </c>
       <c r="C69">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D69">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G69">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
       <c r="H69">
-        <v>66.5</v>
+        <v>322</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B70" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C70">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D70">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G70">
-        <v>322.5</v>
+        <v>64.5</v>
       </c>
       <c r="H70">
-        <v>332</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -25441,48 +25441,48 @@
         <v>369</v>
       </c>
       <c r="C71">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D71">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G71">
-        <v>66.5</v>
+        <v>300</v>
       </c>
       <c r="H71">
-        <v>68.5</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B72" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C72">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D72">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G72">
-        <v>195</v>
+        <v>62</v>
       </c>
       <c r="H72">
-        <v>201</v>
+        <v>64</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -25493,48 +25493,48 @@
         <v>371</v>
       </c>
       <c r="C73">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D73">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G73">
-        <v>41</v>
+        <v>180</v>
       </c>
       <c r="H73">
-        <v>42</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B74" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C74">
-        <v>211</v>
+        <v>2321</v>
       </c>
       <c r="D74">
-        <v>22.68</v>
+        <v>5</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G74">
-        <v>187.5</v>
+        <v>38</v>
       </c>
       <c r="H74">
-        <v>193</v>
+        <v>39</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
@@ -25545,10 +25545,10 @@
         <v>373</v>
       </c>
       <c r="C75">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D75">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
@@ -25557,10 +25557,10 @@
         <v>14</v>
       </c>
       <c r="G75">
-        <v>375</v>
+        <v>187.5</v>
       </c>
       <c r="H75">
-        <v>386.5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -25571,48 +25571,48 @@
         <v>373</v>
       </c>
       <c r="C76">
-        <v>2322</v>
+        <v>41</v>
       </c>
       <c r="D76">
-        <v>5</v>
+        <v>45.36</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G76">
-        <v>43.5</v>
+        <v>375</v>
       </c>
       <c r="H76">
-        <v>44.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B77" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C77">
-        <v>67</v>
+        <v>2322</v>
       </c>
       <c r="D77">
-        <v>45.36</v>
+        <v>5</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
       </c>
       <c r="F77" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G77">
-        <v>626</v>
+        <v>43.5</v>
       </c>
       <c r="H77">
-        <v>645</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
@@ -25623,10 +25623,10 @@
         <v>375</v>
       </c>
       <c r="C78">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D78">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
@@ -25635,10 +25635,10 @@
         <v>14</v>
       </c>
       <c r="G78">
-        <v>313</v>
+        <v>626</v>
       </c>
       <c r="H78">
-        <v>322.5</v>
+        <v>645</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -25649,74 +25649,74 @@
         <v>375</v>
       </c>
       <c r="C79">
-        <v>2488</v>
+        <v>2244</v>
       </c>
       <c r="D79">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
       </c>
       <c r="F79" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G79">
-        <v>71</v>
+        <v>313</v>
       </c>
       <c r="H79">
-        <v>73</v>
+        <v>322.5</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B80" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C80">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D80">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G80">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H80">
-        <v>53.5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B81" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C81">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D81">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G81">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="H81">
-        <v>187.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
@@ -25727,22 +25727,22 @@
         <v>379</v>
       </c>
       <c r="C82">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D82">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G82">
-        <v>350</v>
+        <v>182</v>
       </c>
       <c r="H82">
-        <v>360.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -25753,10 +25753,10 @@
         <v>379</v>
       </c>
       <c r="C83">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D83">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
@@ -25765,10 +25765,10 @@
         <v>14</v>
       </c>
       <c r="G83">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="H83">
-        <v>721</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -25779,62 +25779,62 @@
         <v>379</v>
       </c>
       <c r="C84">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D84">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
       </c>
       <c r="F84" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G84">
-        <v>106</v>
+        <v>700</v>
       </c>
       <c r="H84">
-        <v>109.5</v>
+        <v>721</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>99</v>
+        <v>378</v>
       </c>
       <c r="B85" t="s">
-        <v>100</v>
+        <v>379</v>
       </c>
       <c r="C85">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D85">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
       </c>
       <c r="F85" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G85">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H85">
-        <v>91.5</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>380</v>
+        <v>99</v>
       </c>
       <c r="B86" t="s">
-        <v>381</v>
+        <v>100</v>
       </c>
       <c r="C86">
-        <v>135</v>
+        <v>3110</v>
       </c>
       <c r="D86">
-        <v>22.68</v>
+        <v>25</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
@@ -25843,24 +25843,24 @@
         <v>14</v>
       </c>
       <c r="G86">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H86">
-        <v>85.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B87" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C87">
-        <v>2463</v>
+        <v>135</v>
       </c>
       <c r="D87">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -25869,24 +25869,24 @@
         <v>14</v>
       </c>
       <c r="G87">
-        <v>20</v>
+        <v>85</v>
       </c>
       <c r="H87">
-        <v>20.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B88" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C88">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D88">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -25895,10 +25895,10 @@
         <v>14</v>
       </c>
       <c r="G88">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="H88">
-        <v>118</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -25909,10 +25909,10 @@
         <v>385</v>
       </c>
       <c r="C89">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D89">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -25921,10 +25921,10 @@
         <v>14</v>
       </c>
       <c r="G89">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="H89">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -25935,10 +25935,10 @@
         <v>385</v>
       </c>
       <c r="C90">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D90">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -25947,24 +25947,24 @@
         <v>14</v>
       </c>
       <c r="G90">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="H90">
-        <v>235</v>
+        <v>28</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B91" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C91">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D91">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -25973,10 +25973,10 @@
         <v>14</v>
       </c>
       <c r="G91">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="H91">
-        <v>129</v>
+        <v>235</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
@@ -25987,21 +25987,47 @@
         <v>387</v>
       </c>
       <c r="C92">
+        <v>4223</v>
+      </c>
+      <c r="D92">
+        <v>25</v>
+      </c>
+      <c r="E92" t="s">
+        <v>10</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92">
+        <v>125</v>
+      </c>
+      <c r="H92">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>386</v>
+      </c>
+      <c r="B93" t="s">
+        <v>387</v>
+      </c>
+      <c r="C93">
         <v>4224</v>
       </c>
-      <c r="D92">
-        <v>5</v>
-      </c>
-      <c r="E92" t="s">
-        <v>10</v>
-      </c>
-      <c r="F92" t="s">
-        <v>11</v>
-      </c>
-      <c r="G92">
+      <c r="D93">
+        <v>5</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>11</v>
+      </c>
+      <c r="G93">
         <v>27</v>
       </c>
-      <c r="H92">
+      <c r="H93">
         <v>28</v>
       </c>
     </row>
@@ -26095,10 +26121,10 @@
         <v>14</v>
       </c>
       <c r="G3">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H3">
-        <v>201</v>
+        <v>191.5</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -26121,10 +26147,10 @@
         <v>11</v>
       </c>
       <c r="G4">
-        <v>41</v>
+        <v>39.5</v>
       </c>
       <c r="H4">
-        <v>42</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -26173,10 +26199,10 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H6">
-        <v>99</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -26615,10 +26641,10 @@
         <v>14</v>
       </c>
       <c r="G23">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H23">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -26641,10 +26667,10 @@
         <v>14</v>
       </c>
       <c r="G24">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H24">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D51440-EC86-4394-A221-0F40A3558554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFC7F47-35D5-4AF8-B032-3453EDCC6962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4005" yWindow="420" windowWidth="13710" windowHeight="13920" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -26095,10 +26095,10 @@
         <v>14</v>
       </c>
       <c r="G2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="H2">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\listaProdutosToufic\lista-de-produtos-toufic\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EFC7F47-35D5-4AF8-B032-3453EDCC6962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73C1E4DD-BC9F-4823-ADE2-FD2290814425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3608" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3612" uniqueCount="1107">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3354,6 +3354,12 @@
   </si>
   <si>
     <t>DOCE ABÓBORA C/ COCO</t>
+  </si>
+  <si>
+    <t>canjicao-amarelo</t>
+  </si>
+  <si>
+    <t>CANJICÃO AMARELO</t>
   </si>
 </sst>
 </file>
@@ -6330,10 +6336,10 @@
         <v>11</v>
       </c>
       <c r="G88">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="H88">
-        <v>206</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
@@ -6356,10 +6362,10 @@
         <v>11</v>
       </c>
       <c r="G89">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="H89">
-        <v>105</v>
+        <v>95</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -23602,7 +23608,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
@@ -23745,16 +23751,16 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>310</v>
+        <v>1105</v>
       </c>
       <c r="B6" t="s">
-        <v>311</v>
+        <v>1106</v>
       </c>
       <c r="C6">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D6">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -23763,10 +23769,10 @@
         <v>14</v>
       </c>
       <c r="G6">
-        <v>63</v>
+        <v>85</v>
       </c>
       <c r="H6">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -23777,48 +23783,48 @@
         <v>311</v>
       </c>
       <c r="C7">
-        <v>2637</v>
+        <v>127</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G7">
-        <v>14.5</v>
+        <v>63</v>
       </c>
       <c r="H7">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B8" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C8">
-        <v>12</v>
+        <v>2637</v>
       </c>
       <c r="D8">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G8">
-        <v>63</v>
+        <v>14.5</v>
       </c>
       <c r="H8">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -23829,36 +23835,36 @@
         <v>313</v>
       </c>
       <c r="C9">
-        <v>2501</v>
+        <v>12</v>
       </c>
       <c r="D9">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G9">
-        <v>14.5</v>
+        <v>63</v>
       </c>
       <c r="H9">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C10">
-        <v>24</v>
+        <v>2501</v>
       </c>
       <c r="D10">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -23867,10 +23873,10 @@
         <v>11</v>
       </c>
       <c r="G10">
-        <v>63</v>
+        <v>14.5</v>
       </c>
       <c r="H10">
-        <v>65</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -23881,36 +23887,36 @@
         <v>315</v>
       </c>
       <c r="C11">
-        <v>2726</v>
+        <v>24</v>
       </c>
       <c r="D11">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G11">
-        <v>14.5</v>
+        <v>63</v>
       </c>
       <c r="H11">
-        <v>15</v>
+        <v>65</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="B12" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C12">
-        <v>4221</v>
+        <v>2726</v>
       </c>
       <c r="D12">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -23919,10 +23925,10 @@
         <v>14</v>
       </c>
       <c r="G12">
-        <v>142.5</v>
+        <v>14.5</v>
       </c>
       <c r="H12">
-        <v>147</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -23933,33 +23939,33 @@
         <v>317</v>
       </c>
       <c r="C13">
-        <v>4222</v>
+        <v>4221</v>
       </c>
       <c r="D13">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G13">
-        <v>30.5</v>
+        <v>142.5</v>
       </c>
       <c r="H13">
-        <v>31.5</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B14" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C14">
-        <v>2580</v>
+        <v>4222</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -23971,10 +23977,10 @@
         <v>11</v>
       </c>
       <c r="G14">
-        <v>38</v>
+        <v>30.5</v>
       </c>
       <c r="H14">
-        <v>39</v>
+        <v>31.5</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -23985,33 +23991,33 @@
         <v>319</v>
       </c>
       <c r="C15">
-        <v>123</v>
+        <v>2580</v>
       </c>
       <c r="D15">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>180</v>
+        <v>38</v>
       </c>
       <c r="H15">
-        <v>185.5</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B16" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C16">
-        <v>4016</v>
+        <v>123</v>
       </c>
       <c r="D16">
         <v>25</v>
@@ -24023,10 +24029,10 @@
         <v>14</v>
       </c>
       <c r="G16">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="H16">
-        <v>152.5</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -24037,10 +24043,10 @@
         <v>321</v>
       </c>
       <c r="C17">
-        <v>4017</v>
+        <v>4016</v>
       </c>
       <c r="D17">
-        <v>45.36</v>
+        <v>25</v>
       </c>
       <c r="E17" t="s">
         <v>10</v>
@@ -24049,10 +24055,10 @@
         <v>14</v>
       </c>
       <c r="G17">
-        <v>268.5</v>
+        <v>148</v>
       </c>
       <c r="H17">
-        <v>276.5</v>
+        <v>152.5</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -24063,10 +24069,10 @@
         <v>321</v>
       </c>
       <c r="C18">
-        <v>210</v>
+        <v>4017</v>
       </c>
       <c r="D18">
-        <v>5</v>
+        <v>45.36</v>
       </c>
       <c r="E18" t="s">
         <v>10</v>
@@ -24075,24 +24081,24 @@
         <v>14</v>
       </c>
       <c r="G18">
-        <v>31.5</v>
+        <v>268.5</v>
       </c>
       <c r="H18">
-        <v>32.5</v>
+        <v>276.5</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B19" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C19">
-        <v>4545</v>
+        <v>210</v>
       </c>
       <c r="D19">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E19" t="s">
         <v>10</v>
@@ -24101,10 +24107,10 @@
         <v>14</v>
       </c>
       <c r="G19">
-        <v>590</v>
+        <v>31.5</v>
       </c>
       <c r="H19">
-        <v>608</v>
+        <v>32.5</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -24115,48 +24121,48 @@
         <v>323</v>
       </c>
       <c r="C20">
-        <v>3363</v>
+        <v>4545</v>
       </c>
       <c r="D20">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
         <v>10</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G20">
-        <v>100.5</v>
+        <v>590</v>
       </c>
       <c r="H20">
-        <v>103.5</v>
+        <v>608</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B21" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C21">
-        <v>2482</v>
+        <v>3363</v>
       </c>
       <c r="D21">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E21" t="s">
         <v>10</v>
       </c>
       <c r="F21" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G21">
-        <v>540</v>
+        <v>100.5</v>
       </c>
       <c r="H21">
-        <v>556</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -24167,36 +24173,36 @@
         <v>325</v>
       </c>
       <c r="C22">
-        <v>34</v>
+        <v>2482</v>
       </c>
       <c r="D22">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E22" t="s">
         <v>10</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G22">
-        <v>92</v>
+        <v>540</v>
       </c>
       <c r="H22">
-        <v>95</v>
+        <v>556</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B23" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C23">
-        <v>89</v>
+        <v>34</v>
       </c>
       <c r="D23">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E23" t="s">
         <v>10</v>
@@ -24205,10 +24211,10 @@
         <v>11</v>
       </c>
       <c r="G23">
-        <v>540</v>
+        <v>92</v>
       </c>
       <c r="H23">
-        <v>556</v>
+        <v>95</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -24219,36 +24225,36 @@
         <v>327</v>
       </c>
       <c r="C24">
-        <v>114</v>
+        <v>89</v>
       </c>
       <c r="D24">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E24" t="s">
         <v>10</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G24">
-        <v>92</v>
+        <v>540</v>
       </c>
       <c r="H24">
-        <v>95</v>
+        <v>556</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B25" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C25">
-        <v>2486</v>
+        <v>114</v>
       </c>
       <c r="D25">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
         <v>10</v>
@@ -24257,10 +24263,10 @@
         <v>14</v>
       </c>
       <c r="G25">
-        <v>540</v>
+        <v>92</v>
       </c>
       <c r="H25">
-        <v>556</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -24271,48 +24277,48 @@
         <v>329</v>
       </c>
       <c r="C26">
-        <v>2241</v>
+        <v>2486</v>
       </c>
       <c r="D26">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E26" t="s">
         <v>10</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G26">
-        <v>92</v>
+        <v>540</v>
       </c>
       <c r="H26">
-        <v>95</v>
+        <v>556</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B27" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C27">
-        <v>2487</v>
+        <v>2241</v>
       </c>
       <c r="D27">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E27" t="s">
         <v>10</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G27">
-        <v>540</v>
+        <v>92</v>
       </c>
       <c r="H27">
-        <v>556</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -24323,48 +24329,48 @@
         <v>331</v>
       </c>
       <c r="C28">
-        <v>23</v>
+        <v>2487</v>
       </c>
       <c r="D28">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E28" t="s">
         <v>10</v>
       </c>
       <c r="F28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G28">
-        <v>92</v>
+        <v>540</v>
       </c>
       <c r="H28">
-        <v>95</v>
+        <v>556</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B29" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C29">
-        <v>2260</v>
+        <v>23</v>
       </c>
       <c r="D29">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E29" t="s">
         <v>10</v>
       </c>
       <c r="F29" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G29">
-        <v>430</v>
+        <v>92</v>
       </c>
       <c r="H29">
-        <v>443</v>
+        <v>95</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -24375,10 +24381,10 @@
         <v>333</v>
       </c>
       <c r="C30">
-        <v>214</v>
+        <v>2260</v>
       </c>
       <c r="D30">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E30" t="s">
         <v>10</v>
@@ -24387,24 +24393,24 @@
         <v>14</v>
       </c>
       <c r="G30">
-        <v>73.5</v>
+        <v>430</v>
       </c>
       <c r="H30">
-        <v>76</v>
+        <v>443</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B31" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C31">
-        <v>28</v>
+        <v>214</v>
       </c>
       <c r="D31">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E31" t="s">
         <v>10</v>
@@ -24413,10 +24419,10 @@
         <v>14</v>
       </c>
       <c r="G31">
-        <v>270</v>
+        <v>73.5</v>
       </c>
       <c r="H31">
-        <v>278</v>
+        <v>76</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -24427,33 +24433,33 @@
         <v>335</v>
       </c>
       <c r="C32">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D32">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E32" t="s">
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G32">
-        <v>47</v>
+        <v>270</v>
       </c>
       <c r="H32">
-        <v>48.5</v>
+        <v>278</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C33">
-        <v>2302</v>
+        <v>68</v>
       </c>
       <c r="D33">
         <v>5</v>
@@ -24462,13 +24468,13 @@
         <v>10</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G33">
-        <v>54.5</v>
+        <v>47</v>
       </c>
       <c r="H33">
-        <v>56</v>
+        <v>48.5</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -24479,10 +24485,10 @@
         <v>337</v>
       </c>
       <c r="C34">
-        <v>320</v>
+        <v>2302</v>
       </c>
       <c r="D34">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E34" t="s">
         <v>10</v>
@@ -24491,24 +24497,24 @@
         <v>14</v>
       </c>
       <c r="G34">
-        <v>315</v>
+        <v>54.5</v>
       </c>
       <c r="H34">
-        <v>324.5</v>
+        <v>56</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B35" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="C35">
-        <v>3479</v>
+        <v>320</v>
       </c>
       <c r="D35">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E35" t="s">
         <v>10</v>
@@ -24517,10 +24523,10 @@
         <v>14</v>
       </c>
       <c r="G35">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="H35">
-        <v>366.5</v>
+        <v>324.5</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -24531,10 +24537,10 @@
         <v>339</v>
       </c>
       <c r="C36">
-        <v>130</v>
+        <v>3479</v>
       </c>
       <c r="D36">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E36" t="s">
         <v>10</v>
@@ -24543,10 +24549,10 @@
         <v>14</v>
       </c>
       <c r="G36">
-        <v>178</v>
+        <v>356</v>
       </c>
       <c r="H36">
-        <v>183.5</v>
+        <v>366.5</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -24557,48 +24563,48 @@
         <v>339</v>
       </c>
       <c r="C37">
-        <v>2464</v>
+        <v>130</v>
       </c>
       <c r="D37">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E37" t="s">
         <v>10</v>
       </c>
       <c r="F37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G37">
-        <v>37.5</v>
+        <v>178</v>
       </c>
       <c r="H37">
-        <v>39</v>
+        <v>183.5</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B38" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="C38">
-        <v>101</v>
+        <v>2464</v>
       </c>
       <c r="D38">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E38" t="s">
         <v>10</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G38">
-        <v>360</v>
+        <v>37.5</v>
       </c>
       <c r="H38">
-        <v>372</v>
+        <v>39</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -24609,33 +24615,33 @@
         <v>341</v>
       </c>
       <c r="C39">
-        <v>2465</v>
+        <v>101</v>
       </c>
       <c r="D39">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E39" t="s">
         <v>10</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G39">
-        <v>62</v>
+        <v>360</v>
       </c>
       <c r="H39">
-        <v>64</v>
+        <v>372</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="B40" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C40">
-        <v>65</v>
+        <v>2465</v>
       </c>
       <c r="D40">
         <v>5</v>
@@ -24647,10 +24653,10 @@
         <v>11</v>
       </c>
       <c r="G40">
-        <v>24.5</v>
+        <v>62</v>
       </c>
       <c r="H40">
-        <v>25</v>
+        <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
@@ -24661,22 +24667,22 @@
         <v>343</v>
       </c>
       <c r="C41">
-        <v>2624</v>
+        <v>65</v>
       </c>
       <c r="D41">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E41" t="s">
         <v>10</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G41">
-        <v>135</v>
+        <v>24.5</v>
       </c>
       <c r="H41">
-        <v>139</v>
+        <v>25</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -24687,10 +24693,10 @@
         <v>343</v>
       </c>
       <c r="C42">
-        <v>119</v>
+        <v>2624</v>
       </c>
       <c r="D42">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E42" t="s">
         <v>10</v>
@@ -24699,24 +24705,24 @@
         <v>14</v>
       </c>
       <c r="G42">
-        <v>270</v>
+        <v>135</v>
       </c>
       <c r="H42">
-        <v>278</v>
+        <v>139</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B43" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C43">
-        <v>2834</v>
+        <v>119</v>
       </c>
       <c r="D43">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E43" t="s">
         <v>10</v>
@@ -24725,10 +24731,10 @@
         <v>14</v>
       </c>
       <c r="G43">
-        <v>123</v>
+        <v>270</v>
       </c>
       <c r="H43">
-        <v>127</v>
+        <v>278</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -24739,10 +24745,10 @@
         <v>345</v>
       </c>
       <c r="C44">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D44">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E44" t="s">
         <v>10</v>
@@ -24751,10 +24757,10 @@
         <v>14</v>
       </c>
       <c r="G44">
-        <v>102.5</v>
+        <v>123</v>
       </c>
       <c r="H44">
-        <v>105.5</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -24765,10 +24771,10 @@
         <v>345</v>
       </c>
       <c r="C45">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D45">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E45" t="s">
         <v>10</v>
@@ -24777,24 +24783,24 @@
         <v>14</v>
       </c>
       <c r="G45">
-        <v>23</v>
+        <v>102.5</v>
       </c>
       <c r="H45">
-        <v>24</v>
+        <v>105.5</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B46" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="C46">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D46">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E46" t="s">
         <v>10</v>
@@ -24803,10 +24809,10 @@
         <v>14</v>
       </c>
       <c r="G46">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="H46">
-        <v>206</v>
+        <v>24</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -24817,48 +24823,48 @@
         <v>347</v>
       </c>
       <c r="C47">
-        <v>2543</v>
+        <v>3025</v>
       </c>
       <c r="D47">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E47" t="s">
         <v>10</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G47">
-        <v>35.5</v>
+        <v>200</v>
       </c>
       <c r="H47">
-        <v>36.5</v>
+        <v>206</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B48" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="C48">
-        <v>98</v>
+        <v>2543</v>
       </c>
       <c r="D48">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" t="s">
         <v>10</v>
       </c>
       <c r="F48" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G48">
-        <v>320</v>
+        <v>35.5</v>
       </c>
       <c r="H48">
-        <v>329.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -24869,10 +24875,10 @@
         <v>349</v>
       </c>
       <c r="C49">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D49">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E49" t="s">
         <v>10</v>
@@ -24881,24 +24887,24 @@
         <v>14</v>
       </c>
       <c r="G49">
-        <v>55.5</v>
+        <v>320</v>
       </c>
       <c r="H49">
-        <v>57</v>
+        <v>329.5</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B50" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="C50">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D50">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E50" t="s">
         <v>10</v>
@@ -24907,10 +24913,10 @@
         <v>14</v>
       </c>
       <c r="G50">
-        <v>362.5</v>
+        <v>55.5</v>
       </c>
       <c r="H50">
-        <v>373.5</v>
+        <v>57</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -24921,48 +24927,48 @@
         <v>351</v>
       </c>
       <c r="C51">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D51">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E51" t="s">
         <v>10</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G51">
-        <v>74.5</v>
+        <v>362.5</v>
       </c>
       <c r="H51">
-        <v>77</v>
+        <v>373.5</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B52" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C52">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D52">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E52" t="s">
         <v>10</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G52">
-        <v>255</v>
+        <v>74.5</v>
       </c>
       <c r="H52">
-        <v>262.5</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
@@ -24973,10 +24979,10 @@
         <v>353</v>
       </c>
       <c r="C53">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D53">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E53" t="s">
         <v>10</v>
@@ -24985,10 +24991,10 @@
         <v>14</v>
       </c>
       <c r="G53">
-        <v>212.5</v>
+        <v>255</v>
       </c>
       <c r="H53">
-        <v>219</v>
+        <v>262.5</v>
       </c>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
@@ -24999,48 +25005,48 @@
         <v>353</v>
       </c>
       <c r="C54">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D54">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E54" t="s">
         <v>10</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G54">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
       <c r="H54">
-        <v>46</v>
+        <v>219</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B55" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C55">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D55">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E55" t="s">
         <v>10</v>
       </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G55">
-        <v>350</v>
+        <v>44.5</v>
       </c>
       <c r="H55">
-        <v>360.5</v>
+        <v>46</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -25051,10 +25057,10 @@
         <v>355</v>
       </c>
       <c r="C56">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D56">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E56" t="s">
         <v>10</v>
@@ -25063,10 +25069,10 @@
         <v>14</v>
       </c>
       <c r="G56">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="H56">
-        <v>180.5</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -25077,48 +25083,48 @@
         <v>355</v>
       </c>
       <c r="C57">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D57">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E57" t="s">
         <v>10</v>
       </c>
       <c r="F57" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G57">
-        <v>31</v>
+        <v>175</v>
       </c>
       <c r="H57">
-        <v>32</v>
+        <v>180.5</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B58" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C58">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D58">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E58" t="s">
         <v>10</v>
       </c>
       <c r="F58" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G58">
-        <v>275</v>
+        <v>31</v>
       </c>
       <c r="H58">
-        <v>283.5</v>
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -25129,48 +25135,48 @@
         <v>357</v>
       </c>
       <c r="C59">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D59">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E59" t="s">
         <v>10</v>
       </c>
       <c r="F59" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G59">
-        <v>57</v>
+        <v>275</v>
       </c>
       <c r="H59">
-        <v>59</v>
+        <v>283.5</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B60" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C60">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D60">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E60" t="s">
         <v>10</v>
       </c>
       <c r="F60" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G60">
-        <v>280</v>
+        <v>57</v>
       </c>
       <c r="H60">
-        <v>288.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -25181,10 +25187,10 @@
         <v>359</v>
       </c>
       <c r="C61">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D61">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E61" t="s">
         <v>10</v>
@@ -25193,24 +25199,24 @@
         <v>14</v>
       </c>
       <c r="G61">
-        <v>48.5</v>
+        <v>280</v>
       </c>
       <c r="H61">
-        <v>50</v>
+        <v>288.5</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B62" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C62">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D62">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" t="s">
         <v>10</v>
@@ -25219,10 +25225,10 @@
         <v>14</v>
       </c>
       <c r="G62">
-        <v>375</v>
+        <v>48.5</v>
       </c>
       <c r="H62">
-        <v>386.5</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -25233,48 +25239,48 @@
         <v>361</v>
       </c>
       <c r="C63">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D63">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E63" t="s">
         <v>10</v>
       </c>
       <c r="F63" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G63">
-        <v>64.5</v>
+        <v>375</v>
       </c>
       <c r="H63">
-        <v>66.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B64" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C64">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D64">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" t="s">
         <v>10</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G64">
-        <v>330</v>
+        <v>64.5</v>
       </c>
       <c r="H64">
-        <v>340</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -25285,48 +25291,48 @@
         <v>363</v>
       </c>
       <c r="C65">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D65">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E65" t="s">
         <v>10</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G65">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="H65">
-        <v>59</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B66" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C66">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D66">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E66" t="s">
         <v>10</v>
       </c>
       <c r="F66" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G66">
-        <v>285</v>
+        <v>57</v>
       </c>
       <c r="H66">
-        <v>293.5</v>
+        <v>59</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -25337,10 +25343,10 @@
         <v>365</v>
       </c>
       <c r="C67">
-        <v>3740</v>
+        <v>3670</v>
       </c>
       <c r="D67">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E67" t="s">
         <v>10</v>
@@ -25349,10 +25355,10 @@
         <v>14</v>
       </c>
       <c r="G67">
-        <v>237.5</v>
+        <v>285</v>
       </c>
       <c r="H67">
-        <v>244.5</v>
+        <v>293.5</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -25363,48 +25369,48 @@
         <v>365</v>
       </c>
       <c r="C68">
-        <v>2469</v>
+        <v>3740</v>
       </c>
       <c r="D68">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E68" t="s">
         <v>10</v>
       </c>
       <c r="F68" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G68">
-        <v>49.5</v>
+        <v>237.5</v>
       </c>
       <c r="H68">
-        <v>51</v>
+        <v>244.5</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B69" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C69">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D69">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E69" t="s">
         <v>10</v>
       </c>
       <c r="F69" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G69">
-        <v>312.5</v>
+        <v>49.5</v>
       </c>
       <c r="H69">
-        <v>322</v>
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -25415,48 +25421,48 @@
         <v>367</v>
       </c>
       <c r="C70">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D70">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E70" t="s">
         <v>10</v>
       </c>
       <c r="F70" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G70">
-        <v>64.5</v>
+        <v>312.5</v>
       </c>
       <c r="H70">
-        <v>66.5</v>
+        <v>322</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B71" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C71">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D71">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E71" t="s">
         <v>10</v>
       </c>
       <c r="F71" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G71">
-        <v>300</v>
+        <v>64.5</v>
       </c>
       <c r="H71">
-        <v>309</v>
+        <v>66.5</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -25467,48 +25473,48 @@
         <v>369</v>
       </c>
       <c r="C72">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D72">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E72" t="s">
         <v>10</v>
       </c>
       <c r="F72" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G72">
-        <v>62</v>
+        <v>300</v>
       </c>
       <c r="H72">
-        <v>64</v>
+        <v>309</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B73" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C73">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D73">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E73" t="s">
         <v>10</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G73">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="H73">
-        <v>185.5</v>
+        <v>64</v>
       </c>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
@@ -25519,48 +25525,48 @@
         <v>371</v>
       </c>
       <c r="C74">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D74">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E74" t="s">
         <v>10</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G74">
-        <v>38</v>
+        <v>180</v>
       </c>
       <c r="H74">
-        <v>39</v>
+        <v>185.5</v>
       </c>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B75" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C75">
-        <v>211</v>
+        <v>2321</v>
       </c>
       <c r="D75">
-        <v>22.68</v>
+        <v>5</v>
       </c>
       <c r="E75" t="s">
         <v>10</v>
       </c>
       <c r="F75" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G75">
-        <v>187.5</v>
+        <v>38</v>
       </c>
       <c r="H75">
-        <v>193</v>
+        <v>39</v>
       </c>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
@@ -25571,10 +25577,10 @@
         <v>373</v>
       </c>
       <c r="C76">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D76">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E76" t="s">
         <v>10</v>
@@ -25583,10 +25589,10 @@
         <v>14</v>
       </c>
       <c r="G76">
-        <v>375</v>
+        <v>187.5</v>
       </c>
       <c r="H76">
-        <v>386.5</v>
+        <v>193</v>
       </c>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
@@ -25597,48 +25603,48 @@
         <v>373</v>
       </c>
       <c r="C77">
-        <v>2322</v>
+        <v>41</v>
       </c>
       <c r="D77">
-        <v>5</v>
+        <v>45.36</v>
       </c>
       <c r="E77" t="s">
         <v>10</v>
       </c>
       <c r="F77" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G77">
-        <v>43.5</v>
+        <v>375</v>
       </c>
       <c r="H77">
-        <v>44.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B78" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C78">
-        <v>67</v>
+        <v>2322</v>
       </c>
       <c r="D78">
-        <v>45.36</v>
+        <v>5</v>
       </c>
       <c r="E78" t="s">
         <v>10</v>
       </c>
       <c r="F78" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G78">
-        <v>626</v>
+        <v>43.5</v>
       </c>
       <c r="H78">
-        <v>645</v>
+        <v>44.5</v>
       </c>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
@@ -25649,10 +25655,10 @@
         <v>375</v>
       </c>
       <c r="C79">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D79">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E79" t="s">
         <v>10</v>
@@ -25661,10 +25667,10 @@
         <v>14</v>
       </c>
       <c r="G79">
-        <v>313</v>
+        <v>626</v>
       </c>
       <c r="H79">
-        <v>322.5</v>
+        <v>645</v>
       </c>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
@@ -25675,74 +25681,74 @@
         <v>375</v>
       </c>
       <c r="C80">
-        <v>2488</v>
+        <v>2244</v>
       </c>
       <c r="D80">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E80" t="s">
         <v>10</v>
       </c>
       <c r="F80" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G80">
-        <v>71</v>
+        <v>313</v>
       </c>
       <c r="H80">
-        <v>73</v>
+        <v>322.5</v>
       </c>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B81" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C81">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D81">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E81" t="s">
         <v>10</v>
       </c>
       <c r="F81" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G81">
-        <v>52</v>
+        <v>71</v>
       </c>
       <c r="H81">
-        <v>53.5</v>
+        <v>73</v>
       </c>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B82" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C82">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D82">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E82" t="s">
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G82">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="H82">
-        <v>187.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
@@ -25753,22 +25759,22 @@
         <v>379</v>
       </c>
       <c r="C83">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D83">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" t="s">
         <v>10</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G83">
-        <v>350</v>
+        <v>182</v>
       </c>
       <c r="H83">
-        <v>360.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -25779,10 +25785,10 @@
         <v>379</v>
       </c>
       <c r="C84">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D84">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E84" t="s">
         <v>10</v>
@@ -25791,10 +25797,10 @@
         <v>14</v>
       </c>
       <c r="G84">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="H84">
-        <v>721</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -25805,62 +25811,62 @@
         <v>379</v>
       </c>
       <c r="C85">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D85">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E85" t="s">
         <v>10</v>
       </c>
       <c r="F85" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="G85">
-        <v>106</v>
+        <v>700</v>
       </c>
       <c r="H85">
-        <v>109.5</v>
+        <v>721</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>99</v>
+        <v>378</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>379</v>
       </c>
       <c r="C86">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D86">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E86" t="s">
         <v>10</v>
       </c>
       <c r="F86" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G86">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="H86">
-        <v>89.5</v>
+        <v>109.5</v>
       </c>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>380</v>
+        <v>99</v>
       </c>
       <c r="B87" t="s">
-        <v>381</v>
+        <v>100</v>
       </c>
       <c r="C87">
-        <v>135</v>
+        <v>3110</v>
       </c>
       <c r="D87">
-        <v>22.68</v>
+        <v>25</v>
       </c>
       <c r="E87" t="s">
         <v>10</v>
@@ -25869,24 +25875,24 @@
         <v>14</v>
       </c>
       <c r="G87">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H87">
-        <v>87.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B88" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C88">
-        <v>2463</v>
+        <v>135</v>
       </c>
       <c r="D88">
-        <v>5</v>
+        <v>22.68</v>
       </c>
       <c r="E88" t="s">
         <v>10</v>
@@ -25895,24 +25901,24 @@
         <v>14</v>
       </c>
       <c r="G88">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H88">
-        <v>21.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="B89" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="C89">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D89">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E89" t="s">
         <v>10</v>
@@ -25921,10 +25927,10 @@
         <v>14</v>
       </c>
       <c r="G89">
-        <v>114</v>
+        <v>21</v>
       </c>
       <c r="H89">
-        <v>118</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
@@ -25935,10 +25941,10 @@
         <v>385</v>
       </c>
       <c r="C90">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D90">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E90" t="s">
         <v>10</v>
@@ -25947,10 +25953,10 @@
         <v>14</v>
       </c>
       <c r="G90">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="H90">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
@@ -25961,10 +25967,10 @@
         <v>385</v>
       </c>
       <c r="C91">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D91">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E91" t="s">
         <v>10</v>
@@ -25973,24 +25979,24 @@
         <v>14</v>
       </c>
       <c r="G91">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="H91">
-        <v>235</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="B92" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C92">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D92">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E92" t="s">
         <v>10</v>
@@ -25999,10 +26005,10 @@
         <v>14</v>
       </c>
       <c r="G92">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="H92">
-        <v>129</v>
+        <v>235</v>
       </c>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
@@ -26013,21 +26019,47 @@
         <v>387</v>
       </c>
       <c r="C93">
+        <v>4223</v>
+      </c>
+      <c r="D93">
+        <v>25</v>
+      </c>
+      <c r="E93" t="s">
+        <v>10</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93">
+        <v>125</v>
+      </c>
+      <c r="H93">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>386</v>
+      </c>
+      <c r="B94" t="s">
+        <v>387</v>
+      </c>
+      <c r="C94">
         <v>4224</v>
       </c>
-      <c r="D93">
-        <v>5</v>
-      </c>
-      <c r="E93" t="s">
-        <v>10</v>
-      </c>
-      <c r="F93" t="s">
-        <v>11</v>
-      </c>
-      <c r="G93">
+      <c r="D94">
+        <v>5</v>
+      </c>
+      <c r="E94" t="s">
+        <v>10</v>
+      </c>
+      <c r="F94" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94">
         <v>27</v>
       </c>
-      <c r="H93">
+      <c r="H94">
         <v>28</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -3367,7 +3367,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3385,6 +3385,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3444,16 +3450,16 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -3468,7 +3474,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -9228,10 +9234,10 @@
         <v>145</v>
       </c>
       <c r="G21" s="5">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="H21" s="5">
-        <v>268</v>
+        <v>288.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
@@ -9245,7 +9251,7 @@
         <v>3009</v>
       </c>
       <c r="D22" s="5">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>30</v>
@@ -9254,10 +9260,10 @@
         <v>11</v>
       </c>
       <c r="G22" s="5">
-        <v>78</v>
+        <v>142.5</v>
       </c>
       <c r="H22" s="6">
-        <v>80.5</v>
+        <v>147</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
@@ -9286,7 +9292,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>344</v>
       </c>
@@ -9312,7 +9318,7 @@
         <v>268</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>346</v>
       </c>
@@ -9338,7 +9344,7 @@
         <v>721</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
         <v>346</v>
       </c>
@@ -9364,7 +9370,7 @@
         <v>159.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
         <v>346</v>
       </c>
@@ -9390,7 +9396,7 @@
         <v>88</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4" t="s">
         <v>348</v>
       </c>
@@ -9416,7 +9422,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4" t="s">
         <v>348</v>
       </c>
@@ -9442,7 +9448,7 @@
         <v>613</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="4" t="s">
         <v>348</v>
       </c>
@@ -9468,7 +9474,7 @@
         <v>308.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="4" t="s">
         <v>350</v>
       </c>
@@ -9520,7 +9526,7 @@
         <v>165</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
         <v>354</v>
       </c>
@@ -9546,7 +9552,7 @@
         <v>149.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
         <v>356</v>
       </c>
@@ -9572,7 +9578,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
         <v>358</v>
       </c>
@@ -9598,7 +9604,7 @@
         <v>226.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4" t="s">
         <v>358</v>
       </c>
@@ -9624,7 +9630,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="4" t="s">
         <v>360</v>
       </c>
@@ -9650,7 +9656,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="4" t="s">
         <v>360</v>
       </c>
@@ -9676,7 +9682,7 @@
         <v>129</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="4" t="s">
         <v>362</v>
       </c>
@@ -9702,7 +9708,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="4" t="s">
         <v>364</v>
       </c>
@@ -9728,7 +9734,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="4" t="s">
         <v>366</v>
       </c>
@@ -9754,7 +9760,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="4" t="s">
         <v>368</v>
       </c>
@@ -9780,7 +9786,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="4" t="s">
         <v>370</v>
       </c>
@@ -9806,7 +9812,7 @@
         <v>85</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="4" t="s">
         <v>372</v>
       </c>
@@ -9832,7 +9838,7 @@
         <v>166.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="4" t="s">
         <v>374</v>
       </c>
@@ -9858,7 +9864,7 @@
         <v>194.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="4" t="s">
         <v>374</v>
       </c>
@@ -9884,7 +9890,7 @@
         <v>99.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="4" t="s">
         <v>376</v>
       </c>
@@ -9910,7 +9916,7 @@
         <v>130</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
         <v>376</v>
       </c>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8682,7 +8682,7 @@
     <col min="8" max="8" style="9" width="20.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8708,7 +8708,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>319</v>
       </c>
@@ -8734,7 +8734,7 @@
         <v>343</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>321</v>
       </c>
@@ -11484,10 +11484,10 @@
         <v>11</v>
       </c>
       <c r="G108" s="3">
-        <v>440</v>
+        <v>510</v>
       </c>
       <c r="H108" s="3">
-        <v>440</v>
+        <v>525.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="12"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -18466,10 +18466,10 @@
         <v>11</v>
       </c>
       <c r="G64" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H64" s="3">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -18492,10 +18492,10 @@
         <v>11</v>
       </c>
       <c r="G65" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="H65" s="5">
-        <v>71.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
@@ -18518,10 +18518,10 @@
         <v>11</v>
       </c>
       <c r="G66" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="H66" s="5">
-        <v>71.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -18544,10 +18544,10 @@
         <v>11</v>
       </c>
       <c r="G67" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H67" s="3">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -18570,10 +18570,10 @@
         <v>11</v>
       </c>
       <c r="G68" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H68" s="3">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -18596,10 +18596,10 @@
         <v>11</v>
       </c>
       <c r="G69" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="H69" s="5">
-        <v>71.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -18674,10 +18674,10 @@
         <v>11</v>
       </c>
       <c r="G72" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H72" s="3">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -18700,10 +18700,10 @@
         <v>11</v>
       </c>
       <c r="G73" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="H73" s="5">
-        <v>71.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -18726,10 +18726,10 @@
         <v>11</v>
       </c>
       <c r="G74" s="3">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H74" s="3">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -18752,10 +18752,10 @@
         <v>11</v>
       </c>
       <c r="G75" s="5">
-        <v>69.5</v>
+        <v>72.5</v>
       </c>
       <c r="H75" s="5">
-        <v>71.5</v>
+        <v>74.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -8523,10 +8523,10 @@
         <v>145</v>
       </c>
       <c r="G31" s="3">
-        <v>900</v>
+        <v>1325</v>
       </c>
       <c r="H31" s="3">
-        <v>927</v>
+        <v>1365</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -8575,10 +8575,10 @@
         <v>145</v>
       </c>
       <c r="G33" s="3">
-        <v>182</v>
+        <v>278.5</v>
       </c>
       <c r="H33" s="5">
-        <v>187.5</v>
+        <v>287</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
@@ -24561,10 +24561,10 @@
         <v>145</v>
       </c>
       <c r="G30" s="3">
-        <v>430</v>
+        <v>390</v>
       </c>
       <c r="H30" s="3">
-        <v>443</v>
+        <v>402</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -24587,10 +24587,10 @@
         <v>145</v>
       </c>
       <c r="G31" s="5">
-        <v>73.5</v>
+        <v>68</v>
       </c>
       <c r="H31" s="3">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4863,10 +4863,10 @@
         <v>145</v>
       </c>
       <c r="G29" s="5">
-        <v>112.5</v>
+        <v>77.5</v>
       </c>
       <c r="H29" s="3">
-        <v>116</v>
+        <v>80</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
@@ -4889,10 +4889,10 @@
         <v>145</v>
       </c>
       <c r="G30" s="3">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="H30" s="5">
-        <v>46.5</v>
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
@@ -4915,10 +4915,10 @@
         <v>145</v>
       </c>
       <c r="G31" s="3">
-        <v>125</v>
+        <v>112.5</v>
       </c>
       <c r="H31" s="3">
-        <v>129</v>
+        <v>116</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
@@ -8217,7 +8217,7 @@
         <v>204</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>491</v>
       </c>
@@ -8243,7 +8243,7 @@
         <v>407</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>494</v>
       </c>
@@ -8269,7 +8269,7 @@
         <v>98</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>494</v>
       </c>
@@ -8295,7 +8295,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>496</v>
       </c>
@@ -8321,7 +8321,7 @@
         <v>412</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>496</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>374</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>496</v>
       </c>
@@ -8373,7 +8373,7 @@
         <v>84.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
         <v>498</v>
       </c>
@@ -8399,7 +8399,7 @@
         <v>463.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
         <v>498</v>
       </c>
@@ -8425,7 +8425,7 @@
         <v>618</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4" t="s">
         <v>498</v>
       </c>
@@ -8451,7 +8451,7 @@
         <v>94</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4" t="s">
         <v>500</v>
       </c>
@@ -8477,7 +8477,7 @@
         <v>105</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="4" t="s">
         <v>500</v>
       </c>
@@ -8503,7 +8503,7 @@
         <v>515</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="4" t="s">
         <v>502</v>
       </c>
@@ -8529,7 +8529,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="4" t="s">
         <v>502</v>
       </c>
@@ -8555,7 +8555,7 @@
         <v>741.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
         <v>502</v>
       </c>
@@ -8581,7 +8581,7 @@
         <v>287</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
         <v>504</v>
       </c>
@@ -8598,16 +8598,16 @@
         <v>30</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="G34" s="3">
-        <v>475</v>
+        <v>362.5</v>
       </c>
       <c r="H34" s="5">
-        <v>489.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+        <v>373.5</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
         <v>504</v>
       </c>
@@ -8624,16 +8624,16 @@
         <v>30</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G35" s="3">
-        <v>97</v>
+        <v>75.5</v>
       </c>
       <c r="H35" s="3">
-        <v>100</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+        <v>78</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4" t="s">
         <v>506</v>
       </c>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4115,7 +4115,7 @@
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4141,7 +4141,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>538</v>
       </c>
@@ -4167,7 +4167,7 @@
         <v>391.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>538</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>61</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>540</v>
       </c>
@@ -4219,7 +4219,7 @@
         <v>360.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>540</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>542</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>542</v>
       </c>
@@ -4297,7 +4297,7 @@
         <v>150.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>544</v>
       </c>
@@ -4323,7 +4323,7 @@
         <v>62</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>544</v>
       </c>
@@ -4349,7 +4349,7 @@
         <v>34.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>546</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>142</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>548</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>132.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>550</v>
       </c>
@@ -4427,7 +4427,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>550</v>
       </c>
@@ -4453,7 +4453,7 @@
         <v>401</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>552</v>
       </c>
@@ -4479,7 +4479,7 @@
         <v>190.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>552</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>98.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>554</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>554</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>556</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>556</v>
       </c>
@@ -4609,7 +4609,7 @@
         <v>386.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>558</v>
       </c>
@@ -4635,7 +4635,7 @@
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>560</v>
       </c>
@@ -4661,7 +4661,7 @@
         <v>64.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>560</v>
       </c>
@@ -4687,7 +4687,7 @@
         <v>34</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>562</v>
       </c>
@@ -4713,7 +4713,7 @@
         <v>329.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>562</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>100</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>564</v>
       </c>
@@ -7590,10 +7590,10 @@
         <v>16</v>
       </c>
       <c r="G19" s="3">
-        <v>175</v>
+        <v>250</v>
       </c>
       <c r="H19" s="3">
-        <v>180</v>
+        <v>257.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="10"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4421,10 +4421,10 @@
         <v>11</v>
       </c>
       <c r="G12" s="3">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="H12" s="3">
-        <v>40</v>
+        <v>50.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
@@ -4447,10 +4447,10 @@
         <v>16</v>
       </c>
       <c r="G13" s="3">
-        <v>390</v>
+        <v>490</v>
       </c>
       <c r="H13" s="3">
-        <v>401</v>
+        <v>505</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
@@ -7102,7 +7102,7 @@
     <col min="8" max="8" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7128,7 +7128,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>508</v>
       </c>
@@ -7154,7 +7154,7 @@
         <v>319.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>510</v>
       </c>
@@ -7180,7 +7180,7 @@
         <v>396.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>510</v>
       </c>
@@ -7206,7 +7206,7 @@
         <v>177</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>512</v>
       </c>
@@ -7232,7 +7232,7 @@
         <v>515</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>514</v>
       </c>
@@ -7258,7 +7258,7 @@
         <v>130</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>516</v>
       </c>
@@ -7284,7 +7284,7 @@
         <v>494.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>516</v>
       </c>
@@ -7310,7 +7310,7 @@
         <v>249.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>518</v>
       </c>
@@ -7336,7 +7336,7 @@
         <v>90</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>518</v>
       </c>
@@ -7362,7 +7362,7 @@
         <v>478</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>520</v>
       </c>
@@ -7388,7 +7388,7 @@
         <v>86.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>520</v>
       </c>
@@ -7414,7 +7414,7 @@
         <v>299</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>522</v>
       </c>
@@ -7440,7 +7440,7 @@
         <v>695.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>522</v>
       </c>
@@ -7466,7 +7466,7 @@
         <v>347.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>524</v>
       </c>
@@ -7492,7 +7492,7 @@
         <v>597.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>524</v>
       </c>
@@ -7518,7 +7518,7 @@
         <v>299</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>526</v>
       </c>
@@ -7544,7 +7544,7 @@
         <v>468.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>526</v>
       </c>
@@ -7570,7 +7570,7 @@
         <v>234.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>528</v>
       </c>
@@ -7596,7 +7596,7 @@
         <v>257.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>530</v>
       </c>
@@ -7622,7 +7622,7 @@
         <v>151.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>532</v>
       </c>
@@ -7648,7 +7648,7 @@
         <v>146</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>534</v>
       </c>
@@ -7674,7 +7674,7 @@
         <v>432.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>536</v>
       </c>
@@ -7899,10 +7899,10 @@
         <v>11</v>
       </c>
       <c r="G7" s="5">
-        <v>34.5</v>
+        <v>38</v>
       </c>
       <c r="H7" s="5">
-        <v>35.5</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
@@ -7925,10 +7925,10 @@
         <v>145</v>
       </c>
       <c r="G8" s="5">
-        <v>162.5</v>
+        <v>175</v>
       </c>
       <c r="H8" s="5">
-        <v>167.5</v>
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -10626,10 +10626,10 @@
         <v>145</v>
       </c>
       <c r="G75" s="3">
-        <v>255</v>
+        <v>300</v>
       </c>
       <c r="H75" s="5">
-        <v>262.5</v>
+        <v>309</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -10652,10 +10652,10 @@
         <v>11</v>
       </c>
       <c r="G76" s="3">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="H76" s="5">
-        <v>54.5</v>
+        <v>65</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-libanes\produtos-libanes\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE1D251-360B-4A3F-B8CC-A3F78955F645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBC497F-C1D8-4AC2-8B5F-659EB2F8A2AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="15585" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -8778,10 +8778,10 @@
         <v>16</v>
       </c>
       <c r="G22" s="3">
-        <v>420</v>
+        <v>340</v>
       </c>
       <c r="H22" s="4">
-        <v>432.5</v>
+        <v>350</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10280,10 +10280,10 @@
         <v>145</v>
       </c>
       <c r="G19" s="3">
-        <v>750</v>
+        <v>575</v>
       </c>
       <c r="H19" s="4">
-        <v>772.5</v>
+        <v>592</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10306,10 +10306,10 @@
         <v>11</v>
       </c>
       <c r="G20" s="3">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="H20" s="3">
-        <v>95</v>
+        <v>73</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -10592,10 +10592,10 @@
         <v>11</v>
       </c>
       <c r="G31" s="4">
-        <v>259.5</v>
+        <v>228.5</v>
       </c>
       <c r="H31" s="3">
-        <v>267</v>
+        <v>235.5</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11996,10 +11996,10 @@
         <v>11</v>
       </c>
       <c r="G85" s="4">
-        <v>145.5</v>
+        <v>127</v>
       </c>
       <c r="H85" s="3">
-        <v>150</v>
+        <v>131.5</v>
       </c>
     </row>
     <row r="86" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12022,10 +12022,10 @@
         <v>145</v>
       </c>
       <c r="G86" s="3">
-        <v>360</v>
+        <v>310</v>
       </c>
       <c r="H86" s="3">
-        <v>371</v>
+        <v>319.5</v>
       </c>
     </row>
     <row r="87" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12048,10 +12048,10 @@
         <v>11</v>
       </c>
       <c r="G87" s="3">
-        <v>900</v>
+        <v>775</v>
       </c>
       <c r="H87" s="3">
-        <v>927</v>
+        <v>798.5</v>
       </c>
     </row>
     <row r="88" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12360,10 +12360,10 @@
         <v>145</v>
       </c>
       <c r="G99" s="3">
-        <v>390</v>
+        <v>350</v>
       </c>
       <c r="H99" s="3">
-        <v>402</v>
+        <v>360.5</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12386,10 +12386,10 @@
         <v>11</v>
       </c>
       <c r="G100" s="3">
-        <v>197</v>
+        <v>178.5</v>
       </c>
       <c r="H100" s="3">
-        <v>203</v>
+        <v>184</v>
       </c>
     </row>
     <row r="101" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24790,10 +24790,10 @@
         <v>145</v>
       </c>
       <c r="G68" s="3">
-        <v>300</v>
+        <v>280</v>
       </c>
       <c r="H68" s="3">
-        <v>309</v>
+        <v>288.5</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24816,10 +24816,10 @@
         <v>11</v>
       </c>
       <c r="G69" s="3">
-        <v>150</v>
+        <v>143.5</v>
       </c>
       <c r="H69" s="4">
-        <v>154.5</v>
+        <v>148</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24842,10 +24842,10 @@
         <v>145</v>
       </c>
       <c r="G70" s="3">
-        <v>420</v>
+        <v>360</v>
       </c>
       <c r="H70" s="4">
-        <v>432.5</v>
+        <v>371</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24868,10 +24868,10 @@
         <v>145</v>
       </c>
       <c r="G71" s="3">
-        <v>210</v>
+        <v>183.5</v>
       </c>
       <c r="H71" s="4">
-        <v>216.5</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="5"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3780" uniqueCount="1111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="1111">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -8808,7 +8808,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H36"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -9621,10 +9621,10 @@
         <v>145</v>
       </c>
       <c r="G31" s="3">
-        <v>1325</v>
+        <v>1550</v>
       </c>
       <c r="H31" s="3">
-        <v>1365</v>
+        <v>1596.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -9635,36 +9635,36 @@
         <v>503</v>
       </c>
       <c r="C32" s="3">
-        <v>2680</v>
+        <v>2676</v>
       </c>
       <c r="D32" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>16</v>
+        <v>145</v>
       </c>
       <c r="G32" s="3">
-        <v>720</v>
+        <v>313.5</v>
       </c>
       <c r="H32" s="5">
-        <v>741.5</v>
+        <v>323</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C33" s="3">
-        <v>2676</v>
+        <v>571</v>
       </c>
       <c r="D33" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>30</v>
@@ -9673,10 +9673,10 @@
         <v>145</v>
       </c>
       <c r="G33" s="3">
-        <v>278.5</v>
+        <v>287.5</v>
       </c>
       <c r="H33" s="5">
-        <v>287</v>
+        <v>296</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -9687,36 +9687,36 @@
         <v>505</v>
       </c>
       <c r="C34" s="3">
-        <v>571</v>
+        <v>2245</v>
       </c>
       <c r="D34" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G34" s="3">
-        <v>362.5</v>
-      </c>
-      <c r="H34" s="5">
-        <v>373.5</v>
+        <v>60.5</v>
+      </c>
+      <c r="H34" s="3">
+        <v>62.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C35" s="3">
-        <v>2245</v>
+        <v>3754</v>
       </c>
       <c r="D35" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>30</v>
@@ -9725,35 +9725,9 @@
         <v>11</v>
       </c>
       <c r="G35" s="3">
-        <v>75.5</v>
-      </c>
-      <c r="H35" s="3">
-        <v>78</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
-      <c r="A36" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="C36" s="3">
-        <v>3754</v>
-      </c>
-      <c r="D36" s="3">
-        <v>3</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="3">
         <v>450</v>
       </c>
-      <c r="H36" s="5">
+      <c r="H35" s="5">
         <v>463.5</v>
       </c>
     </row>
@@ -21043,7 +21017,7 @@
     <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21069,7 +21043,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
         <v>904</v>
       </c>
@@ -21095,7 +21069,7 @@
         <v>461.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
         <v>904</v>
       </c>
@@ -21121,7 +21095,7 @@
         <v>117.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>906</v>
       </c>
@@ -21147,7 +21121,7 @@
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>908</v>
       </c>
@@ -21173,7 +21147,7 @@
         <v>391.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>908</v>
       </c>
@@ -21199,7 +21173,7 @@
         <v>196</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>908</v>
       </c>
@@ -21225,7 +21199,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>910</v>
       </c>
@@ -21251,7 +21225,7 @@
         <v>978.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>910</v>
       </c>
@@ -21277,7 +21251,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>912</v>
       </c>
@@ -21303,7 +21277,7 @@
         <v>309</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>912</v>
       </c>
@@ -21329,7 +21303,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>914</v>
       </c>
@@ -21355,7 +21329,7 @@
         <v>329.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>914</v>
       </c>
@@ -21381,7 +21355,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>916</v>
       </c>
@@ -21407,7 +21381,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>916</v>
       </c>
@@ -21433,7 +21407,7 @@
         <v>175</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>918</v>
       </c>
@@ -21459,7 +21433,7 @@
         <v>232</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>918</v>
       </c>
@@ -21485,7 +21459,7 @@
         <v>15.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>920</v>
       </c>
@@ -21511,7 +21485,7 @@
         <v>350</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>920</v>
       </c>
@@ -21537,7 +21511,7 @@
         <v>54</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>922</v>
       </c>
@@ -21563,7 +21537,7 @@
         <v>546</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>922</v>
       </c>
@@ -21589,7 +21563,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>924</v>
       </c>
@@ -21615,7 +21589,7 @@
         <v>93</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>926</v>
       </c>
@@ -21641,7 +21615,7 @@
         <v>309</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>926</v>
       </c>
@@ -21667,7 +21641,7 @@
         <v>20.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>928</v>
       </c>
@@ -24846,7 +24820,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -25867,10 +25841,10 @@
         <v>145</v>
       </c>
       <c r="G39" s="3">
-        <v>360</v>
+        <v>280</v>
       </c>
       <c r="H39" s="3">
-        <v>372</v>
+        <v>288.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
@@ -25893,10 +25867,10 @@
         <v>11</v>
       </c>
       <c r="G40" s="3">
-        <v>62</v>
+        <v>49.5</v>
       </c>
       <c r="H40" s="3">
-        <v>64</v>
+        <v>51</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -26595,10 +26569,10 @@
         <v>145</v>
       </c>
       <c r="G67" s="3">
-        <v>285</v>
+        <v>225</v>
       </c>
       <c r="H67" s="5">
-        <v>293.5</v>
+        <v>231.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
@@ -26609,48 +26583,48 @@
         <v>807</v>
       </c>
       <c r="C68" s="3">
-        <v>3740</v>
+        <v>2469</v>
       </c>
       <c r="D68" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G68" s="5">
-        <v>237.5</v>
-      </c>
-      <c r="H68" s="5">
-        <v>244.5</v>
+        <v>40.5</v>
+      </c>
+      <c r="H68" s="3">
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C69" s="3">
-        <v>2469</v>
+        <v>3006</v>
       </c>
       <c r="D69" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="G69" s="5">
-        <v>49.5</v>
+        <v>312.5</v>
       </c>
       <c r="H69" s="3">
-        <v>51</v>
+        <v>322</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
@@ -26661,48 +26635,48 @@
         <v>809</v>
       </c>
       <c r="C70" s="3">
-        <v>3006</v>
+        <v>3007</v>
       </c>
       <c r="D70" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G70" s="5">
-        <v>312.5</v>
-      </c>
-      <c r="H70" s="3">
-        <v>322</v>
+        <v>64.5</v>
+      </c>
+      <c r="H70" s="5">
+        <v>66.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C71" s="3">
-        <v>3007</v>
+        <v>117</v>
       </c>
       <c r="D71" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G71" s="5">
-        <v>64.5</v>
-      </c>
-      <c r="H71" s="5">
-        <v>66.5</v>
+        <v>145</v>
+      </c>
+      <c r="G71" s="3">
+        <v>300</v>
+      </c>
+      <c r="H71" s="3">
+        <v>309</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
@@ -26713,48 +26687,48 @@
         <v>811</v>
       </c>
       <c r="C72" s="3">
-        <v>117</v>
+        <v>2320</v>
       </c>
       <c r="D72" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G72" s="3">
-        <v>300</v>
+        <v>62</v>
       </c>
       <c r="H72" s="3">
-        <v>309</v>
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="4" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C73" s="3">
-        <v>2320</v>
+        <v>60</v>
       </c>
       <c r="D73" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="G73" s="3">
-        <v>62</v>
-      </c>
-      <c r="H73" s="3">
-        <v>64</v>
+        <v>180</v>
+      </c>
+      <c r="H73" s="5">
+        <v>185.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
@@ -26765,48 +26739,48 @@
         <v>813</v>
       </c>
       <c r="C74" s="3">
-        <v>60</v>
+        <v>2321</v>
       </c>
       <c r="D74" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G74" s="3">
-        <v>180</v>
-      </c>
-      <c r="H74" s="5">
-        <v>185.5</v>
+        <v>38</v>
+      </c>
+      <c r="H74" s="3">
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="4" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C75" s="3">
-        <v>2321</v>
-      </c>
-      <c r="D75" s="3">
-        <v>5</v>
+        <v>211</v>
+      </c>
+      <c r="D75" s="5">
+        <v>22.68</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" s="3">
-        <v>38</v>
+        <v>145</v>
+      </c>
+      <c r="G75" s="5">
+        <v>187.5</v>
       </c>
       <c r="H75" s="3">
-        <v>39</v>
+        <v>193</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
@@ -26817,10 +26791,10 @@
         <v>815</v>
       </c>
       <c r="C76" s="3">
-        <v>211</v>
+        <v>41</v>
       </c>
       <c r="D76" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>30</v>
@@ -26828,11 +26802,11 @@
       <c r="F76" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="G76" s="5">
-        <v>187.5</v>
-      </c>
-      <c r="H76" s="3">
-        <v>193</v>
+      <c r="G76" s="3">
+        <v>375</v>
+      </c>
+      <c r="H76" s="5">
+        <v>386.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -26843,48 +26817,48 @@
         <v>815</v>
       </c>
       <c r="C77" s="3">
-        <v>41</v>
-      </c>
-      <c r="D77" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D77" s="3">
+        <v>5</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="G77" s="3">
-        <v>375</v>
+        <v>11</v>
+      </c>
+      <c r="G77" s="5">
+        <v>43.5</v>
       </c>
       <c r="H77" s="5">
-        <v>386.5</v>
+        <v>44.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="4" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C78" s="3">
-        <v>2322</v>
-      </c>
-      <c r="D78" s="3">
-        <v>5</v>
+        <v>67</v>
+      </c>
+      <c r="D78" s="5">
+        <v>45.36</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" s="5">
-        <v>43.5</v>
-      </c>
-      <c r="H78" s="5">
-        <v>44.5</v>
+        <v>145</v>
+      </c>
+      <c r="G78" s="3">
+        <v>626</v>
+      </c>
+      <c r="H78" s="3">
+        <v>645</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
@@ -26895,10 +26869,10 @@
         <v>817</v>
       </c>
       <c r="C79" s="3">
-        <v>67</v>
+        <v>2244</v>
       </c>
       <c r="D79" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>30</v>
@@ -26907,10 +26881,10 @@
         <v>145</v>
       </c>
       <c r="G79" s="3">
-        <v>626</v>
-      </c>
-      <c r="H79" s="3">
-        <v>645</v>
+        <v>313</v>
+      </c>
+      <c r="H79" s="5">
+        <v>322.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
@@ -26921,74 +26895,74 @@
         <v>817</v>
       </c>
       <c r="C80" s="3">
-        <v>2244</v>
-      </c>
-      <c r="D80" s="5">
-        <v>22.68</v>
+        <v>2488</v>
+      </c>
+      <c r="D80" s="3">
+        <v>5</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G80" s="3">
-        <v>313</v>
-      </c>
-      <c r="H80" s="5">
-        <v>322.5</v>
+        <v>71</v>
+      </c>
+      <c r="H80" s="3">
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C81" s="3">
-        <v>2488</v>
+        <v>520</v>
       </c>
       <c r="D81" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="G81" s="3">
-        <v>71</v>
-      </c>
-      <c r="H81" s="3">
-        <v>73</v>
+        <v>52</v>
+      </c>
+      <c r="H81" s="5">
+        <v>53.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C82" s="3">
-        <v>520</v>
+        <v>4546</v>
       </c>
       <c r="D82" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G82" s="3">
-        <v>52</v>
+        <v>182</v>
       </c>
       <c r="H82" s="5">
-        <v>53.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
@@ -26999,22 +26973,22 @@
         <v>821</v>
       </c>
       <c r="C83" s="3">
-        <v>4546</v>
+        <v>3695</v>
       </c>
       <c r="D83" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="G83" s="3">
-        <v>182</v>
+        <v>350</v>
       </c>
       <c r="H83" s="5">
-        <v>187.5</v>
+        <v>360.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -27025,10 +26999,10 @@
         <v>821</v>
       </c>
       <c r="C84" s="3">
-        <v>3695</v>
+        <v>3097</v>
       </c>
       <c r="D84" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>30</v>
@@ -27037,10 +27011,10 @@
         <v>145</v>
       </c>
       <c r="G84" s="3">
-        <v>350</v>
-      </c>
-      <c r="H84" s="5">
-        <v>360.5</v>
+        <v>700</v>
+      </c>
+      <c r="H84" s="3">
+        <v>721</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -27051,62 +27025,62 @@
         <v>821</v>
       </c>
       <c r="C85" s="3">
-        <v>3097</v>
+        <v>2460</v>
       </c>
       <c r="D85" s="3">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G85" s="3">
-        <v>700</v>
-      </c>
-      <c r="H85" s="3">
-        <v>721</v>
+        <v>106</v>
+      </c>
+      <c r="H85" s="5">
+        <v>109.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C86" s="3">
-        <v>2460</v>
+        <v>3110</v>
       </c>
       <c r="D86" s="3">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>11</v>
+        <v>145</v>
       </c>
       <c r="G86" s="3">
-        <v>106</v>
+        <v>87</v>
       </c>
       <c r="H86" s="5">
-        <v>109.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C87" s="3">
-        <v>3110</v>
-      </c>
-      <c r="D87" s="3">
-        <v>25</v>
+        <v>135</v>
+      </c>
+      <c r="D87" s="5">
+        <v>22.68</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>30</v>
@@ -27115,24 +27089,24 @@
         <v>145</v>
       </c>
       <c r="G87" s="3">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H87" s="5">
-        <v>89.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C88" s="3">
-        <v>135</v>
-      </c>
-      <c r="D88" s="5">
-        <v>22.68</v>
+        <v>2463</v>
+      </c>
+      <c r="D88" s="3">
+        <v>5</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
@@ -27141,24 +27115,24 @@
         <v>145</v>
       </c>
       <c r="G88" s="3">
-        <v>85</v>
+        <v>21</v>
       </c>
       <c r="H88" s="5">
-        <v>87.5</v>
+        <v>21.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>826</v>
+        <v>828</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="C89" s="3">
-        <v>2463</v>
+        <v>55</v>
       </c>
       <c r="D89" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
@@ -27167,10 +27141,10 @@
         <v>145</v>
       </c>
       <c r="G89" s="3">
-        <v>21</v>
-      </c>
-      <c r="H89" s="5">
-        <v>21.5</v>
+        <v>114</v>
+      </c>
+      <c r="H89" s="3">
+        <v>118</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -27181,10 +27155,10 @@
         <v>829</v>
       </c>
       <c r="C90" s="3">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D90" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
@@ -27193,10 +27167,10 @@
         <v>145</v>
       </c>
       <c r="G90" s="3">
-        <v>114</v>
+        <v>27</v>
       </c>
       <c r="H90" s="3">
-        <v>118</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -27207,10 +27181,10 @@
         <v>829</v>
       </c>
       <c r="C91" s="3">
-        <v>51</v>
+        <v>201</v>
       </c>
       <c r="D91" s="3">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>30</v>
@@ -27219,24 +27193,24 @@
         <v>145</v>
       </c>
       <c r="G91" s="3">
-        <v>27</v>
+        <v>228</v>
       </c>
       <c r="H91" s="3">
-        <v>28</v>
+        <v>235</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="C92" s="3">
-        <v>201</v>
+        <v>4223</v>
       </c>
       <c r="D92" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>30</v>
@@ -27245,10 +27219,10 @@
         <v>145</v>
       </c>
       <c r="G92" s="3">
-        <v>228</v>
+        <v>125</v>
       </c>
       <c r="H92" s="3">
-        <v>235</v>
+        <v>129</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
@@ -27259,47 +27233,21 @@
         <v>831</v>
       </c>
       <c r="C93" s="3">
-        <v>4223</v>
+        <v>4224</v>
       </c>
       <c r="D93" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="G93" s="3">
-        <v>125</v>
+        <v>27</v>
       </c>
       <c r="H93" s="3">
-        <v>129</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
-      <c r="A94" s="4" t="s">
-        <v>830</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>831</v>
-      </c>
-      <c r="C94" s="3">
-        <v>4224</v>
-      </c>
-      <c r="D94" s="3">
-        <v>5</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="3">
-        <v>27</v>
-      </c>
-      <c r="H94" s="3">
         <v>28</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -3379,7 +3379,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3397,6 +3397,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3474,10 +3480,10 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -6103,10 +6109,10 @@
         <v>16</v>
       </c>
       <c r="G35" s="3">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="H35" s="3">
-        <v>198</v>
+        <v>215.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
@@ -9061,10 +9067,10 @@
         <v>11</v>
       </c>
       <c r="G9" s="3">
-        <v>147</v>
+        <v>108.5</v>
       </c>
       <c r="H9" s="5">
-        <v>151.5</v>
+        <v>112</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
@@ -9087,10 +9093,10 @@
         <v>147</v>
       </c>
       <c r="G10" s="3">
-        <v>725</v>
+        <v>525</v>
       </c>
       <c r="H10" s="3">
-        <v>747</v>
+        <v>540.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3379,7 +3379,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3397,12 +3397,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3454,7 +3448,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3479,12 +3473,6 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3800,8 +3788,8 @@
     <col min="4" max="4" style="7" width="10.719285714285713" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.719285714285713" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="8.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -5202,7 +5190,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -5881,7 +5869,7 @@
         <v>247</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
         <v>568</v>
       </c>
@@ -5907,7 +5895,7 @@
         <v>125.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4" t="s">
         <v>570</v>
       </c>
@@ -5933,7 +5921,7 @@
         <v>358.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4" t="s">
         <v>570</v>
       </c>
@@ -5959,7 +5947,7 @@
         <v>30</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="4" t="s">
         <v>572</v>
       </c>
@@ -5985,7 +5973,7 @@
         <v>80</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="4" t="s">
         <v>572</v>
       </c>
@@ -6011,7 +5999,7 @@
         <v>32</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="4" t="s">
         <v>574</v>
       </c>
@@ -6037,7 +6025,7 @@
         <v>116</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
         <v>576</v>
       </c>
@@ -6063,7 +6051,7 @@
         <v>125.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
         <v>578</v>
       </c>
@@ -6089,7 +6077,7 @@
         <v>88.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
         <v>580</v>
       </c>
@@ -8836,7 +8824,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -9639,10 +9627,10 @@
         <v>147</v>
       </c>
       <c r="G31" s="3">
-        <v>1550</v>
+        <v>1875</v>
       </c>
       <c r="H31" s="3">
-        <v>1596.5</v>
+        <v>1931</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -9665,10 +9653,10 @@
         <v>147</v>
       </c>
       <c r="G32" s="3">
-        <v>313.5</v>
+        <v>378.5</v>
       </c>
       <c r="H32" s="5">
-        <v>323</v>
+        <v>390</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -9769,7 +9757,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="20.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="20.862142857142857" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -12834,7 +12822,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -13116,8 +13104,8 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -13605,7 +13593,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -16923,10 +16911,10 @@
     <col min="1" max="1" style="6" width="28.862142857142857" customWidth="1" bestFit="1"/>
     <col min="2" max="2" style="6" width="32.86214285714286" customWidth="1" bestFit="1"/>
     <col min="3" max="3" style="7" width="6.862142857142857" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="11" width="10.719285714285713" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="9" width="10.719285714285713" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="13.719285714285713" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="8.290714285714287" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="12.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="12.43357142857143" customWidth="1" bestFit="1"/>
     <col min="8" max="8" style="7" width="20.433571428571426" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
@@ -17223,10 +17211,10 @@
       <c r="B12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="3">
         <v>2205</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="5">
         <v>2.5</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -17235,10 +17223,10 @@
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="10">
+      <c r="G12" s="5">
         <v>126</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="3">
         <v>130</v>
       </c>
     </row>
@@ -17920,8 +17908,8 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -20336,7 +20324,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -21058,7 +21046,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
@@ -23005,7 +22993,7 @@
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
     <col min="7" max="7" style="7" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
@@ -25885,10 +25873,10 @@
         <v>147</v>
       </c>
       <c r="G39" s="3">
-        <v>280</v>
+        <v>320</v>
       </c>
       <c r="H39" s="3">
-        <v>288.5</v>
+        <v>329.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
@@ -25911,10 +25899,10 @@
         <v>11</v>
       </c>
       <c r="G40" s="3">
-        <v>49.5</v>
+        <v>56.5</v>
       </c>
       <c r="H40" s="3">
-        <v>51</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
@@ -25937,10 +25925,10 @@
         <v>11</v>
       </c>
       <c r="G41" s="5">
-        <v>24.5</v>
+        <v>30.5</v>
       </c>
       <c r="H41" s="3">
-        <v>25</v>
+        <v>31.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
@@ -25963,10 +25951,10 @@
         <v>147</v>
       </c>
       <c r="G42" s="3">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="H42" s="3">
-        <v>139</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
@@ -25989,10 +25977,10 @@
         <v>147</v>
       </c>
       <c r="G43" s="3">
-        <v>270</v>
+        <v>330</v>
       </c>
       <c r="H43" s="3">
-        <v>278</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
@@ -27314,8 +27302,8 @@
     <col min="4" max="4" style="7" width="15.005" customWidth="1" bestFit="1"/>
     <col min="5" max="5" style="6" width="15.005" customWidth="1" bestFit="1"/>
     <col min="6" max="6" style="6" width="12.005" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="11" width="15.005" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="9" width="15.005" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3776" uniqueCount="1113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3764" uniqueCount="1114">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3372,6 +3372,9 @@
   </si>
   <si>
     <t>XEREM DE AMENDOIM</t>
+  </si>
+  <si>
+    <t/>
   </si>
 </sst>
 </file>
@@ -3448,7 +3451,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3476,6 +3479,15 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3779,7 +3791,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H53"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="15.290714285714287" customWidth="1" bestFit="1"/>
@@ -3846,28 +3858,28 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>1054</v>
+        <v>1046</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1055</v>
+        <v>1047</v>
       </c>
       <c r="C3" s="3">
-        <v>103</v>
+        <v>2419</v>
       </c>
       <c r="D3" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G3" s="5">
-        <v>215</v>
+        <v>34.5</v>
       </c>
       <c r="H3" s="5">
-        <v>221.5</v>
+        <v>35.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
@@ -3898,403 +3910,403 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>248</v>
+        <v>1034</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>249</v>
+        <v>1035</v>
       </c>
       <c r="C5" s="3">
-        <v>3974</v>
+        <v>3821</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="5">
-        <v>63</v>
-      </c>
-      <c r="H5" s="5">
-        <v>65</v>
+        <v>147</v>
+      </c>
+      <c r="G5" s="3">
+        <v>140</v>
+      </c>
+      <c r="H5" s="3">
+        <v>144</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>250</v>
+        <v>1034</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>251</v>
+        <v>1035</v>
       </c>
       <c r="C6" s="3">
-        <v>3530</v>
-      </c>
-      <c r="D6" s="3">
-        <v>2</v>
+        <v>2263</v>
+      </c>
+      <c r="D6" s="5">
+        <v>12.5</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="5">
-        <v>63</v>
-      </c>
-      <c r="H6" s="5">
-        <v>65</v>
+        <v>147</v>
+      </c>
+      <c r="G6" s="3">
+        <v>70</v>
+      </c>
+      <c r="H6" s="3">
+        <v>72</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>252</v>
+        <v>854</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="C7" s="3">
-        <v>4282</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
+        <v>855</v>
+      </c>
+      <c r="C7" s="10">
+        <v>564</v>
+      </c>
+      <c r="D7" s="10">
+        <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G7" s="5">
-        <v>55</v>
-      </c>
-      <c r="H7" s="5">
-        <v>56.5</v>
+        <v>147</v>
+      </c>
+      <c r="G7" s="11">
+        <v>118</v>
+      </c>
+      <c r="H7" s="11">
+        <v>121.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>254</v>
+        <v>854</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="C8" s="3">
-        <v>3870</v>
-      </c>
-      <c r="D8" s="3">
-        <v>500</v>
+        <v>855</v>
+      </c>
+      <c r="C8" s="10">
+        <v>2256</v>
+      </c>
+      <c r="D8" s="10">
+        <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="5">
-        <v>22</v>
-      </c>
-      <c r="H8" s="5">
-        <v>22.5</v>
+      <c r="G8" s="11">
+        <v>16</v>
+      </c>
+      <c r="H8" s="11">
+        <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>256</v>
+        <v>878</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="C9" s="3">
-        <v>3701</v>
-      </c>
-      <c r="D9" s="3">
-        <v>500</v>
+        <v>879</v>
+      </c>
+      <c r="C9" s="10">
+        <v>261</v>
+      </c>
+      <c r="D9" s="10">
+        <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="5">
-        <v>22</v>
-      </c>
-      <c r="H9" s="5">
-        <v>22.5</v>
+        <v>147</v>
+      </c>
+      <c r="G9" s="11">
+        <v>83</v>
+      </c>
+      <c r="H9" s="11">
+        <v>85.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>258</v>
+        <v>878</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="C10" s="3">
-        <v>3800</v>
-      </c>
-      <c r="D10" s="3">
-        <v>500</v>
+        <v>879</v>
+      </c>
+      <c r="C10" s="10">
+        <v>2475</v>
+      </c>
+      <c r="D10" s="10">
+        <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="5">
-        <v>22</v>
-      </c>
-      <c r="H10" s="5">
-        <v>22.5</v>
+      <c r="G10" s="11">
+        <v>18.5</v>
+      </c>
+      <c r="H10" s="11">
+        <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>260</v>
+        <v>880</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="3">
-        <v>3725</v>
-      </c>
-      <c r="D11" s="3">
-        <v>500</v>
+        <v>881</v>
+      </c>
+      <c r="C11" s="10">
+        <v>92</v>
+      </c>
+      <c r="D11" s="10">
+        <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G11" s="5">
-        <v>22</v>
-      </c>
-      <c r="H11" s="5">
-        <v>22.5</v>
+        <v>147</v>
+      </c>
+      <c r="G11" s="11">
+        <v>67</v>
+      </c>
+      <c r="H11" s="11">
+        <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>262</v>
+        <v>880</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="C12" s="3">
-        <v>3871</v>
-      </c>
-      <c r="D12" s="3">
-        <v>500</v>
+        <v>881</v>
+      </c>
+      <c r="C12" s="10">
+        <v>2476</v>
+      </c>
+      <c r="D12" s="10">
+        <v>3</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>243</v>
+        <v>30</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="5">
-        <v>27</v>
-      </c>
-      <c r="H12" s="5">
-        <v>29</v>
+      <c r="G12" s="11">
+        <v>11.5</v>
+      </c>
+      <c r="H12" s="11">
+        <v>12</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>1050</v>
+        <v>700</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1051</v>
-      </c>
-      <c r="C13" s="3">
-        <v>2283</v>
-      </c>
-      <c r="D13" s="3">
-        <v>5</v>
+        <v>701</v>
+      </c>
+      <c r="C13" s="10">
+        <v>27</v>
+      </c>
+      <c r="D13" s="10">
+        <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13" s="5">
-        <v>61</v>
-      </c>
-      <c r="H13" s="5">
-        <v>63</v>
+        <v>147</v>
+      </c>
+      <c r="G13" s="11">
+        <v>110</v>
+      </c>
+      <c r="H13" s="11">
+        <v>113.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>1052</v>
+        <v>702</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1053</v>
-      </c>
-      <c r="C14" s="3">
-        <v>4255</v>
-      </c>
-      <c r="D14" s="3">
-        <v>5</v>
+        <v>703</v>
+      </c>
+      <c r="C14" s="10">
+        <v>2255</v>
+      </c>
+      <c r="D14" s="10">
+        <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" s="5">
-        <v>64</v>
-      </c>
-      <c r="H14" s="5">
-        <v>66</v>
+        <v>147</v>
+      </c>
+      <c r="G14" s="11">
+        <v>99</v>
+      </c>
+      <c r="H14" s="11">
+        <v>102</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>1080</v>
+        <v>530</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3081</v>
-      </c>
-      <c r="D15" s="3">
-        <v>10</v>
+        <v>531</v>
+      </c>
+      <c r="C15" s="10">
+        <v>2350</v>
+      </c>
+      <c r="D15" s="10">
+        <v>5</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G15" s="5">
-        <v>145</v>
-      </c>
-      <c r="H15" s="5">
-        <v>149.5</v>
+        <v>16</v>
+      </c>
+      <c r="G15" s="11">
+        <v>250</v>
+      </c>
+      <c r="H15" s="11">
+        <v>258</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>1080</v>
+        <v>538</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1081</v>
-      </c>
-      <c r="C16" s="3">
-        <v>3818</v>
-      </c>
-      <c r="D16" s="3">
-        <v>5</v>
+        <v>539</v>
+      </c>
+      <c r="C16" s="10">
+        <v>2229</v>
+      </c>
+      <c r="D16" s="10">
+        <v>10</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G16" s="5">
-        <v>75.5</v>
-      </c>
-      <c r="H16" s="5">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="G16" s="11">
+        <v>175</v>
+      </c>
+      <c r="H16" s="11">
+        <v>180</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>1082</v>
+        <v>504</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1083</v>
+        <v>505</v>
       </c>
       <c r="C17" s="3">
-        <v>2534</v>
+        <v>4400</v>
       </c>
       <c r="D17" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G17" s="5">
-        <v>145</v>
-      </c>
-      <c r="H17" s="5">
-        <v>78</v>
+        <v>147</v>
+      </c>
+      <c r="G17" s="3">
+        <v>1875</v>
+      </c>
+      <c r="H17" s="3">
+        <v>1931</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
-        <v>1082</v>
+        <v>504</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1083</v>
+        <v>505</v>
       </c>
       <c r="C18" s="3">
-        <v>2234</v>
+        <v>2676</v>
       </c>
       <c r="D18" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G18" s="5">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="G18" s="3">
+        <v>378.5</v>
       </c>
       <c r="H18" s="5">
-        <v>149.5</v>
+        <v>390</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
-        <v>1084</v>
+        <v>506</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1085</v>
+        <v>507</v>
       </c>
       <c r="C19" s="3">
-        <v>2238</v>
+        <v>571</v>
       </c>
       <c r="D19" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G19" s="5">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="G19" s="3">
+        <v>287.5</v>
       </c>
       <c r="H19" s="5">
-        <v>149.5</v>
+        <v>296</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>1084</v>
+        <v>506</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1086</v>
+        <v>507</v>
       </c>
       <c r="C20" s="3">
-        <v>2535</v>
+        <v>2245</v>
       </c>
       <c r="D20" s="3">
         <v>5</v>
@@ -4305,25 +4317,25 @@
       <c r="F20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="5">
-        <v>75.5</v>
-      </c>
-      <c r="H20" s="5">
-        <v>78</v>
+      <c r="G20" s="3">
+        <v>60.5</v>
+      </c>
+      <c r="H20" s="3">
+        <v>62.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>1089</v>
+        <v>332</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1090</v>
+        <v>333</v>
       </c>
       <c r="C21" s="3">
-        <v>2236</v>
+        <v>2259</v>
       </c>
       <c r="D21" s="3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>30</v>
@@ -4332,24 +4344,24 @@
         <v>11</v>
       </c>
       <c r="G21" s="5">
-        <v>145</v>
-      </c>
-      <c r="H21" s="5">
-        <v>149.5</v>
+        <v>16</v>
+      </c>
+      <c r="H21" s="3">
+        <v>16.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>1089</v>
+        <v>336</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1090</v>
+        <v>337</v>
       </c>
       <c r="C22" s="3">
-        <v>2546</v>
+        <v>2422</v>
       </c>
       <c r="D22" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>30</v>
@@ -4358,154 +4370,154 @@
         <v>11</v>
       </c>
       <c r="G22" s="5">
-        <v>75.5</v>
-      </c>
-      <c r="H22" s="5">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="H22" s="3">
+        <v>16.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>1091</v>
+        <v>336</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1092</v>
+        <v>337</v>
       </c>
       <c r="C23" s="3">
-        <v>2232</v>
+        <v>569</v>
       </c>
       <c r="D23" s="3">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23" s="5">
-        <v>145</v>
+        <v>147</v>
+      </c>
+      <c r="G23" s="3">
+        <v>118</v>
       </c>
       <c r="H23" s="5">
-        <v>149.5</v>
+        <v>121.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>1091</v>
+        <v>332</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1092</v>
+        <v>333</v>
       </c>
       <c r="C24" s="3">
-        <v>2536</v>
+        <v>282</v>
       </c>
       <c r="D24" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24" s="5">
-        <v>75.5</v>
+        <v>147</v>
+      </c>
+      <c r="G24" s="3">
+        <v>118</v>
       </c>
       <c r="H24" s="5">
-        <v>78</v>
+        <v>121.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>1056</v>
+        <v>69</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C25" s="3">
-        <v>2452</v>
-      </c>
-      <c r="D25" s="3">
-        <v>10</v>
+        <v>70</v>
+      </c>
+      <c r="C25" s="10">
+        <v>3438</v>
+      </c>
+      <c r="D25" s="10">
+        <v>15</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G25" s="5">
-        <v>76</v>
-      </c>
-      <c r="H25" s="5">
-        <v>78</v>
+        <v>16</v>
+      </c>
+      <c r="G25" s="11">
+        <v>228</v>
+      </c>
+      <c r="H25" s="11">
+        <v>235</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>1056</v>
+        <v>69</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C26" s="3">
-        <v>150</v>
-      </c>
-      <c r="D26" s="3">
-        <v>25</v>
+        <v>70</v>
+      </c>
+      <c r="C26" s="10">
+        <v>3434</v>
+      </c>
+      <c r="D26" s="10">
+        <v>5</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G26" s="5">
-        <v>190</v>
-      </c>
-      <c r="H26" s="5">
-        <v>196</v>
+        <v>11</v>
+      </c>
+      <c r="G26" s="11">
+        <v>76</v>
+      </c>
+      <c r="H26" s="11">
+        <v>78.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>1056</v>
+        <v>80</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1057</v>
-      </c>
-      <c r="C27" s="3">
-        <v>2453</v>
-      </c>
-      <c r="D27" s="3">
-        <v>5</v>
+        <v>81</v>
+      </c>
+      <c r="C27" s="10">
+        <v>3123</v>
+      </c>
+      <c r="D27" s="10">
+        <v>10</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G27" s="5">
-        <v>41</v>
-      </c>
-      <c r="H27" s="5">
-        <v>42</v>
+        <v>16</v>
+      </c>
+      <c r="G27" s="11">
+        <v>121</v>
+      </c>
+      <c r="H27" s="11">
+        <v>125</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>1058</v>
+        <v>80</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C28" s="3">
-        <v>2450</v>
-      </c>
-      <c r="D28" s="3">
-        <v>10</v>
+        <v>81</v>
+      </c>
+      <c r="C28" s="10">
+        <v>2674</v>
+      </c>
+      <c r="D28" s="10">
+        <v>5</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>30</v>
@@ -4513,50 +4525,50 @@
       <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="5">
-        <v>76</v>
-      </c>
-      <c r="H28" s="5">
-        <v>78</v>
+      <c r="G28" s="11">
+        <v>60.5</v>
+      </c>
+      <c r="H28" s="11">
+        <v>62</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>1058</v>
+        <v>97</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C29" s="3">
-        <v>7</v>
-      </c>
-      <c r="D29" s="3">
-        <v>25</v>
+        <v>98</v>
+      </c>
+      <c r="C29" s="10">
+        <v>3124</v>
+      </c>
+      <c r="D29" s="10">
+        <v>10</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G29" s="5">
-        <v>190</v>
-      </c>
-      <c r="H29" s="5">
-        <v>196</v>
+        <v>16</v>
+      </c>
+      <c r="G29" s="11">
+        <v>161</v>
+      </c>
+      <c r="H29" s="11">
+        <v>166</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>1058</v>
+        <v>97</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1059</v>
-      </c>
-      <c r="C30" s="3">
-        <v>2451</v>
-      </c>
-      <c r="D30" s="3">
+        <v>98</v>
+      </c>
+      <c r="C30" s="10">
+        <v>2824</v>
+      </c>
+      <c r="D30" s="10">
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
@@ -4565,50 +4577,50 @@
       <c r="F30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="5">
-        <v>41</v>
-      </c>
-      <c r="H30" s="5">
-        <v>42</v>
+      <c r="G30" s="11">
+        <v>80.5</v>
+      </c>
+      <c r="H30" s="11">
+        <v>83</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>1038</v>
+        <v>99</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C31" s="3">
-        <v>2643</v>
-      </c>
-      <c r="D31" s="3">
-        <v>5</v>
+        <v>100</v>
+      </c>
+      <c r="C31" s="10">
+        <v>3130</v>
+      </c>
+      <c r="D31" s="10">
+        <v>10</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G31" s="5">
-        <v>68</v>
-      </c>
-      <c r="H31" s="5">
-        <v>70</v>
+        <v>16</v>
+      </c>
+      <c r="G31" s="11">
+        <v>138</v>
+      </c>
+      <c r="H31" s="11">
+        <v>142</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>1040</v>
+        <v>99</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1041</v>
-      </c>
-      <c r="C32" s="3">
-        <v>2644</v>
-      </c>
-      <c r="D32" s="3">
+        <v>100</v>
+      </c>
+      <c r="C32" s="10">
+        <v>3131</v>
+      </c>
+      <c r="D32" s="10">
         <v>5</v>
       </c>
       <c r="E32" s="4" t="s">
@@ -4617,558 +4629,336 @@
       <c r="F32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="5">
-        <v>70</v>
-      </c>
-      <c r="H32" s="5">
-        <v>72</v>
+      <c r="G32" s="11">
+        <v>69</v>
+      </c>
+      <c r="H32" s="11">
+        <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="4" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>1043</v>
-      </c>
-      <c r="C33" s="3">
-        <v>2570</v>
-      </c>
-      <c r="D33" s="3">
-        <v>5</v>
-      </c>
-      <c r="E33" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G33" s="5">
-        <v>57</v>
-      </c>
-      <c r="H33" s="5">
-        <v>59</v>
-      </c>
+      <c r="A33" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C33" s="3"/>
+      <c r="D33" s="3"/>
+      <c r="E33" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F33" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="4" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C34" s="3">
-        <v>3021</v>
-      </c>
-      <c r="D34" s="3">
-        <v>5</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G34" s="5">
-        <v>63</v>
-      </c>
-      <c r="H34" s="5">
-        <v>65</v>
-      </c>
+      <c r="A34" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C34" s="3"/>
+      <c r="D34" s="3"/>
+      <c r="E34" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F34" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="C35" s="3">
-        <v>2825</v>
-      </c>
-      <c r="D35" s="3">
-        <v>2</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G35" s="5">
-        <v>25</v>
-      </c>
-      <c r="H35" s="5">
-        <v>26</v>
-      </c>
+      <c r="A35" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C35" s="3"/>
+      <c r="D35" s="3"/>
+      <c r="E35" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F35" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="C36" s="3">
-        <v>2828</v>
-      </c>
-      <c r="D36" s="3">
-        <v>2</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G36" s="5">
-        <v>25</v>
-      </c>
-      <c r="H36" s="5">
-        <v>26</v>
-      </c>
+      <c r="A36" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C36" s="3"/>
+      <c r="D36" s="3"/>
+      <c r="E36" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F36" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="C37" s="3">
-        <v>2826</v>
-      </c>
-      <c r="D37" s="3">
-        <v>2</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G37" s="5">
-        <v>25</v>
-      </c>
-      <c r="H37" s="5">
-        <v>26</v>
-      </c>
+      <c r="A37" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C37" s="3"/>
+      <c r="D37" s="3"/>
+      <c r="E37" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F37" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="C38" s="3">
-        <v>3058</v>
-      </c>
-      <c r="D38" s="3">
-        <v>2</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="5">
-        <v>25</v>
-      </c>
-      <c r="H38" s="5">
-        <v>26</v>
-      </c>
+      <c r="A38" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C38" s="3"/>
+      <c r="D38" s="3"/>
+      <c r="E38" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="C39" s="3">
-        <v>3059</v>
-      </c>
-      <c r="D39" s="3">
-        <v>2</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="5">
-        <v>25</v>
-      </c>
-      <c r="H39" s="5">
-        <v>26</v>
-      </c>
+      <c r="A39" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C39" s="3"/>
+      <c r="D39" s="3"/>
+      <c r="E39" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="C40" s="3">
-        <v>2829</v>
-      </c>
-      <c r="D40" s="3">
-        <v>2</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G40" s="5">
-        <v>25</v>
-      </c>
-      <c r="H40" s="5">
-        <v>26</v>
-      </c>
+      <c r="A40" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C40" s="3"/>
+      <c r="D40" s="3"/>
+      <c r="E40" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F40" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="C41" s="3">
-        <v>4126</v>
-      </c>
-      <c r="D41" s="3">
-        <v>2</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G41" s="5">
-        <v>25</v>
-      </c>
-      <c r="H41" s="5">
-        <v>26</v>
-      </c>
+      <c r="A41" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C41" s="3"/>
+      <c r="D41" s="3"/>
+      <c r="E41" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F41" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C42" s="3">
-        <v>2827</v>
-      </c>
-      <c r="D42" s="3">
-        <v>2</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G42" s="5">
-        <v>25</v>
-      </c>
-      <c r="H42" s="5">
-        <v>26</v>
-      </c>
+      <c r="A42" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C42" s="3"/>
+      <c r="D42" s="3"/>
+      <c r="E42" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F42" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>281</v>
-      </c>
-      <c r="C43" s="3">
-        <v>3801</v>
-      </c>
-      <c r="D43" s="3">
-        <v>500</v>
-      </c>
-      <c r="E43" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="F43" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G43" s="5">
-        <v>25</v>
-      </c>
-      <c r="H43" s="5">
-        <v>26</v>
-      </c>
+      <c r="A43" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C43" s="3"/>
+      <c r="D43" s="3"/>
+      <c r="E43" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F43" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="C44" s="3">
-        <v>3897</v>
-      </c>
-      <c r="D44" s="3">
-        <v>2</v>
-      </c>
-      <c r="E44" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="5">
-        <v>60</v>
-      </c>
-      <c r="H44" s="5">
-        <v>62</v>
-      </c>
+      <c r="A44" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F44" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="C45" s="3">
-        <v>3764</v>
-      </c>
-      <c r="D45" s="3">
-        <v>2</v>
-      </c>
-      <c r="E45" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F45" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G45" s="5">
-        <v>81</v>
-      </c>
-      <c r="H45" s="5">
-        <v>83.5</v>
-      </c>
+      <c r="A45" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F45" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C46" s="3">
-        <v>3402</v>
-      </c>
-      <c r="D46" s="3">
-        <v>6</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G46" s="5">
-        <v>46.5</v>
-      </c>
-      <c r="H46" s="5">
-        <v>47.5</v>
-      </c>
+      <c r="A46" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C47" s="3">
-        <v>3401</v>
-      </c>
-      <c r="D47" s="3">
-        <v>6</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G47" s="5">
-        <v>66.5</v>
-      </c>
-      <c r="H47" s="5">
-        <v>68.5</v>
-      </c>
+      <c r="A47" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B47" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C47" s="3"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F47" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="C48" s="3">
-        <v>3403</v>
-      </c>
-      <c r="D48" s="3">
-        <v>12</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G48" s="5">
-        <v>38.5</v>
-      </c>
-      <c r="H48" s="5">
-        <v>39.5</v>
-      </c>
+      <c r="A48" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B48" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F48" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="C49" s="3">
-        <v>4032</v>
-      </c>
-      <c r="D49" s="3">
-        <v>12</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G49" s="5">
-        <v>57.5</v>
-      </c>
-      <c r="H49" s="5">
-        <v>59</v>
-      </c>
+      <c r="A49" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B49" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C49" s="3"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F49" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="C50" s="3">
-        <v>4460</v>
-      </c>
-      <c r="D50" s="3">
-        <v>12</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G50" s="5">
-        <v>57.5</v>
-      </c>
-      <c r="H50" s="5">
-        <v>59</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
-      <c r="A51" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="C51" s="3">
-        <v>2551</v>
-      </c>
-      <c r="D51" s="3">
-        <v>12</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G51" s="5">
-        <v>82</v>
-      </c>
-      <c r="H51" s="5">
-        <v>84.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
-      <c r="A52" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="C52" s="3">
-        <v>2550</v>
-      </c>
-      <c r="D52" s="3">
-        <v>6</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="F52" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G52" s="5">
-        <v>25.5</v>
-      </c>
-      <c r="H52" s="5">
-        <v>26.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
-      <c r="A53" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="C53" s="3">
-        <v>4383</v>
-      </c>
-      <c r="D53" s="3">
-        <v>12</v>
-      </c>
-      <c r="E53" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="F53" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G53" s="5">
-        <v>53</v>
-      </c>
-      <c r="H53" s="5">
-        <v>54.5</v>
-      </c>
+      <c r="A50" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="B50" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F50" s="12" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -25671,7 +25461,7 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="4" t="s">
         <v>778</v>
       </c>
@@ -25697,7 +25487,7 @@
         <v>278</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
         <v>778</v>
       </c>
@@ -25723,7 +25513,7 @@
         <v>48.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
         <v>780</v>
       </c>
@@ -25749,7 +25539,7 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
         <v>780</v>
       </c>
@@ -25775,7 +25565,7 @@
         <v>324.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4" t="s">
         <v>782</v>
       </c>
@@ -25801,7 +25591,7 @@
         <v>366.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="4" t="s">
         <v>782</v>
       </c>
@@ -25827,7 +25617,7 @@
         <v>183.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="4" t="s">
         <v>782</v>
       </c>
@@ -25853,7 +25643,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="4" t="s">
         <v>784</v>
       </c>
@@ -25879,7 +25669,7 @@
         <v>329.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="4" t="s">
         <v>784</v>
       </c>
@@ -25905,7 +25695,7 @@
         <v>58</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="4" t="s">
         <v>786</v>
       </c>
@@ -25931,7 +25721,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="4" t="s">
         <v>786</v>
       </c>
@@ -25957,7 +25747,7 @@
         <v>170</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="4" t="s">
         <v>786</v>
       </c>
@@ -25983,7 +25773,7 @@
         <v>340</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="4" t="s">
         <v>788</v>
       </c>
@@ -26009,7 +25799,7 @@
         <v>127</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="4" t="s">
         <v>788</v>
       </c>
@@ -26035,7 +25825,7 @@
         <v>105.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="4" t="s">
         <v>788</v>
       </c>
@@ -26061,7 +25851,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="4" t="s">
         <v>790</v>
       </c>
@@ -26087,7 +25877,7 @@
         <v>206</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
         <v>790</v>
       </c>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3764" uniqueCount="1114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="1115">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -2369,6 +2369,12 @@
     <t>FEIJÃO ANDU</t>
   </si>
   <si>
+    <t>feijao-andu-paulista</t>
+  </si>
+  <si>
+    <t>FEIJÃO ANDU PAULISTA</t>
+  </si>
+  <si>
     <t>feijo-azuki</t>
   </si>
   <si>
@@ -3372,9 +3378,6 @@
   </si>
   <si>
     <t>XEREM DE AMENDOIM</t>
-  </si>
-  <si>
-    <t/>
   </si>
 </sst>
 </file>
@@ -3382,7 +3385,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3400,6 +3403,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3483,11 +3492,11 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="general"/>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3832,10 +3841,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C2" s="3">
         <v>109</v>
@@ -3858,10 +3867,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C3" s="3">
         <v>2419</v>
@@ -3884,10 +3893,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>825</v>
+        <v>827</v>
       </c>
       <c r="C4" s="3">
         <v>3110</v>
@@ -3910,10 +3919,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C5" s="3">
         <v>3821</v>
@@ -3936,10 +3945,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C6" s="3">
         <v>2263</v>
@@ -3962,15 +3971,15 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="C7" s="10">
+        <v>857</v>
+      </c>
+      <c r="C7" s="11">
         <v>564</v>
       </c>
-      <c r="D7" s="10">
+      <c r="D7" s="11">
         <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -3979,24 +3988,24 @@
       <c r="F7" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="11">
+      <c r="G7" s="12">
         <v>118</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="12">
         <v>121.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="C8" s="10">
+        <v>857</v>
+      </c>
+      <c r="C8" s="11">
         <v>2256</v>
       </c>
-      <c r="D8" s="10">
+      <c r="D8" s="11">
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -4005,24 +4014,24 @@
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="11">
+      <c r="G8" s="12">
         <v>16</v>
       </c>
-      <c r="H8" s="11">
+      <c r="H8" s="12">
         <v>17</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>879</v>
-      </c>
-      <c r="C9" s="10">
+        <v>881</v>
+      </c>
+      <c r="C9" s="11">
         <v>261</v>
       </c>
-      <c r="D9" s="10">
+      <c r="D9" s="11">
         <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -4031,24 +4040,24 @@
       <c r="F9" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="12">
         <v>83</v>
       </c>
-      <c r="H9" s="11">
+      <c r="H9" s="12">
         <v>85.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>879</v>
-      </c>
-      <c r="C10" s="10">
+        <v>881</v>
+      </c>
+      <c r="C10" s="11">
         <v>2475</v>
       </c>
-      <c r="D10" s="10">
+      <c r="D10" s="11">
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -4057,24 +4066,24 @@
       <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="11">
+      <c r="G10" s="12">
         <v>18.5</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="12">
         <v>19</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>881</v>
-      </c>
-      <c r="C11" s="10">
+        <v>883</v>
+      </c>
+      <c r="C11" s="11">
         <v>92</v>
       </c>
-      <c r="D11" s="10">
+      <c r="D11" s="11">
         <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -4083,24 +4092,24 @@
       <c r="F11" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="11">
+      <c r="G11" s="12">
         <v>67</v>
       </c>
-      <c r="H11" s="11">
+      <c r="H11" s="12">
         <v>69</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>881</v>
-      </c>
-      <c r="C12" s="10">
+        <v>883</v>
+      </c>
+      <c r="C12" s="11">
         <v>2476</v>
       </c>
-      <c r="D12" s="10">
+      <c r="D12" s="11">
         <v>3</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -4109,10 +4118,10 @@
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="11">
+      <c r="G12" s="12">
         <v>11.5</v>
       </c>
-      <c r="H12" s="11">
+      <c r="H12" s="12">
         <v>12</v>
       </c>
     </row>
@@ -4123,10 +4132,10 @@
       <c r="B13" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="C13" s="10">
+      <c r="C13" s="11">
         <v>27</v>
       </c>
-      <c r="D13" s="10">
+      <c r="D13" s="11">
         <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -4135,10 +4144,10 @@
       <c r="F13" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="11">
+      <c r="G13" s="12">
         <v>110</v>
       </c>
-      <c r="H13" s="11">
+      <c r="H13" s="12">
         <v>113.5</v>
       </c>
     </row>
@@ -4149,10 +4158,10 @@
       <c r="B14" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="C14" s="10">
+      <c r="C14" s="11">
         <v>2255</v>
       </c>
-      <c r="D14" s="10">
+      <c r="D14" s="11">
         <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -4161,10 +4170,10 @@
       <c r="F14" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G14" s="11">
+      <c r="G14" s="12">
         <v>99</v>
       </c>
-      <c r="H14" s="11">
+      <c r="H14" s="12">
         <v>102</v>
       </c>
     </row>
@@ -4175,10 +4184,10 @@
       <c r="B15" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="C15" s="10">
+      <c r="C15" s="11">
         <v>2350</v>
       </c>
-      <c r="D15" s="10">
+      <c r="D15" s="11">
         <v>5</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -4187,10 +4196,10 @@
       <c r="F15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="11">
+      <c r="G15" s="12">
         <v>250</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="12">
         <v>258</v>
       </c>
     </row>
@@ -4201,10 +4210,10 @@
       <c r="B16" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="11">
         <v>2229</v>
       </c>
-      <c r="D16" s="10">
+      <c r="D16" s="11">
         <v>10</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -4213,10 +4222,10 @@
       <c r="F16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="11">
+      <c r="G16" s="12">
         <v>175</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="12">
         <v>180</v>
       </c>
     </row>
@@ -4435,10 +4444,10 @@
       <c r="B25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="10">
+      <c r="C25" s="11">
         <v>3438</v>
       </c>
-      <c r="D25" s="10">
+      <c r="D25" s="11">
         <v>15</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -4447,10 +4456,10 @@
       <c r="F25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="11">
+      <c r="G25" s="12">
         <v>228</v>
       </c>
-      <c r="H25" s="11">
+      <c r="H25" s="12">
         <v>235</v>
       </c>
     </row>
@@ -4461,10 +4470,10 @@
       <c r="B26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="10">
+      <c r="C26" s="11">
         <v>3434</v>
       </c>
-      <c r="D26" s="10">
+      <c r="D26" s="11">
         <v>5</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -4473,10 +4482,10 @@
       <c r="F26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="11">
+      <c r="G26" s="12">
         <v>76</v>
       </c>
-      <c r="H26" s="11">
+      <c r="H26" s="12">
         <v>78.5</v>
       </c>
     </row>
@@ -4487,10 +4496,10 @@
       <c r="B27" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="10">
+      <c r="C27" s="11">
         <v>3123</v>
       </c>
-      <c r="D27" s="10">
+      <c r="D27" s="11">
         <v>10</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -4499,10 +4508,10 @@
       <c r="F27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="11">
+      <c r="G27" s="12">
         <v>121</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="12">
         <v>125</v>
       </c>
     </row>
@@ -4513,10 +4522,10 @@
       <c r="B28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="10">
+      <c r="C28" s="11">
         <v>2674</v>
       </c>
-      <c r="D28" s="10">
+      <c r="D28" s="11">
         <v>5</v>
       </c>
       <c r="E28" s="4" t="s">
@@ -4525,10 +4534,10 @@
       <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="11">
+      <c r="G28" s="12">
         <v>60.5</v>
       </c>
-      <c r="H28" s="11">
+      <c r="H28" s="12">
         <v>62</v>
       </c>
     </row>
@@ -4539,10 +4548,10 @@
       <c r="B29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="11">
         <v>3124</v>
       </c>
-      <c r="D29" s="10">
+      <c r="D29" s="11">
         <v>10</v>
       </c>
       <c r="E29" s="4" t="s">
@@ -4551,10 +4560,10 @@
       <c r="F29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="11">
+      <c r="G29" s="12">
         <v>161</v>
       </c>
-      <c r="H29" s="11">
+      <c r="H29" s="12">
         <v>166</v>
       </c>
     </row>
@@ -4565,10 +4574,10 @@
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="10">
+      <c r="C30" s="11">
         <v>2824</v>
       </c>
-      <c r="D30" s="10">
+      <c r="D30" s="11">
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
@@ -4577,10 +4586,10 @@
       <c r="F30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="11">
+      <c r="G30" s="12">
         <v>80.5</v>
       </c>
-      <c r="H30" s="11">
+      <c r="H30" s="12">
         <v>83</v>
       </c>
     </row>
@@ -4591,10 +4600,10 @@
       <c r="B31" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="10">
+      <c r="C31" s="11">
         <v>3130</v>
       </c>
-      <c r="D31" s="10">
+      <c r="D31" s="11">
         <v>10</v>
       </c>
       <c r="E31" s="4" t="s">
@@ -4603,10 +4612,10 @@
       <c r="F31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="11">
+      <c r="G31" s="12">
         <v>138</v>
       </c>
-      <c r="H31" s="11">
+      <c r="H31" s="12">
         <v>142</v>
       </c>
     </row>
@@ -4617,10 +4626,10 @@
       <c r="B32" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="10">
+      <c r="C32" s="11">
         <v>3131</v>
       </c>
-      <c r="D32" s="10">
+      <c r="D32" s="11">
         <v>5</v>
       </c>
       <c r="E32" s="4" t="s">
@@ -4629,334 +4638,190 @@
       <c r="F32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="11">
+      <c r="G32" s="12">
         <v>69</v>
       </c>
-      <c r="H32" s="11">
+      <c r="H32" s="12">
         <v>71</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
-      <c r="A33" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B33" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A33" s="4"/>
+      <c r="B33" s="4"/>
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
-      <c r="E33" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F33" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E33" s="4"/>
+      <c r="F33" s="4"/>
       <c r="G33" s="5"/>
       <c r="H33" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
-      <c r="A34" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B34" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A34" s="4"/>
+      <c r="B34" s="4"/>
       <c r="C34" s="3"/>
       <c r="D34" s="3"/>
-      <c r="E34" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
-      <c r="A35" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B35" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A35" s="4"/>
+      <c r="B35" s="4"/>
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
-      <c r="E35" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F35" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
-      <c r="A36" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B36" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A36" s="4"/>
+      <c r="B36" s="4"/>
       <c r="C36" s="3"/>
       <c r="D36" s="3"/>
-      <c r="E36" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F36" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
-      <c r="A37" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B37" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A37" s="4"/>
+      <c r="B37" s="4"/>
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
-      <c r="E37" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F37" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
-      <c r="A38" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A38" s="4"/>
+      <c r="B38" s="4"/>
       <c r="C38" s="3"/>
       <c r="D38" s="3"/>
-      <c r="E38" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E38" s="4"/>
+      <c r="F38" s="4"/>
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
-      <c r="A39" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B39" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A39" s="4"/>
+      <c r="B39" s="4"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
-      <c r="E39" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F39" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E39" s="4"/>
+      <c r="F39" s="4"/>
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
-      <c r="A40" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
       <c r="C40" s="3"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
-      <c r="A41" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B41" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A41" s="4"/>
+      <c r="B41" s="4"/>
       <c r="C41" s="3"/>
       <c r="D41" s="3"/>
-      <c r="E41" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F41" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E41" s="4"/>
+      <c r="F41" s="4"/>
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
-      <c r="A42" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A42" s="4"/>
+      <c r="B42" s="4"/>
       <c r="C42" s="3"/>
       <c r="D42" s="3"/>
-      <c r="E42" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E42" s="4"/>
+      <c r="F42" s="4"/>
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
-      <c r="A43" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A43" s="4"/>
+      <c r="B43" s="4"/>
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
-      <c r="E43" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F43" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E43" s="4"/>
+      <c r="F43" s="4"/>
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
-      <c r="A44" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A44" s="4"/>
+      <c r="B44" s="4"/>
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
-      <c r="E44" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
-      <c r="A45" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A45" s="4"/>
+      <c r="B45" s="4"/>
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
-      <c r="E45" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E45" s="4"/>
+      <c r="F45" s="4"/>
       <c r="G45" s="5"/>
       <c r="H45" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
-      <c r="A46" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A46" s="4"/>
+      <c r="B46" s="4"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
-      <c r="E46" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F46" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E46" s="4"/>
+      <c r="F46" s="4"/>
       <c r="G46" s="5"/>
       <c r="H46" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
-      <c r="A47" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E47" s="4"/>
+      <c r="F47" s="4"/>
       <c r="G47" s="5"/>
       <c r="H47" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
-      <c r="A48" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B48" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A48" s="4"/>
+      <c r="B48" s="4"/>
       <c r="C48" s="3"/>
       <c r="D48" s="3"/>
-      <c r="E48" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E48" s="4"/>
+      <c r="F48" s="4"/>
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
-      <c r="A49" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A49" s="4"/>
+      <c r="B49" s="4"/>
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
-      <c r="E49" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F49" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E49" s="4"/>
+      <c r="F49" s="4"/>
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="B50" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="A50" s="4"/>
+      <c r="B50" s="4"/>
       <c r="C50" s="3"/>
       <c r="D50" s="3"/>
-      <c r="E50" s="12" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>1113</v>
-      </c>
+      <c r="E50" s="4"/>
+      <c r="F50" s="4"/>
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
     </row>
@@ -8432,10 +8297,10 @@
         <v>16</v>
       </c>
       <c r="G17" s="3">
-        <v>455</v>
+        <v>850</v>
       </c>
       <c r="H17" s="5">
-        <v>468.5</v>
+        <v>875.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
@@ -8458,10 +8323,10 @@
         <v>11</v>
       </c>
       <c r="G18" s="5">
-        <v>227.5</v>
+        <v>425</v>
       </c>
       <c r="H18" s="5">
-        <v>234.5</v>
+        <v>437.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
@@ -9105,10 +8970,10 @@
         <v>11</v>
       </c>
       <c r="G19" s="5">
-        <v>197.5</v>
+        <v>202.5</v>
       </c>
       <c r="H19" s="3">
-        <v>204</v>
+        <v>208.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
@@ -9131,10 +8996,10 @@
         <v>16</v>
       </c>
       <c r="G20" s="3">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="H20" s="3">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
@@ -17730,10 +17595,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>1012</v>
+        <v>1014</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1013</v>
+        <v>1015</v>
       </c>
       <c r="C2" s="3">
         <v>585</v>
@@ -17756,10 +17621,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>1014</v>
+        <v>1016</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1015</v>
+        <v>1017</v>
       </c>
       <c r="C3" s="3">
         <v>467</v>
@@ -17782,10 +17647,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C4" s="3">
         <v>3391</v>
@@ -17808,10 +17673,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>1016</v>
+        <v>1018</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1017</v>
+        <v>1019</v>
       </c>
       <c r="C5" s="3">
         <v>3399</v>
@@ -17834,10 +17699,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C6" s="3">
         <v>2405</v>
@@ -17860,10 +17725,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>1018</v>
+        <v>1020</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1019</v>
+        <v>1021</v>
       </c>
       <c r="C7" s="3">
         <v>2444</v>
@@ -17886,10 +17751,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C8" s="3">
         <v>3390</v>
@@ -17912,10 +17777,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>1020</v>
+        <v>1022</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1021</v>
+        <v>1023</v>
       </c>
       <c r="C9" s="3">
         <v>3404</v>
@@ -17938,10 +17803,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C10" s="3">
         <v>3105</v>
@@ -17964,10 +17829,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>1022</v>
+        <v>1024</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="C11" s="3">
         <v>2445</v>
@@ -17990,10 +17855,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C12" s="3">
         <v>2446</v>
@@ -18016,10 +17881,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="C13" s="3">
         <v>2781</v>
@@ -18042,10 +17907,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C14" s="3">
         <v>3463</v>
@@ -18068,10 +17933,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="C15" s="3">
         <v>3367</v>
@@ -18094,10 +17959,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C16" s="3">
         <v>3464</v>
@@ -18120,10 +17985,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="C17" s="3">
         <v>3368</v>
@@ -18146,10 +18011,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C18" s="3">
         <v>3465</v>
@@ -18172,10 +18037,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
-        <v>1030</v>
+        <v>1032</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1031</v>
+        <v>1033</v>
       </c>
       <c r="C19" s="3">
         <v>3372</v>
@@ -18198,10 +18063,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C20" s="3">
         <v>3466</v>
@@ -18224,10 +18089,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>1032</v>
+        <v>1034</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1033</v>
+        <v>1035</v>
       </c>
       <c r="C21" s="3">
         <v>3380</v>
@@ -18250,10 +18115,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C22" s="3">
         <v>3821</v>
@@ -18276,10 +18141,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1035</v>
+        <v>1037</v>
       </c>
       <c r="C23" s="3">
         <v>2263</v>
@@ -18302,10 +18167,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="C24" s="3">
         <v>465</v>
@@ -18328,10 +18193,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C25" s="3">
         <v>2643</v>
@@ -18354,10 +18219,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C26" s="3">
         <v>2644</v>
@@ -18380,10 +18245,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C27" s="3">
         <v>2570</v>
@@ -18406,10 +18271,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C28" s="3">
         <v>3021</v>
@@ -18432,10 +18297,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C29" s="3">
         <v>109</v>
@@ -18458,10 +18323,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C30" s="3">
         <v>2419</v>
@@ -18484,10 +18349,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C31" s="3">
         <v>3505</v>
@@ -18510,10 +18375,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="C32" s="3">
         <v>2443</v>
@@ -18536,10 +18401,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C33" s="3">
         <v>2283</v>
@@ -18562,10 +18427,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="C34" s="3">
         <v>4255</v>
@@ -18588,10 +18453,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C35" s="3">
         <v>103</v>
@@ -18614,10 +18479,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C36" s="3">
         <v>2629</v>
@@ -18640,10 +18505,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C37" s="3">
         <v>2452</v>
@@ -18666,10 +18531,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C38" s="3">
         <v>150</v>
@@ -18692,10 +18557,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C39" s="3">
         <v>2453</v>
@@ -18718,10 +18583,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C40" s="3">
         <v>2450</v>
@@ -18744,10 +18609,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C41" s="3">
         <v>7</v>
@@ -18770,10 +18635,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="C42" s="3">
         <v>2451</v>
@@ -18796,10 +18661,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C43" s="3">
         <v>468</v>
@@ -18822,10 +18687,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="C44" s="3">
         <v>4138</v>
@@ -18848,10 +18713,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="C45" s="3">
         <v>2508</v>
@@ -18874,10 +18739,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C46" s="3">
         <v>2442</v>
@@ -18900,10 +18765,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C47" s="3">
         <v>2524</v>
@@ -18926,10 +18791,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C48" s="3">
         <v>3441</v>
@@ -18952,10 +18817,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="C49" s="3">
         <v>2523</v>
@@ -18978,10 +18843,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C50" s="3">
         <v>3408</v>
@@ -19004,10 +18869,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C51" s="3">
         <v>2273</v>
@@ -19030,10 +18895,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="C52" s="3">
         <v>2271</v>
@@ -19056,10 +18921,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C53" s="3">
         <v>3409</v>
@@ -19082,10 +18947,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C54" s="3">
         <v>459</v>
@@ -19108,10 +18973,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="C55" s="3">
         <v>285</v>
@@ -19134,10 +18999,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C56" s="3">
         <v>2291</v>
@@ -19160,10 +19025,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="C57" s="3">
         <v>2252</v>
@@ -19186,10 +19051,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C58" s="3">
         <v>3534</v>
@@ -19212,10 +19077,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="C59" s="3">
         <v>2250</v>
@@ -19238,10 +19103,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C60" s="3">
         <v>2340</v>
@@ -19264,10 +19129,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="C61" s="3">
         <v>3533</v>
@@ -19290,10 +19155,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C62" s="3">
         <v>3532</v>
@@ -19316,10 +19181,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="C63" s="3">
         <v>2251</v>
@@ -19342,10 +19207,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C64" s="3">
         <v>3081</v>
@@ -19368,10 +19233,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="C65" s="3">
         <v>3818</v>
@@ -19394,10 +19259,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C66" s="3">
         <v>2534</v>
@@ -19420,10 +19285,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="C67" s="3">
         <v>2234</v>
@@ -19446,10 +19311,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="C68" s="3">
         <v>2238</v>
@@ -19472,10 +19337,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C69" s="3">
         <v>2535</v>
@@ -19498,10 +19363,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C70" s="3">
         <v>2512</v>
@@ -19524,10 +19389,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C71" s="3">
         <v>2537</v>
@@ -19550,10 +19415,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C72" s="3">
         <v>2236</v>
@@ -19576,10 +19441,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="4" t="s">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C73" s="3">
         <v>2546</v>
@@ -19602,10 +19467,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C74" s="3">
         <v>2232</v>
@@ -19628,10 +19493,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="4" t="s">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C75" s="3">
         <v>2536</v>
@@ -19654,10 +19519,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="4" t="s">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="C76" s="3">
         <v>3815</v>
@@ -19680,10 +19545,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="4" t="s">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C77" s="3">
         <v>3713</v>
@@ -19706,10 +19571,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="4" t="s">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C78" s="3">
         <v>3712</v>
@@ -19732,10 +19597,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="4" t="s">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="C79" s="3">
         <v>3714</v>
@@ -19758,10 +19623,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="4" t="s">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="C80" s="3">
         <v>3715</v>
@@ -19784,10 +19649,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C81" s="3">
         <v>4021</v>
@@ -19810,10 +19675,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="C82" s="3">
         <v>4135</v>
@@ -19836,10 +19701,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C83" s="3">
         <v>2852</v>
@@ -19862,10 +19727,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="C84" s="3">
         <v>3601</v>
@@ -19888,10 +19753,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C85" s="3">
         <v>3093</v>
@@ -19914,10 +19779,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C86" s="3">
         <v>263</v>
@@ -19940,10 +19805,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C87" s="3">
         <v>2632</v>
@@ -19966,10 +19831,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C88" s="3">
         <v>2330</v>
@@ -19992,10 +19857,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C89" s="3">
         <v>2385</v>
@@ -20018,10 +19883,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C90" s="3">
         <v>2384</v>
@@ -20044,10 +19909,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C91" s="3">
         <v>3851</v>
@@ -20070,10 +19935,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C92" s="3">
         <v>2424</v>
@@ -20145,10 +20010,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C2" s="3">
         <v>85</v>
@@ -20171,10 +20036,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>996</v>
+        <v>998</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>997</v>
+        <v>999</v>
       </c>
       <c r="C3" s="3">
         <v>2447</v>
@@ -20197,10 +20062,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C4" s="3">
         <v>551</v>
@@ -20223,10 +20088,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>998</v>
+        <v>1000</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>999</v>
+        <v>1001</v>
       </c>
       <c r="C5" s="3">
         <v>2448</v>
@@ -20249,10 +20114,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C6" s="3">
         <v>3559</v>
@@ -20275,10 +20140,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>1000</v>
+        <v>1002</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1001</v>
+        <v>1003</v>
       </c>
       <c r="C7" s="3">
         <v>3560</v>
@@ -20301,10 +20166,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C8" s="3">
         <v>255</v>
@@ -20327,10 +20192,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>1002</v>
+        <v>1004</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="C9" s="3">
         <v>2456</v>
@@ -20353,10 +20218,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C10" s="3">
         <v>80</v>
@@ -20379,10 +20244,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>1004</v>
+        <v>1006</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1005</v>
+        <v>1007</v>
       </c>
       <c r="C11" s="3">
         <v>2457</v>
@@ -20405,10 +20270,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C12" s="3">
         <v>94</v>
@@ -20431,10 +20296,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>1006</v>
+        <v>1008</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1007</v>
+        <v>1009</v>
       </c>
       <c r="C13" s="3">
         <v>2458</v>
@@ -20457,10 +20322,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C14" s="3">
         <v>2454</v>
@@ -20483,10 +20348,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1009</v>
+        <v>1011</v>
       </c>
       <c r="C15" s="3">
         <v>2455</v>
@@ -20509,10 +20374,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C16" s="3">
         <v>450</v>
@@ -20535,10 +20400,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>1010</v>
+        <v>1012</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1011</v>
+        <v>1013</v>
       </c>
       <c r="C17" s="3">
         <v>2459</v>
@@ -20610,10 +20475,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>980</v>
+        <v>982</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>981</v>
+        <v>983</v>
       </c>
       <c r="C2" s="3">
         <v>2314</v>
@@ -20636,10 +20501,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>982</v>
+        <v>984</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>983</v>
+        <v>985</v>
       </c>
       <c r="C3" s="3">
         <v>2313</v>
@@ -20662,10 +20527,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>984</v>
+        <v>986</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="C4" s="3">
         <v>2316</v>
@@ -20688,10 +20553,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>986</v>
+        <v>988</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>987</v>
+        <v>989</v>
       </c>
       <c r="C5" s="3">
         <v>2312</v>
@@ -20714,10 +20579,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>988</v>
+        <v>990</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>989</v>
+        <v>991</v>
       </c>
       <c r="C6" s="3">
         <v>3513</v>
@@ -20740,10 +20605,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>990</v>
+        <v>992</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>991</v>
+        <v>993</v>
       </c>
       <c r="C7" s="3">
         <v>2315</v>
@@ -20766,10 +20631,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>992</v>
+        <v>994</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>993</v>
+        <v>995</v>
       </c>
       <c r="C8" s="3">
         <v>3512</v>
@@ -20792,10 +20657,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>994</v>
+        <v>996</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>995</v>
+        <v>997</v>
       </c>
       <c r="C9" s="3">
         <v>2311</v>
@@ -20867,10 +20732,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C2" s="3">
         <v>3440</v>
@@ -20893,10 +20758,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
-        <v>906</v>
+        <v>908</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>907</v>
+        <v>909</v>
       </c>
       <c r="C3" s="3">
         <v>2832</v>
@@ -20919,10 +20784,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
-        <v>908</v>
+        <v>910</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>909</v>
+        <v>911</v>
       </c>
       <c r="C4" s="3">
         <v>4337</v>
@@ -20945,10 +20810,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C5" s="3">
         <v>3045</v>
@@ -20971,10 +20836,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C6" s="3">
         <v>4376</v>
@@ -20997,10 +20862,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
-        <v>910</v>
+        <v>912</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>911</v>
+        <v>913</v>
       </c>
       <c r="C7" s="3">
         <v>2625</v>
@@ -21023,10 +20888,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C8" s="3">
         <v>2717</v>
@@ -21049,10 +20914,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
-        <v>912</v>
+        <v>914</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>913</v>
+        <v>915</v>
       </c>
       <c r="C9" s="3">
         <v>2573</v>
@@ -21075,10 +20940,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C10" s="3">
         <v>2504</v>
@@ -21101,10 +20966,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
-        <v>914</v>
+        <v>916</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>915</v>
+        <v>917</v>
       </c>
       <c r="C11" s="3">
         <v>2505</v>
@@ -21127,10 +20992,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C12" s="3">
         <v>3043</v>
@@ -21153,10 +21018,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
-        <v>916</v>
+        <v>918</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>917</v>
+        <v>919</v>
       </c>
       <c r="C13" s="3">
         <v>2557</v>
@@ -21179,10 +21044,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C14" s="3">
         <v>2540</v>
@@ -21205,10 +21070,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
-        <v>918</v>
+        <v>920</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>919</v>
+        <v>921</v>
       </c>
       <c r="C15" s="3">
         <v>3503</v>
@@ -21231,10 +21096,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C16" s="3">
         <v>2691</v>
@@ -21257,10 +21122,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
-        <v>920</v>
+        <v>922</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>921</v>
+        <v>923</v>
       </c>
       <c r="C17" s="3">
         <v>2692</v>
@@ -21283,10 +21148,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C18" s="3">
         <v>3484</v>
@@ -21309,10 +21174,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
-        <v>922</v>
+        <v>924</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>923</v>
+        <v>925</v>
       </c>
       <c r="C19" s="3">
         <v>3485</v>
@@ -21335,10 +21200,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C20" s="3">
         <v>3976</v>
@@ -21361,10 +21226,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
-        <v>924</v>
+        <v>926</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>925</v>
+        <v>927</v>
       </c>
       <c r="C21" s="3">
         <v>2780</v>
@@ -21387,10 +21252,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
-        <v>926</v>
+        <v>928</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>927</v>
+        <v>929</v>
       </c>
       <c r="C22" s="3">
         <v>3406</v>
@@ -21413,10 +21278,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C23" s="3">
         <v>3040</v>
@@ -21439,10 +21304,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
-        <v>928</v>
+        <v>930</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>929</v>
+        <v>931</v>
       </c>
       <c r="C24" s="3">
         <v>3041</v>
@@ -21465,10 +21330,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C25" s="3">
         <v>2741</v>
@@ -21491,10 +21356,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>930</v>
+        <v>932</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>931</v>
+        <v>933</v>
       </c>
       <c r="C26" s="3">
         <v>2559</v>
@@ -21517,10 +21382,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C27" s="3">
         <v>2526</v>
@@ -21543,10 +21408,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>932</v>
+        <v>934</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>933</v>
+        <v>935</v>
       </c>
       <c r="C28" s="3">
         <v>2527</v>
@@ -21569,10 +21434,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>934</v>
+        <v>936</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>935</v>
+        <v>937</v>
       </c>
       <c r="C29" s="3">
         <v>3063</v>
@@ -21595,10 +21460,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C30" s="3">
         <v>4251</v>
@@ -21621,10 +21486,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>936</v>
+        <v>938</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>937</v>
+        <v>939</v>
       </c>
       <c r="C31" s="3">
         <v>4250</v>
@@ -21647,10 +21512,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C32" s="3">
         <v>2739</v>
@@ -21673,10 +21538,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>938</v>
+        <v>940</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>939</v>
+        <v>941</v>
       </c>
       <c r="C33" s="3">
         <v>2560</v>
@@ -21699,10 +21564,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C34" s="3">
         <v>2742</v>
@@ -21725,10 +21590,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>940</v>
+        <v>942</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>941</v>
+        <v>943</v>
       </c>
       <c r="C35" s="3">
         <v>2744</v>
@@ -21751,10 +21616,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C36" s="3">
         <v>4072</v>
@@ -21777,10 +21642,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>942</v>
+        <v>944</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>943</v>
+        <v>945</v>
       </c>
       <c r="C37" s="3">
         <v>4071</v>
@@ -21803,10 +21668,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C38" s="3">
         <v>2696</v>
@@ -21829,10 +21694,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>944</v>
+        <v>946</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>945</v>
+        <v>947</v>
       </c>
       <c r="C39" s="3">
         <v>2697</v>
@@ -21855,10 +21720,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C40" s="3">
         <v>3044</v>
@@ -21881,10 +21746,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>946</v>
+        <v>948</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>947</v>
+        <v>949</v>
       </c>
       <c r="C41" s="3">
         <v>2746</v>
@@ -21907,10 +21772,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>948</v>
+        <v>950</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>949</v>
+        <v>951</v>
       </c>
       <c r="C42" s="3">
         <v>2713</v>
@@ -21933,10 +21798,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C43" s="3">
         <v>3037</v>
@@ -21959,10 +21824,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>950</v>
+        <v>952</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>951</v>
+        <v>953</v>
       </c>
       <c r="C44" s="3">
         <v>3038</v>
@@ -21985,10 +21850,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C45" s="3">
         <v>2248</v>
@@ -22011,10 +21876,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>952</v>
+        <v>954</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>953</v>
+        <v>955</v>
       </c>
       <c r="C46" s="3">
         <v>2436</v>
@@ -22037,10 +21902,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C47" s="3">
         <v>2466</v>
@@ -22063,10 +21928,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>954</v>
+        <v>956</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>955</v>
+        <v>957</v>
       </c>
       <c r="C48" s="3">
         <v>2465</v>
@@ -22089,10 +21954,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C49" s="3">
         <v>4318</v>
@@ -22115,10 +21980,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>956</v>
+        <v>958</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>957</v>
+        <v>959</v>
       </c>
       <c r="C50" s="3">
         <v>4319</v>
@@ -22141,10 +22006,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C51" s="3">
         <v>4254</v>
@@ -22167,10 +22032,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>958</v>
+        <v>960</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>959</v>
+        <v>961</v>
       </c>
       <c r="C52" s="3">
         <v>2563</v>
@@ -22193,10 +22058,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C53" s="3">
         <v>2725</v>
@@ -22219,10 +22084,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>960</v>
+        <v>962</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>961</v>
+        <v>963</v>
       </c>
       <c r="C54" s="3">
         <v>2562</v>
@@ -22245,10 +22110,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C55" s="3">
         <v>2782</v>
@@ -22271,10 +22136,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>962</v>
+        <v>964</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>963</v>
+        <v>965</v>
       </c>
       <c r="C56" s="3">
         <v>2745</v>
@@ -22297,10 +22162,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C57" s="3">
         <v>4207</v>
@@ -22323,10 +22188,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>964</v>
+        <v>966</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>965</v>
+        <v>967</v>
       </c>
       <c r="C58" s="3">
         <v>3769</v>
@@ -22349,10 +22214,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C59" s="3">
         <v>3034</v>
@@ -22375,10 +22240,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>966</v>
+        <v>968</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>967</v>
+        <v>969</v>
       </c>
       <c r="C60" s="3">
         <v>3039</v>
@@ -22401,10 +22266,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C61" s="3">
         <v>3421</v>
@@ -22427,10 +22292,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C62" s="3">
         <v>2748</v>
@@ -22453,10 +22318,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>968</v>
+        <v>970</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>969</v>
+        <v>971</v>
       </c>
       <c r="C63" s="3">
         <v>2576</v>
@@ -22479,10 +22344,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>970</v>
+        <v>972</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="C64" s="3">
         <v>3032</v>
@@ -22505,10 +22370,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C65" s="3">
         <v>2740</v>
@@ -22531,10 +22396,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C66" s="3">
         <v>3098</v>
@@ -22557,10 +22422,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>972</v>
+        <v>974</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>973</v>
+        <v>975</v>
       </c>
       <c r="C67" s="3">
         <v>2743</v>
@@ -22583,10 +22448,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C68" s="3">
         <v>3360</v>
@@ -22609,10 +22474,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C69" s="3">
         <v>2611</v>
@@ -22635,10 +22500,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>974</v>
+        <v>976</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>975</v>
+        <v>977</v>
       </c>
       <c r="C70" s="3">
         <v>2558</v>
@@ -22661,10 +22526,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C71" s="3">
         <v>3042</v>
@@ -22687,10 +22552,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>976</v>
+        <v>978</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>977</v>
+        <v>979</v>
       </c>
       <c r="C72" s="3">
         <v>2561</v>
@@ -22713,10 +22578,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C73" s="3">
         <v>4226</v>
@@ -22739,10 +22604,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>979</v>
+        <v>981</v>
       </c>
       <c r="C74" s="3">
         <v>4227</v>
@@ -22814,10 +22679,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="C2" s="3">
         <v>4295</v>
@@ -22840,10 +22705,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C3" s="3">
         <v>203</v>
@@ -22866,10 +22731,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="C4" s="3">
         <v>2490</v>
@@ -22892,10 +22757,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="C5" s="3">
         <v>4552</v>
@@ -22918,10 +22783,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="C6" s="3">
         <v>3893</v>
@@ -22944,10 +22809,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C7" s="3">
         <v>2242</v>
@@ -22970,10 +22835,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="C8" s="3">
         <v>2518</v>
@@ -22996,10 +22861,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C9" s="3">
         <v>845</v>
@@ -23022,10 +22887,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>845</v>
+        <v>847</v>
       </c>
       <c r="C10" s="3">
         <v>2517</v>
@@ -23048,10 +22913,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C11" s="3">
         <v>2631</v>
@@ -23074,10 +22939,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="C12" s="3">
         <v>3088</v>
@@ -23100,10 +22965,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C13" s="3">
         <v>3850</v>
@@ -23126,10 +22991,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>848</v>
+        <v>850</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="C14" s="3">
         <v>2489</v>
@@ -23152,10 +23017,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C15" s="3">
         <v>2437</v>
@@ -23178,10 +23043,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C16" s="3">
         <v>582</v>
@@ -23204,10 +23069,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>850</v>
+        <v>852</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>851</v>
+        <v>853</v>
       </c>
       <c r="C17" s="3">
         <v>3415</v>
@@ -23230,10 +23095,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C18" s="3">
         <v>2485</v>
@@ -23256,10 +23121,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C19" s="3">
         <v>583</v>
@@ -23282,10 +23147,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>852</v>
+        <v>854</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>853</v>
+        <v>855</v>
       </c>
       <c r="C20" s="3">
         <v>3416</v>
@@ -23308,10 +23173,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C21" s="3">
         <v>564</v>
@@ -23334,10 +23199,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>854</v>
+        <v>856</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>855</v>
+        <v>857</v>
       </c>
       <c r="C22" s="3">
         <v>2256</v>
@@ -23360,10 +23225,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C23" s="3">
         <v>3398</v>
@@ -23386,10 +23251,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>856</v>
+        <v>858</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>857</v>
+        <v>859</v>
       </c>
       <c r="C24" s="3">
         <v>4025</v>
@@ -23412,10 +23277,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C25" s="3">
         <v>4162</v>
@@ -23438,10 +23303,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>858</v>
+        <v>860</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>859</v>
+        <v>861</v>
       </c>
       <c r="C26" s="3">
         <v>3424</v>
@@ -23464,10 +23329,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C27" s="3">
         <v>4161</v>
@@ -23490,10 +23355,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>860</v>
+        <v>862</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>861</v>
+        <v>863</v>
       </c>
       <c r="C28" s="3">
         <v>3718</v>
@@ -23516,10 +23381,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C29" s="3">
         <v>4277</v>
@@ -23542,10 +23407,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C30" s="3">
         <v>4163</v>
@@ -23568,10 +23433,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="C31" s="3">
         <v>4117</v>
@@ -23594,10 +23459,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C32" s="3">
         <v>3738</v>
@@ -23620,10 +23485,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>865</v>
+        <v>867</v>
       </c>
       <c r="C33" s="3">
         <v>4317</v>
@@ -23646,10 +23511,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C34" s="3">
         <v>2924</v>
@@ -23672,10 +23537,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>867</v>
+        <v>869</v>
       </c>
       <c r="C35" s="3">
         <v>3078</v>
@@ -23698,10 +23563,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C36" s="3">
         <v>2348</v>
@@ -23724,10 +23589,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>868</v>
+        <v>870</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>869</v>
+        <v>871</v>
       </c>
       <c r="C37" s="3">
         <v>2538</v>
@@ -23750,10 +23615,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C38" s="3">
         <v>2811</v>
@@ -23776,10 +23641,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>870</v>
+        <v>872</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>871</v>
+        <v>873</v>
       </c>
       <c r="C39" s="3">
         <v>2820</v>
@@ -23802,10 +23667,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C40" s="3">
         <v>3722</v>
@@ -23828,10 +23693,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="C41" s="3">
         <v>4050</v>
@@ -23854,10 +23719,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="C42" s="3">
         <v>415</v>
@@ -23880,10 +23745,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="C43" s="3">
         <v>93</v>
@@ -23906,10 +23771,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C44" s="3">
         <v>261</v>
@@ -23932,10 +23797,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="C45" s="3">
         <v>2475</v>
@@ -23958,10 +23823,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C46" s="3">
         <v>92</v>
@@ -23984,10 +23849,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="C47" s="3">
         <v>2476</v>
@@ -24010,10 +23875,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C48" s="3">
         <v>18</v>
@@ -24036,10 +23901,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="C49" s="3">
         <v>2477</v>
@@ -24062,10 +23927,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C50" s="3">
         <v>4164</v>
@@ -24088,10 +23953,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="C51" s="3">
         <v>3706</v>
@@ -24114,10 +23979,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C52" s="3">
         <v>19</v>
@@ -24140,10 +24005,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C53" s="3">
         <v>2246</v>
@@ -24166,10 +24031,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="C54" s="3">
         <v>575</v>
@@ -24192,10 +24057,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C55" s="3">
         <v>221</v>
@@ -24218,10 +24083,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C56" s="3">
         <v>258</v>
@@ -24244,10 +24109,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="C57" s="3">
         <v>20</v>
@@ -24270,10 +24135,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C58" s="3">
         <v>2520</v>
@@ -24296,10 +24161,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
       <c r="C59" s="3">
         <v>4089</v>
@@ -24322,10 +24187,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>892</v>
+        <v>894</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>893</v>
+        <v>895</v>
       </c>
       <c r="C60" s="3">
         <v>21</v>
@@ -24348,10 +24213,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C61" s="3">
         <v>262</v>
@@ -24374,10 +24239,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>894</v>
+        <v>896</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>895</v>
+        <v>897</v>
       </c>
       <c r="C62" s="3">
         <v>2513</v>
@@ -24400,10 +24265,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C63" s="3">
         <v>16</v>
@@ -24426,10 +24291,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>896</v>
+        <v>898</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>897</v>
+        <v>899</v>
       </c>
       <c r="C64" s="3">
         <v>3114</v>
@@ -24452,10 +24317,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>898</v>
+        <v>900</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>899</v>
+        <v>901</v>
       </c>
       <c r="C65" s="3">
         <v>4086</v>
@@ -24478,10 +24343,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C66" s="3">
         <v>15</v>
@@ -24504,10 +24369,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="C67" s="3">
         <v>3115</v>
@@ -24530,10 +24395,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C68" s="3">
         <v>4165</v>
@@ -24556,10 +24421,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>902</v>
+        <v>904</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>903</v>
+        <v>905</v>
       </c>
       <c r="C69" s="3">
         <v>4100</v>
@@ -24582,10 +24447,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C70" s="3">
         <v>4280</v>
@@ -24608,10 +24473,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>905</v>
+        <v>907</v>
       </c>
       <c r="C71" s="3">
         <v>4281</v>
@@ -24642,7 +24507,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H93"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -25461,18 +25326,18 @@
         <v>70</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
         <v>778</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>779</v>
       </c>
-      <c r="C32" s="3">
-        <v>28</v>
-      </c>
-      <c r="D32" s="3">
-        <v>30</v>
+      <c r="C32" s="10">
+        <v>4664</v>
+      </c>
+      <c r="D32" s="10">
+        <v>25</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>30</v>
@@ -25480,37 +25345,37 @@
       <c r="F32" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G32" s="3">
-        <v>270</v>
-      </c>
-      <c r="H32" s="3">
-        <v>278</v>
+      <c r="G32" s="10">
+        <v>350</v>
+      </c>
+      <c r="H32" s="10">
+        <v>360.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C33" s="3">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G33" s="3">
-        <v>47</v>
-      </c>
-      <c r="H33" s="5">
-        <v>48.5</v>
+        <v>270</v>
+      </c>
+      <c r="H33" s="3">
+        <v>278</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -25521,7 +25386,7 @@
         <v>781</v>
       </c>
       <c r="C34" s="3">
-        <v>2302</v>
+        <v>68</v>
       </c>
       <c r="D34" s="3">
         <v>5</v>
@@ -25530,27 +25395,27 @@
         <v>30</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G34" s="5">
-        <v>54.5</v>
-      </c>
-      <c r="H34" s="3">
-        <v>56</v>
+        <v>11</v>
+      </c>
+      <c r="G34" s="3">
+        <v>47</v>
+      </c>
+      <c r="H34" s="5">
+        <v>48.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C35" s="3">
-        <v>320</v>
+        <v>2302</v>
       </c>
       <c r="D35" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>30</v>
@@ -25558,11 +25423,11 @@
       <c r="F35" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G35" s="3">
-        <v>315</v>
-      </c>
-      <c r="H35" s="5">
-        <v>324.5</v>
+      <c r="G35" s="5">
+        <v>54.5</v>
+      </c>
+      <c r="H35" s="3">
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
@@ -25573,10 +25438,10 @@
         <v>783</v>
       </c>
       <c r="C36" s="3">
-        <v>3479</v>
+        <v>320</v>
       </c>
       <c r="D36" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>30</v>
@@ -25585,24 +25450,24 @@
         <v>147</v>
       </c>
       <c r="G36" s="3">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="H36" s="5">
-        <v>366.5</v>
+        <v>324.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="4" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C37" s="3">
-        <v>130</v>
+        <v>3479</v>
       </c>
       <c r="D37" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>30</v>
@@ -25611,36 +25476,36 @@
         <v>147</v>
       </c>
       <c r="G37" s="3">
-        <v>178</v>
+        <v>356</v>
       </c>
       <c r="H37" s="5">
-        <v>183.5</v>
+        <v>366.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="4" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C38" s="3">
-        <v>2464</v>
+        <v>130</v>
       </c>
       <c r="D38" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="5">
-        <v>37.5</v>
-      </c>
-      <c r="H38" s="3">
-        <v>39</v>
+        <v>147</v>
+      </c>
+      <c r="G38" s="3">
+        <v>178</v>
+      </c>
+      <c r="H38" s="5">
+        <v>183.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -25651,48 +25516,48 @@
         <v>785</v>
       </c>
       <c r="C39" s="3">
-        <v>101</v>
+        <v>2464</v>
       </c>
       <c r="D39" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G39" s="3">
-        <v>320</v>
+        <v>11</v>
+      </c>
+      <c r="G39" s="5">
+        <v>37.5</v>
       </c>
       <c r="H39" s="3">
-        <v>329.5</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="4" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C40" s="3">
-        <v>2465</v>
+        <v>101</v>
       </c>
       <c r="D40" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G40" s="3">
-        <v>56.5</v>
+        <v>320</v>
       </c>
       <c r="H40" s="3">
-        <v>58</v>
+        <v>329.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -25703,7 +25568,7 @@
         <v>787</v>
       </c>
       <c r="C41" s="3">
-        <v>65</v>
+        <v>2465</v>
       </c>
       <c r="D41" s="3">
         <v>5</v>
@@ -25714,51 +25579,51 @@
       <c r="F41" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G41" s="5">
-        <v>30.5</v>
+      <c r="G41" s="3">
+        <v>56.5</v>
       </c>
       <c r="H41" s="3">
-        <v>31.5</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="4" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C42" s="3">
-        <v>2624</v>
+        <v>65</v>
       </c>
       <c r="D42" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G42" s="3">
-        <v>165</v>
+        <v>11</v>
+      </c>
+      <c r="G42" s="5">
+        <v>30.5</v>
       </c>
       <c r="H42" s="3">
-        <v>170</v>
+        <v>31.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="4" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C43" s="3">
-        <v>119</v>
+        <v>2624</v>
       </c>
       <c r="D43" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>30</v>
@@ -25767,10 +25632,10 @@
         <v>147</v>
       </c>
       <c r="G43" s="3">
-        <v>330</v>
+        <v>165</v>
       </c>
       <c r="H43" s="3">
-        <v>340</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
@@ -25781,10 +25646,10 @@
         <v>789</v>
       </c>
       <c r="C44" s="3">
-        <v>2834</v>
+        <v>119</v>
       </c>
       <c r="D44" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>30</v>
@@ -25793,24 +25658,24 @@
         <v>147</v>
       </c>
       <c r="G44" s="3">
-        <v>123</v>
+        <v>330</v>
       </c>
       <c r="H44" s="3">
-        <v>127</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="4" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C45" s="3">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D45" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>30</v>
@@ -25818,25 +25683,25 @@
       <c r="F45" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G45" s="5">
-        <v>102.5</v>
-      </c>
-      <c r="H45" s="5">
-        <v>105.5</v>
+      <c r="G45" s="3">
+        <v>123</v>
+      </c>
+      <c r="H45" s="3">
+        <v>127</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="4" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="C46" s="3">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D46" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>30</v>
@@ -25844,11 +25709,11 @@
       <c r="F46" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G46" s="3">
-        <v>23</v>
-      </c>
-      <c r="H46" s="3">
-        <v>24</v>
+      <c r="G46" s="5">
+        <v>102.5</v>
+      </c>
+      <c r="H46" s="5">
+        <v>105.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
@@ -25859,10 +25724,10 @@
         <v>791</v>
       </c>
       <c r="C47" s="3">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D47" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>30</v>
@@ -25871,39 +25736,39 @@
         <v>147</v>
       </c>
       <c r="G47" s="3">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="H47" s="3">
-        <v>206</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C48" s="3">
-        <v>2543</v>
+        <v>3025</v>
       </c>
       <c r="D48" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G48" s="5">
-        <v>35.5</v>
-      </c>
-      <c r="H48" s="5">
-        <v>36.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
+        <v>147</v>
+      </c>
+      <c r="G48" s="3">
+        <v>200</v>
+      </c>
+      <c r="H48" s="3">
+        <v>206</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="4" t="s">
         <v>792</v>
       </c>
@@ -25911,36 +25776,36 @@
         <v>793</v>
       </c>
       <c r="C49" s="3">
-        <v>98</v>
+        <v>2543</v>
       </c>
       <c r="D49" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G49" s="3">
-        <v>320</v>
+        <v>11</v>
+      </c>
+      <c r="G49" s="5">
+        <v>35.5</v>
       </c>
       <c r="H49" s="5">
-        <v>329.5</v>
+        <v>36.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C50" s="3">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D50" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>30</v>
@@ -25948,11 +25813,11 @@
       <c r="F50" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G50" s="5">
-        <v>55.5</v>
-      </c>
-      <c r="H50" s="3">
-        <v>57</v>
+      <c r="G50" s="3">
+        <v>320</v>
+      </c>
+      <c r="H50" s="5">
+        <v>329.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -25963,10 +25828,10 @@
         <v>795</v>
       </c>
       <c r="C51" s="3">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D51" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>30</v>
@@ -25975,36 +25840,36 @@
         <v>147</v>
       </c>
       <c r="G51" s="5">
-        <v>362.5</v>
-      </c>
-      <c r="H51" s="5">
-        <v>373.5</v>
+        <v>55.5</v>
+      </c>
+      <c r="H51" s="3">
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="C52" s="3">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D52" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G52" s="5">
-        <v>74.5</v>
-      </c>
-      <c r="H52" s="3">
-        <v>77</v>
+        <v>362.5</v>
+      </c>
+      <c r="H52" s="5">
+        <v>373.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -26015,36 +25880,36 @@
         <v>797</v>
       </c>
       <c r="C53" s="3">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D53" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G53" s="3">
-        <v>255</v>
-      </c>
-      <c r="H53" s="5">
-        <v>262.5</v>
+        <v>11</v>
+      </c>
+      <c r="G53" s="5">
+        <v>74.5</v>
+      </c>
+      <c r="H53" s="3">
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C54" s="3">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D54" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>30</v>
@@ -26052,37 +25917,37 @@
       <c r="F54" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G54" s="5">
-        <v>212.5</v>
-      </c>
-      <c r="H54" s="3">
-        <v>219</v>
+      <c r="G54" s="3">
+        <v>255</v>
+      </c>
+      <c r="H54" s="5">
+        <v>262.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="C55" s="3">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D55" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G55" s="5">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
       <c r="H55" s="3">
-        <v>46</v>
+        <v>219</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -26093,36 +25958,36 @@
         <v>799</v>
       </c>
       <c r="C56" s="3">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D56" s="3">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G56" s="3">
-        <v>350</v>
-      </c>
-      <c r="H56" s="5">
-        <v>360.5</v>
+        <v>11</v>
+      </c>
+      <c r="G56" s="5">
+        <v>44.5</v>
+      </c>
+      <c r="H56" s="3">
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C57" s="3">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D57" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>30</v>
@@ -26131,36 +25996,36 @@
         <v>147</v>
       </c>
       <c r="G57" s="3">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="H57" s="5">
-        <v>180.5</v>
+        <v>360.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="C58" s="3">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D58" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G58" s="3">
-        <v>31</v>
-      </c>
-      <c r="H58" s="3">
-        <v>32</v>
+        <v>175</v>
+      </c>
+      <c r="H58" s="5">
+        <v>180.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -26171,48 +26036,48 @@
         <v>801</v>
       </c>
       <c r="C59" s="3">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D59" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G59" s="3">
-        <v>275</v>
-      </c>
-      <c r="H59" s="5">
-        <v>283.5</v>
+        <v>31</v>
+      </c>
+      <c r="H59" s="3">
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="C60" s="3">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D60" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G60" s="3">
-        <v>57</v>
-      </c>
-      <c r="H60" s="3">
-        <v>59</v>
+        <v>275</v>
+      </c>
+      <c r="H60" s="5">
+        <v>283.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -26223,36 +26088,36 @@
         <v>803</v>
       </c>
       <c r="C61" s="3">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D61" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G61" s="3">
-        <v>280</v>
-      </c>
-      <c r="H61" s="5">
-        <v>288.5</v>
+        <v>57</v>
+      </c>
+      <c r="H61" s="3">
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="C62" s="3">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D62" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>30</v>
@@ -26260,11 +26125,11 @@
       <c r="F62" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G62" s="5">
-        <v>48.5</v>
-      </c>
-      <c r="H62" s="3">
-        <v>50</v>
+      <c r="G62" s="3">
+        <v>280</v>
+      </c>
+      <c r="H62" s="5">
+        <v>288.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -26275,10 +26140,10 @@
         <v>805</v>
       </c>
       <c r="C63" s="3">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D63" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>30</v>
@@ -26286,37 +26151,37 @@
       <c r="F63" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G63" s="3">
-        <v>375</v>
-      </c>
-      <c r="H63" s="5">
-        <v>386.5</v>
+      <c r="G63" s="5">
+        <v>48.5</v>
+      </c>
+      <c r="H63" s="3">
+        <v>50</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="C64" s="3">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D64" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G64" s="5">
-        <v>64.5</v>
+        <v>147</v>
+      </c>
+      <c r="G64" s="3">
+        <v>375</v>
       </c>
       <c r="H64" s="5">
-        <v>66.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -26327,48 +26192,48 @@
         <v>807</v>
       </c>
       <c r="C65" s="3">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D65" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G65" s="3">
-        <v>330</v>
-      </c>
-      <c r="H65" s="3">
-        <v>340</v>
+        <v>11</v>
+      </c>
+      <c r="G65" s="5">
+        <v>64.5</v>
+      </c>
+      <c r="H65" s="5">
+        <v>66.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="C66" s="3">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D66" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G66" s="3">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="H66" s="3">
-        <v>59</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -26379,48 +26244,48 @@
         <v>809</v>
       </c>
       <c r="C67" s="3">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D67" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G67" s="3">
-        <v>225</v>
-      </c>
-      <c r="H67" s="5">
-        <v>231.5</v>
+        <v>57</v>
+      </c>
+      <c r="H67" s="3">
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
       <c r="C68" s="3">
-        <v>2469</v>
+        <v>3670</v>
       </c>
       <c r="D68" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G68" s="5">
-        <v>40.5</v>
-      </c>
-      <c r="H68" s="3">
-        <v>42</v>
+        <v>147</v>
+      </c>
+      <c r="G68" s="3">
+        <v>225</v>
+      </c>
+      <c r="H68" s="5">
+        <v>231.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -26431,48 +26296,48 @@
         <v>811</v>
       </c>
       <c r="C69" s="3">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D69" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G69" s="5">
-        <v>312.5</v>
+        <v>40.5</v>
       </c>
       <c r="H69" s="3">
-        <v>322</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="C70" s="3">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D70" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G70" s="5">
-        <v>64.5</v>
-      </c>
-      <c r="H70" s="5">
-        <v>66.5</v>
+        <v>312.5</v>
+      </c>
+      <c r="H70" s="3">
+        <v>322</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -26483,48 +26348,48 @@
         <v>813</v>
       </c>
       <c r="C71" s="3">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D71" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G71" s="3">
-        <v>300</v>
-      </c>
-      <c r="H71" s="3">
-        <v>309</v>
+        <v>11</v>
+      </c>
+      <c r="G71" s="5">
+        <v>64.5</v>
+      </c>
+      <c r="H71" s="5">
+        <v>66.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="C72" s="3">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D72" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G72" s="3">
-        <v>62</v>
+        <v>300</v>
       </c>
       <c r="H72" s="3">
-        <v>64</v>
+        <v>309</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -26535,48 +26400,48 @@
         <v>815</v>
       </c>
       <c r="C73" s="3">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D73" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G73" s="3">
-        <v>180</v>
-      </c>
-      <c r="H73" s="5">
-        <v>185.5</v>
+        <v>62</v>
+      </c>
+      <c r="H73" s="3">
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="C74" s="3">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D74" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G74" s="3">
-        <v>38</v>
-      </c>
-      <c r="H74" s="3">
-        <v>39</v>
+        <v>180</v>
+      </c>
+      <c r="H74" s="5">
+        <v>185.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -26587,36 +26452,36 @@
         <v>817</v>
       </c>
       <c r="C75" s="3">
-        <v>211</v>
-      </c>
-      <c r="D75" s="5">
-        <v>22.68</v>
+        <v>2321</v>
+      </c>
+      <c r="D75" s="3">
+        <v>5</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G75" s="5">
-        <v>187.5</v>
+        <v>11</v>
+      </c>
+      <c r="G75" s="3">
+        <v>38</v>
       </c>
       <c r="H75" s="3">
-        <v>193</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C76" s="3">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D76" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>30</v>
@@ -26624,37 +26489,37 @@
       <c r="F76" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="3">
-        <v>375</v>
-      </c>
-      <c r="H76" s="5">
-        <v>386.5</v>
+      <c r="G76" s="5">
+        <v>187.5</v>
+      </c>
+      <c r="H76" s="3">
+        <v>193</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="4" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C77" s="3">
-        <v>2322</v>
-      </c>
-      <c r="D77" s="3">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="D77" s="5">
+        <v>45.36</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G77" s="5">
-        <v>43.5</v>
+        <v>147</v>
+      </c>
+      <c r="G77" s="3">
+        <v>375</v>
       </c>
       <c r="H77" s="5">
-        <v>44.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -26665,36 +26530,36 @@
         <v>819</v>
       </c>
       <c r="C78" s="3">
-        <v>67</v>
-      </c>
-      <c r="D78" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D78" s="3">
+        <v>5</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G78" s="3">
-        <v>626</v>
-      </c>
-      <c r="H78" s="3">
-        <v>645</v>
+        <v>11</v>
+      </c>
+      <c r="G78" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="H78" s="5">
+        <v>44.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="4" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C79" s="3">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D79" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>30</v>
@@ -26703,36 +26568,36 @@
         <v>147</v>
       </c>
       <c r="G79" s="3">
-        <v>313</v>
-      </c>
-      <c r="H79" s="5">
-        <v>322.5</v>
+        <v>626</v>
+      </c>
+      <c r="H79" s="3">
+        <v>645</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="4" t="s">
-        <v>818</v>
+        <v>820</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>819</v>
+        <v>821</v>
       </c>
       <c r="C80" s="3">
-        <v>2488</v>
-      </c>
-      <c r="D80" s="3">
-        <v>5</v>
+        <v>2244</v>
+      </c>
+      <c r="D80" s="5">
+        <v>22.68</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G80" s="3">
-        <v>71</v>
-      </c>
-      <c r="H80" s="3">
-        <v>73</v>
+        <v>313</v>
+      </c>
+      <c r="H80" s="5">
+        <v>322.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -26743,22 +26608,22 @@
         <v>821</v>
       </c>
       <c r="C81" s="3">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D81" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G81" s="3">
-        <v>52</v>
-      </c>
-      <c r="H81" s="5">
-        <v>53.5</v>
+        <v>71</v>
+      </c>
+      <c r="H81" s="3">
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
@@ -26769,62 +26634,62 @@
         <v>823</v>
       </c>
       <c r="C82" s="3">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D82" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G82" s="3">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="H82" s="5">
-        <v>187.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C83" s="3">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D83" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G83" s="3">
-        <v>350</v>
+        <v>182</v>
       </c>
       <c r="H83" s="5">
-        <v>360.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C84" s="3">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D84" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>30</v>
@@ -26833,36 +26698,36 @@
         <v>147</v>
       </c>
       <c r="G84" s="3">
-        <v>700</v>
-      </c>
-      <c r="H84" s="3">
-        <v>721</v>
+        <v>350</v>
+      </c>
+      <c r="H84" s="5">
+        <v>360.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C85" s="3">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D85" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G85" s="3">
-        <v>106</v>
-      </c>
-      <c r="H85" s="5">
-        <v>109.5</v>
+        <v>700</v>
+      </c>
+      <c r="H85" s="3">
+        <v>721</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -26873,22 +26738,22 @@
         <v>825</v>
       </c>
       <c r="C86" s="3">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D86" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G86" s="3">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="H86" s="5">
-        <v>89.5</v>
+        <v>109.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
@@ -26899,10 +26764,10 @@
         <v>827</v>
       </c>
       <c r="C87" s="3">
-        <v>135</v>
-      </c>
-      <c r="D87" s="5">
-        <v>22.68</v>
+        <v>3110</v>
+      </c>
+      <c r="D87" s="3">
+        <v>25</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>30</v>
@@ -26911,10 +26776,10 @@
         <v>147</v>
       </c>
       <c r="G87" s="3">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H87" s="5">
-        <v>87.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
@@ -26925,10 +26790,10 @@
         <v>829</v>
       </c>
       <c r="C88" s="3">
-        <v>2463</v>
-      </c>
-      <c r="D88" s="3">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="D88" s="5">
+        <v>22.68</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
@@ -26937,10 +26802,10 @@
         <v>147</v>
       </c>
       <c r="G88" s="3">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H88" s="5">
-        <v>21.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -26951,10 +26816,10 @@
         <v>831</v>
       </c>
       <c r="C89" s="3">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D89" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
@@ -26963,24 +26828,24 @@
         <v>147</v>
       </c>
       <c r="G89" s="3">
-        <v>114</v>
-      </c>
-      <c r="H89" s="3">
-        <v>118</v>
+        <v>21</v>
+      </c>
+      <c r="H89" s="5">
+        <v>21.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C90" s="3">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D90" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
@@ -26989,24 +26854,24 @@
         <v>147</v>
       </c>
       <c r="G90" s="3">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="H90" s="3">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="C91" s="3">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D91" s="3">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>30</v>
@@ -27015,10 +26880,10 @@
         <v>147</v>
       </c>
       <c r="G91" s="3">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="H91" s="3">
-        <v>235</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -27029,10 +26894,10 @@
         <v>833</v>
       </c>
       <c r="C92" s="3">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D92" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>30</v>
@@ -27041,35 +26906,61 @@
         <v>147</v>
       </c>
       <c r="G92" s="3">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="H92" s="3">
-        <v>129</v>
+        <v>235</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="4" t="s">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="C93" s="3">
+        <v>4223</v>
+      </c>
+      <c r="D93" s="3">
+        <v>25</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G93" s="3">
+        <v>125</v>
+      </c>
+      <c r="H93" s="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
+      <c r="A94" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="C94" s="3">
         <v>4224</v>
       </c>
-      <c r="D93" s="3">
-        <v>5</v>
-      </c>
-      <c r="E93" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F93" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G93" s="3">
+      <c r="D94" s="3">
+        <v>5</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G94" s="3">
         <v>27</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H94" s="3">
         <v>28</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3696" uniqueCount="1115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3700" uniqueCount="1115">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3460,7 +3460,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3489,13 +3489,7 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -3976,10 +3970,10 @@
       <c r="B7" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="3">
         <v>564</v>
       </c>
-      <c r="D7" s="11">
+      <c r="D7" s="3">
         <v>25</v>
       </c>
       <c r="E7" s="4" t="s">
@@ -3988,10 +3982,10 @@
       <c r="F7" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="5">
         <v>118</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="5">
         <v>121.5</v>
       </c>
     </row>
@@ -4002,10 +3996,10 @@
       <c r="B8" s="4" t="s">
         <v>857</v>
       </c>
-      <c r="C8" s="11">
+      <c r="C8" s="3">
         <v>2256</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="3">
         <v>3</v>
       </c>
       <c r="E8" s="4" t="s">
@@ -4014,10 +4008,10 @@
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="5">
         <v>16</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="5">
         <v>17</v>
       </c>
     </row>
@@ -4028,10 +4022,10 @@
       <c r="B9" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="3">
         <v>261</v>
       </c>
-      <c r="D9" s="11">
+      <c r="D9" s="3">
         <v>25</v>
       </c>
       <c r="E9" s="4" t="s">
@@ -4040,10 +4034,10 @@
       <c r="F9" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="5">
         <v>83</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="5">
         <v>85.5</v>
       </c>
     </row>
@@ -4054,10 +4048,10 @@
       <c r="B10" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="C10" s="11">
+      <c r="C10" s="3">
         <v>2475</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="3">
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
@@ -4066,10 +4060,10 @@
       <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="5">
         <v>18.5</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="5">
         <v>19</v>
       </c>
     </row>
@@ -4080,10 +4074,10 @@
       <c r="B11" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="3">
         <v>92</v>
       </c>
-      <c r="D11" s="11">
+      <c r="D11" s="3">
         <v>20</v>
       </c>
       <c r="E11" s="4" t="s">
@@ -4092,10 +4086,10 @@
       <c r="F11" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="5">
         <v>67</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="5">
         <v>69</v>
       </c>
     </row>
@@ -4106,10 +4100,10 @@
       <c r="B12" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="C12" s="11">
+      <c r="C12" s="3">
         <v>2476</v>
       </c>
-      <c r="D12" s="11">
+      <c r="D12" s="3">
         <v>3</v>
       </c>
       <c r="E12" s="4" t="s">
@@ -4118,10 +4112,10 @@
       <c r="F12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="5">
         <v>11.5</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="5">
         <v>12</v>
       </c>
     </row>
@@ -4132,10 +4126,10 @@
       <c r="B13" s="4" t="s">
         <v>701</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="3">
         <v>27</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="3">
         <v>25</v>
       </c>
       <c r="E13" s="4" t="s">
@@ -4144,10 +4138,10 @@
       <c r="F13" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="5">
         <v>110</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="5">
         <v>113.5</v>
       </c>
     </row>
@@ -4158,10 +4152,10 @@
       <c r="B14" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="C14" s="11">
+      <c r="C14" s="3">
         <v>2255</v>
       </c>
-      <c r="D14" s="11">
+      <c r="D14" s="3">
         <v>25</v>
       </c>
       <c r="E14" s="4" t="s">
@@ -4170,10 +4164,10 @@
       <c r="F14" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="5">
         <v>99</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="5">
         <v>102</v>
       </c>
     </row>
@@ -4184,10 +4178,10 @@
       <c r="B15" s="4" t="s">
         <v>531</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="3">
         <v>2350</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="3">
         <v>5</v>
       </c>
       <c r="E15" s="4" t="s">
@@ -4196,10 +4190,10 @@
       <c r="F15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="12">
+      <c r="G15" s="5">
         <v>250</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="5">
         <v>258</v>
       </c>
     </row>
@@ -4210,10 +4204,10 @@
       <c r="B16" s="4" t="s">
         <v>539</v>
       </c>
-      <c r="C16" s="11">
+      <c r="C16" s="3">
         <v>2229</v>
       </c>
-      <c r="D16" s="11">
+      <c r="D16" s="3">
         <v>10</v>
       </c>
       <c r="E16" s="4" t="s">
@@ -4222,10 +4216,10 @@
       <c r="F16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="5">
         <v>175</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="5">
         <v>180</v>
       </c>
     </row>
@@ -4444,10 +4438,10 @@
       <c r="B25" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C25" s="11">
+      <c r="C25" s="3">
         <v>3438</v>
       </c>
-      <c r="D25" s="11">
+      <c r="D25" s="3">
         <v>15</v>
       </c>
       <c r="E25" s="4" t="s">
@@ -4456,10 +4450,10 @@
       <c r="F25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="5">
         <v>228</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="5">
         <v>235</v>
       </c>
     </row>
@@ -4470,10 +4464,10 @@
       <c r="B26" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="11">
+      <c r="C26" s="3">
         <v>3434</v>
       </c>
-      <c r="D26" s="11">
+      <c r="D26" s="3">
         <v>5</v>
       </c>
       <c r="E26" s="4" t="s">
@@ -4482,10 +4476,10 @@
       <c r="F26" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="5">
         <v>76</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="5">
         <v>78.5</v>
       </c>
     </row>
@@ -4496,10 +4490,10 @@
       <c r="B27" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C27" s="11">
+      <c r="C27" s="3">
         <v>3123</v>
       </c>
-      <c r="D27" s="11">
+      <c r="D27" s="3">
         <v>10</v>
       </c>
       <c r="E27" s="4" t="s">
@@ -4508,10 +4502,10 @@
       <c r="F27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="5">
         <v>121</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="5">
         <v>125</v>
       </c>
     </row>
@@ -4522,10 +4516,10 @@
       <c r="B28" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="C28" s="11">
+      <c r="C28" s="3">
         <v>2674</v>
       </c>
-      <c r="D28" s="11">
+      <c r="D28" s="3">
         <v>5</v>
       </c>
       <c r="E28" s="4" t="s">
@@ -4534,10 +4528,10 @@
       <c r="F28" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="5">
         <v>60.5</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="5">
         <v>62</v>
       </c>
     </row>
@@ -4548,10 +4542,10 @@
       <c r="B29" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="11">
+      <c r="C29" s="3">
         <v>3124</v>
       </c>
-      <c r="D29" s="11">
+      <c r="D29" s="3">
         <v>10</v>
       </c>
       <c r="E29" s="4" t="s">
@@ -4560,10 +4554,10 @@
       <c r="F29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="5">
         <v>161</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="5">
         <v>166</v>
       </c>
     </row>
@@ -4574,10 +4568,10 @@
       <c r="B30" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="C30" s="11">
+      <c r="C30" s="3">
         <v>2824</v>
       </c>
-      <c r="D30" s="11">
+      <c r="D30" s="3">
         <v>5</v>
       </c>
       <c r="E30" s="4" t="s">
@@ -4586,10 +4580,10 @@
       <c r="F30" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="5">
         <v>80.5</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="5">
         <v>83</v>
       </c>
     </row>
@@ -4600,10 +4594,10 @@
       <c r="B31" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C31" s="11">
+      <c r="C31" s="3">
         <v>3130</v>
       </c>
-      <c r="D31" s="11">
+      <c r="D31" s="3">
         <v>10</v>
       </c>
       <c r="E31" s="4" t="s">
@@ -4612,10 +4606,10 @@
       <c r="F31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="5">
         <v>138</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="5">
         <v>142</v>
       </c>
     </row>
@@ -4626,10 +4620,10 @@
       <c r="B32" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C32" s="11">
+      <c r="C32" s="3">
         <v>3131</v>
       </c>
-      <c r="D32" s="11">
+      <c r="D32" s="3">
         <v>5</v>
       </c>
       <c r="E32" s="4" t="s">
@@ -4638,10 +4632,10 @@
       <c r="F32" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="5">
         <v>69</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="5">
         <v>71</v>
       </c>
     </row>
@@ -9282,10 +9276,10 @@
         <v>147</v>
       </c>
       <c r="G31" s="3">
-        <v>1875</v>
+        <v>1625</v>
       </c>
       <c r="H31" s="3">
-        <v>1931</v>
+        <v>1674</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
@@ -9308,10 +9302,10 @@
         <v>147</v>
       </c>
       <c r="G32" s="3">
-        <v>378.5</v>
+        <v>328.5</v>
       </c>
       <c r="H32" s="5">
-        <v>390</v>
+        <v>338.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
@@ -10189,10 +10183,10 @@
         <v>11</v>
       </c>
       <c r="G30" s="5">
-        <v>299.5</v>
+        <v>313.5</v>
       </c>
       <c r="H30" s="5">
-        <v>308.5</v>
+        <v>323</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
@@ -16076,10 +16070,10 @@
         <v>11</v>
       </c>
       <c r="G84" s="3">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="H84" s="5">
-        <v>426.5</v>
+        <v>436.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -16102,10 +16096,10 @@
         <v>11</v>
       </c>
       <c r="G85" s="3">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="H85" s="3">
-        <v>87</v>
+        <v>90.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -20288,10 +20282,10 @@
         <v>147</v>
       </c>
       <c r="G12" s="3">
-        <v>550</v>
+        <v>650</v>
       </c>
       <c r="H12" s="5">
-        <v>566.5</v>
+        <v>669.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
@@ -20314,10 +20308,10 @@
         <v>11</v>
       </c>
       <c r="G13" s="3">
-        <v>113.5</v>
+        <v>133.5</v>
       </c>
       <c r="H13" s="5">
-        <v>117</v>
+        <v>138</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
@@ -24507,7 +24501,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H94"/>
+  <dimension ref="A1:H95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="6" width="30.005" customWidth="1" bestFit="1"/>
@@ -24806,7 +24800,7 @@
         <v>65</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>758</v>
       </c>
@@ -24832,7 +24826,7 @@
         <v>16</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>760</v>
       </c>
@@ -24858,7 +24852,7 @@
         <v>147</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>760</v>
       </c>
@@ -24884,7 +24878,7 @@
         <v>31.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>762</v>
       </c>
@@ -24910,7 +24904,7 @@
         <v>39</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>762</v>
       </c>
@@ -24936,7 +24930,7 @@
         <v>185.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>764</v>
       </c>
@@ -24962,7 +24956,7 @@
         <v>152.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>764</v>
       </c>
@@ -24988,7 +24982,7 @@
         <v>276.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>764</v>
       </c>
@@ -25014,7 +25008,7 @@
         <v>32.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>766</v>
       </c>
@@ -25040,7 +25034,7 @@
         <v>608</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>766</v>
       </c>
@@ -25066,7 +25060,7 @@
         <v>103.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>768</v>
       </c>
@@ -25092,7 +25086,7 @@
         <v>556</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>768</v>
       </c>
@@ -25118,7 +25112,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>770</v>
       </c>
@@ -25144,7 +25138,7 @@
         <v>556</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>770</v>
       </c>
@@ -25170,7 +25164,7 @@
         <v>95</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
         <v>772</v>
       </c>
@@ -25352,30 +25346,30 @@
         <v>360.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>781</v>
-      </c>
-      <c r="C33" s="3">
-        <v>28</v>
-      </c>
-      <c r="D33" s="3">
-        <v>30</v>
+        <v>779</v>
+      </c>
+      <c r="C33" s="10">
+        <v>4665</v>
+      </c>
+      <c r="D33" s="10">
+        <v>5</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G33" s="3">
-        <v>270</v>
-      </c>
-      <c r="H33" s="3">
-        <v>278</v>
+        <v>11</v>
+      </c>
+      <c r="G33" s="10">
+        <v>73</v>
+      </c>
+      <c r="H33" s="10">
+        <v>75</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
@@ -25386,33 +25380,33 @@
         <v>781</v>
       </c>
       <c r="C34" s="3">
-        <v>68</v>
+        <v>28</v>
       </c>
       <c r="D34" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G34" s="3">
-        <v>47</v>
-      </c>
-      <c r="H34" s="5">
-        <v>48.5</v>
+        <v>270</v>
+      </c>
+      <c r="H34" s="3">
+        <v>278</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C35" s="3">
-        <v>2302</v>
+        <v>68</v>
       </c>
       <c r="D35" s="3">
         <v>5</v>
@@ -25421,13 +25415,13 @@
         <v>30</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G35" s="5">
-        <v>54.5</v>
-      </c>
-      <c r="H35" s="3">
-        <v>56</v>
+        <v>11</v>
+      </c>
+      <c r="G35" s="3">
+        <v>47</v>
+      </c>
+      <c r="H35" s="5">
+        <v>48.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
@@ -25438,10 +25432,10 @@
         <v>783</v>
       </c>
       <c r="C36" s="3">
-        <v>320</v>
+        <v>2302</v>
       </c>
       <c r="D36" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>30</v>
@@ -25449,25 +25443,25 @@
       <c r="F36" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G36" s="3">
-        <v>315</v>
-      </c>
-      <c r="H36" s="5">
-        <v>324.5</v>
+      <c r="G36" s="5">
+        <v>54.5</v>
+      </c>
+      <c r="H36" s="3">
+        <v>56</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="4" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C37" s="3">
-        <v>3479</v>
+        <v>320</v>
       </c>
       <c r="D37" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>30</v>
@@ -25476,10 +25470,10 @@
         <v>147</v>
       </c>
       <c r="G37" s="3">
-        <v>356</v>
+        <v>315</v>
       </c>
       <c r="H37" s="5">
-        <v>366.5</v>
+        <v>324.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
@@ -25490,10 +25484,10 @@
         <v>785</v>
       </c>
       <c r="C38" s="3">
-        <v>130</v>
+        <v>3479</v>
       </c>
       <c r="D38" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>30</v>
@@ -25502,10 +25496,10 @@
         <v>147</v>
       </c>
       <c r="G38" s="3">
-        <v>178</v>
+        <v>356</v>
       </c>
       <c r="H38" s="5">
-        <v>183.5</v>
+        <v>366.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
@@ -25516,48 +25510,48 @@
         <v>785</v>
       </c>
       <c r="C39" s="3">
-        <v>2464</v>
+        <v>130</v>
       </c>
       <c r="D39" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G39" s="5">
-        <v>37.5</v>
-      </c>
-      <c r="H39" s="3">
-        <v>39</v>
+        <v>147</v>
+      </c>
+      <c r="G39" s="3">
+        <v>178</v>
+      </c>
+      <c r="H39" s="5">
+        <v>183.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="4" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C40" s="3">
-        <v>101</v>
+        <v>2464</v>
       </c>
       <c r="D40" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G40" s="3">
-        <v>320</v>
+        <v>11</v>
+      </c>
+      <c r="G40" s="5">
+        <v>37.5</v>
       </c>
       <c r="H40" s="3">
-        <v>329.5</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
@@ -25568,33 +25562,33 @@
         <v>787</v>
       </c>
       <c r="C41" s="3">
-        <v>2465</v>
+        <v>101</v>
       </c>
       <c r="D41" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G41" s="3">
-        <v>56.5</v>
+        <v>320</v>
       </c>
       <c r="H41" s="3">
-        <v>58</v>
+        <v>329.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="4" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C42" s="3">
-        <v>65</v>
+        <v>2465</v>
       </c>
       <c r="D42" s="3">
         <v>5</v>
@@ -25605,11 +25599,11 @@
       <c r="F42" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G42" s="5">
-        <v>30.5</v>
+      <c r="G42" s="3">
+        <v>56.5</v>
       </c>
       <c r="H42" s="3">
-        <v>31.5</v>
+        <v>58</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
@@ -25620,22 +25614,22 @@
         <v>789</v>
       </c>
       <c r="C43" s="3">
-        <v>2624</v>
+        <v>65</v>
       </c>
       <c r="D43" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G43" s="3">
-        <v>165</v>
+        <v>11</v>
+      </c>
+      <c r="G43" s="5">
+        <v>30.5</v>
       </c>
       <c r="H43" s="3">
-        <v>170</v>
+        <v>31.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
@@ -25646,10 +25640,10 @@
         <v>789</v>
       </c>
       <c r="C44" s="3">
-        <v>119</v>
+        <v>2624</v>
       </c>
       <c r="D44" s="3">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>30</v>
@@ -25658,24 +25652,24 @@
         <v>147</v>
       </c>
       <c r="G44" s="3">
-        <v>330</v>
+        <v>165</v>
       </c>
       <c r="H44" s="3">
-        <v>340</v>
+        <v>170</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="4" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C45" s="3">
-        <v>2834</v>
+        <v>119</v>
       </c>
       <c r="D45" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>30</v>
@@ -25684,10 +25678,10 @@
         <v>147</v>
       </c>
       <c r="G45" s="3">
-        <v>123</v>
+        <v>330</v>
       </c>
       <c r="H45" s="3">
-        <v>127</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
@@ -25698,10 +25692,10 @@
         <v>791</v>
       </c>
       <c r="C46" s="3">
-        <v>3621</v>
+        <v>2834</v>
       </c>
       <c r="D46" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>30</v>
@@ -25709,11 +25703,11 @@
       <c r="F46" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G46" s="5">
-        <v>102.5</v>
-      </c>
-      <c r="H46" s="5">
-        <v>105.5</v>
+      <c r="G46" s="3">
+        <v>123</v>
+      </c>
+      <c r="H46" s="3">
+        <v>127</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
@@ -25724,10 +25718,10 @@
         <v>791</v>
       </c>
       <c r="C47" s="3">
-        <v>141</v>
+        <v>3621</v>
       </c>
       <c r="D47" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>30</v>
@@ -25735,25 +25729,25 @@
       <c r="F47" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G47" s="3">
-        <v>23</v>
-      </c>
-      <c r="H47" s="3">
-        <v>24</v>
+      <c r="G47" s="5">
+        <v>102.5</v>
+      </c>
+      <c r="H47" s="5">
+        <v>105.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C48" s="3">
-        <v>3025</v>
+        <v>141</v>
       </c>
       <c r="D48" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>30</v>
@@ -25762,10 +25756,10 @@
         <v>147</v>
       </c>
       <c r="G48" s="3">
-        <v>200</v>
+        <v>23</v>
       </c>
       <c r="H48" s="3">
-        <v>206</v>
+        <v>24</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
@@ -25776,48 +25770,48 @@
         <v>793</v>
       </c>
       <c r="C49" s="3">
+        <v>3025</v>
+      </c>
+      <c r="D49" s="3">
+        <v>30</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G49" s="3">
+        <v>200</v>
+      </c>
+      <c r="H49" s="3">
+        <v>206</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="19.5">
+      <c r="A50" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="C50" s="3">
         <v>2543</v>
       </c>
-      <c r="D49" s="3">
-        <v>5</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G49" s="5">
+      <c r="D50" s="3">
+        <v>5</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50" s="5">
         <v>35.5</v>
       </c>
-      <c r="H49" s="5">
+      <c r="H50" s="5">
         <v>36.5</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
-      <c r="A50" s="4" t="s">
-        <v>794</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>795</v>
-      </c>
-      <c r="C50" s="3">
-        <v>98</v>
-      </c>
-      <c r="D50" s="3">
-        <v>30</v>
-      </c>
-      <c r="E50" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G50" s="3">
-        <v>320</v>
-      </c>
-      <c r="H50" s="5">
-        <v>329.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
@@ -25828,10 +25822,10 @@
         <v>795</v>
       </c>
       <c r="C51" s="3">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="D51" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>30</v>
@@ -25839,25 +25833,25 @@
       <c r="F51" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G51" s="5">
-        <v>55.5</v>
-      </c>
-      <c r="H51" s="3">
-        <v>57</v>
+      <c r="G51" s="3">
+        <v>320</v>
+      </c>
+      <c r="H51" s="5">
+        <v>329.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C52" s="3">
-        <v>2353</v>
+        <v>35</v>
       </c>
       <c r="D52" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>30</v>
@@ -25866,10 +25860,10 @@
         <v>147</v>
       </c>
       <c r="G52" s="5">
-        <v>362.5</v>
-      </c>
-      <c r="H52" s="5">
-        <v>373.5</v>
+        <v>55.5</v>
+      </c>
+      <c r="H52" s="3">
+        <v>57</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
@@ -25880,48 +25874,48 @@
         <v>797</v>
       </c>
       <c r="C53" s="3">
-        <v>2466</v>
+        <v>2353</v>
       </c>
       <c r="D53" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G53" s="5">
-        <v>74.5</v>
-      </c>
-      <c r="H53" s="3">
-        <v>77</v>
+        <v>362.5</v>
+      </c>
+      <c r="H53" s="5">
+        <v>373.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C54" s="3">
-        <v>3089</v>
+        <v>2466</v>
       </c>
       <c r="D54" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G54" s="3">
-        <v>255</v>
-      </c>
-      <c r="H54" s="5">
-        <v>262.5</v>
+        <v>11</v>
+      </c>
+      <c r="G54" s="5">
+        <v>74.5</v>
+      </c>
+      <c r="H54" s="3">
+        <v>77</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
@@ -25932,10 +25926,10 @@
         <v>799</v>
       </c>
       <c r="C55" s="3">
-        <v>2666</v>
+        <v>3089</v>
       </c>
       <c r="D55" s="3">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>30</v>
@@ -25943,11 +25937,11 @@
       <c r="F55" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G55" s="5">
-        <v>212.5</v>
-      </c>
-      <c r="H55" s="3">
-        <v>219</v>
+      <c r="G55" s="3">
+        <v>255</v>
+      </c>
+      <c r="H55" s="5">
+        <v>262.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
@@ -25958,48 +25952,48 @@
         <v>799</v>
       </c>
       <c r="C56" s="3">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="D56" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G56" s="5">
-        <v>44.5</v>
+        <v>212.5</v>
       </c>
       <c r="H56" s="3">
-        <v>46</v>
+        <v>219</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C57" s="3">
-        <v>3478</v>
+        <v>2667</v>
       </c>
       <c r="D57" s="3">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G57" s="3">
-        <v>350</v>
-      </c>
-      <c r="H57" s="5">
-        <v>360.5</v>
+        <v>11</v>
+      </c>
+      <c r="G57" s="5">
+        <v>44.5</v>
+      </c>
+      <c r="H57" s="3">
+        <v>46</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
@@ -26010,10 +26004,10 @@
         <v>801</v>
       </c>
       <c r="C58" s="3">
-        <v>190</v>
+        <v>3478</v>
       </c>
       <c r="D58" s="3">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>30</v>
@@ -26022,10 +26016,10 @@
         <v>147</v>
       </c>
       <c r="G58" s="3">
-        <v>175</v>
+        <v>350</v>
       </c>
       <c r="H58" s="5">
-        <v>180.5</v>
+        <v>360.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
@@ -26036,48 +26030,48 @@
         <v>801</v>
       </c>
       <c r="C59" s="3">
-        <v>2335</v>
+        <v>190</v>
       </c>
       <c r="D59" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G59" s="3">
-        <v>31</v>
-      </c>
-      <c r="H59" s="3">
-        <v>32</v>
+        <v>175</v>
+      </c>
+      <c r="H59" s="5">
+        <v>180.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C60" s="3">
-        <v>3446</v>
+        <v>2335</v>
       </c>
       <c r="D60" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G60" s="3">
-        <v>275</v>
-      </c>
-      <c r="H60" s="5">
-        <v>283.5</v>
+        <v>31</v>
+      </c>
+      <c r="H60" s="3">
+        <v>32</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
@@ -26088,48 +26082,48 @@
         <v>803</v>
       </c>
       <c r="C61" s="3">
-        <v>3447</v>
+        <v>3446</v>
       </c>
       <c r="D61" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G61" s="3">
-        <v>57</v>
-      </c>
-      <c r="H61" s="3">
-        <v>59</v>
+        <v>275</v>
+      </c>
+      <c r="H61" s="5">
+        <v>283.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C62" s="3">
-        <v>100</v>
+        <v>3447</v>
       </c>
       <c r="D62" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G62" s="3">
-        <v>280</v>
-      </c>
-      <c r="H62" s="5">
-        <v>288.5</v>
+        <v>57</v>
+      </c>
+      <c r="H62" s="3">
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
@@ -26140,10 +26134,10 @@
         <v>805</v>
       </c>
       <c r="C63" s="3">
-        <v>136</v>
+        <v>100</v>
       </c>
       <c r="D63" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>30</v>
@@ -26151,25 +26145,25 @@
       <c r="F63" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G63" s="5">
-        <v>48.5</v>
-      </c>
-      <c r="H63" s="3">
-        <v>50</v>
+      <c r="G63" s="3">
+        <v>280</v>
+      </c>
+      <c r="H63" s="5">
+        <v>288.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C64" s="3">
-        <v>259</v>
+        <v>136</v>
       </c>
       <c r="D64" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>30</v>
@@ -26177,11 +26171,11 @@
       <c r="F64" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G64" s="3">
-        <v>375</v>
-      </c>
-      <c r="H64" s="5">
-        <v>386.5</v>
+      <c r="G64" s="5">
+        <v>48.5</v>
+      </c>
+      <c r="H64" s="3">
+        <v>50</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
@@ -26192,48 +26186,48 @@
         <v>807</v>
       </c>
       <c r="C65" s="3">
-        <v>2319</v>
+        <v>259</v>
       </c>
       <c r="D65" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G65" s="5">
-        <v>64.5</v>
+        <v>147</v>
+      </c>
+      <c r="G65" s="3">
+        <v>375</v>
       </c>
       <c r="H65" s="5">
-        <v>66.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C66" s="3">
-        <v>125</v>
+        <v>2319</v>
       </c>
       <c r="D66" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G66" s="3">
-        <v>330</v>
-      </c>
-      <c r="H66" s="3">
-        <v>340</v>
+        <v>11</v>
+      </c>
+      <c r="G66" s="5">
+        <v>64.5</v>
+      </c>
+      <c r="H66" s="5">
+        <v>66.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
@@ -26244,48 +26238,48 @@
         <v>809</v>
       </c>
       <c r="C67" s="3">
-        <v>2468</v>
+        <v>125</v>
       </c>
       <c r="D67" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G67" s="3">
-        <v>57</v>
+        <v>330</v>
       </c>
       <c r="H67" s="3">
-        <v>59</v>
+        <v>340</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C68" s="3">
-        <v>3670</v>
+        <v>2468</v>
       </c>
       <c r="D68" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G68" s="3">
-        <v>225</v>
-      </c>
-      <c r="H68" s="5">
-        <v>231.5</v>
+        <v>57</v>
+      </c>
+      <c r="H68" s="3">
+        <v>59</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
@@ -26296,48 +26290,48 @@
         <v>811</v>
       </c>
       <c r="C69" s="3">
-        <v>2469</v>
+        <v>3670</v>
       </c>
       <c r="D69" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" s="5">
-        <v>40.5</v>
-      </c>
-      <c r="H69" s="3">
-        <v>42</v>
+        <v>147</v>
+      </c>
+      <c r="G69" s="3">
+        <v>225</v>
+      </c>
+      <c r="H69" s="5">
+        <v>231.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C70" s="3">
-        <v>3006</v>
+        <v>2469</v>
       </c>
       <c r="D70" s="3">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G70" s="5">
-        <v>312.5</v>
+        <v>40.5</v>
       </c>
       <c r="H70" s="3">
-        <v>322</v>
+        <v>42</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
@@ -26348,48 +26342,48 @@
         <v>813</v>
       </c>
       <c r="C71" s="3">
-        <v>3007</v>
+        <v>3006</v>
       </c>
       <c r="D71" s="3">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G71" s="5">
-        <v>64.5</v>
-      </c>
-      <c r="H71" s="5">
-        <v>66.5</v>
+        <v>312.5</v>
+      </c>
+      <c r="H71" s="3">
+        <v>322</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C72" s="3">
-        <v>117</v>
+        <v>3007</v>
       </c>
       <c r="D72" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G72" s="3">
-        <v>300</v>
-      </c>
-      <c r="H72" s="3">
-        <v>309</v>
+        <v>11</v>
+      </c>
+      <c r="G72" s="5">
+        <v>64.5</v>
+      </c>
+      <c r="H72" s="5">
+        <v>66.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
@@ -26400,48 +26394,48 @@
         <v>815</v>
       </c>
       <c r="C73" s="3">
-        <v>2320</v>
+        <v>117</v>
       </c>
       <c r="D73" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G73" s="3">
-        <v>62</v>
+        <v>300</v>
       </c>
       <c r="H73" s="3">
-        <v>64</v>
+        <v>309</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C74" s="3">
-        <v>60</v>
+        <v>2320</v>
       </c>
       <c r="D74" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G74" s="3">
-        <v>180</v>
-      </c>
-      <c r="H74" s="5">
-        <v>185.5</v>
+        <v>62</v>
+      </c>
+      <c r="H74" s="3">
+        <v>64</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
@@ -26452,48 +26446,48 @@
         <v>817</v>
       </c>
       <c r="C75" s="3">
-        <v>2321</v>
+        <v>60</v>
       </c>
       <c r="D75" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G75" s="3">
-        <v>38</v>
-      </c>
-      <c r="H75" s="3">
-        <v>39</v>
+        <v>180</v>
+      </c>
+      <c r="H75" s="5">
+        <v>185.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="4" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C76" s="3">
-        <v>211</v>
-      </c>
-      <c r="D76" s="5">
-        <v>22.68</v>
+        <v>2321</v>
+      </c>
+      <c r="D76" s="3">
+        <v>5</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G76" s="5">
-        <v>187.5</v>
+        <v>11</v>
+      </c>
+      <c r="G76" s="3">
+        <v>38</v>
       </c>
       <c r="H76" s="3">
-        <v>193</v>
+        <v>39</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
@@ -26504,10 +26498,10 @@
         <v>819</v>
       </c>
       <c r="C77" s="3">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="D77" s="5">
-        <v>45.36</v>
+        <v>22.68</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>30</v>
@@ -26515,11 +26509,11 @@
       <c r="F77" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G77" s="3">
-        <v>375</v>
-      </c>
-      <c r="H77" s="5">
-        <v>386.5</v>
+      <c r="G77" s="5">
+        <v>187.5</v>
+      </c>
+      <c r="H77" s="3">
+        <v>193</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
@@ -26530,48 +26524,48 @@
         <v>819</v>
       </c>
       <c r="C78" s="3">
-        <v>2322</v>
-      </c>
-      <c r="D78" s="3">
-        <v>5</v>
+        <v>41</v>
+      </c>
+      <c r="D78" s="5">
+        <v>45.36</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G78" s="5">
-        <v>43.5</v>
+        <v>147</v>
+      </c>
+      <c r="G78" s="3">
+        <v>375</v>
       </c>
       <c r="H78" s="5">
-        <v>44.5</v>
+        <v>386.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="4" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C79" s="3">
-        <v>67</v>
-      </c>
-      <c r="D79" s="5">
-        <v>45.36</v>
+        <v>2322</v>
+      </c>
+      <c r="D79" s="3">
+        <v>5</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G79" s="3">
-        <v>626</v>
-      </c>
-      <c r="H79" s="3">
-        <v>645</v>
+        <v>11</v>
+      </c>
+      <c r="G79" s="5">
+        <v>43.5</v>
+      </c>
+      <c r="H79" s="5">
+        <v>44.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
@@ -26582,10 +26576,10 @@
         <v>821</v>
       </c>
       <c r="C80" s="3">
-        <v>2244</v>
+        <v>67</v>
       </c>
       <c r="D80" s="5">
-        <v>22.68</v>
+        <v>45.36</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>30</v>
@@ -26594,10 +26588,10 @@
         <v>147</v>
       </c>
       <c r="G80" s="3">
-        <v>313</v>
-      </c>
-      <c r="H80" s="5">
-        <v>322.5</v>
+        <v>626</v>
+      </c>
+      <c r="H80" s="3">
+        <v>645</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
@@ -26608,74 +26602,74 @@
         <v>821</v>
       </c>
       <c r="C81" s="3">
-        <v>2488</v>
-      </c>
-      <c r="D81" s="3">
-        <v>5</v>
+        <v>2244</v>
+      </c>
+      <c r="D81" s="5">
+        <v>22.68</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G81" s="3">
-        <v>71</v>
-      </c>
-      <c r="H81" s="3">
-        <v>73</v>
+        <v>313</v>
+      </c>
+      <c r="H81" s="5">
+        <v>322.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C82" s="3">
-        <v>520</v>
+        <v>2488</v>
       </c>
       <c r="D82" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G82" s="3">
-        <v>52</v>
-      </c>
-      <c r="H82" s="5">
-        <v>53.5</v>
+        <v>71</v>
+      </c>
+      <c r="H82" s="3">
+        <v>73</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C83" s="3">
-        <v>4546</v>
+        <v>520</v>
       </c>
       <c r="D83" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G83" s="3">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="H83" s="5">
-        <v>187.5</v>
+        <v>53.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
@@ -26686,22 +26680,22 @@
         <v>825</v>
       </c>
       <c r="C84" s="3">
-        <v>3695</v>
+        <v>4546</v>
       </c>
       <c r="D84" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G84" s="3">
-        <v>350</v>
+        <v>182</v>
       </c>
       <c r="H84" s="5">
-        <v>360.5</v>
+        <v>187.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -26712,10 +26706,10 @@
         <v>825</v>
       </c>
       <c r="C85" s="3">
-        <v>3097</v>
+        <v>3695</v>
       </c>
       <c r="D85" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>30</v>
@@ -26724,10 +26718,10 @@
         <v>147</v>
       </c>
       <c r="G85" s="3">
-        <v>700</v>
-      </c>
-      <c r="H85" s="3">
-        <v>721</v>
+        <v>350</v>
+      </c>
+      <c r="H85" s="5">
+        <v>360.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
@@ -26738,62 +26732,62 @@
         <v>825</v>
       </c>
       <c r="C86" s="3">
-        <v>2460</v>
+        <v>3097</v>
       </c>
       <c r="D86" s="3">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G86" s="3">
-        <v>106</v>
-      </c>
-      <c r="H86" s="5">
-        <v>109.5</v>
+        <v>700</v>
+      </c>
+      <c r="H86" s="3">
+        <v>721</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C87" s="3">
-        <v>3110</v>
+        <v>2460</v>
       </c>
       <c r="D87" s="3">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G87" s="3">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="H87" s="5">
-        <v>89.5</v>
+        <v>109.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C88" s="3">
-        <v>135</v>
-      </c>
-      <c r="D88" s="5">
-        <v>22.68</v>
+        <v>3110</v>
+      </c>
+      <c r="D88" s="3">
+        <v>25</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
@@ -26802,24 +26796,24 @@
         <v>147</v>
       </c>
       <c r="G88" s="3">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H88" s="5">
-        <v>87.5</v>
+        <v>89.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="C89" s="3">
-        <v>2463</v>
-      </c>
-      <c r="D89" s="3">
-        <v>5</v>
+        <v>135</v>
+      </c>
+      <c r="D89" s="5">
+        <v>22.68</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
@@ -26828,24 +26822,24 @@
         <v>147</v>
       </c>
       <c r="G89" s="3">
-        <v>21</v>
+        <v>85</v>
       </c>
       <c r="H89" s="5">
-        <v>21.5</v>
+        <v>87.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="C90" s="3">
-        <v>55</v>
+        <v>2463</v>
       </c>
       <c r="D90" s="3">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
@@ -26854,10 +26848,10 @@
         <v>147</v>
       </c>
       <c r="G90" s="3">
-        <v>114</v>
-      </c>
-      <c r="H90" s="3">
-        <v>118</v>
+        <v>21</v>
+      </c>
+      <c r="H90" s="5">
+        <v>21.5</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
@@ -26868,10 +26862,10 @@
         <v>833</v>
       </c>
       <c r="C91" s="3">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D91" s="3">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E91" s="4" t="s">
         <v>30</v>
@@ -26880,10 +26874,10 @@
         <v>147</v>
       </c>
       <c r="G91" s="3">
-        <v>27</v>
+        <v>114</v>
       </c>
       <c r="H91" s="3">
-        <v>28</v>
+        <v>118</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
@@ -26894,10 +26888,10 @@
         <v>833</v>
       </c>
       <c r="C92" s="3">
-        <v>201</v>
+        <v>51</v>
       </c>
       <c r="D92" s="3">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="E92" s="4" t="s">
         <v>30</v>
@@ -26906,24 +26900,24 @@
         <v>147</v>
       </c>
       <c r="G92" s="3">
-        <v>228</v>
+        <v>27</v>
       </c>
       <c r="H92" s="3">
-        <v>235</v>
+        <v>28</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="4" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="C93" s="3">
-        <v>4223</v>
+        <v>201</v>
       </c>
       <c r="D93" s="3">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="E93" s="4" t="s">
         <v>30</v>
@@ -26932,10 +26926,10 @@
         <v>147</v>
       </c>
       <c r="G93" s="3">
-        <v>125</v>
+        <v>228</v>
       </c>
       <c r="H93" s="3">
-        <v>129</v>
+        <v>235</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
@@ -26946,21 +26940,47 @@
         <v>835</v>
       </c>
       <c r="C94" s="3">
+        <v>4223</v>
+      </c>
+      <c r="D94" s="3">
+        <v>25</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G94" s="3">
+        <v>125</v>
+      </c>
+      <c r="H94" s="3">
+        <v>129</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
+      <c r="A95" s="4" t="s">
+        <v>834</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>835</v>
+      </c>
+      <c r="C95" s="3">
         <v>4224</v>
       </c>
-      <c r="D94" s="3">
-        <v>5</v>
-      </c>
-      <c r="E94" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F94" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G94" s="3">
+      <c r="D95" s="3">
+        <v>5</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G95" s="3">
         <v>27</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H95" s="3">
         <v>28</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-libanes\produtos-libanes\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EC787C4-4568-4A74-981D-81C11B8C2AEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70A4DA-B02F-4225-B4B0-B9621810AADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3712" uniqueCount="1117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3716" uniqueCount="1119">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3403,6 +3403,12 @@
   </si>
   <si>
     <t>XEREM DE AMENDOIM</t>
+  </si>
+  <si>
+    <t>ch-melao</t>
+  </si>
+  <si>
+    <t>CHÁ MELÃO SÃO CAETANO</t>
   </si>
 </sst>
 </file>
@@ -10108,7 +10114,7 @@
         <v>46</v>
       </c>
       <c r="H98" s="4">
-        <f t="shared" ref="H98:H129" si="3">MROUND(G98*1.03, 0.5)</f>
+        <f t="shared" ref="H98:H117" si="3">MROUND(G98*1.03, 0.5)</f>
         <v>47.5</v>
       </c>
     </row>
@@ -14781,7 +14787,7 @@
         <v>60</v>
       </c>
       <c r="H98" s="3">
-        <f t="shared" ref="H98:H129" si="3">MROUND(G98*1.03, 0.5)</f>
+        <f t="shared" ref="H98:H103" si="3">MROUND(G98*1.03, 0.5)</f>
         <v>62</v>
       </c>
     </row>
@@ -19129,7 +19135,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" bestFit="1" customWidth="1"/>
@@ -20055,7 +20061,7 @@
         <v>290</v>
       </c>
       <c r="H34" s="4">
-        <f t="shared" ref="H34:H65" si="1">MROUND(G34*1.03, 0.5)</f>
+        <f t="shared" ref="H34:H66" si="1">MROUND(G34*1.03, 0.5)</f>
         <v>298.5</v>
       </c>
     </row>
@@ -20601,29 +20607,29 @@
     </row>
     <row r="55" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>972</v>
+        <v>1117</v>
       </c>
       <c r="B55" t="s">
-        <v>973</v>
+        <v>1118</v>
       </c>
       <c r="C55" s="3">
-        <v>2725</v>
+        <v>4689</v>
       </c>
       <c r="D55" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E55" t="s">
         <v>30</v>
       </c>
       <c r="F55" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G55" s="3">
-        <v>550</v>
-      </c>
-      <c r="H55" s="3">
+        <v>33</v>
+      </c>
+      <c r="H55" s="4">
         <f t="shared" si="1"/>
-        <v>566.5</v>
+        <v>34</v>
       </c>
     </row>
     <row r="56" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20634,50 +20640,50 @@
         <v>973</v>
       </c>
       <c r="C56" s="3">
-        <v>2562</v>
+        <v>2725</v>
       </c>
       <c r="D56" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E56" t="s">
         <v>30</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G56" s="3">
-        <v>55</v>
+        <v>550</v>
       </c>
       <c r="H56" s="3">
         <f t="shared" si="1"/>
-        <v>56.5</v>
+        <v>566.5</v>
       </c>
     </row>
     <row r="57" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="B57" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="C57" s="3">
-        <v>2782</v>
+        <v>2562</v>
       </c>
       <c r="D57" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E57" t="s">
         <v>30</v>
       </c>
       <c r="F57" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G57" s="3">
-        <v>380</v>
-      </c>
-      <c r="H57" s="4">
+        <v>55</v>
+      </c>
+      <c r="H57" s="3">
         <f t="shared" si="1"/>
-        <v>391.5</v>
+        <v>56.5</v>
       </c>
     </row>
     <row r="58" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20688,50 +20694,50 @@
         <v>975</v>
       </c>
       <c r="C58" s="3">
-        <v>2745</v>
+        <v>2782</v>
       </c>
       <c r="D58" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E58" t="s">
         <v>30</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G58" s="3">
-        <v>19</v>
+        <v>380</v>
       </c>
       <c r="H58" s="4">
         <f t="shared" si="1"/>
-        <v>19.5</v>
+        <v>391.5</v>
       </c>
     </row>
     <row r="59" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="B59" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="C59" s="3">
-        <v>4207</v>
+        <v>2745</v>
       </c>
       <c r="D59" s="3">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="E59" t="s">
         <v>30</v>
       </c>
       <c r="F59" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G59" s="3">
-        <v>380</v>
+        <v>19</v>
       </c>
       <c r="H59" s="4">
         <f t="shared" si="1"/>
-        <v>391.5</v>
+        <v>19.5</v>
       </c>
     </row>
     <row r="60" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20742,37 +20748,37 @@
         <v>977</v>
       </c>
       <c r="C60" s="3">
-        <v>3769</v>
+        <v>4207</v>
       </c>
       <c r="D60" s="3">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E60" t="s">
         <v>30</v>
       </c>
       <c r="F60" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G60" s="3">
-        <v>190</v>
+        <v>380</v>
       </c>
       <c r="H60" s="4">
         <f t="shared" si="1"/>
-        <v>195.5</v>
+        <v>391.5</v>
       </c>
     </row>
     <row r="61" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="B61" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="C61" s="3">
-        <v>3034</v>
+        <v>3769</v>
       </c>
       <c r="D61" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E61" t="s">
         <v>30</v>
@@ -20781,11 +20787,11 @@
         <v>11</v>
       </c>
       <c r="G61" s="3">
-        <v>30</v>
-      </c>
-      <c r="H61" s="3">
+        <v>190</v>
+      </c>
+      <c r="H61" s="4">
         <f t="shared" si="1"/>
-        <v>31</v>
+        <v>195.5</v>
       </c>
     </row>
     <row r="62" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20796,50 +20802,50 @@
         <v>979</v>
       </c>
       <c r="C62" s="3">
+        <v>3034</v>
+      </c>
+      <c r="D62" s="3">
+        <v>1</v>
+      </c>
+      <c r="E62" t="s">
+        <v>30</v>
+      </c>
+      <c r="F62" t="s">
+        <v>11</v>
+      </c>
+      <c r="G62" s="3">
+        <v>30</v>
+      </c>
+      <c r="H62" s="3">
+        <f t="shared" si="1"/>
+        <v>31</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>978</v>
+      </c>
+      <c r="B63" t="s">
+        <v>979</v>
+      </c>
+      <c r="C63" s="3">
         <v>3039</v>
       </c>
-      <c r="D62" s="3">
+      <c r="D63" s="3">
         <v>25</v>
       </c>
-      <c r="E62" t="s">
-        <v>30</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="E63" t="s">
+        <v>30</v>
+      </c>
+      <c r="F63" t="s">
         <v>147</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G63" s="3">
         <v>750</v>
       </c>
-      <c r="H62" s="4">
+      <c r="H63" s="4">
         <f t="shared" si="1"/>
         <v>772.5</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>980</v>
-      </c>
-      <c r="B63" t="s">
-        <v>981</v>
-      </c>
-      <c r="C63" s="3">
-        <v>3421</v>
-      </c>
-      <c r="D63" s="3">
-        <v>20</v>
-      </c>
-      <c r="E63" t="s">
-        <v>30</v>
-      </c>
-      <c r="F63" t="s">
-        <v>147</v>
-      </c>
-      <c r="G63" s="3">
-        <v>420</v>
-      </c>
-      <c r="H63" s="4">
-        <f t="shared" si="1"/>
-        <v>432.5</v>
       </c>
     </row>
     <row r="64" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20850,10 +20856,10 @@
         <v>981</v>
       </c>
       <c r="C64" s="3">
-        <v>2748</v>
+        <v>3421</v>
       </c>
       <c r="D64" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E64" t="s">
         <v>30</v>
@@ -20862,11 +20868,11 @@
         <v>147</v>
       </c>
       <c r="G64" s="3">
-        <v>210</v>
+        <v>420</v>
       </c>
       <c r="H64" s="4">
         <f t="shared" si="1"/>
-        <v>216.5</v>
+        <v>432.5</v>
       </c>
     </row>
     <row r="65" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20877,34 +20883,34 @@
         <v>981</v>
       </c>
       <c r="C65" s="3">
-        <v>2576</v>
+        <v>2748</v>
       </c>
       <c r="D65" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E65" t="s">
         <v>30</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G65" s="3">
-        <v>21</v>
+        <v>210</v>
       </c>
       <c r="H65" s="4">
         <f t="shared" si="1"/>
-        <v>21.5</v>
+        <v>216.5</v>
       </c>
     </row>
     <row r="66" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="B66" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="C66" s="3">
-        <v>3032</v>
+        <v>2576</v>
       </c>
       <c r="D66" s="3">
         <v>1</v>
@@ -20916,38 +20922,38 @@
         <v>11</v>
       </c>
       <c r="G66" s="3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="H66" s="4">
-        <f t="shared" ref="H66:H97" si="2">MROUND(G66*1.03, 0.5)</f>
-        <v>19.5</v>
+        <f t="shared" si="1"/>
+        <v>21.5</v>
       </c>
     </row>
     <row r="67" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
       <c r="B67" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="C67" s="3">
-        <v>2740</v>
+        <v>3032</v>
       </c>
       <c r="D67" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E67" t="s">
         <v>30</v>
       </c>
       <c r="F67" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G67" s="3">
-        <v>780</v>
+        <v>19</v>
       </c>
       <c r="H67" s="4">
-        <f t="shared" si="2"/>
-        <v>803.5</v>
+        <f t="shared" ref="H67:H77" si="2">MROUND(G67*1.03, 0.5)</f>
+        <v>19.5</v>
       </c>
     </row>
     <row r="68" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20958,10 +20964,10 @@
         <v>985</v>
       </c>
       <c r="C68" s="3">
-        <v>3098</v>
+        <v>2740</v>
       </c>
       <c r="D68" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E68" t="s">
         <v>30</v>
@@ -20970,11 +20976,11 @@
         <v>147</v>
       </c>
       <c r="G68" s="3">
-        <v>390</v>
+        <v>780</v>
       </c>
       <c r="H68" s="4">
         <f t="shared" si="2"/>
-        <v>401.5</v>
+        <v>803.5</v>
       </c>
     </row>
     <row r="69" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20985,50 +20991,50 @@
         <v>985</v>
       </c>
       <c r="C69" s="3">
+        <v>3098</v>
+      </c>
+      <c r="D69" s="3">
+        <v>10</v>
+      </c>
+      <c r="E69" t="s">
+        <v>30</v>
+      </c>
+      <c r="F69" t="s">
+        <v>147</v>
+      </c>
+      <c r="G69" s="3">
+        <v>390</v>
+      </c>
+      <c r="H69" s="4">
+        <f t="shared" si="2"/>
+        <v>401.5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>984</v>
+      </c>
+      <c r="B70" t="s">
+        <v>985</v>
+      </c>
+      <c r="C70" s="3">
         <v>2743</v>
       </c>
-      <c r="D69" s="3">
+      <c r="D70" s="3">
         <v>1</v>
       </c>
-      <c r="E69" t="s">
-        <v>30</v>
-      </c>
-      <c r="F69" t="s">
-        <v>11</v>
-      </c>
-      <c r="G69" s="3">
+      <c r="E70" t="s">
+        <v>30</v>
+      </c>
+      <c r="F70" t="s">
+        <v>11</v>
+      </c>
+      <c r="G70" s="3">
         <v>39</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H70" s="3">
         <f t="shared" si="2"/>
         <v>40</v>
-      </c>
-    </row>
-    <row r="70" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>986</v>
-      </c>
-      <c r="B70" t="s">
-        <v>987</v>
-      </c>
-      <c r="C70" s="3">
-        <v>3360</v>
-      </c>
-      <c r="D70" s="3">
-        <v>25</v>
-      </c>
-      <c r="E70" t="s">
-        <v>30</v>
-      </c>
-      <c r="F70" t="s">
-        <v>147</v>
-      </c>
-      <c r="G70" s="3">
-        <v>300</v>
-      </c>
-      <c r="H70" s="3">
-        <f t="shared" si="2"/>
-        <v>309</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21039,10 +21045,10 @@
         <v>987</v>
       </c>
       <c r="C71" s="3">
-        <v>2611</v>
+        <v>3360</v>
       </c>
       <c r="D71" s="3">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="E71" t="s">
         <v>30</v>
@@ -21051,11 +21057,11 @@
         <v>147</v>
       </c>
       <c r="G71" s="3">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="H71" s="3">
         <f t="shared" si="2"/>
-        <v>618</v>
+        <v>309</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21066,50 +21072,50 @@
         <v>987</v>
       </c>
       <c r="C72" s="3">
+        <v>2611</v>
+      </c>
+      <c r="D72" s="3">
+        <v>50</v>
+      </c>
+      <c r="E72" t="s">
+        <v>30</v>
+      </c>
+      <c r="F72" t="s">
+        <v>147</v>
+      </c>
+      <c r="G72" s="3">
+        <v>600</v>
+      </c>
+      <c r="H72" s="3">
+        <f t="shared" si="2"/>
+        <v>618</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>986</v>
+      </c>
+      <c r="B73" t="s">
+        <v>987</v>
+      </c>
+      <c r="C73" s="3">
         <v>2558</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D73" s="3">
         <v>2</v>
       </c>
-      <c r="E72" t="s">
-        <v>30</v>
-      </c>
-      <c r="F72" t="s">
-        <v>11</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="E73" t="s">
+        <v>30</v>
+      </c>
+      <c r="F73" t="s">
+        <v>11</v>
+      </c>
+      <c r="G73" s="3">
         <v>24</v>
       </c>
-      <c r="H72" s="4">
+      <c r="H73" s="4">
         <f t="shared" si="2"/>
         <v>24.5</v>
-      </c>
-    </row>
-    <row r="73" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>988</v>
-      </c>
-      <c r="B73" t="s">
-        <v>989</v>
-      </c>
-      <c r="C73" s="3">
-        <v>3042</v>
-      </c>
-      <c r="D73" s="3">
-        <v>20</v>
-      </c>
-      <c r="E73" t="s">
-        <v>30</v>
-      </c>
-      <c r="F73" t="s">
-        <v>11</v>
-      </c>
-      <c r="G73" s="3">
-        <v>400</v>
-      </c>
-      <c r="H73" s="3">
-        <f t="shared" si="2"/>
-        <v>412</v>
       </c>
     </row>
     <row r="74" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21120,50 +21126,50 @@
         <v>989</v>
       </c>
       <c r="C74" s="3">
+        <v>3042</v>
+      </c>
+      <c r="D74" s="3">
+        <v>20</v>
+      </c>
+      <c r="E74" t="s">
+        <v>30</v>
+      </c>
+      <c r="F74" t="s">
+        <v>11</v>
+      </c>
+      <c r="G74" s="3">
+        <v>400</v>
+      </c>
+      <c r="H74" s="3">
+        <f t="shared" si="2"/>
+        <v>412</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>988</v>
+      </c>
+      <c r="B75" t="s">
+        <v>989</v>
+      </c>
+      <c r="C75" s="3">
         <v>2561</v>
       </c>
-      <c r="D74" s="3">
+      <c r="D75" s="3">
         <v>1</v>
       </c>
-      <c r="E74" t="s">
-        <v>30</v>
-      </c>
-      <c r="F74" t="s">
-        <v>11</v>
-      </c>
-      <c r="G74" s="3">
+      <c r="E75" t="s">
+        <v>30</v>
+      </c>
+      <c r="F75" t="s">
+        <v>11</v>
+      </c>
+      <c r="G75" s="3">
         <v>20</v>
       </c>
-      <c r="H74" s="4">
+      <c r="H75" s="4">
         <f t="shared" si="2"/>
         <v>20.5</v>
-      </c>
-    </row>
-    <row r="75" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>990</v>
-      </c>
-      <c r="B75" t="s">
-        <v>991</v>
-      </c>
-      <c r="C75" s="3">
-        <v>4226</v>
-      </c>
-      <c r="D75" s="3">
-        <v>1</v>
-      </c>
-      <c r="E75" t="s">
-        <v>30</v>
-      </c>
-      <c r="F75" t="s">
-        <v>11</v>
-      </c>
-      <c r="G75" s="3">
-        <v>35</v>
-      </c>
-      <c r="H75" s="3">
-        <f t="shared" si="2"/>
-        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21174,21 +21180,48 @@
         <v>991</v>
       </c>
       <c r="C76" s="3">
+        <v>4226</v>
+      </c>
+      <c r="D76" s="3">
+        <v>1</v>
+      </c>
+      <c r="E76" t="s">
+        <v>30</v>
+      </c>
+      <c r="F76" t="s">
+        <v>11</v>
+      </c>
+      <c r="G76" s="3">
+        <v>35</v>
+      </c>
+      <c r="H76" s="3">
+        <f t="shared" si="2"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>990</v>
+      </c>
+      <c r="B77" t="s">
+        <v>991</v>
+      </c>
+      <c r="C77" s="3">
         <v>4227</v>
       </c>
-      <c r="D76" s="3">
+      <c r="D77" s="3">
         <v>10</v>
       </c>
-      <c r="E76" t="s">
-        <v>30</v>
-      </c>
-      <c r="F76" t="s">
+      <c r="E77" t="s">
+        <v>30</v>
+      </c>
+      <c r="F77" t="s">
         <v>147</v>
       </c>
-      <c r="G76" s="3">
+      <c r="G77" s="3">
         <v>350</v>
       </c>
-      <c r="H76" s="4">
+      <c r="H77" s="4">
         <f t="shared" si="2"/>
         <v>360.5</v>
       </c>
@@ -22993,7 +23026,7 @@
         <v>190</v>
       </c>
       <c r="H66" s="4">
-        <f t="shared" ref="H66:H97" si="2">MROUND(G66*1.03, 0.5)</f>
+        <f t="shared" ref="H66:H71" si="2">MROUND(G66*1.03, 0.5)</f>
         <v>195.5</v>
       </c>
     </row>
@@ -23957,11 +23990,11 @@
         <v>147</v>
       </c>
       <c r="G30" s="3">
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="H30" s="4">
         <f t="shared" si="0"/>
-        <v>401.5</v>
+        <v>329.5</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -23984,11 +24017,11 @@
         <v>147</v>
       </c>
       <c r="G31" s="4">
-        <v>68</v>
+        <v>56.5</v>
       </c>
       <c r="H31" s="3">
         <f t="shared" si="0"/>
-        <v>70</v>
+        <v>58</v>
       </c>
     </row>
     <row r="32" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24011,11 +24044,11 @@
         <v>147</v>
       </c>
       <c r="G32" s="3">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="H32" s="4">
         <f t="shared" si="0"/>
-        <v>360.5</v>
+        <v>340</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -24038,11 +24071,11 @@
         <v>11</v>
       </c>
       <c r="G33" s="3">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="H33" s="3">
         <f t="shared" si="0"/>
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -24932,7 +24965,7 @@
         <v>330</v>
       </c>
       <c r="H66" s="3">
-        <f t="shared" ref="H66:H97" si="2">MROUND(G66*1.03, 0.5)</f>
+        <f t="shared" ref="H66:H94" si="2">MROUND(G66*1.03, 0.5)</f>
         <v>340</v>
       </c>
     </row>
@@ -28356,7 +28389,7 @@
         <v>95</v>
       </c>
       <c r="H98" s="3">
-        <f t="shared" ref="H98:H129" si="3">MROUND(G98*1.03, 0.5)</f>
+        <f t="shared" ref="H98:H116" si="3">MROUND(G98*1.03, 0.5)</f>
         <v>98</v>
       </c>
     </row>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\astra\Documents\lista-libanes\produtos-libanes\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB70A4DA-B02F-4225-B4B0-B9621810AADD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F36B131-B8ED-4793-9118-226863C244A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="3" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="promoçoes" sheetId="1" r:id="rId1"/>
@@ -10862,11 +10862,11 @@
         <v>90</v>
       </c>
       <c r="G8" s="3">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="H8" s="4">
         <f t="shared" si="0"/>
-        <v>84.5</v>
+        <v>88.5</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10889,11 +10889,11 @@
         <v>90</v>
       </c>
       <c r="G9" s="4">
-        <v>25.5</v>
+        <v>26.5</v>
       </c>
       <c r="H9" s="4">
         <f t="shared" si="0"/>
-        <v>26.5</v>
+        <v>27.5</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -4981,7 +4981,7 @@
         <v>147</v>
       </c>
       <c r="G5" s="3">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H5" s="5">
         <f>MROUND(G5*1.03, 0.5)</f>
@@ -5007,7 +5007,7 @@
         <v>147</v>
       </c>
       <c r="G6" s="3">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="H6" s="3">
         <f>MROUND(G6*1.03, 0.5)</f>
@@ -5449,7 +5449,7 @@
         <v>147</v>
       </c>
       <c r="G23" s="3">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="H23" s="3">
         <f>MROUND(G23*1.03, 0.5)</f>
@@ -5475,7 +5475,7 @@
         <v>147</v>
       </c>
       <c r="G24" s="3">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H24" s="3">
         <f>MROUND(G24*1.03, 0.5)</f>
@@ -5683,7 +5683,7 @@
         <v>147</v>
       </c>
       <c r="G32" s="3">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H32" s="3">
         <f>MROUND(G32*1.03, 0.5)</f>
@@ -5709,7 +5709,7 @@
         <v>11</v>
       </c>
       <c r="G33" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H33" s="3">
         <f>MROUND(G33*1.03, 0.5)</f>
@@ -5735,7 +5735,7 @@
         <v>147</v>
       </c>
       <c r="G34" s="3">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H34" s="3">
         <f>MROUND(G34*1.03, 0.5)</f>
@@ -5761,7 +5761,7 @@
         <v>11</v>
       </c>
       <c r="G35" s="3">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H35" s="3">
         <f>MROUND(G35*1.03, 0.5)</f>
@@ -17362,7 +17362,7 @@
         <v>16</v>
       </c>
       <c r="G66" s="3">
-        <v>1110</v>
+        <v>1240</v>
       </c>
       <c r="H66" s="3">
         <f>MROUND(G64*1.03, 0.5)</f>
@@ -17388,7 +17388,7 @@
         <v>11</v>
       </c>
       <c r="G67" s="3">
-        <v>281</v>
+        <v>313.5</v>
       </c>
       <c r="H67" s="5">
         <f>MROUND(G65*1.03, 0.5)</f>
@@ -25404,7 +25404,7 @@
         <v>147</v>
       </c>
       <c r="G11" s="5">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="H11" s="3">
         <f>MROUND(G11*1.03, 0.5)</f>
@@ -25430,7 +25430,7 @@
         <v>147</v>
       </c>
       <c r="G12" s="3">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="H12" s="3">
         <f>MROUND(G12*1.03, 0.5)</f>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="2"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -3403,7 +3403,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3421,12 +3421,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3478,7 +3472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3511,12 +3505,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4244,10 +4232,10 @@
         <v>16</v>
       </c>
       <c r="G16" s="6">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H16" s="6">
-        <v>180</v>
+        <v>160</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
@@ -6498,7 +6486,7 @@
         <v>16</v>
       </c>
       <c r="G24" s="5">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="H24" s="6">
         <f>MROUND(G24*1.03, 0.5)</f>
@@ -16893,10 +16881,10 @@
       <c r="B48" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="5">
         <v>4691</v>
       </c>
-      <c r="D48" s="12">
+      <c r="D48" s="5">
         <v>11.34</v>
       </c>
       <c r="E48" s="4" t="s">
@@ -16905,7 +16893,7 @@
       <c r="F48" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="G48" s="13">
+      <c r="G48" s="6">
         <v>476</v>
       </c>
       <c r="H48" s="6">
@@ -16919,10 +16907,10 @@
       <c r="B49" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="5">
         <v>4692</v>
       </c>
-      <c r="D49" s="12">
+      <c r="D49" s="5">
         <v>5</v>
       </c>
       <c r="E49" s="4" t="s">
@@ -16931,7 +16919,7 @@
       <c r="F49" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G49" s="13">
+      <c r="G49" s="6">
         <v>213.5</v>
       </c>
       <c r="H49" s="6">
@@ -17094,7 +17082,7 @@
         <f>MROUND(G53*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="4" t="s">
         <v>1086</v>
       </c>
@@ -17120,7 +17108,7 @@
         <f>MROUND(G54*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="4" t="s">
         <v>1088</v>
       </c>
@@ -17146,7 +17134,7 @@
         <f>MROUND(G55*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
       <c r="A58" s="4" t="s">
         <v>1088</v>
       </c>
@@ -17172,7 +17160,7 @@
         <f>MROUND(G56*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="4" t="s">
         <v>1088</v>
       </c>
@@ -17198,7 +17186,7 @@
         <f>MROUND(G57*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="4" t="s">
         <v>1090</v>
       </c>
@@ -17224,7 +17212,7 @@
         <f>MROUND(G58*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="4" t="s">
         <v>1090</v>
       </c>
@@ -17250,7 +17238,7 @@
         <f>MROUND(G59*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="4" t="s">
         <v>1092</v>
       </c>
@@ -17276,7 +17264,7 @@
         <f>MROUND(G60*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
       <c r="A63" s="4" t="s">
         <v>1092</v>
       </c>
@@ -17302,7 +17290,7 @@
         <f>MROUND(G61*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="4" t="s">
         <v>1094</v>
       </c>
@@ -17328,7 +17316,7 @@
         <f>MROUND(G62*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="4" t="s">
         <v>1094</v>
       </c>
@@ -17354,7 +17342,7 @@
         <f>MROUND(G63*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="4" t="s">
         <v>1096</v>
       </c>
@@ -17380,7 +17368,7 @@
         <f>MROUND(G64*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="4" t="s">
         <v>1096</v>
       </c>
@@ -17406,7 +17394,7 @@
         <f>MROUND(G65*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="4" t="s">
         <v>1098</v>
       </c>
@@ -17432,7 +17420,7 @@
         <f>MROUND(G66*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
       <c r="A69" s="4" t="s">
         <v>1098</v>
       </c>
@@ -17458,7 +17446,7 @@
         <f>MROUND(G67*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="4" t="s">
         <v>1100</v>
       </c>
@@ -17484,7 +17472,7 @@
         <f>MROUND(G68*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="4" t="s">
         <v>1100</v>
       </c>
@@ -17510,7 +17498,7 @@
         <f>MROUND(G69*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="4" t="s">
         <v>1102</v>
       </c>
@@ -17536,7 +17524,7 @@
         <f>MROUND(G70*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="4" t="s">
         <v>1102</v>
       </c>
@@ -17562,7 +17550,7 @@
         <f>MROUND(G71*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="4" t="s">
         <v>1105</v>
       </c>
@@ -17588,7 +17576,7 @@
         <f>MROUND(G72*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="4" t="s">
         <v>1105</v>
       </c>
@@ -17614,7 +17602,7 @@
         <f>MROUND(G73*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="4" t="s">
         <v>1107</v>
       </c>
@@ -17640,7 +17628,7 @@
         <f>MROUND(G74*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="4" t="s">
         <v>1107</v>
       </c>
@@ -17666,7 +17654,7 @@
         <f>MROUND(G75*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="4" t="s">
         <v>1109</v>
       </c>
@@ -17692,7 +17680,7 @@
         <f>MROUND(G76*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="4" t="s">
         <v>1109</v>
       </c>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3724" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="1122">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -1731,6 +1731,9 @@
   </si>
   <si>
     <t>FLOCAO DE ARROZ CORINGA</t>
+  </si>
+  <si>
+    <t>floco-de-arroz</t>
   </si>
   <si>
     <t>floco-de-milho-coringa</t>
@@ -3472,7 +3475,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -3503,6 +3506,12 @@
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="2" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -3850,10 +3859,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C2" s="5">
         <v>109</v>
@@ -3876,10 +3885,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C3" s="5">
         <v>2419</v>
@@ -3900,12 +3909,12 @@
         <v>35.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C4" s="5">
         <v>3110</v>
@@ -3926,12 +3935,12 @@
         <v>89.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C5" s="5">
         <v>3821</v>
@@ -3952,12 +3961,12 @@
         <v>144</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C6" s="5">
         <v>2263</v>
@@ -3978,12 +3987,12 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C7" s="5">
         <v>564</v>
@@ -4004,12 +4013,12 @@
         <v>121.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C8" s="5">
         <v>2256</v>
@@ -4030,12 +4039,12 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C9" s="5">
         <v>261</v>
@@ -4056,12 +4065,12 @@
         <v>85.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C10" s="5">
         <v>2475</v>
@@ -4082,12 +4091,12 @@
         <v>19</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C11" s="5">
         <v>92</v>
@@ -4108,12 +4117,12 @@
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C12" s="5">
         <v>2476</v>
@@ -4134,7 +4143,7 @@
         <v>12</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>548</v>
       </c>
@@ -4160,7 +4169,7 @@
         <v>113.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>550</v>
       </c>
@@ -4186,7 +4195,7 @@
         <v>102</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>532</v>
       </c>
@@ -4212,7 +4221,7 @@
         <v>258</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>542</v>
       </c>
@@ -4238,7 +4247,7 @@
         <v>160</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>506</v>
       </c>
@@ -4264,7 +4273,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>506</v>
       </c>
@@ -4290,7 +4299,7 @@
         <v>390</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>508</v>
       </c>
@@ -4316,7 +4325,7 @@
         <v>296</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>508</v>
       </c>
@@ -4342,7 +4351,7 @@
         <v>62.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>334</v>
       </c>
@@ -4368,7 +4377,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>338</v>
       </c>
@@ -4394,7 +4403,7 @@
         <v>16.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>338</v>
       </c>
@@ -4420,7 +4429,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>334</v>
       </c>
@@ -4446,7 +4455,7 @@
         <v>121.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>69</v>
       </c>
@@ -4472,7 +4481,7 @@
         <v>235</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
         <v>69</v>
       </c>
@@ -4498,7 +4507,7 @@
         <v>78.5</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
         <v>80</v>
       </c>
@@ -4844,7 +4853,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H38"/>
+  <dimension ref="A1:H39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -5304,166 +5313,166 @@
         <v>566</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="C18" s="5">
-        <v>4048</v>
-      </c>
-      <c r="D18" s="5">
-        <v>20</v>
+        <v>375</v>
+      </c>
+      <c r="C18" s="12">
+        <v>4697</v>
+      </c>
+      <c r="D18" s="12">
+        <v>1</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="G18" s="5">
-        <v>55</v>
+        <v>11</v>
+      </c>
+      <c r="G18" s="13">
+        <v>14</v>
       </c>
       <c r="H18" s="6">
-        <f>MROUND(G18*1.03, 0.5)</f>
+        <f>MROUND(G17*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>569</v>
-      </c>
       <c r="C19" s="5">
-        <v>2519</v>
+        <v>4048</v>
       </c>
       <c r="D19" s="5">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>30</v>
+        <v>115</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>147</v>
+        <v>90</v>
       </c>
       <c r="G19" s="5">
-        <v>530</v>
-      </c>
-      <c r="H19" s="5">
-        <f>MROUND(G19*1.03, 0.5)</f>
+        <v>55</v>
+      </c>
+      <c r="H19" s="6">
+        <f>MROUND(G18*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="C20" s="5">
-        <v>2525</v>
+        <v>2519</v>
       </c>
       <c r="D20" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G20" s="5">
-        <v>275</v>
-      </c>
-      <c r="H20" s="6">
-        <f>MROUND(G20*1.03, 0.5)</f>
+        <v>530</v>
+      </c>
+      <c r="H20" s="5">
+        <f>MROUND(G19*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="B21" s="4" t="s">
-        <v>571</v>
-      </c>
       <c r="C21" s="5">
-        <v>3433</v>
+        <v>2525</v>
       </c>
       <c r="D21" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G21" s="5">
-        <v>940</v>
-      </c>
-      <c r="H21" s="5">
-        <f>MROUND(G21*1.03, 0.5)</f>
+        <v>275</v>
+      </c>
+      <c r="H21" s="6">
+        <f>MROUND(G20*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="C22" s="5">
-        <v>3394</v>
+        <v>3433</v>
       </c>
       <c r="D22" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G22" s="5">
-        <v>237</v>
+        <v>940</v>
       </c>
       <c r="H22" s="5">
-        <f>MROUND(G22*1.03, 0.5)</f>
+        <f>MROUND(G21*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
+        <v>571</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>573</v>
-      </c>
       <c r="C23" s="5">
-        <v>47</v>
+        <v>3394</v>
       </c>
       <c r="D23" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G23" s="5">
-        <v>139</v>
+        <v>237</v>
       </c>
       <c r="H23" s="5">
-        <f>MROUND(G23*1.03, 0.5)</f>
+        <f>MROUND(G22*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>575</v>
-      </c>
       <c r="C24" s="5">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D24" s="5">
         <v>25</v>
@@ -5475,24 +5484,24 @@
         <v>147</v>
       </c>
       <c r="G24" s="5">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="H24" s="5">
-        <f>MROUND(G24*1.03, 0.5)</f>
+        <f>MROUND(G23*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
+        <v>575</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="B25" s="4" t="s">
-        <v>577</v>
-      </c>
       <c r="C25" s="5">
-        <v>3100</v>
+        <v>46</v>
       </c>
       <c r="D25" s="5">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>30</v>
@@ -5501,24 +5510,24 @@
         <v>147</v>
       </c>
       <c r="G25" s="5">
-        <v>209</v>
-      </c>
-      <c r="H25" s="6">
-        <f>MROUND(G25*1.03, 0.5)</f>
+        <v>135</v>
+      </c>
+      <c r="H25" s="5">
+        <f>MROUND(G24*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
+        <v>577</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>579</v>
-      </c>
       <c r="C26" s="5">
-        <v>3746</v>
+        <v>3100</v>
       </c>
       <c r="D26" s="5">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>30</v>
@@ -5527,21 +5536,21 @@
         <v>147</v>
       </c>
       <c r="G26" s="5">
-        <v>119</v>
+        <v>209</v>
       </c>
       <c r="H26" s="6">
-        <f>MROUND(G26*1.03, 0.5)</f>
+        <f>MROUND(G25*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>581</v>
-      </c>
       <c r="C27" s="5">
-        <v>3639</v>
+        <v>3746</v>
       </c>
       <c r="D27" s="5">
         <v>15</v>
@@ -5556,21 +5565,21 @@
         <v>119</v>
       </c>
       <c r="H27" s="6">
-        <f>MROUND(G27*1.03, 0.5)</f>
+        <f>MROUND(G26*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
+        <v>581</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="B28" s="4" t="s">
-        <v>583</v>
-      </c>
       <c r="C28" s="5">
-        <v>2415</v>
+        <v>3639</v>
       </c>
       <c r="D28" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>30</v>
@@ -5578,25 +5587,25 @@
       <c r="F28" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G28" s="6">
-        <v>158.5</v>
+      <c r="G28" s="5">
+        <v>119</v>
       </c>
       <c r="H28" s="6">
-        <f>MROUND(G28*1.03, 0.5)</f>
+        <f>MROUND(G27*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
+        <v>583</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="B29" s="4" t="s">
-        <v>585</v>
-      </c>
       <c r="C29" s="5">
-        <v>3747</v>
+        <v>2415</v>
       </c>
       <c r="D29" s="5">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>30</v>
@@ -5604,22 +5613,22 @@
       <c r="F29" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G29" s="5">
-        <v>119</v>
+      <c r="G29" s="6">
+        <v>158.5</v>
       </c>
       <c r="H29" s="6">
-        <f>MROUND(G29*1.03, 0.5)</f>
+        <f>MROUND(G28*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
+        <v>585</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="B30" s="4" t="s">
-        <v>587</v>
-      </c>
       <c r="C30" s="5">
-        <v>3640</v>
+        <v>3747</v>
       </c>
       <c r="D30" s="5">
         <v>15</v>
@@ -5631,24 +5640,24 @@
         <v>147</v>
       </c>
       <c r="G30" s="5">
-        <v>158.5</v>
+        <v>119</v>
       </c>
       <c r="H30" s="6">
-        <f>MROUND(G30*1.03, 0.5)</f>
+        <f>MROUND(G29*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="B31" s="4" t="s">
-        <v>589</v>
-      </c>
       <c r="C31" s="5">
-        <v>2416</v>
+        <v>3640</v>
       </c>
       <c r="D31" s="5">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>30</v>
@@ -5656,25 +5665,25 @@
       <c r="F31" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G31" s="6">
-        <v>153.5</v>
-      </c>
-      <c r="H31" s="5">
-        <f>MROUND(G31*1.03, 0.5)</f>
+      <c r="G31" s="5">
+        <v>158.5</v>
+      </c>
+      <c r="H31" s="6">
+        <f>MROUND(G30*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="B32" s="4" t="s">
-        <v>591</v>
-      </c>
       <c r="C32" s="5">
-        <v>50</v>
+        <v>2416</v>
       </c>
       <c r="D32" s="5">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>30</v>
@@ -5682,126 +5691,126 @@
       <c r="F32" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="G32" s="5">
-        <v>170</v>
+      <c r="G32" s="6">
+        <v>153.5</v>
       </c>
       <c r="H32" s="5">
-        <f>MROUND(G32*1.03, 0.5)</f>
+        <f>MROUND(G31*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C33" s="5">
-        <v>2533</v>
+        <v>50</v>
       </c>
       <c r="D33" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G33" s="5">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="H33" s="5">
-        <f>MROUND(G33*1.03, 0.5)</f>
+        <f>MROUND(G32*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="B34" s="4" t="s">
-        <v>593</v>
-      </c>
       <c r="C34" s="5">
-        <v>52</v>
+        <v>2533</v>
       </c>
       <c r="D34" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G34" s="5">
-        <v>170</v>
+        <v>37</v>
       </c>
       <c r="H34" s="5">
-        <f>MROUND(G34*1.03, 0.5)</f>
+        <f>MROUND(G33*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C35" s="5">
-        <v>2470</v>
+        <v>52</v>
       </c>
       <c r="D35" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>11</v>
+        <v>147</v>
       </c>
       <c r="G35" s="5">
-        <v>37</v>
+        <v>170</v>
       </c>
       <c r="H35" s="5">
-        <f>MROUND(G35*1.03, 0.5)</f>
+        <f>MROUND(G34*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>595</v>
-      </c>
       <c r="C36" s="5">
-        <v>4671</v>
+        <v>2470</v>
       </c>
       <c r="D36" s="5">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>147</v>
+        <v>11</v>
       </c>
       <c r="G36" s="5">
-        <v>164</v>
+        <v>37</v>
       </c>
       <c r="H36" s="5">
-        <f>MROUND(G36*1.03, 0.5)</f>
+        <f>MROUND(G35*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>597</v>
-      </c>
       <c r="C37" s="5">
-        <v>53</v>
+        <v>4671</v>
       </c>
       <c r="D37" s="5">
         <v>25</v>
@@ -5813,35 +5822,61 @@
         <v>147</v>
       </c>
       <c r="G37" s="5">
-        <v>118</v>
-      </c>
-      <c r="H37" s="6">
-        <f>MROUND(G37*1.03, 0.5)</f>
+        <v>164</v>
+      </c>
+      <c r="H37" s="5">
+        <f>MROUND(G36*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C38" s="5">
+        <v>53</v>
+      </c>
+      <c r="D38" s="5">
+        <v>25</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="G38" s="5">
+        <v>125</v>
+      </c>
+      <c r="H38" s="6">
+        <f>MROUND(G37*1.03, 0.5)</f>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
+      <c r="A39" s="4" t="s">
         <v>597</v>
       </c>
-      <c r="C38" s="5">
+      <c r="B39" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="C39" s="5">
         <v>2435</v>
       </c>
-      <c r="D38" s="5">
-        <v>5</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G38" s="6">
-        <v>25.5</v>
-      </c>
-      <c r="H38" s="6">
+      <c r="D39" s="5">
+        <v>5</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G39" s="6">
+        <v>28</v>
+      </c>
+      <c r="H39" s="6">
         <f>MROUND(G38*1.03, 0.5)</f>
       </c>
     </row>
@@ -15680,10 +15715,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="C2" s="5">
         <v>585</v>
@@ -15706,10 +15741,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C3" s="5">
         <v>467</v>
@@ -15732,10 +15767,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C4" s="5">
         <v>4685</v>
@@ -15758,10 +15793,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C5" s="5">
         <v>4686</v>
@@ -15784,10 +15819,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C6" s="5">
         <v>3391</v>
@@ -15810,10 +15845,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C7" s="5">
         <v>3399</v>
@@ -15836,10 +15871,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C8" s="5">
         <v>2405</v>
@@ -15862,10 +15897,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C9" s="5">
         <v>2444</v>
@@ -15888,10 +15923,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C10" s="5">
         <v>3390</v>
@@ -15914,10 +15949,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C11" s="5">
         <v>3404</v>
@@ -15940,10 +15975,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C12" s="5">
         <v>3105</v>
@@ -15966,10 +16001,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="C13" s="5">
         <v>2445</v>
@@ -15992,10 +16027,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C14" s="5">
         <v>2446</v>
@@ -16018,10 +16053,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C15" s="5">
         <v>2781</v>
@@ -16044,10 +16079,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C16" s="5">
         <v>3463</v>
@@ -16070,10 +16105,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="C17" s="5">
         <v>3367</v>
@@ -16096,10 +16131,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C18" s="5">
         <v>3464</v>
@@ -16122,10 +16157,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="C19" s="5">
         <v>3368</v>
@@ -16148,10 +16183,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C20" s="5">
         <v>3465</v>
@@ -16174,10 +16209,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="C21" s="5">
         <v>3372</v>
@@ -16200,10 +16235,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C22" s="5">
         <v>3466</v>
@@ -16226,10 +16261,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C23" s="5">
         <v>3380</v>
@@ -16252,10 +16287,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C24" s="5">
         <v>3821</v>
@@ -16278,10 +16313,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="C25" s="5">
         <v>2263</v>
@@ -16304,10 +16339,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C26" s="5">
         <v>465</v>
@@ -16330,10 +16365,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="C27" s="5">
         <v>2643</v>
@@ -16356,10 +16391,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C28" s="5">
         <v>2644</v>
@@ -16382,10 +16417,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="C29" s="5">
         <v>2570</v>
@@ -16408,10 +16443,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C30" s="5">
         <v>3021</v>
@@ -16434,10 +16469,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C31" s="5">
         <v>109</v>
@@ -16460,10 +16495,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="C32" s="5">
         <v>2419</v>
@@ -16486,10 +16521,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C33" s="5">
         <v>3505</v>
@@ -16512,10 +16547,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="C34" s="5">
         <v>2443</v>
@@ -16538,10 +16573,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C35" s="5">
         <v>2283</v>
@@ -16564,10 +16599,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C36" s="5">
         <v>4255</v>
@@ -16590,10 +16625,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C37" s="5">
         <v>103</v>
@@ -16616,10 +16651,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C38" s="5">
         <v>2629</v>
@@ -16642,10 +16677,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C39" s="5">
         <v>2452</v>
@@ -16668,10 +16703,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C40" s="5">
         <v>150</v>
@@ -16694,10 +16729,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C41" s="5">
         <v>2453</v>
@@ -16720,10 +16755,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C42" s="5">
         <v>2450</v>
@@ -16746,10 +16781,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C43" s="5">
         <v>7</v>
@@ -16772,10 +16807,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="C44" s="5">
         <v>2451</v>
@@ -16798,10 +16833,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C45" s="5">
         <v>468</v>
@@ -16824,10 +16859,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C46" s="5">
         <v>4138</v>
@@ -16850,10 +16885,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C47" s="5">
         <v>2508</v>
@@ -16876,10 +16911,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C48" s="5">
         <v>4691</v>
@@ -16902,10 +16937,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C49" s="5">
         <v>4692</v>
@@ -16928,10 +16963,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C50" s="5">
         <v>2442</v>
@@ -16954,10 +16989,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C51" s="5">
         <v>2524</v>
@@ -16980,10 +17015,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C52" s="5">
         <v>3441</v>
@@ -17006,10 +17041,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C53" s="5">
         <v>2523</v>
@@ -17032,10 +17067,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C54" s="5">
         <v>3408</v>
@@ -17058,10 +17093,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C55" s="5">
         <v>2273</v>
@@ -17084,10 +17119,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="19.5">
       <c r="A56" s="4" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C56" s="5">
         <v>2271</v>
@@ -17110,10 +17145,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="19.5">
       <c r="A57" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C57" s="5">
         <v>3409</v>
@@ -17136,10 +17171,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="19.5">
       <c r="A58" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C58" s="5">
         <v>459</v>
@@ -17162,10 +17197,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="19.5">
       <c r="A59" s="4" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C59" s="5">
         <v>285</v>
@@ -17188,10 +17223,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="19.5">
       <c r="A60" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C60" s="5">
         <v>2291</v>
@@ -17214,10 +17249,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="19.5">
       <c r="A61" s="4" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C61" s="5">
         <v>2252</v>
@@ -17240,10 +17275,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="19.5">
       <c r="A62" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C62" s="5">
         <v>3534</v>
@@ -17266,10 +17301,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="19.5">
       <c r="A63" s="4" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C63" s="5">
         <v>2250</v>
@@ -17292,10 +17327,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="19.5">
       <c r="A64" s="4" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C64" s="5">
         <v>2340</v>
@@ -17318,10 +17353,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="19.5">
       <c r="A65" s="4" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="C65" s="5">
         <v>3533</v>
@@ -17344,10 +17379,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="19.5">
       <c r="A66" s="4" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C66" s="5">
         <v>3532</v>
@@ -17370,10 +17405,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="19.5">
       <c r="A67" s="4" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="C67" s="5">
         <v>2251</v>
@@ -17396,10 +17431,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="19.5">
       <c r="A68" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C68" s="5">
         <v>3081</v>
@@ -17422,10 +17457,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="19.5">
       <c r="A69" s="4" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C69" s="5">
         <v>3818</v>
@@ -17448,10 +17483,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="19.5">
       <c r="A70" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C70" s="5">
         <v>2534</v>
@@ -17474,10 +17509,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="19.5">
       <c r="A71" s="4" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="C71" s="5">
         <v>2234</v>
@@ -17500,10 +17535,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="19.5">
       <c r="A72" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C72" s="5">
         <v>2238</v>
@@ -17526,10 +17561,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="19.5">
       <c r="A73" s="4" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="C73" s="5">
         <v>2535</v>
@@ -17552,10 +17587,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="19.5">
       <c r="A74" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C74" s="5">
         <v>2512</v>
@@ -17578,10 +17613,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="19.5">
       <c r="A75" s="4" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C75" s="5">
         <v>2537</v>
@@ -17604,10 +17639,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="19.5">
       <c r="A76" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C76" s="5">
         <v>2236</v>
@@ -17630,10 +17665,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="19.5">
       <c r="A77" s="4" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="C77" s="5">
         <v>2546</v>
@@ -17656,10 +17691,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="19.5">
       <c r="A78" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C78" s="5">
         <v>2232</v>
@@ -17682,10 +17717,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="19.5">
       <c r="A79" s="4" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="C79" s="5">
         <v>2536</v>
@@ -17708,10 +17743,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C80" s="5">
         <v>4021</v>
@@ -17734,10 +17769,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="4" t="s">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C81" s="5">
         <v>4135</v>
@@ -17760,10 +17795,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C82" s="5">
         <v>2852</v>
@@ -17786,10 +17821,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C83" s="5">
         <v>3601</v>
@@ -17812,10 +17847,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C84" s="5">
         <v>3093</v>
@@ -17838,10 +17873,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C85" s="5">
         <v>263</v>
@@ -17864,10 +17899,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C86" s="5">
         <v>2632</v>
@@ -17890,10 +17925,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C87" s="5">
         <v>2330</v>
@@ -17916,10 +17951,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C88" s="5">
         <v>2385</v>
@@ -17942,10 +17977,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C89" s="5">
         <v>2384</v>
@@ -17968,10 +18003,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C90" s="5">
         <v>3851</v>
@@ -17994,10 +18029,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C91" s="5">
         <v>2424</v>
@@ -18069,10 +18104,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C2" s="5">
         <v>85</v>
@@ -18095,10 +18130,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="C3" s="5">
         <v>2447</v>
@@ -18121,10 +18156,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C4" s="5">
         <v>551</v>
@@ -18147,10 +18182,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C5" s="5">
         <v>2448</v>
@@ -18173,10 +18208,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C6" s="5">
         <v>3559</v>
@@ -18199,10 +18234,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="C7" s="5">
         <v>3560</v>
@@ -18225,10 +18260,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C8" s="5">
         <v>255</v>
@@ -18251,10 +18286,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C9" s="5">
         <v>2456</v>
@@ -18277,10 +18312,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C10" s="5">
         <v>80</v>
@@ -18303,10 +18338,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="C11" s="5">
         <v>2457</v>
@@ -18329,10 +18364,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C12" s="5">
         <v>94</v>
@@ -18355,10 +18390,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C13" s="5">
         <v>2458</v>
@@ -18381,10 +18416,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C14" s="5">
         <v>2454</v>
@@ -18407,10 +18442,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C15" s="5">
         <v>2455</v>
@@ -18433,10 +18468,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C16" s="5">
         <v>450</v>
@@ -18459,10 +18494,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C17" s="5">
         <v>2459</v>
@@ -18534,10 +18569,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="C2" s="5">
         <v>2314</v>
@@ -18560,10 +18595,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="C3" s="5">
         <v>2313</v>
@@ -18586,10 +18621,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="C4" s="5">
         <v>2316</v>
@@ -18612,10 +18647,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="C5" s="5">
         <v>2312</v>
@@ -18638,10 +18673,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="C6" s="5">
         <v>3513</v>
@@ -18664,10 +18699,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C7" s="5">
         <v>2315</v>
@@ -18690,10 +18725,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="C8" s="5">
         <v>3512</v>
@@ -18716,10 +18751,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="C9" s="5">
         <v>2311</v>
@@ -18791,10 +18826,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C2" s="5">
         <v>3440</v>
@@ -18817,10 +18852,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="C3" s="5">
         <v>2832</v>
@@ -18843,10 +18878,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="C4" s="5">
         <v>4337</v>
@@ -18869,10 +18904,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C5" s="5">
         <v>4667</v>
@@ -18895,10 +18930,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="C6" s="5">
         <v>4668</v>
@@ -18921,10 +18956,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C7" s="5">
         <v>3045</v>
@@ -18947,10 +18982,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C8" s="5">
         <v>4376</v>
@@ -18973,10 +19008,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C9" s="5">
         <v>2625</v>
@@ -18999,10 +19034,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C10" s="5">
         <v>2717</v>
@@ -19025,10 +19060,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="C11" s="5">
         <v>2573</v>
@@ -19051,10 +19086,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C12" s="5">
         <v>2504</v>
@@ -19077,10 +19112,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="C13" s="5">
         <v>2505</v>
@@ -19103,10 +19138,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C14" s="5">
         <v>3043</v>
@@ -19129,10 +19164,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="C15" s="5">
         <v>2557</v>
@@ -19155,10 +19190,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C16" s="5">
         <v>2540</v>
@@ -19181,10 +19216,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="C17" s="5">
         <v>3503</v>
@@ -19207,10 +19242,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C18" s="5">
         <v>2691</v>
@@ -19233,10 +19268,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C19" s="5">
         <v>2692</v>
@@ -19259,10 +19294,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C20" s="5">
         <v>3484</v>
@@ -19285,10 +19320,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="C21" s="5">
         <v>3485</v>
@@ -19311,10 +19346,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C22" s="5">
         <v>3976</v>
@@ -19337,10 +19372,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="C23" s="5">
         <v>2780</v>
@@ -19363,10 +19398,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="C24" s="5">
         <v>3406</v>
@@ -19389,10 +19424,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C25" s="5">
         <v>3040</v>
@@ -19415,10 +19450,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="C26" s="5">
         <v>3041</v>
@@ -19441,10 +19476,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C27" s="5">
         <v>2741</v>
@@ -19467,10 +19502,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C28" s="5">
         <v>2559</v>
@@ -19493,10 +19528,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C29" s="5">
         <v>2526</v>
@@ -19519,10 +19554,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="C30" s="5">
         <v>2527</v>
@@ -19545,10 +19580,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="C31" s="5">
         <v>3063</v>
@@ -19571,10 +19606,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C32" s="5">
         <v>4251</v>
@@ -19597,10 +19632,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="C33" s="5">
         <v>4250</v>
@@ -19623,10 +19658,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C34" s="5">
         <v>2739</v>
@@ -19649,10 +19684,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="C35" s="5">
         <v>2560</v>
@@ -19675,10 +19710,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C36" s="5">
         <v>2742</v>
@@ -19701,10 +19736,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C37" s="5">
         <v>2744</v>
@@ -19727,10 +19762,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C38" s="5">
         <v>4072</v>
@@ -19753,10 +19788,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="C39" s="5">
         <v>4071</v>
@@ -19779,10 +19814,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C40" s="5">
         <v>2696</v>
@@ -19805,10 +19840,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="C41" s="5">
         <v>2697</v>
@@ -19831,10 +19866,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C42" s="5">
         <v>3044</v>
@@ -19857,10 +19892,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="C43" s="5">
         <v>2746</v>
@@ -19883,10 +19918,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="C44" s="5">
         <v>2713</v>
@@ -19909,10 +19944,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C45" s="5">
         <v>3037</v>
@@ -19935,10 +19970,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C46" s="5">
         <v>3038</v>
@@ -19961,10 +19996,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C47" s="5">
         <v>2248</v>
@@ -19987,10 +20022,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="C48" s="5">
         <v>2436</v>
@@ -20013,10 +20048,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C49" s="5">
         <v>2466</v>
@@ -20039,10 +20074,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="C50" s="5">
         <v>2465</v>
@@ -20065,10 +20100,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C51" s="5">
         <v>4318</v>
@@ -20091,10 +20126,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="C52" s="5">
         <v>4319</v>
@@ -20117,10 +20152,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C53" s="5">
         <v>4254</v>
@@ -20143,10 +20178,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="C54" s="5">
         <v>2563</v>
@@ -20169,10 +20204,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C55" s="5">
         <v>4689</v>
@@ -20195,10 +20230,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C56" s="5">
         <v>2725</v>
@@ -20221,10 +20256,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="C57" s="5">
         <v>2562</v>
@@ -20247,10 +20282,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C58" s="5">
         <v>2782</v>
@@ -20273,10 +20308,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="C59" s="5">
         <v>2745</v>
@@ -20299,10 +20334,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C60" s="5">
         <v>4207</v>
@@ -20325,10 +20360,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="C61" s="5">
         <v>3769</v>
@@ -20351,10 +20386,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C62" s="5">
         <v>3034</v>
@@ -20377,10 +20412,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="C63" s="5">
         <v>3039</v>
@@ -20403,10 +20438,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C64" s="5">
         <v>3421</v>
@@ -20429,10 +20464,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C65" s="5">
         <v>2748</v>
@@ -20455,10 +20490,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C66" s="5">
         <v>2576</v>
@@ -20481,10 +20516,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="C67" s="5">
         <v>3032</v>
@@ -20507,10 +20542,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C68" s="5">
         <v>2740</v>
@@ -20533,10 +20568,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C69" s="5">
         <v>3098</v>
@@ -20559,10 +20594,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="C70" s="5">
         <v>2743</v>
@@ -20585,10 +20620,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C71" s="5">
         <v>3360</v>
@@ -20611,10 +20646,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C72" s="5">
         <v>2611</v>
@@ -20637,10 +20672,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="4" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="C73" s="5">
         <v>2558</v>
@@ -20663,10 +20698,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C74" s="5">
         <v>3042</v>
@@ -20689,10 +20724,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="4" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="C75" s="5">
         <v>2561</v>
@@ -20715,10 +20750,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C76" s="5">
         <v>4226</v>
@@ -20741,10 +20776,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="4" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C77" s="5">
         <v>4227</v>
@@ -20816,10 +20851,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C2" s="5">
         <v>4295</v>
@@ -20842,10 +20877,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C3" s="5">
         <v>203</v>
@@ -20868,10 +20903,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="C4" s="5">
         <v>2490</v>
@@ -20894,10 +20929,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C5" s="5">
         <v>4552</v>
@@ -20920,10 +20955,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="C6" s="5">
         <v>3893</v>
@@ -20946,10 +20981,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C7" s="5">
         <v>2242</v>
@@ -20972,10 +21007,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="C8" s="5">
         <v>2518</v>
@@ -20998,10 +21033,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C9" s="5">
         <v>845</v>
@@ -21024,10 +21059,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="C10" s="5">
         <v>2517</v>
@@ -21050,10 +21085,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C11" s="5">
         <v>2631</v>
@@ -21076,10 +21111,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
       <c r="A12" s="4" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="C12" s="5">
         <v>3088</v>
@@ -21102,10 +21137,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
       <c r="A13" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C13" s="5">
         <v>3850</v>
@@ -21128,10 +21163,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
       <c r="A14" s="4" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C14" s="5">
         <v>2489</v>
@@ -21154,10 +21189,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C15" s="5">
         <v>2437</v>
@@ -21180,10 +21215,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
       <c r="A16" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C16" s="5">
         <v>582</v>
@@ -21206,10 +21241,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
       <c r="A17" s="4" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C17" s="5">
         <v>3415</v>
@@ -21232,10 +21267,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
       <c r="A18" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C18" s="5">
         <v>2485</v>
@@ -21258,10 +21293,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
       <c r="A19" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C19" s="5">
         <v>583</v>
@@ -21284,10 +21319,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
       <c r="A20" s="4" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="C20" s="5">
         <v>3416</v>
@@ -21310,10 +21345,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
       <c r="A21" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C21" s="5">
         <v>564</v>
@@ -21336,10 +21371,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
       <c r="A22" s="4" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="C22" s="5">
         <v>2256</v>
@@ -21362,10 +21397,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
       <c r="A23" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C23" s="5">
         <v>3398</v>
@@ -21388,10 +21423,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
       <c r="A24" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="C24" s="5">
         <v>4025</v>
@@ -21414,10 +21449,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
       <c r="A25" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C25" s="5">
         <v>4162</v>
@@ -21440,10 +21475,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
       <c r="A26" s="4" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C26" s="5">
         <v>3424</v>
@@ -21466,10 +21501,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C27" s="5">
         <v>4161</v>
@@ -21492,10 +21527,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="C28" s="5">
         <v>3718</v>
@@ -21518,10 +21553,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C29" s="5">
         <v>4277</v>
@@ -21544,10 +21579,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C30" s="5">
         <v>4163</v>
@@ -21570,10 +21605,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="C31" s="5">
         <v>4117</v>
@@ -21596,10 +21631,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C32" s="5">
         <v>3738</v>
@@ -21622,10 +21657,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="C33" s="5">
         <v>4317</v>
@@ -21648,10 +21683,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="18.75">
       <c r="A34" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C34" s="5">
         <v>2924</v>
@@ -21674,10 +21709,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="18.75">
       <c r="A35" s="4" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="C35" s="5">
         <v>3078</v>
@@ -21700,10 +21735,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="18.75">
       <c r="A36" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C36" s="5">
         <v>2348</v>
@@ -21726,10 +21761,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C37" s="5">
         <v>2538</v>
@@ -21752,10 +21787,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C38" s="5">
         <v>2811</v>
@@ -21778,10 +21813,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="C39" s="5">
         <v>2820</v>
@@ -21804,10 +21839,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C40" s="5">
         <v>3722</v>
@@ -21830,10 +21865,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="C41" s="5">
         <v>4050</v>
@@ -21856,10 +21891,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="C42" s="5">
         <v>415</v>
@@ -21882,10 +21917,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="C43" s="5">
         <v>93</v>
@@ -21908,10 +21943,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C44" s="5">
         <v>261</v>
@@ -21934,10 +21969,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C45" s="5">
         <v>2475</v>
@@ -21960,10 +21995,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C46" s="5">
         <v>92</v>
@@ -21986,10 +22021,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="C47" s="5">
         <v>2476</v>
@@ -22012,10 +22047,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C48" s="5">
         <v>18</v>
@@ -22038,10 +22073,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="C49" s="5">
         <v>2477</v>
@@ -22064,10 +22099,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C50" s="5">
         <v>4164</v>
@@ -22090,10 +22125,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="C51" s="5">
         <v>3706</v>
@@ -22116,10 +22151,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C52" s="5">
         <v>19</v>
@@ -22142,10 +22177,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C53" s="5">
         <v>2246</v>
@@ -22168,10 +22203,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="C54" s="5">
         <v>575</v>
@@ -22194,10 +22229,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C55" s="5">
         <v>221</v>
@@ -22220,10 +22255,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C56" s="5">
         <v>258</v>
@@ -22246,10 +22281,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C57" s="5">
         <v>20</v>
@@ -22272,10 +22307,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C58" s="5">
         <v>2520</v>
@@ -22290,7 +22325,7 @@
         <v>11</v>
       </c>
       <c r="G58" s="5">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H58" s="5">
         <f>MROUND(G58*1.03, 0.5)</f>
@@ -22298,10 +22333,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="C59" s="5">
         <v>4089</v>
@@ -22316,7 +22351,7 @@
         <v>147</v>
       </c>
       <c r="G59" s="5">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="H59" s="6">
         <f>MROUND(G59*1.03, 0.5)</f>
@@ -22324,10 +22359,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C60" s="5">
         <v>21</v>
@@ -22350,10 +22385,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C61" s="5">
         <v>262</v>
@@ -22376,10 +22411,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C62" s="5">
         <v>2513</v>
@@ -22402,10 +22437,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C63" s="5">
         <v>16</v>
@@ -22428,10 +22463,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="C64" s="5">
         <v>3114</v>
@@ -22454,10 +22489,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="C65" s="5">
         <v>4086</v>
@@ -22480,10 +22515,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C66" s="5">
         <v>15</v>
@@ -22506,10 +22541,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="C67" s="5">
         <v>3115</v>
@@ -22532,10 +22567,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C68" s="5">
         <v>4165</v>
@@ -22558,10 +22593,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C69" s="5">
         <v>4100</v>
@@ -22584,10 +22619,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C70" s="5">
         <v>4280</v>
@@ -22610,10 +22645,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="C71" s="5">
         <v>4281</v>
@@ -22685,10 +22720,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C2" s="5">
         <v>11</v>
@@ -22711,10 +22746,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
       <c r="A3" s="4" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="C3" s="5">
         <v>2471</v>
@@ -22737,10 +22772,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
       <c r="A4" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C4" s="5">
         <v>3472</v>
@@ -22763,10 +22798,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
       <c r="A5" s="4" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="C5" s="5">
         <v>2472</v>
@@ -22789,10 +22824,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
       <c r="A6" s="4" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="C6" s="5">
         <v>133</v>
@@ -22815,10 +22850,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
       <c r="A7" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C7" s="5">
         <v>127</v>
@@ -22841,10 +22876,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
       <c r="A8" s="4" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="C8" s="5">
         <v>2637</v>
@@ -22867,10 +22902,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
       <c r="A9" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C9" s="5">
         <v>12</v>
@@ -22893,10 +22928,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
       <c r="A10" s="4" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C10" s="5">
         <v>2501</v>
@@ -22919,10 +22954,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
       <c r="A11" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C11" s="5">
         <v>24</v>
@@ -22945,10 +22980,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="C12" s="5">
         <v>2726</v>
@@ -22971,10 +23006,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C13" s="5">
         <v>4221</v>
@@ -22997,10 +23032,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="C14" s="5">
         <v>4222</v>
@@ -23023,10 +23058,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C15" s="5">
         <v>2580</v>
@@ -23049,10 +23084,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="C16" s="5">
         <v>123</v>
@@ -23075,10 +23110,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C17" s="5">
         <v>4016</v>
@@ -23101,10 +23136,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C18" s="5">
         <v>4017</v>
@@ -23127,10 +23162,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="C19" s="5">
         <v>210</v>
@@ -23153,10 +23188,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C20" s="5">
         <v>4545</v>
@@ -23179,10 +23214,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="C21" s="5">
         <v>3363</v>
@@ -23205,10 +23240,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C22" s="5">
         <v>2482</v>
@@ -23231,10 +23266,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="C23" s="5">
         <v>34</v>
@@ -23257,10 +23292,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C24" s="5">
         <v>89</v>
@@ -23283,10 +23318,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="C25" s="5">
         <v>114</v>
@@ -23309,10 +23344,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C26" s="5">
         <v>2486</v>
@@ -23335,10 +23370,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="18.75">
       <c r="A27" s="4" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C27" s="5">
         <v>2241</v>
@@ -23361,10 +23396,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="18.75">
       <c r="A28" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C28" s="5">
         <v>2487</v>
@@ -23387,10 +23422,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="18.75">
       <c r="A29" s="4" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C29" s="5">
         <v>23</v>
@@ -23413,10 +23448,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="18.75">
       <c r="A30" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C30" s="5">
         <v>2260</v>
@@ -23439,10 +23474,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="18.75">
       <c r="A31" s="4" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="C31" s="5">
         <v>214</v>
@@ -23465,10 +23500,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="18.75">
       <c r="A32" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C32" s="5">
         <v>4664</v>
@@ -23491,10 +23526,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="18.75">
       <c r="A33" s="4" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C33" s="5">
         <v>4665</v>
@@ -23517,10 +23552,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C34" s="5">
         <v>28</v>
@@ -23543,10 +23578,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="C35" s="5">
         <v>68</v>
@@ -23569,10 +23604,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C36" s="5">
         <v>2302</v>
@@ -23595,10 +23630,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="19.5">
       <c r="A37" s="4" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="C37" s="5">
         <v>320</v>
@@ -23621,10 +23656,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="19.5">
       <c r="A38" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C38" s="5">
         <v>3479</v>
@@ -23647,10 +23682,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="19.5">
       <c r="A39" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C39" s="5">
         <v>130</v>
@@ -23673,10 +23708,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="19.5">
       <c r="A40" s="4" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C40" s="5">
         <v>2464</v>
@@ -23699,10 +23734,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="19.5">
       <c r="A41" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C41" s="5">
         <v>101</v>
@@ -23725,10 +23760,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="19.5">
       <c r="A42" s="4" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="C42" s="5">
         <v>2465</v>
@@ -23751,10 +23786,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="19.5">
       <c r="A43" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C43" s="5">
         <v>65</v>
@@ -23777,10 +23812,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="19.5">
       <c r="A44" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C44" s="5">
         <v>2624</v>
@@ -23803,10 +23838,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="19.5">
       <c r="A45" s="4" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C45" s="5">
         <v>119</v>
@@ -23829,10 +23864,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="19.5">
       <c r="A46" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C46" s="5">
         <v>3621</v>
@@ -23855,10 +23890,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="19.5">
       <c r="A47" s="4" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="C47" s="5">
         <v>141</v>
@@ -23881,10 +23916,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="19.5">
       <c r="A48" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C48" s="5">
         <v>3025</v>
@@ -23907,10 +23942,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="19.5">
       <c r="A49" s="4" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="C49" s="5">
         <v>2543</v>
@@ -23933,10 +23968,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C50" s="5">
         <v>98</v>
@@ -23959,10 +23994,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C51" s="5">
         <v>35</v>
@@ -23985,10 +24020,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C52" s="5">
         <v>2353</v>
@@ -24011,10 +24046,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C53" s="5">
         <v>2466</v>
@@ -24037,10 +24072,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C54" s="5">
         <v>3089</v>
@@ -24063,10 +24098,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C55" s="5">
         <v>2666</v>
@@ -24089,10 +24124,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="C56" s="5">
         <v>2667</v>
@@ -24115,10 +24150,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C57" s="5">
         <v>3478</v>
@@ -24141,10 +24176,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C58" s="5">
         <v>190</v>
@@ -24167,10 +24202,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C59" s="5">
         <v>2335</v>
@@ -24193,10 +24228,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C60" s="5">
         <v>3446</v>
@@ -24219,10 +24254,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="C61" s="5">
         <v>3447</v>
@@ -24245,10 +24280,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C62" s="5">
         <v>100</v>
@@ -24271,10 +24306,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C63" s="5">
         <v>136</v>
@@ -24297,10 +24332,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C64" s="5">
         <v>259</v>
@@ -24323,10 +24358,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="C65" s="5">
         <v>2319</v>
@@ -24349,10 +24384,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C66" s="5">
         <v>125</v>
@@ -24375,10 +24410,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C67" s="5">
         <v>2468</v>
@@ -24401,10 +24436,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C68" s="5">
         <v>3670</v>
@@ -24419,7 +24454,7 @@
         <v>147</v>
       </c>
       <c r="G68" s="5">
-        <v>225</v>
+        <v>285</v>
       </c>
       <c r="H68" s="5">
         <f>MROUND(G68*1.03, 0.5)</f>
@@ -24427,10 +24462,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C69" s="5">
         <v>2469</v>
@@ -24445,7 +24480,7 @@
         <v>11</v>
       </c>
       <c r="G69" s="6">
-        <v>40.5</v>
+        <v>50.5</v>
       </c>
       <c r="H69" s="6">
         <f>MROUND(G69*1.03, 0.5)</f>
@@ -24453,10 +24488,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C70" s="5">
         <v>3006</v>
@@ -24479,10 +24514,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C71" s="5">
         <v>3007</v>
@@ -24505,10 +24540,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C72" s="5">
         <v>117</v>
@@ -24531,10 +24566,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="4" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C73" s="5">
         <v>2320</v>
@@ -24557,10 +24592,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C74" s="5">
         <v>60</v>
@@ -24583,10 +24618,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="4" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C75" s="5">
         <v>2321</v>
@@ -24609,10 +24644,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C76" s="5">
         <v>211</v>
@@ -24635,10 +24670,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C77" s="5">
         <v>41</v>
@@ -24661,10 +24696,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="4" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="C78" s="5">
         <v>2322</v>
@@ -24687,10 +24722,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C79" s="5">
         <v>67</v>
@@ -24713,10 +24748,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C80" s="5">
         <v>2244</v>
@@ -24739,10 +24774,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="4" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C81" s="5">
         <v>2488</v>
@@ -24765,10 +24800,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="C82" s="5">
         <v>520</v>
@@ -24791,10 +24826,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C83" s="5">
         <v>4546</v>
@@ -24817,10 +24852,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C84" s="5">
         <v>3695</v>
@@ -24843,10 +24878,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C85" s="5">
         <v>3097</v>
@@ -24869,10 +24904,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="C86" s="5">
         <v>2460</v>
@@ -24895,10 +24930,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C87" s="5">
         <v>3110</v>
@@ -24921,10 +24956,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="C88" s="5">
         <v>135</v>
@@ -24947,10 +24982,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C89" s="5">
         <v>2463</v>
@@ -24973,10 +25008,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C90" s="5">
         <v>55</v>
@@ -24999,10 +25034,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C91" s="5">
         <v>51</v>
@@ -25025,10 +25060,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="C92" s="5">
         <v>201</v>
@@ -25051,10 +25086,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C93" s="5">
         <v>4223</v>
@@ -25077,10 +25112,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="4" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="C94" s="5">
         <v>4224</v>
@@ -25152,10 +25187,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C2" s="5">
         <v>4139</v>
@@ -25178,10 +25213,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="4" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C3" s="5">
         <v>3383</v>
@@ -25204,10 +25239,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C4" s="5">
         <v>4520</v>
@@ -25230,10 +25265,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C5" s="5">
         <v>3381</v>
@@ -25256,10 +25291,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C6" s="5">
         <v>3498</v>
@@ -25282,10 +25317,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C7" s="5">
         <v>4112</v>
@@ -25308,10 +25343,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C8" s="5">
         <v>4116</v>
@@ -25334,10 +25369,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C9" s="5">
         <v>4107</v>
@@ -25360,10 +25395,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C10" s="5">
         <v>4657</v>
@@ -25386,10 +25421,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C11" s="5">
         <v>2222</v>
@@ -25412,10 +25447,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C12" s="5">
         <v>3572</v>
@@ -25438,10 +25473,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C13" s="5">
         <v>4669</v>
@@ -25464,10 +25499,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C14" s="5">
         <v>2522</v>
@@ -25490,10 +25525,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C15" s="5">
         <v>2521</v>
@@ -25516,10 +25551,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C16" s="5">
         <v>2571</v>
@@ -25542,10 +25577,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C17" s="5">
         <v>4108</v>
@@ -25568,10 +25603,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C18" s="5">
         <v>4111</v>
@@ -25594,10 +25629,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C19" s="5">
         <v>3499</v>
@@ -25620,10 +25655,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C20" s="5">
         <v>2616</v>
@@ -25646,10 +25681,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C21" s="5">
         <v>2615</v>
@@ -25672,10 +25707,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C22" s="5">
         <v>4283</v>
@@ -25698,10 +25733,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C23" s="5">
         <v>4114</v>
@@ -25724,10 +25759,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="C24" s="5">
         <v>3493</v>
@@ -25750,10 +25785,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C25" s="5">
         <v>4395</v>
@@ -25776,10 +25811,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C26" s="5">
         <v>4394</v>
@@ -25802,10 +25837,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="19.5">
       <c r="A27" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C27" s="5">
         <v>4115</v>
@@ -25828,10 +25863,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="19.5">
       <c r="A28" s="4" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="C28" s="5">
         <v>3497</v>
@@ -25854,10 +25889,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="19.5">
       <c r="A29" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C29" s="5">
         <v>2492</v>
@@ -25880,10 +25915,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="19.5">
       <c r="A30" s="4" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="C30" s="5">
         <v>2499</v>
@@ -25906,10 +25941,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="19.5">
       <c r="A31" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C31" s="5">
         <v>3101</v>
@@ -25932,10 +25967,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="19.5">
       <c r="A32" s="4" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C32" s="5">
         <v>580</v>
@@ -25958,10 +25993,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="19.5">
       <c r="A33" s="4" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C33" s="5">
         <v>581</v>
@@ -25984,10 +26019,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="19.5">
       <c r="A34" s="4" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C34" s="5">
         <v>4029</v>
@@ -26010,10 +26045,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="19.5">
       <c r="A35" s="4" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C35" s="5">
         <v>4203</v>
@@ -26036,10 +26071,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="19.5">
       <c r="A36" s="4" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C36" s="5">
         <v>3936</v>
@@ -26062,10 +26097,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="18.75">
       <c r="A37" s="4" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C37" s="5">
         <v>4302</v>
@@ -26088,10 +26123,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="18.75">
       <c r="A38" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C38" s="5">
         <v>3027</v>
@@ -26114,10 +26149,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="18.75">
       <c r="A39" s="4" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C39" s="5">
         <v>3026</v>
@@ -26140,10 +26175,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="18.75">
       <c r="A40" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C40" s="5">
         <v>3514</v>
@@ -26166,10 +26201,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="18.75">
       <c r="A41" s="4" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C41" s="5">
         <v>3515</v>
@@ -26192,10 +26227,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="18.75">
       <c r="A42" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C42" s="5">
         <v>3139</v>
@@ -26218,10 +26253,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="18.75">
       <c r="A43" s="4" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C43" s="5">
         <v>3138</v>
@@ -26244,10 +26279,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="18.75">
       <c r="A44" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C44" s="5">
         <v>2592</v>
@@ -26270,10 +26305,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="18.75">
       <c r="A45" s="4" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C45" s="5">
         <v>2591</v>
@@ -26296,10 +26331,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="18.75">
       <c r="A46" s="4" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C46" s="5">
         <v>2597</v>
@@ -26322,10 +26357,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="18.75">
       <c r="A47" s="4" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C47" s="5">
         <v>4174</v>
@@ -26348,10 +26383,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="18.75">
       <c r="A48" s="4" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C48" s="5">
         <v>4176</v>
@@ -26374,10 +26409,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="18.75">
       <c r="A49" s="4" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C49" s="5">
         <v>2686</v>
@@ -26400,10 +26435,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="18.75">
       <c r="A50" s="4" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C50" s="5">
         <v>2687</v>
@@ -26426,10 +26461,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="18.75">
       <c r="A51" s="4" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C51" s="5">
         <v>4496</v>
@@ -26452,10 +26487,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="18.75">
       <c r="A52" s="4" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C52" s="5">
         <v>4061</v>
@@ -26478,10 +26513,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="18.75">
       <c r="A53" s="4" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C53" s="5">
         <v>4166</v>
@@ -26504,10 +26539,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="18.75">
       <c r="A54" s="4" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C54" s="5">
         <v>2681</v>
@@ -26530,10 +26565,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="18.75">
       <c r="A55" s="4" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C55" s="5">
         <v>2682</v>
@@ -26556,10 +26591,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="18.75">
       <c r="A56" s="4" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C56" s="5">
         <v>2683</v>
@@ -26582,10 +26617,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="18.75">
       <c r="A57" s="4" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C57" s="5">
         <v>2600</v>
@@ -26608,10 +26643,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="18.75">
       <c r="A58" s="4" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C58" s="5">
         <v>4167</v>
@@ -26634,10 +26669,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="18.75">
       <c r="A59" s="4" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C59" s="5">
         <v>2595</v>
@@ -26660,10 +26695,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="18.75">
       <c r="A60" s="4" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C60" s="5">
         <v>4062</v>
@@ -26686,10 +26721,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="18.75">
       <c r="A61" s="4" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C61" s="5">
         <v>2707</v>
@@ -26712,10 +26747,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="18.75">
       <c r="A62" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C62" s="5">
         <v>3605</v>
@@ -26738,10 +26773,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="18.75">
       <c r="A63" s="4" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C63" s="5">
         <v>3606</v>
@@ -26764,10 +26799,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="18.75">
       <c r="A64" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C64" s="5">
         <v>4402</v>
@@ -26790,10 +26825,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="18.75">
       <c r="A65" s="4" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C65" s="5">
         <v>4401</v>
@@ -26816,10 +26851,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="18.75">
       <c r="A66" s="4" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C66" s="5">
         <v>2684</v>
@@ -26842,10 +26877,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="18.75">
       <c r="A67" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C67" s="5">
         <v>2723</v>
@@ -26868,10 +26903,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="18.75">
       <c r="A68" s="4" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C68" s="5">
         <v>2734</v>
@@ -26894,10 +26929,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="18.75">
       <c r="A69" s="4" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C69" s="5">
         <v>4168</v>
@@ -26920,10 +26955,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="18.75">
       <c r="A70" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C70" s="5">
         <v>2718</v>
@@ -26946,10 +26981,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="18.75">
       <c r="A71" s="4" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C71" s="5">
         <v>2719</v>
@@ -26972,10 +27007,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="18.75">
       <c r="A72" s="4" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C72" s="5">
         <v>3094</v>
@@ -26998,10 +27033,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="18.75">
       <c r="A73" s="4" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C73" s="5">
         <v>4169</v>
@@ -27024,10 +27059,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="18.75">
       <c r="A74" s="4" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C74" s="5">
         <v>2685</v>
@@ -27050,10 +27085,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="18.75">
       <c r="A75" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C75" s="5">
         <v>4113</v>
@@ -27076,10 +27111,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="18.75">
       <c r="A76" s="4" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="C76" s="5">
         <v>4106</v>
@@ -27102,10 +27137,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="18.75">
       <c r="A77" s="4" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C77" s="5">
         <v>2596</v>
@@ -27128,10 +27163,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="18.75">
       <c r="A78" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C78" s="5">
         <v>4457</v>
@@ -27154,10 +27189,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="18.75">
       <c r="A79" s="4" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C79" s="5">
         <v>4458</v>
@@ -27180,10 +27215,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="18.75">
       <c r="A80" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C80" s="5">
         <v>2602</v>
@@ -27206,10 +27241,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="18.75">
       <c r="A81" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C81" s="5">
         <v>2605</v>
@@ -27232,10 +27267,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="18.75">
       <c r="A82" s="4" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C82" s="5">
         <v>3894</v>
@@ -27258,10 +27293,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="18.75">
       <c r="A83" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C83" s="5">
         <v>4109</v>
@@ -27284,10 +27319,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="18.75">
       <c r="A84" s="4" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="C84" s="5">
         <v>4110</v>
@@ -27310,10 +27345,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
       <c r="A85" s="4" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="C85" s="5">
         <v>4171</v>
@@ -27336,10 +27371,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C86" s="5">
         <v>2653</v>
@@ -27362,10 +27397,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
       <c r="A87" s="4" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="C87" s="5">
         <v>3675</v>
@@ -27388,10 +27423,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C88" s="5">
         <v>2417</v>
@@ -27414,10 +27449,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
       <c r="A89" s="4" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C89" s="5">
         <v>3109</v>
@@ -27440,10 +27475,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
       <c r="A90" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C90" s="5">
         <v>2777</v>
@@ -27466,10 +27501,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
       <c r="A91" s="4" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C91" s="5">
         <v>2776</v>
@@ -27492,10 +27527,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="18.75">
       <c r="A92" s="4" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="C92" s="5">
         <v>4173</v>
@@ -27518,10 +27553,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="93" customHeight="1" ht="18.75">
       <c r="A93" s="4" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C93" s="5">
         <v>2689</v>
@@ -27544,10 +27579,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="94" customHeight="1" ht="18.75">
       <c r="A94" s="4" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C94" s="5">
         <v>4170</v>
@@ -27570,10 +27605,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="95" customHeight="1" ht="18.75">
       <c r="A95" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C95" s="5">
         <v>4494</v>
@@ -27596,10 +27631,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="96" customHeight="1" ht="18.75">
       <c r="A96" s="4" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="C96" s="5">
         <v>4495</v>
@@ -27622,10 +27657,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="97" customHeight="1" ht="18.75">
       <c r="A97" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C97" s="5">
         <v>2785</v>
@@ -27648,10 +27683,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="98" customHeight="1" ht="18.75">
       <c r="A98" s="4" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="C98" s="5">
         <v>2784</v>
@@ -27674,10 +27709,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="99" customHeight="1" ht="18.75">
       <c r="A99" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C99" s="5">
         <v>2788</v>
@@ -27700,10 +27735,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="100" customHeight="1" ht="18.75">
       <c r="A100" s="4" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C100" s="5">
         <v>2789</v>
@@ -27726,10 +27761,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="101" customHeight="1" ht="18.75">
       <c r="A101" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C101" s="5">
         <v>4539</v>
@@ -27752,10 +27787,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="102" customHeight="1" ht="18.75">
       <c r="A102" s="4" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="C102" s="5">
         <v>3495</v>
@@ -27778,10 +27813,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="103" customHeight="1" ht="18.75">
       <c r="A103" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C103" s="5">
         <v>2786</v>
@@ -27804,10 +27839,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="104" customHeight="1" ht="18.75">
       <c r="A104" s="4" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C104" s="5">
         <v>2787</v>
@@ -27830,10 +27865,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="105" customHeight="1" ht="18.75">
       <c r="A105" s="4" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="C105" s="5">
         <v>2598</v>
@@ -27856,10 +27891,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="106" customHeight="1" ht="18.75">
       <c r="A106" s="4" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C106" s="5">
         <v>4060</v>
@@ -27882,10 +27917,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="107" customHeight="1" ht="18.75">
       <c r="A107" s="4" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B107" s="4" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="C107" s="5">
         <v>2690</v>
@@ -27908,10 +27943,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="108" customHeight="1" ht="18.75">
       <c r="A108" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C108" s="5">
         <v>3355</v>
@@ -27934,10 +27969,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="109" customHeight="1" ht="18.75">
       <c r="A109" s="4" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C109" s="5">
         <v>3066</v>
@@ -27960,10 +27995,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="110" customHeight="1" ht="18.75">
       <c r="A110" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C110" s="5">
         <v>1515</v>
@@ -27986,10 +28021,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="111" customHeight="1" ht="18.75">
       <c r="A111" s="4" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C111" s="5">
         <v>2552</v>
@@ -28012,10 +28047,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="112" customHeight="1" ht="18.75">
       <c r="A112" s="4" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="C112" s="5">
         <v>3092</v>
@@ -28038,10 +28073,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="113" customHeight="1" ht="18.75">
       <c r="A113" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C113" s="5">
         <v>2589</v>
@@ -28064,10 +28099,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="114" customHeight="1" ht="18.75">
       <c r="A114" s="4" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="B114" s="4" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="C114" s="5">
         <v>2588</v>
@@ -28090,10 +28125,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="115" customHeight="1" ht="18.75">
       <c r="A115" s="4" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B115" s="4" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C115" s="5">
         <v>2688</v>
@@ -28116,10 +28151,10 @@
     </row>
     <row x14ac:dyDescent="0.25" r="116" customHeight="1" ht="18.75">
       <c r="A116" s="4" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="C116" s="5">
         <v>2599</v>

--- a/data/ProdutosFomatodosLibanes.xlsx
+++ b/data/ProdutosFomatodosLibanes.xlsx
@@ -4,7 +4,7 @@
   <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="9"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet r:id="rId1" sheetId="1" name="promoçoes"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3728" uniqueCount="1122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3724" uniqueCount="1122">
   <si>
     <t>produto_grupo</t>
   </si>
@@ -3406,7 +3406,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3424,6 +3424,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -3510,10 +3516,10 @@
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="3" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -4944,7 +4950,7 @@
         <f>MROUND(G3*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="4" t="s">
         <v>546</v>
       </c>
@@ -4970,7 +4976,7 @@
         <f>MROUND(G4*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="4" t="s">
         <v>548</v>
       </c>
@@ -4996,7 +5002,7 @@
         <f>MROUND(G5*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="4" t="s">
         <v>550</v>
       </c>
@@ -5022,7 +5028,7 @@
         <f>MROUND(G6*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="4" t="s">
         <v>552</v>
       </c>
@@ -5048,7 +5054,7 @@
         <f>MROUND(G7*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="4" t="s">
         <v>552</v>
       </c>
@@ -5074,7 +5080,7 @@
         <f>MROUND(G8*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="4" t="s">
         <v>554</v>
       </c>
@@ -5100,7 +5106,7 @@
         <f>MROUND(G9*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="19.5">
       <c r="A10" s="4" t="s">
         <v>556</v>
       </c>
@@ -5126,7 +5132,7 @@
         <f>MROUND(G10*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="4" t="s">
         <v>558</v>
       </c>
@@ -5152,7 +5158,7 @@
         <f>MROUND(G11*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="19.5">
       <c r="A12" s="4" t="s">
         <v>558</v>
       </c>
@@ -5178,7 +5184,7 @@
         <f>MROUND(G12*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="4" t="s">
         <v>560</v>
       </c>
@@ -5204,7 +5210,7 @@
         <f>MROUND(G13*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="4" t="s">
         <v>560</v>
       </c>
@@ -5230,7 +5236,7 @@
         <f>MROUND(G14*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="4" t="s">
         <v>562</v>
       </c>
@@ -5256,7 +5262,7 @@
         <f>MROUND(G15*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="4" t="s">
         <v>562</v>
       </c>
@@ -5282,7 +5288,7 @@
         <f>MROUND(G16*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="4" t="s">
         <v>564</v>
       </c>
@@ -5308,7 +5314,7 @@
         <f>MROUND(G17*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="19.5">
       <c r="A18" s="4" t="s">
         <v>566</v>
       </c>
@@ -5334,7 +5340,7 @@
         <f>MROUND(G17*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="4" t="s">
         <v>567</v>
       </c>
@@ -5360,7 +5366,7 @@
         <f>MROUND(G18*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="4" t="s">
         <v>569</v>
       </c>
@@ -5386,7 +5392,7 @@
         <f>MROUND(G19*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="4" t="s">
         <v>569</v>
       </c>
@@ -5412,7 +5418,7 @@
         <f>MROUND(G20*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="19.5">
       <c r="A22" s="4" t="s">
         <v>571</v>
       </c>
@@ -5438,7 +5444,7 @@
         <f>MROUND(G21*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="19.5">
       <c r="A23" s="4" t="s">
         <v>571</v>
       </c>
@@ -5464,7 +5470,7 @@
         <f>MROUND(G22*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="19.5">
       <c r="A24" s="4" t="s">
         <v>573</v>
       </c>
@@ -5490,7 +5496,7 @@
         <f>MROUND(G23*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="19.5">
       <c r="A25" s="4" t="s">
         <v>575</v>
       </c>
@@ -5516,7 +5522,7 @@
         <f>MROUND(G24*1.03, 0.5)</f>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="19.5">
       <c r="A26" s="4" t="s">
         <v>577</v>
       </c>
@@ -15674,7 +15680,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H91"/>
+  <dimension ref="A1:H90"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" style="7" width="30.005" customWidth="1" bestFit="1"/>
@@ -17853,10 +17859,10 @@
         <v>1117</v>
       </c>
       <c r="C84" s="5">
-        <v>3093</v>
+        <v>263</v>
       </c>
       <c r="D84" s="5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>30</v>
@@ -17865,10 +17871,10 @@
         <v>16</v>
       </c>
       <c r="G84" s="5">
-        <v>583</v>
-      </c>
-      <c r="H84" s="6">
-        <f>MROUND(G82*1.03, 0.5)</f>
+        <v>580</v>
+      </c>
+      <c r="H84" s="5">
+        <f>MROUND(G83*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="18.75">
@@ -17879,48 +17885,48 @@
         <v>1117</v>
       </c>
       <c r="C85" s="5">
-        <v>263</v>
+        <v>2632</v>
       </c>
       <c r="D85" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G85" s="5">
-        <v>530</v>
+        <v>293.5</v>
       </c>
       <c r="H85" s="5">
-        <f>MROUND(G83*1.03, 0.5)</f>
+        <f>MROUND(G84*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="18.75">
       <c r="A86" s="4" t="s">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="C86" s="5">
-        <v>2632</v>
+        <v>2330</v>
       </c>
       <c r="D86" s="5">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G86" s="5">
-        <v>267</v>
-      </c>
-      <c r="H86" s="5">
-        <f>MROUND(G84*1.03, 0.5)</f>
+        <v>480</v>
+      </c>
+      <c r="H86" s="6">
+        <f>MROUND(G85*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="18.75">
@@ -17931,48 +17937,48 @@
         <v>1119</v>
       </c>
       <c r="C87" s="5">
-        <v>2330</v>
+        <v>2385</v>
       </c>
       <c r="D87" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="G87" s="5">
-        <v>480</v>
+        <v>242</v>
       </c>
       <c r="H87" s="6">
-        <f>MROUND(G85*1.03, 0.5)</f>
+        <f>MROUND(G86*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="18.75">
       <c r="A88" s="4" t="s">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="C88" s="5">
-        <v>2385</v>
+        <v>2384</v>
       </c>
       <c r="D88" s="5">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G88" s="5">
-        <v>242</v>
-      </c>
-      <c r="H88" s="6">
-        <f>MROUND(G86*1.03, 0.5)</f>
+        <v>16</v>
+      </c>
+      <c r="G88" s="6">
+        <v>187.5</v>
+      </c>
+      <c r="H88" s="5">
+        <f>MROUND(G87*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="18.75">
@@ -17983,22 +17989,22 @@
         <v>1121</v>
       </c>
       <c r="C89" s="5">
-        <v>2384</v>
+        <v>3851</v>
       </c>
       <c r="D89" s="5">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G89" s="6">
-        <v>187.5</v>
-      </c>
-      <c r="H89" s="5">
-        <f>MROUND(G87*1.03, 0.5)</f>
+        <v>147</v>
+      </c>
+      <c r="G89" s="5">
+        <v>75</v>
+      </c>
+      <c r="H89" s="6">
+        <f>MROUND(G88*1.03, 0.5)</f>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="18.75">
@@ -18009,47 +18015,21 @@
         <v>1121</v>
       </c>
       <c r="C90" s="5">
-        <v>3851</v>
+        <v>2424</v>
       </c>
       <c r="D90" s="5">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="G90" s="5">
-        <v>75</v>
+        <v>11</v>
+      </c>
+      <c r="G90" s="6">
+        <v>39.5</v>
       </c>
       <c r="H90" s="6">
-        <f>MROUND(G88*1.03, 0.5)</f>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="18.75">
-      <c r="A91" s="4" t="s">
-        <v>1120</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>1121</v>
-      </c>
-      <c r="C91" s="5">
-        <v>2424</v>
-      </c>
-      <c r="D91" s="5">
-        <v>5</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G91" s="6">
-        <v>39.5</v>
-      </c>
-      <c r="H91" s="6">
         <f>MROUND(G89*1.03, 0.5)</f>
       </c>
     </row>
@@ -24442,10 +24422,10 @@
         <v>820</v>
       </c>
       <c r="C68" s="5">
-        <v>3670</v>
+        <v>3740</v>
       </c>
       <c r="D68" s="5">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>30</v>
@@ -24454,7 +24434,7 @@
         <v>147</v>
       </c>
       <c r="G68" s="5">
-        <v>285</v>
+        <v>237.5</v>
       </c>
       <c r="H68" s="5">
         <f>MROUND(G68*1.03, 0.5)</f>
